--- a/ANALITICA.xlsx
+++ b/ANALITICA.xlsx
@@ -4468,16 +4468,16 @@
         <v>231</v>
       </c>
       <c r="G55" s="11">
-        <v>0.9702</v>
+        <v>0.9754</v>
       </c>
       <c r="H55" s="12">
         <v>56189486.28</v>
       </c>
       <c r="I55" s="13">
-        <v>54515037.34</v>
+        <v>54809333.5</v>
       </c>
       <c r="J55" s="12">
-        <v>1674448.9399999976</v>
+        <v>1380152.7800000012</v>
       </c>
       <c r="K55" s="14">
         <v>45035</v>
@@ -5342,16 +5342,16 @@
         <v>318</v>
       </c>
       <c r="G78" s="11">
-        <v>0</v>
+        <v>0.0134</v>
       </c>
       <c r="H78" s="12">
         <v>4705907.3</v>
       </c>
       <c r="I78" s="13">
-        <v>0</v>
+        <v>63006.28</v>
       </c>
       <c r="J78" s="12">
-        <v>4705907.3</v>
+        <v>4642901.02</v>
       </c>
       <c r="K78" s="14">
         <v>46009</v>

--- a/ANALITICA.xlsx
+++ b/ANALITICA.xlsx
@@ -1,11 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D6FBC53-382A-4ACC-ABC9-CE7744161055}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="MyWorkSheet-1" state="visible" r:id="rId4"/>
+    <sheet name="MyWorkSheet-1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MyWorkSheet-1'!$A$1:$L$168</definedName>
+  </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
@@ -1919,22 +1926,24 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="R$#,##0.00;-R$#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="DD-MM-YYYY"/>
+    <numFmt numFmtId="164" formatCode="\R\$#,##0.00;\-\R\$#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="dd\-mm\-yyyy"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="13"/>
       <color rgb="FF404040"/>
-      <sz val="13"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1995,57 +2004,60 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{E8B2EFBD-0C0E-4A81-AE34-F75C53EDCEE5}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2378,6408 +2390,6410 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L168"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.46153846153846" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.571428571428573" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.153846153846153" style="1" customWidth="1"/>
-    <col min="5" max="5" width="36.15384615384615" style="1" customWidth="1"/>
-    <col min="6" max="6" width="33.07692307692308" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.76923076923077" style="1" customWidth="1"/>
-    <col min="8" max="8" width="21.23076923076923" style="2" customWidth="1"/>
-    <col min="9" max="9" width="20.76923076923077" style="3" customWidth="1"/>
-    <col min="10" max="10" width="19.846153846153847" style="2" customWidth="1"/>
-    <col min="11" max="11" width="18.92857142857143" style="4" customWidth="1"/>
-    <col min="12" max="12" width="15.214285714285715" style="4" customWidth="1"/>
+    <col min="1" max="1" width="30.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.28515625" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="255.7109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="180.28515625" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.28515625" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.42578125" style="14" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20" style="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.5703125" style="14" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13" style="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="11">
-        <v>0.8916</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="G2" s="7">
+        <v>0.89159999999999995</v>
+      </c>
+      <c r="H2" s="8">
         <v>14782911.98</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="9">
         <v>13180256.4</v>
       </c>
-      <c r="J2" s="12">
+      <c r="J2" s="8">
         <v>1602655.58</v>
       </c>
-      <c r="K2" s="14">
+      <c r="K2" s="10">
         <v>44917</v>
       </c>
-      <c r="L2" s="14">
+      <c r="L2" s="10">
         <v>45513</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="7">
         <v>0</v>
       </c>
-      <c r="H3" s="12">
+      <c r="H3" s="8">
         <v>10134014.66</v>
       </c>
-      <c r="I3" s="13">
+      <c r="I3" s="9">
         <v>0</v>
       </c>
-      <c r="J3" s="12">
+      <c r="J3" s="8">
         <v>10134014.66</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3" s="10">
         <v>45365</v>
       </c>
-      <c r="L3" s="14">
+      <c r="L3" s="10">
         <v>45476</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="7">
         <v>0.6744</v>
       </c>
-      <c r="H4" s="12">
-        <v>37535912.65</v>
-      </c>
-      <c r="I4" s="13">
-        <v>25313733.22</v>
-      </c>
-      <c r="J4" s="12">
+      <c r="H4" s="8">
+        <v>37535912.649999999</v>
+      </c>
+      <c r="I4" s="9">
+        <v>25313733.219999999</v>
+      </c>
+      <c r="J4" s="8">
         <v>12222179.43</v>
       </c>
-      <c r="K4" s="14">
+      <c r="K4" s="10">
         <v>44807</v>
       </c>
-      <c r="L4" s="14">
+      <c r="L4" s="10">
         <v>45208</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="7">
         <v>1</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="8">
         <v>4928388.09</v>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="9">
         <v>4928388.26</v>
       </c>
-      <c r="J5" s="12">
-        <v>-0.1699999999254942</v>
-      </c>
-      <c r="K5" s="14">
+      <c r="J5" s="8">
+        <v>-0.16999999992549419</v>
+      </c>
+      <c r="K5" s="10">
         <v>45478</v>
       </c>
-      <c r="L5" s="14">
+      <c r="L5" s="10">
         <v>45327</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="G6" s="11">
-        <v>0.2004</v>
-      </c>
-      <c r="H6" s="12">
-        <v>18990162.94</v>
-      </c>
-      <c r="I6" s="13">
+      <c r="G6" s="7">
+        <v>0.20039999999999999</v>
+      </c>
+      <c r="H6" s="8">
+        <v>18990162.940000001</v>
+      </c>
+      <c r="I6" s="9">
         <v>3806174.66</v>
       </c>
-      <c r="J6" s="12">
+      <c r="J6" s="8">
         <v>15183988.280000001</v>
       </c>
-      <c r="K6" s="14">
+      <c r="K6" s="10">
         <v>45868</v>
       </c>
-      <c r="L6" s="14">
+      <c r="L6" s="10">
         <v>46228</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="G7" s="11">
-        <v>0.0076</v>
-      </c>
-      <c r="H7" s="12">
-        <v>16774604.06</v>
-      </c>
-      <c r="I7" s="13">
+      <c r="G7" s="7">
+        <v>7.6E-3</v>
+      </c>
+      <c r="H7" s="8">
+        <v>16774604.060000001</v>
+      </c>
+      <c r="I7" s="9">
         <v>127835.64</v>
       </c>
-      <c r="J7" s="12">
+      <c r="J7" s="8">
         <v>16646768.42</v>
       </c>
-      <c r="K7" s="14">
+      <c r="K7" s="10">
         <v>45100</v>
       </c>
-      <c r="L7" s="14">
+      <c r="L7" s="10">
         <v>45460</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="7">
         <v>1</v>
       </c>
-      <c r="H8" s="12">
-        <v>5581731.3</v>
-      </c>
-      <c r="I8" s="13">
-        <v>5581730.3</v>
-      </c>
-      <c r="J8" s="12">
+      <c r="H8" s="8">
+        <v>5581731.2999999998</v>
+      </c>
+      <c r="I8" s="9">
+        <v>5581730.2999999998</v>
+      </c>
+      <c r="J8" s="8">
         <v>1</v>
       </c>
-      <c r="K8" s="14">
+      <c r="K8" s="10">
         <v>44777</v>
       </c>
-      <c r="L8" s="14">
+      <c r="L8" s="10">
         <v>45348</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="G9" s="11">
-        <v>0.9902</v>
-      </c>
-      <c r="H9" s="12">
+      <c r="G9" s="7">
+        <v>0.99019999999999997</v>
+      </c>
+      <c r="H9" s="8">
         <v>5312585.57</v>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="9">
         <v>5260332.26</v>
       </c>
-      <c r="J9" s="12">
-        <v>52253.31000000052</v>
-      </c>
-      <c r="K9" s="14">
+      <c r="J9" s="8">
+        <v>52253.310000000522</v>
+      </c>
+      <c r="K9" s="10">
         <v>44536</v>
       </c>
-      <c r="L9" s="14">
+      <c r="L9" s="10">
         <v>45289</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="G10" s="11">
-        <v>0.9712999999999999</v>
-      </c>
-      <c r="H10" s="12">
+      <c r="G10" s="7">
+        <v>0.97129999999999994</v>
+      </c>
+      <c r="H10" s="8">
         <v>7795660.46</v>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="9">
         <v>7571952.29</v>
       </c>
-      <c r="J10" s="12">
+      <c r="J10" s="8">
         <v>223708.16999999993</v>
       </c>
-      <c r="K10" s="14">
+      <c r="K10" s="10">
         <v>44909</v>
       </c>
-      <c r="L10" s="14">
+      <c r="L10" s="10">
         <v>46144</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="G11" s="11">
-        <v>0.8916</v>
-      </c>
-      <c r="H11" s="12">
-        <v>7234583.77</v>
-      </c>
-      <c r="I11" s="13">
-        <v>6450491.31</v>
-      </c>
-      <c r="J11" s="12">
+      <c r="G11" s="7">
+        <v>0.89159999999999995</v>
+      </c>
+      <c r="H11" s="8">
+        <v>7234583.7699999996</v>
+      </c>
+      <c r="I11" s="9">
+        <v>6450491.3099999996</v>
+      </c>
+      <c r="J11" s="8">
         <v>784092.46</v>
       </c>
-      <c r="K11" s="14">
+      <c r="K11" s="10">
         <v>45425</v>
       </c>
-      <c r="L11" s="14">
+      <c r="L11" s="10">
         <v>45999</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="7">
         <v>0.8456999999999999</v>
       </c>
-      <c r="H12" s="12">
-        <v>36782151.81</v>
-      </c>
-      <c r="I12" s="13">
+      <c r="H12" s="8">
+        <v>36782151.810000002</v>
+      </c>
+      <c r="I12" s="9">
         <v>31106158.75</v>
       </c>
-      <c r="J12" s="12">
-        <v>5675993.060000002</v>
-      </c>
-      <c r="K12" s="14">
+      <c r="J12" s="8">
+        <v>5675993.0600000024</v>
+      </c>
+      <c r="K12" s="10">
         <v>45566</v>
       </c>
-      <c r="L12" s="14">
+      <c r="L12" s="10">
         <v>46228</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="G13" s="11">
-        <v>0.4067</v>
-      </c>
-      <c r="H13" s="12">
+      <c r="G13" s="7">
+        <v>0.40670000000000001</v>
+      </c>
+      <c r="H13" s="8">
         <v>11928823.02</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="9">
         <v>4852042.8</v>
       </c>
-      <c r="J13" s="12">
-        <v>7076780.22</v>
-      </c>
-      <c r="K13" s="14">
+      <c r="J13" s="8">
+        <v>7076780.2199999997</v>
+      </c>
+      <c r="K13" s="10">
         <v>44903</v>
       </c>
-      <c r="L13" s="14">
+      <c r="L13" s="10">
         <v>45239</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="7">
         <v>0.5746</v>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="8">
         <v>22825141.32</v>
       </c>
-      <c r="I14" s="13">
-        <v>13115141.81</v>
-      </c>
-      <c r="J14" s="12">
-        <v>9709999.51</v>
-      </c>
-      <c r="K14" s="14">
+      <c r="I14" s="9">
+        <v>13115141.810000001</v>
+      </c>
+      <c r="J14" s="8">
+        <v>9709999.5099999998</v>
+      </c>
+      <c r="K14" s="10">
         <v>45019</v>
       </c>
-      <c r="L14" s="14">
+      <c r="L14" s="10">
         <v>46193</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="G15" s="11">
-        <v>0.9990000000000001</v>
-      </c>
-      <c r="H15" s="12">
-        <v>7155724.39</v>
-      </c>
-      <c r="I15" s="13">
-        <v>7148655.6</v>
-      </c>
-      <c r="J15" s="12">
-        <v>7068.790000000037</v>
-      </c>
-      <c r="K15" s="14">
+      <c r="G15" s="7">
+        <v>0.99900000000000011</v>
+      </c>
+      <c r="H15" s="8">
+        <v>7155724.3899999997</v>
+      </c>
+      <c r="I15" s="9">
+        <v>7148655.5999999996</v>
+      </c>
+      <c r="J15" s="8">
+        <v>7068.7900000000373</v>
+      </c>
+      <c r="K15" s="10">
         <v>45314</v>
       </c>
-      <c r="L15" s="14">
+      <c r="L15" s="10">
         <v>45617</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="G16" s="11">
-        <v>0.8856</v>
-      </c>
-      <c r="H16" s="12">
+      <c r="G16" s="7">
+        <v>0.88560000000000005</v>
+      </c>
+      <c r="H16" s="8">
         <v>6765672.29</v>
       </c>
-      <c r="I16" s="13">
-        <v>5991696.58</v>
-      </c>
-      <c r="J16" s="12">
+      <c r="I16" s="9">
+        <v>5991696.5800000001</v>
+      </c>
+      <c r="J16" s="8">
         <v>773975.71</v>
       </c>
-      <c r="K16" s="14">
+      <c r="K16" s="10">
         <v>45398</v>
       </c>
-      <c r="L16" s="14">
+      <c r="L16" s="10">
         <v>46062</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="7">
         <v>0</v>
       </c>
-      <c r="H17" s="12">
+      <c r="H17" s="8">
         <v>2742607.66</v>
       </c>
-      <c r="I17" s="13">
+      <c r="I17" s="9">
         <v>0</v>
       </c>
-      <c r="J17" s="12">
+      <c r="J17" s="8">
         <v>2742607.66</v>
       </c>
-      <c r="K17" s="14">
+      <c r="K17" s="10">
         <v>45917</v>
       </c>
-      <c r="L17" s="14">
+      <c r="L17" s="10">
         <v>46097</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="F18" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="G18" s="11">
-        <v>0.9954000000000001</v>
-      </c>
-      <c r="H18" s="12">
-        <v>32464769.58</v>
-      </c>
-      <c r="I18" s="13">
-        <v>32314427.7</v>
-      </c>
-      <c r="J18" s="12">
+      <c r="G18" s="7">
+        <v>0.99540000000000006</v>
+      </c>
+      <c r="H18" s="8">
+        <v>32464769.579999998</v>
+      </c>
+      <c r="I18" s="9">
+        <v>32314427.699999999</v>
+      </c>
+      <c r="J18" s="8">
         <v>150341.87999999896</v>
       </c>
-      <c r="K18" s="14">
+      <c r="K18" s="10">
         <v>44697</v>
       </c>
-      <c r="L18" s="14">
+      <c r="L18" s="10">
         <v>45972</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="E19" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="F19" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="7">
         <v>0.94</v>
       </c>
-      <c r="H19" s="12">
+      <c r="H19" s="8">
         <v>44149151.5</v>
       </c>
-      <c r="I19" s="13">
-        <v>41500959.49</v>
-      </c>
-      <c r="J19" s="12">
-        <v>2648192.009999998</v>
-      </c>
-      <c r="K19" s="14">
+      <c r="I19" s="9">
+        <v>41500959.490000002</v>
+      </c>
+      <c r="J19" s="8">
+        <v>2648192.0099999979</v>
+      </c>
+      <c r="K19" s="10">
         <v>44763</v>
       </c>
-      <c r="L19" s="14">
+      <c r="L19" s="10">
         <v>45999</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E20" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="F20" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="G20" s="11">
-        <v>0.773</v>
-      </c>
-      <c r="H20" s="12">
+      <c r="G20" s="7">
+        <v>0.77300000000000002</v>
+      </c>
+      <c r="H20" s="8">
         <v>16880240</v>
       </c>
-      <c r="I20" s="13">
-        <v>13048536.54</v>
-      </c>
-      <c r="J20" s="12">
-        <v>3831703.460000001</v>
-      </c>
-      <c r="K20" s="14">
+      <c r="I20" s="9">
+        <v>13048536.539999999</v>
+      </c>
+      <c r="J20" s="8">
+        <v>3831703.4600000009</v>
+      </c>
+      <c r="K20" s="10">
         <v>45034</v>
       </c>
-      <c r="L20" s="14">
+      <c r="L20" s="10">
         <v>45253</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E21" s="11" t="s">
+      <c r="E21" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="F21" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="G21" s="11">
-        <v>0.5163</v>
-      </c>
-      <c r="H21" s="12">
-        <v>31022838.12</v>
-      </c>
-      <c r="I21" s="13">
+      <c r="G21" s="7">
+        <v>0.51629999999999998</v>
+      </c>
+      <c r="H21" s="8">
+        <v>31022838.120000001</v>
+      </c>
+      <c r="I21" s="9">
         <v>16018051.23</v>
       </c>
-      <c r="J21" s="12">
-        <v>15004786.89</v>
-      </c>
-      <c r="K21" s="14">
+      <c r="J21" s="8">
+        <v>15004786.890000001</v>
+      </c>
+      <c r="K21" s="10">
         <v>45309</v>
       </c>
-      <c r="L21" s="14">
+      <c r="L21" s="10">
         <v>46392</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="E22" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="F22" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="G22" s="11">
-        <v>0.6607999999999999</v>
-      </c>
-      <c r="H22" s="12">
-        <v>48872552.26</v>
-      </c>
-      <c r="I22" s="13">
-        <v>32294745.04</v>
-      </c>
-      <c r="J22" s="12">
+      <c r="G22" s="7">
+        <v>0.66079999999999994</v>
+      </c>
+      <c r="H22" s="8">
+        <v>48872552.259999998</v>
+      </c>
+      <c r="I22" s="9">
+        <v>32294745.039999999</v>
+      </c>
+      <c r="J22" s="8">
         <v>16577807.219999999</v>
       </c>
-      <c r="K22" s="14">
+      <c r="K22" s="10">
         <v>44875</v>
       </c>
-      <c r="L22" s="14">
+      <c r="L22" s="10">
         <v>46375</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E23" s="11" t="s">
+      <c r="E23" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="F23" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="G23" s="11">
-        <v>0.7193</v>
-      </c>
-      <c r="H23" s="12">
-        <v>89008310.65</v>
-      </c>
-      <c r="I23" s="13">
-        <v>64026819.34</v>
-      </c>
-      <c r="J23" s="12">
+      <c r="G23" s="7">
+        <v>0.71930000000000005</v>
+      </c>
+      <c r="H23" s="8">
+        <v>89008310.650000006</v>
+      </c>
+      <c r="I23" s="9">
+        <v>64026819.340000004</v>
+      </c>
+      <c r="J23" s="8">
         <v>24981491.310000002</v>
       </c>
-      <c r="K23" s="14">
+      <c r="K23" s="10">
         <v>44789</v>
       </c>
-      <c r="L23" s="14">
+      <c r="L23" s="10">
         <v>45510</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="E24" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F24" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="G24" s="11">
+      <c r="G24" s="7">
         <v>0.43520000000000003</v>
       </c>
-      <c r="H24" s="12">
-        <v>60543657.33</v>
-      </c>
-      <c r="I24" s="13">
-        <v>26345865.47</v>
-      </c>
-      <c r="J24" s="12">
-        <v>34197791.86</v>
-      </c>
-      <c r="K24" s="14">
+      <c r="H24" s="8">
+        <v>60543657.329999998</v>
+      </c>
+      <c r="I24" s="9">
+        <v>26345865.469999999</v>
+      </c>
+      <c r="J24" s="8">
+        <v>34197791.859999999</v>
+      </c>
+      <c r="K24" s="10">
         <v>44883</v>
       </c>
-      <c r="L24" s="14">
+      <c r="L24" s="10">
         <v>46144</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="D25" s="11" t="s">
+      <c r="D25" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E25" s="11" t="s">
+      <c r="E25" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="F25" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="G25" s="11">
-        <v>0.9922</v>
-      </c>
-      <c r="H25" s="12">
+      <c r="G25" s="7">
+        <v>0.99219999999999997</v>
+      </c>
+      <c r="H25" s="8">
         <v>5361446.28</v>
       </c>
-      <c r="I25" s="13">
+      <c r="I25" s="9">
         <v>5319761.7</v>
       </c>
-      <c r="J25" s="12">
+      <c r="J25" s="8">
         <v>41684.580000000075</v>
       </c>
-      <c r="K25" s="14">
+      <c r="K25" s="10">
         <v>44637</v>
       </c>
-      <c r="L25" s="14">
+      <c r="L25" s="10">
         <v>45484</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="D26" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="E26" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="F26" s="11" t="s">
+      <c r="F26" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="G26" s="11">
-        <v>0.8786</v>
-      </c>
-      <c r="H26" s="12">
-        <v>2601911.32</v>
-      </c>
-      <c r="I26" s="13">
+      <c r="G26" s="7">
+        <v>0.87860000000000005</v>
+      </c>
+      <c r="H26" s="8">
+        <v>2601911.3199999998</v>
+      </c>
+      <c r="I26" s="9">
         <v>2286080.42</v>
       </c>
-      <c r="J26" s="12">
-        <v>315830.8999999999</v>
-      </c>
-      <c r="K26" s="14">
+      <c r="J26" s="8">
+        <v>315830.89999999991</v>
+      </c>
+      <c r="K26" s="10">
         <v>45624</v>
       </c>
-      <c r="L26" s="14">
+      <c r="L26" s="10">
         <v>46106</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="B27" s="11" t="s">
+      <c r="B27" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="D27" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E27" s="11" t="s">
+      <c r="E27" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="F27" s="11" t="s">
+      <c r="F27" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="G27" s="11">
+      <c r="G27" s="7">
         <v>0.1104</v>
       </c>
-      <c r="H27" s="12">
-        <v>2394811.95</v>
-      </c>
-      <c r="I27" s="13">
-        <v>264324.6</v>
-      </c>
-      <c r="J27" s="12">
+      <c r="H27" s="8">
+        <v>2394811.9500000002</v>
+      </c>
+      <c r="I27" s="9">
+        <v>264324.59999999998</v>
+      </c>
+      <c r="J27" s="8">
         <v>2130487.35</v>
       </c>
-      <c r="K27" s="14">
+      <c r="K27" s="10">
         <v>44840</v>
       </c>
-      <c r="L27" s="14">
+      <c r="L27" s="10">
         <v>45390</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="11" t="s">
+      <c r="A28" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="B28" s="11" t="s">
+      <c r="B28" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C28" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="D28" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E28" s="11" t="s">
+      <c r="E28" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="F28" s="11" t="s">
+      <c r="F28" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="G28" s="11">
+      <c r="G28" s="7">
         <v>0.9998999999999999</v>
       </c>
-      <c r="H28" s="12">
+      <c r="H28" s="8">
         <v>2975474.34</v>
       </c>
-      <c r="I28" s="13">
+      <c r="I28" s="9">
         <v>2975297.32</v>
       </c>
-      <c r="J28" s="12">
+      <c r="J28" s="8">
         <v>177.02000000001863</v>
       </c>
-      <c r="K28" s="14">
+      <c r="K28" s="10">
         <v>44883</v>
       </c>
-      <c r="L28" s="14">
+      <c r="L28" s="10">
         <v>45411</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="D29" s="11" t="s">
+      <c r="D29" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E29" s="11" t="s">
+      <c r="E29" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="F29" s="11" t="s">
+      <c r="F29" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="G29" s="11">
+      <c r="G29" s="7">
         <v>1</v>
       </c>
-      <c r="H29" s="12">
+      <c r="H29" s="8">
         <v>4808707.09</v>
       </c>
-      <c r="I29" s="13">
+      <c r="I29" s="9">
         <v>4808707.09</v>
       </c>
-      <c r="J29" s="12">
+      <c r="J29" s="8">
         <v>0</v>
       </c>
-      <c r="K29" s="14">
+      <c r="K29" s="10">
         <v>44743</v>
       </c>
-      <c r="L29" s="14">
+      <c r="L29" s="10">
         <v>45341</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="B30" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="D30" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E30" s="11" t="s">
+      <c r="E30" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="F30" s="11" t="s">
+      <c r="F30" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G30" s="11">
-        <v>0.9109999999999999</v>
-      </c>
-      <c r="H30" s="12">
-        <v>13208831.36</v>
-      </c>
-      <c r="I30" s="13">
+      <c r="G30" s="7">
+        <v>0.91099999999999992</v>
+      </c>
+      <c r="H30" s="8">
+        <v>13208831.359999999</v>
+      </c>
+      <c r="I30" s="9">
         <v>12032786.93</v>
       </c>
-      <c r="J30" s="12">
+      <c r="J30" s="8">
         <v>1176044.4299999997</v>
       </c>
-      <c r="K30" s="14">
+      <c r="K30" s="10">
         <v>44708</v>
       </c>
-      <c r="L30" s="14">
+      <c r="L30" s="10">
         <v>45398</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="D31" s="11" t="s">
+      <c r="D31" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E31" s="11" t="s">
+      <c r="E31" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="F31" s="11" t="s">
+      <c r="F31" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="G31" s="11">
+      <c r="G31" s="7">
         <v>1</v>
       </c>
-      <c r="H31" s="12">
-        <v>11551184.44</v>
-      </c>
-      <c r="I31" s="13">
+      <c r="H31" s="8">
+        <v>11551184.439999999</v>
+      </c>
+      <c r="I31" s="9">
         <v>11551184.4</v>
       </c>
-      <c r="J31" s="12">
-        <v>0.03999999910593033</v>
-      </c>
-      <c r="K31" s="14">
+      <c r="J31" s="8">
+        <v>3.9999999105930328E-2</v>
+      </c>
+      <c r="K31" s="10">
         <v>44733</v>
       </c>
-      <c r="L31" s="14">
+      <c r="L31" s="10">
         <v>45953</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="11" t="s">
+      <c r="A32" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="D32" s="11" t="s">
+      <c r="D32" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E32" s="11" t="s">
+      <c r="E32" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="F32" s="11" t="s">
+      <c r="F32" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="G32" s="11">
-        <v>0.9908</v>
-      </c>
-      <c r="H32" s="12">
-        <v>9751616.37</v>
-      </c>
-      <c r="I32" s="13">
-        <v>9661616.37</v>
-      </c>
-      <c r="J32" s="12">
+      <c r="G32" s="7">
+        <v>0.99080000000000001</v>
+      </c>
+      <c r="H32" s="8">
+        <v>9751616.3699999992</v>
+      </c>
+      <c r="I32" s="9">
+        <v>9661616.3699999992</v>
+      </c>
+      <c r="J32" s="8">
         <v>90000</v>
       </c>
-      <c r="K32" s="14">
+      <c r="K32" s="10">
         <v>44873</v>
       </c>
-      <c r="L32" s="14">
+      <c r="L32" s="10">
         <v>45485</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="11" t="s">
+      <c r="A33" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="B33" s="11" t="s">
+      <c r="B33" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="C33" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="D33" s="11" t="s">
+      <c r="D33" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E33" s="11" t="s">
+      <c r="E33" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="F33" s="11" t="s">
+      <c r="F33" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="G33" s="11">
+      <c r="G33" s="7">
         <v>0.5958</v>
       </c>
-      <c r="H33" s="12">
-        <v>6016602.48</v>
-      </c>
-      <c r="I33" s="13">
+      <c r="H33" s="8">
+        <v>6016602.4800000004</v>
+      </c>
+      <c r="I33" s="9">
         <v>3584685.32</v>
       </c>
-      <c r="J33" s="12">
+      <c r="J33" s="8">
         <v>2431917.1600000006</v>
       </c>
-      <c r="K33" s="14">
+      <c r="K33" s="10">
         <v>45133</v>
       </c>
-      <c r="L33" s="14">
+      <c r="L33" s="10">
         <v>46128</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="11" t="s">
+      <c r="A34" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="D34" s="11" t="s">
+      <c r="D34" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E34" s="11" t="s">
+      <c r="E34" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="F34" s="11" t="s">
+      <c r="F34" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="G34" s="11">
-        <v>0.9998</v>
-      </c>
-      <c r="H34" s="12">
-        <v>8396309.76</v>
-      </c>
-      <c r="I34" s="13">
-        <v>8394769.02</v>
-      </c>
-      <c r="J34" s="12">
+      <c r="G34" s="7">
+        <v>0.99980000000000002</v>
+      </c>
+      <c r="H34" s="8">
+        <v>8396309.7599999998</v>
+      </c>
+      <c r="I34" s="9">
+        <v>8394769.0199999996</v>
+      </c>
+      <c r="J34" s="8">
         <v>1540.7400000002235</v>
       </c>
-      <c r="K34" s="14">
+      <c r="K34" s="10">
         <v>44868</v>
       </c>
-      <c r="L34" s="14">
+      <c r="L34" s="10">
         <v>45560</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="11" t="s">
+      <c r="A35" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="B35" s="11" t="s">
+      <c r="B35" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="C35" s="11" t="s">
+      <c r="C35" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="D35" s="11" t="s">
+      <c r="D35" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E35" s="11" t="s">
+      <c r="E35" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="F35" s="11" t="s">
+      <c r="F35" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="G35" s="11">
-        <v>0.9865</v>
-      </c>
-      <c r="H35" s="12">
-        <v>45237596.81</v>
-      </c>
-      <c r="I35" s="13">
-        <v>44626728.2</v>
-      </c>
-      <c r="J35" s="12">
+      <c r="G35" s="7">
+        <v>0.98650000000000004</v>
+      </c>
+      <c r="H35" s="8">
+        <v>45237596.810000002</v>
+      </c>
+      <c r="I35" s="9">
+        <v>44626728.200000003</v>
+      </c>
+      <c r="J35" s="8">
         <v>610868.6099999994</v>
       </c>
-      <c r="K35" s="14">
+      <c r="K35" s="10">
         <v>44769</v>
       </c>
-      <c r="L35" s="14">
+      <c r="L35" s="10">
         <v>45701</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="11" t="s">
+      <c r="A36" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="B36" s="11" t="s">
+      <c r="B36" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="C36" s="11" t="s">
+      <c r="C36" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="D36" s="11" t="s">
+      <c r="D36" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E36" s="11" t="s">
+      <c r="E36" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="F36" s="11" t="s">
+      <c r="F36" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G36" s="11">
+      <c r="G36" s="7">
         <v>0.9899</v>
       </c>
-      <c r="H36" s="12">
-        <v>148784461.49</v>
-      </c>
-      <c r="I36" s="13">
+      <c r="H36" s="8">
+        <v>148784461.49000001</v>
+      </c>
+      <c r="I36" s="9">
         <v>147280622.62</v>
       </c>
-      <c r="J36" s="12">
+      <c r="J36" s="8">
         <v>1503838.8700000048</v>
       </c>
-      <c r="K36" s="14">
+      <c r="K36" s="10">
         <v>45503</v>
       </c>
-      <c r="L36" s="14">
+      <c r="L36" s="10">
         <v>46043</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" s="11" t="s">
+      <c r="A37" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="B37" s="11" t="s">
+      <c r="B37" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="C37" s="11" t="s">
+      <c r="C37" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="D37" s="11" t="s">
+      <c r="D37" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E37" s="11" t="s">
+      <c r="E37" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="F37" s="11" t="s">
+      <c r="F37" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="G37" s="11">
-        <v>0.9781</v>
-      </c>
-      <c r="H37" s="12">
-        <v>90986818.17</v>
-      </c>
-      <c r="I37" s="13">
-        <v>88995375.53</v>
-      </c>
-      <c r="J37" s="12">
+      <c r="G37" s="7">
+        <v>0.97809999999999997</v>
+      </c>
+      <c r="H37" s="8">
+        <v>90986818.170000002</v>
+      </c>
+      <c r="I37" s="9">
+        <v>88995375.530000001</v>
+      </c>
+      <c r="J37" s="8">
         <v>1991442.6400000006</v>
       </c>
-      <c r="K37" s="14">
+      <c r="K37" s="10">
         <v>44986</v>
       </c>
-      <c r="L37" s="14">
+      <c r="L37" s="10">
         <v>45589</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="11" t="s">
+      <c r="A38" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="B38" s="11" t="s">
+      <c r="B38" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="C38" s="11" t="s">
+      <c r="C38" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="D38" s="11" t="s">
+      <c r="D38" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E38" s="11" t="s">
+      <c r="E38" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="F38" s="11" t="s">
+      <c r="F38" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G38" s="11">
-        <v>0.9786</v>
-      </c>
-      <c r="H38" s="12">
-        <v>113557951.65</v>
-      </c>
-      <c r="I38" s="13">
-        <v>111133195.68</v>
-      </c>
-      <c r="J38" s="12">
-        <v>2424755.969999999</v>
-      </c>
-      <c r="K38" s="14">
+      <c r="G38" s="7">
+        <v>0.97860000000000003</v>
+      </c>
+      <c r="H38" s="8">
+        <v>113557951.65000001</v>
+      </c>
+      <c r="I38" s="9">
+        <v>111133195.68000001</v>
+      </c>
+      <c r="J38" s="8">
+        <v>2424755.9699999988</v>
+      </c>
+      <c r="K38" s="10">
         <v>45498</v>
       </c>
-      <c r="L38" s="14">
+      <c r="L38" s="10">
         <v>46038</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="11" t="s">
+      <c r="A39" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="B39" s="11" t="s">
+      <c r="B39" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="C39" s="11" t="s">
+      <c r="C39" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="D39" s="11" t="s">
+      <c r="D39" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E39" s="11" t="s">
+      <c r="E39" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="F39" s="11" t="s">
+      <c r="F39" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G39" s="11">
-        <v>0.9301</v>
-      </c>
-      <c r="H39" s="12">
-        <v>41651255.98</v>
-      </c>
-      <c r="I39" s="13">
-        <v>38738669.02</v>
-      </c>
-      <c r="J39" s="12">
+      <c r="G39" s="7">
+        <v>0.93010000000000004</v>
+      </c>
+      <c r="H39" s="8">
+        <v>41651255.979999997</v>
+      </c>
+      <c r="I39" s="9">
+        <v>38738669.020000003</v>
+      </c>
+      <c r="J39" s="8">
         <v>2912586.9599999934</v>
       </c>
-      <c r="K39" s="14">
+      <c r="K39" s="10">
         <v>45391</v>
       </c>
-      <c r="L39" s="14">
+      <c r="L39" s="10">
         <v>46057</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="11" t="s">
+      <c r="A40" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="B40" s="11" t="s">
+      <c r="B40" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="C40" s="11" t="s">
+      <c r="C40" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="D40" s="11" t="s">
+      <c r="D40" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E40" s="11" t="s">
+      <c r="E40" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="F40" s="11" t="s">
+      <c r="F40" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G40" s="11">
-        <v>0.5526</v>
-      </c>
-      <c r="H40" s="12">
+      <c r="G40" s="7">
+        <v>0.55259999999999998</v>
+      </c>
+      <c r="H40" s="8">
         <v>22759968.59</v>
       </c>
-      <c r="I40" s="13">
+      <c r="I40" s="9">
         <v>12576165.07</v>
       </c>
-      <c r="J40" s="12">
+      <c r="J40" s="8">
         <v>10183803.52</v>
       </c>
-      <c r="K40" s="14">
+      <c r="K40" s="10">
         <v>44511</v>
       </c>
-      <c r="L40" s="14">
+      <c r="L40" s="10">
         <v>44958</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41" s="11" t="s">
+      <c r="A41" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="B41" s="11" t="s">
+      <c r="B41" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="C41" s="11" t="s">
+      <c r="C41" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="D41" s="11" t="s">
+      <c r="D41" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E41" s="11" t="s">
+      <c r="E41" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="F41" s="11" t="s">
+      <c r="F41" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="G41" s="11">
-        <v>0.5414</v>
-      </c>
-      <c r="H41" s="12">
+      <c r="G41" s="7">
+        <v>0.54139999999999999</v>
+      </c>
+      <c r="H41" s="8">
         <v>26504288.68</v>
       </c>
-      <c r="I41" s="13">
+      <c r="I41" s="9">
         <v>14348711.09</v>
       </c>
-      <c r="J41" s="12">
+      <c r="J41" s="8">
         <v>12155577.59</v>
       </c>
-      <c r="K41" s="14">
+      <c r="K41" s="10">
         <v>45190</v>
       </c>
-      <c r="L41" s="14">
+      <c r="L41" s="10">
         <v>46153</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="11" t="s">
+      <c r="A42" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="B42" s="11" t="s">
+      <c r="B42" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="C42" s="11" t="s">
+      <c r="C42" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="D42" s="11" t="s">
+      <c r="D42" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E42" s="11" t="s">
+      <c r="E42" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="F42" s="11" t="s">
+      <c r="F42" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="G42" s="11">
-        <v>0.0105</v>
-      </c>
-      <c r="H42" s="12">
+      <c r="G42" s="7">
+        <v>1.0500000000000001E-2</v>
+      </c>
+      <c r="H42" s="8">
         <v>12679339.18</v>
       </c>
-      <c r="I42" s="13">
-        <v>133236.58</v>
-      </c>
-      <c r="J42" s="12">
+      <c r="I42" s="9">
+        <v>133236.57999999999</v>
+      </c>
+      <c r="J42" s="8">
         <v>12546102.6</v>
       </c>
-      <c r="K42" s="14">
+      <c r="K42" s="10">
         <v>44753</v>
       </c>
-      <c r="L42" s="14">
+      <c r="L42" s="10">
         <v>44984</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43" s="11" t="s">
+      <c r="A43" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="B43" s="11" t="s">
+      <c r="B43" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="C43" s="11" t="s">
+      <c r="C43" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="D43" s="11" t="s">
+      <c r="D43" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E43" s="11" t="s">
+      <c r="E43" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="F43" s="11" t="s">
+      <c r="F43" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="G43" s="11">
-        <v>0.0063</v>
-      </c>
-      <c r="H43" s="12">
-        <v>21672861.46</v>
-      </c>
-      <c r="I43" s="13">
+      <c r="G43" s="7">
+        <v>6.3E-3</v>
+      </c>
+      <c r="H43" s="8">
+        <v>21672861.460000001</v>
+      </c>
+      <c r="I43" s="9">
         <v>137475.09</v>
       </c>
-      <c r="J43" s="12">
-        <v>21535386.37</v>
-      </c>
-      <c r="K43" s="14">
+      <c r="J43" s="8">
+        <v>21535386.370000001</v>
+      </c>
+      <c r="K43" s="10">
         <v>44783</v>
       </c>
-      <c r="L43" s="14">
+      <c r="L43" s="10">
         <v>44998</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44" s="11" t="s">
+      <c r="A44" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="B44" s="11" t="s">
+      <c r="B44" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="C44" s="11" t="s">
+      <c r="C44" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="D44" s="11" t="s">
+      <c r="D44" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E44" s="11" t="s">
+      <c r="E44" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="F44" s="11" t="s">
+      <c r="F44" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="G44" s="11">
+      <c r="G44" s="7">
         <v>0.2034</v>
       </c>
-      <c r="H44" s="12">
+      <c r="H44" s="8">
         <v>30334596.91</v>
       </c>
-      <c r="I44" s="13">
-        <v>6171237.78</v>
-      </c>
-      <c r="J44" s="12">
-        <v>24163359.13</v>
-      </c>
-      <c r="K44" s="14">
+      <c r="I44" s="9">
+        <v>6171237.7800000003</v>
+      </c>
+      <c r="J44" s="8">
+        <v>24163359.129999999</v>
+      </c>
+      <c r="K44" s="10">
         <v>44753</v>
       </c>
-      <c r="L44" s="14">
+      <c r="L44" s="10">
         <v>45505</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45" s="11" t="s">
+      <c r="A45" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="B45" s="11" t="s">
+      <c r="B45" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="C45" s="11" t="s">
+      <c r="C45" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="D45" s="11" t="s">
+      <c r="D45" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E45" s="11" t="s">
+      <c r="E45" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="F45" s="11" t="s">
+      <c r="F45" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G45" s="11">
+      <c r="G45" s="7">
         <v>0.38670000000000004</v>
       </c>
-      <c r="H45" s="12">
-        <v>58032411.71</v>
-      </c>
-      <c r="I45" s="13">
-        <v>22442987.53</v>
-      </c>
-      <c r="J45" s="12">
+      <c r="H45" s="8">
+        <v>58032411.710000001</v>
+      </c>
+      <c r="I45" s="9">
+        <v>22442987.530000001</v>
+      </c>
+      <c r="J45" s="8">
         <v>35589424.18</v>
       </c>
-      <c r="K45" s="14">
+      <c r="K45" s="10">
         <v>44753</v>
       </c>
-      <c r="L45" s="14">
+      <c r="L45" s="10">
         <v>46077</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" s="11" t="s">
+      <c r="A46" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="B46" s="11" t="s">
+      <c r="B46" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="C46" s="11" t="s">
+      <c r="C46" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="D46" s="11" t="s">
+      <c r="D46" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E46" s="11" t="s">
+      <c r="E46" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="F46" s="11" t="s">
+      <c r="F46" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="G46" s="11">
+      <c r="G46" s="7">
         <v>0.25579999999999997</v>
       </c>
-      <c r="H46" s="12">
-        <v>51119038.92</v>
-      </c>
-      <c r="I46" s="13">
+      <c r="H46" s="8">
+        <v>51119038.920000002</v>
+      </c>
+      <c r="I46" s="9">
         <v>13076598.15</v>
       </c>
-      <c r="J46" s="12">
-        <v>38042440.77</v>
-      </c>
-      <c r="K46" s="14">
+      <c r="J46" s="8">
+        <v>38042440.770000003</v>
+      </c>
+      <c r="K46" s="10">
         <v>44753</v>
       </c>
-      <c r="L46" s="14">
+      <c r="L46" s="10">
         <v>46209</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="11" t="s">
+      <c r="A47" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="B47" s="11" t="s">
+      <c r="B47" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="C47" s="11" t="s">
+      <c r="C47" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="D47" s="11" t="s">
+      <c r="D47" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E47" s="11" t="s">
+      <c r="E47" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="F47" s="11" t="s">
+      <c r="F47" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="G47" s="11">
+      <c r="G47" s="7">
         <v>0.4456</v>
       </c>
-      <c r="H47" s="12">
+      <c r="H47" s="8">
         <v>69450000</v>
       </c>
-      <c r="I47" s="13">
+      <c r="I47" s="9">
         <v>30949430.48</v>
       </c>
-      <c r="J47" s="12">
+      <c r="J47" s="8">
         <v>38500569.519999996</v>
       </c>
-      <c r="K47" s="14">
+      <c r="K47" s="10">
         <v>44449</v>
       </c>
-      <c r="L47" s="14">
+      <c r="L47" s="10">
         <v>45329</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48" s="11" t="s">
+      <c r="A48" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="B48" s="11" t="s">
+      <c r="B48" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="C48" s="11" t="s">
+      <c r="C48" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="D48" s="11" t="s">
+      <c r="D48" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E48" s="11" t="s">
+      <c r="E48" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="F48" s="11" t="s">
+      <c r="F48" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="G48" s="11">
-        <v>0.4495</v>
-      </c>
-      <c r="H48" s="12">
-        <v>84484346.71</v>
-      </c>
-      <c r="I48" s="13">
-        <v>37978980.67</v>
-      </c>
-      <c r="J48" s="12">
-        <v>46505366.03999999</v>
-      </c>
-      <c r="K48" s="14">
+      <c r="G48" s="7">
+        <v>0.44950000000000001</v>
+      </c>
+      <c r="H48" s="8">
+        <v>84484346.709999993</v>
+      </c>
+      <c r="I48" s="9">
+        <v>37978980.670000002</v>
+      </c>
+      <c r="J48" s="8">
+        <v>46505366.039999992</v>
+      </c>
+      <c r="K48" s="10">
         <v>44449</v>
       </c>
-      <c r="L48" s="14">
+      <c r="L48" s="10">
         <v>45329</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A49" s="11" t="s">
+      <c r="A49" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="B49" s="11" t="s">
+      <c r="B49" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="C49" s="11" t="s">
+      <c r="C49" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="D49" s="11" t="s">
+      <c r="D49" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E49" s="11" t="s">
+      <c r="E49" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="F49" s="11" t="s">
+      <c r="F49" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="G49" s="11">
-        <v>0.0028000000000000004</v>
-      </c>
-      <c r="H49" s="12">
-        <v>47996411.38</v>
-      </c>
-      <c r="I49" s="13">
-        <v>133579.45</v>
-      </c>
-      <c r="J49" s="12">
+      <c r="G49" s="7">
+        <v>2.8000000000000004E-3</v>
+      </c>
+      <c r="H49" s="8">
+        <v>47996411.380000003</v>
+      </c>
+      <c r="I49" s="9">
+        <v>133579.45000000001</v>
+      </c>
+      <c r="J49" s="8">
         <v>47862831.93</v>
       </c>
-      <c r="K49" s="14">
+      <c r="K49" s="10">
         <v>44887</v>
       </c>
-      <c r="L49" s="14">
+      <c r="L49" s="10">
         <v>45187</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50" s="11" t="s">
+      <c r="A50" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="B50" s="11" t="s">
+      <c r="B50" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="C50" s="11" t="s">
+      <c r="C50" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="D50" s="11" t="s">
+      <c r="D50" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E50" s="11" t="s">
+      <c r="E50" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="F50" s="11" t="s">
+      <c r="F50" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="G50" s="11">
-        <v>0.0377</v>
-      </c>
-      <c r="H50" s="12">
+      <c r="G50" s="7">
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="H50" s="8">
         <v>54283415</v>
       </c>
-      <c r="I50" s="13">
+      <c r="I50" s="9">
         <v>2045374.39</v>
       </c>
-      <c r="J50" s="12">
-        <v>52238040.61</v>
-      </c>
-      <c r="K50" s="14">
+      <c r="J50" s="8">
+        <v>52238040.609999999</v>
+      </c>
+      <c r="K50" s="10">
         <v>44753</v>
       </c>
-      <c r="L50" s="14">
+      <c r="L50" s="10">
         <v>46195</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51" s="11" t="s">
+      <c r="A51" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="B51" s="11" t="s">
+      <c r="B51" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="C51" s="11" t="s">
+      <c r="C51" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="D51" s="11" t="s">
+      <c r="D51" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E51" s="11" t="s">
+      <c r="E51" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="F51" s="11" t="s">
+      <c r="F51" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="G51" s="11">
-        <v>0.9643999999999999</v>
-      </c>
-      <c r="H51" s="12">
-        <v>1332580.86</v>
-      </c>
-      <c r="I51" s="13">
-        <v>1285178.36</v>
-      </c>
-      <c r="J51" s="12">
+      <c r="G51" s="7">
+        <v>0.96439999999999992</v>
+      </c>
+      <c r="H51" s="8">
+        <v>1332580.8600000001</v>
+      </c>
+      <c r="I51" s="9">
+        <v>1285178.3600000001</v>
+      </c>
+      <c r="J51" s="8">
         <v>47402.5</v>
       </c>
-      <c r="K51" s="14">
+      <c r="K51" s="10">
         <v>44536</v>
       </c>
-      <c r="L51" s="14">
+      <c r="L51" s="10">
         <v>45230</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A52" s="11" t="s">
+      <c r="A52" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="B52" s="11" t="s">
+      <c r="B52" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="C52" s="11" t="s">
+      <c r="C52" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="D52" s="11" t="s">
+      <c r="D52" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E52" s="11" t="s">
+      <c r="E52" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="F52" s="11" t="s">
+      <c r="F52" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="G52" s="11">
+      <c r="G52" s="7">
         <v>1</v>
       </c>
-      <c r="H52" s="12">
-        <v>8156656.19</v>
-      </c>
-      <c r="I52" s="13">
-        <v>8156656.13</v>
-      </c>
-      <c r="J52" s="12">
-        <v>0.06000000052154064</v>
-      </c>
-      <c r="K52" s="14">
+      <c r="H52" s="8">
+        <v>8156656.1900000004</v>
+      </c>
+      <c r="I52" s="9">
+        <v>8156656.1299999999</v>
+      </c>
+      <c r="J52" s="8">
+        <v>6.0000000521540642E-2</v>
+      </c>
+      <c r="K52" s="10">
         <v>44832</v>
       </c>
-      <c r="L52" s="14">
+      <c r="L52" s="10">
         <v>45378</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A53" s="11" t="s">
+      <c r="A53" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="B53" s="11" t="s">
+      <c r="B53" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="C53" s="11" t="s">
+      <c r="C53" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="D53" s="11" t="s">
+      <c r="D53" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E53" s="11" t="s">
+      <c r="E53" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="F53" s="11" t="s">
+      <c r="F53" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="G53" s="11">
-        <v>0.8421</v>
-      </c>
-      <c r="H53" s="12">
-        <v>7704834.91</v>
-      </c>
-      <c r="I53" s="13">
-        <v>6488132.94</v>
-      </c>
-      <c r="J53" s="12">
+      <c r="G53" s="7">
+        <v>0.84209999999999996</v>
+      </c>
+      <c r="H53" s="8">
+        <v>7704834.9100000001</v>
+      </c>
+      <c r="I53" s="9">
+        <v>6488132.9400000004</v>
+      </c>
+      <c r="J53" s="8">
         <v>1216701.9699999997</v>
       </c>
-      <c r="K53" s="14">
+      <c r="K53" s="10">
         <v>45286</v>
       </c>
-      <c r="L53" s="14">
+      <c r="L53" s="10">
         <v>46098</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A54" s="11" t="s">
+      <c r="A54" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="B54" s="11" t="s">
+      <c r="B54" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="C54" s="11" t="s">
+      <c r="C54" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="D54" s="11" t="s">
+      <c r="D54" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E54" s="11" t="s">
+      <c r="E54" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="F54" s="11" t="s">
+      <c r="F54" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="G54" s="11">
+      <c r="G54" s="7">
         <v>0</v>
       </c>
-      <c r="H54" s="12">
-        <v>11620104.78</v>
-      </c>
-      <c r="I54" s="13">
+      <c r="H54" s="8">
+        <v>11620104.779999999</v>
+      </c>
+      <c r="I54" s="9">
         <v>0</v>
       </c>
-      <c r="J54" s="12">
-        <v>11620104.78</v>
-      </c>
-      <c r="K54" s="15" t="s">
+      <c r="J54" s="8">
+        <v>11620104.779999999</v>
+      </c>
+      <c r="K54" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="L54" s="15" t="s">
+      <c r="L54" s="12" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A55" s="11" t="s">
+      <c r="A55" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="B55" s="11" t="s">
+      <c r="B55" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="C55" s="11" t="s">
+      <c r="C55" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="D55" s="11" t="s">
+      <c r="D55" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E55" s="11" t="s">
+      <c r="E55" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="F55" s="11" t="s">
+      <c r="F55" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="G55" s="11">
-        <v>0.9754</v>
-      </c>
-      <c r="H55" s="12">
-        <v>56189486.28</v>
-      </c>
-      <c r="I55" s="13">
+      <c r="G55" s="7">
+        <v>0.97540000000000004</v>
+      </c>
+      <c r="H55" s="8">
+        <v>56189486.280000001</v>
+      </c>
+      <c r="I55" s="9">
         <v>54809333.5</v>
       </c>
-      <c r="J55" s="12">
+      <c r="J55" s="8">
         <v>1380152.7800000012</v>
       </c>
-      <c r="K55" s="14">
+      <c r="K55" s="10">
         <v>45035</v>
       </c>
-      <c r="L55" s="14">
+      <c r="L55" s="10">
         <v>46360</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A56" s="11" t="s">
+      <c r="A56" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="B56" s="11" t="s">
+      <c r="B56" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="C56" s="11" t="s">
+      <c r="C56" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="D56" s="11" t="s">
+      <c r="D56" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E56" s="11" t="s">
+      <c r="E56" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="F56" s="11" t="s">
+      <c r="F56" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="G56" s="11">
+      <c r="G56" s="7">
         <v>1</v>
       </c>
-      <c r="H56" s="12">
+      <c r="H56" s="8">
         <v>4374443.78</v>
       </c>
-      <c r="I56" s="13">
+      <c r="I56" s="9">
         <v>4374443.78</v>
       </c>
-      <c r="J56" s="12">
+      <c r="J56" s="8">
         <v>0</v>
       </c>
-      <c r="K56" s="14">
+      <c r="K56" s="10">
         <v>44707</v>
       </c>
-      <c r="L56" s="14">
+      <c r="L56" s="10">
         <v>45488</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A57" s="11" t="s">
+      <c r="A57" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="B57" s="11" t="s">
+      <c r="B57" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="C57" s="11" t="s">
+      <c r="C57" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="D57" s="11" t="s">
+      <c r="D57" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E57" s="11" t="s">
+      <c r="E57" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="F57" s="11" t="s">
+      <c r="F57" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G57" s="11">
-        <v>0.9994</v>
-      </c>
-      <c r="H57" s="12">
-        <v>14995089.28</v>
-      </c>
-      <c r="I57" s="13">
-        <v>14985558.45</v>
-      </c>
-      <c r="J57" s="12">
-        <v>9530.830000000075</v>
-      </c>
-      <c r="K57" s="14">
+      <c r="G57" s="7">
+        <v>0.99939999999999996</v>
+      </c>
+      <c r="H57" s="8">
+        <v>14995089.279999999</v>
+      </c>
+      <c r="I57" s="9">
+        <v>14985558.449999999</v>
+      </c>
+      <c r="J57" s="8">
+        <v>9530.8300000000745</v>
+      </c>
+      <c r="K57" s="10">
         <v>44719</v>
       </c>
-      <c r="L57" s="14">
+      <c r="L57" s="10">
         <v>45476</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A58" s="11" t="s">
+      <c r="A58" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="B58" s="11" t="s">
+      <c r="B58" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="C58" s="11" t="s">
+      <c r="C58" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="D58" s="11" t="s">
+      <c r="D58" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="E58" s="11" t="s">
+      <c r="E58" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="F58" s="11" t="s">
+      <c r="F58" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="G58" s="11">
-        <v>0.8652</v>
-      </c>
-      <c r="H58" s="12">
-        <v>8463890.94</v>
-      </c>
-      <c r="I58" s="13">
-        <v>7322834.12</v>
-      </c>
-      <c r="J58" s="12">
+      <c r="G58" s="7">
+        <v>0.86519999999999997</v>
+      </c>
+      <c r="H58" s="8">
+        <v>8463890.9399999995</v>
+      </c>
+      <c r="I58" s="9">
+        <v>7322834.1200000001</v>
+      </c>
+      <c r="J58" s="8">
         <v>1141056.8199999994</v>
       </c>
-      <c r="K58" s="14">
+      <c r="K58" s="10">
         <v>44688</v>
       </c>
-      <c r="L58" s="14">
+      <c r="L58" s="10">
         <v>46045</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A59" s="11" t="s">
+      <c r="A59" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="B59" s="11" t="s">
+      <c r="B59" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="C59" s="11" t="s">
+      <c r="C59" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="D59" s="11" t="s">
+      <c r="D59" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E59" s="11" t="s">
+      <c r="E59" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="F59" s="11" t="s">
+      <c r="F59" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="G59" s="11">
+      <c r="G59" s="7">
         <v>0.4113</v>
       </c>
-      <c r="H59" s="12">
+      <c r="H59" s="8">
         <v>30477728.43</v>
       </c>
-      <c r="I59" s="13">
-        <v>12534756.7</v>
-      </c>
-      <c r="J59" s="12">
+      <c r="I59" s="9">
+        <v>12534756.699999999</v>
+      </c>
+      <c r="J59" s="8">
         <v>17942971.73</v>
       </c>
-      <c r="K59" s="14">
+      <c r="K59" s="10">
         <v>44708</v>
       </c>
-      <c r="L59" s="14">
+      <c r="L59" s="10">
         <v>45437</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A60" s="11" t="s">
+      <c r="A60" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="B60" s="11" t="s">
+      <c r="B60" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="C60" s="11" t="s">
+      <c r="C60" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="D60" s="11" t="s">
+      <c r="D60" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E60" s="11" t="s">
+      <c r="E60" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="F60" s="11" t="s">
+      <c r="F60" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="G60" s="11">
+      <c r="G60" s="7">
         <v>0.97</v>
       </c>
-      <c r="H60" s="12">
-        <v>5722613.87</v>
-      </c>
-      <c r="I60" s="13">
+      <c r="H60" s="8">
+        <v>5722613.8700000001</v>
+      </c>
+      <c r="I60" s="9">
         <v>5551029.21</v>
       </c>
-      <c r="J60" s="12">
+      <c r="J60" s="8">
         <v>171584.66000000015</v>
       </c>
-      <c r="K60" s="14">
+      <c r="K60" s="10">
         <v>44727</v>
       </c>
-      <c r="L60" s="14">
+      <c r="L60" s="10">
         <v>45489</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A61" s="11" t="s">
+      <c r="A61" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="B61" s="11" t="s">
+      <c r="B61" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="C61" s="11" t="s">
+      <c r="C61" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="D61" s="11" t="s">
+      <c r="D61" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E61" s="11" t="s">
+      <c r="E61" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="F61" s="11" t="s">
+      <c r="F61" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="G61" s="11">
-        <v>0.8092</v>
-      </c>
-      <c r="H61" s="12">
+      <c r="G61" s="7">
+        <v>0.80920000000000003</v>
+      </c>
+      <c r="H61" s="8">
         <v>51359899.57</v>
       </c>
-      <c r="I61" s="13">
-        <v>41562191.24</v>
-      </c>
-      <c r="J61" s="12">
-        <v>9797708.329999998</v>
-      </c>
-      <c r="K61" s="14">
+      <c r="I61" s="9">
+        <v>41562191.240000002</v>
+      </c>
+      <c r="J61" s="8">
+        <v>9797708.3299999982</v>
+      </c>
+      <c r="K61" s="10">
         <v>45105</v>
       </c>
-      <c r="L61" s="14">
+      <c r="L61" s="10">
         <v>45769</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A62" s="11" t="s">
+      <c r="A62" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="B62" s="11" t="s">
+      <c r="B62" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="C62" s="11" t="s">
+      <c r="C62" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="D62" s="11" t="s">
+      <c r="D62" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E62" s="11" t="s">
+      <c r="E62" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="F62" s="11" t="s">
+      <c r="F62" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G62" s="11">
+      <c r="G62" s="7">
         <v>1</v>
       </c>
-      <c r="H62" s="12">
-        <v>6948720.19</v>
-      </c>
-      <c r="I62" s="13">
-        <v>6948720.19</v>
-      </c>
-      <c r="J62" s="12">
+      <c r="H62" s="8">
+        <v>6948720.1900000004</v>
+      </c>
+      <c r="I62" s="9">
+        <v>6948720.1900000004</v>
+      </c>
+      <c r="J62" s="8">
         <v>0</v>
       </c>
-      <c r="K62" s="14">
+      <c r="K62" s="10">
         <v>44882</v>
       </c>
-      <c r="L62" s="14">
+      <c r="L62" s="10">
         <v>45147</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A63" s="11" t="s">
+      <c r="A63" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="B63" s="11" t="s">
+      <c r="B63" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="C63" s="11" t="s">
+      <c r="C63" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="D63" s="11" t="s">
+      <c r="D63" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E63" s="11" t="s">
+      <c r="E63" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="F63" s="11" t="s">
+      <c r="F63" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="G63" s="11">
-        <v>0.9765999999999999</v>
-      </c>
-      <c r="H63" s="12">
+      <c r="G63" s="7">
+        <v>0.97659999999999991</v>
+      </c>
+      <c r="H63" s="8">
         <v>3107538.75</v>
       </c>
-      <c r="I63" s="13">
+      <c r="I63" s="9">
         <v>3034704.58</v>
       </c>
-      <c r="J63" s="12">
-        <v>72834.16999999993</v>
-      </c>
-      <c r="K63" s="14">
+      <c r="J63" s="8">
+        <v>72834.169999999925</v>
+      </c>
+      <c r="K63" s="10">
         <v>44536</v>
       </c>
-      <c r="L63" s="14">
+      <c r="L63" s="10">
         <v>45386</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A64" s="11" t="s">
+      <c r="A64" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="B64" s="11" t="s">
+      <c r="B64" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="C64" s="11" t="s">
+      <c r="C64" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="D64" s="11" t="s">
+      <c r="D64" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E64" s="11" t="s">
+      <c r="E64" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="F64" s="11" t="s">
+      <c r="F64" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="G64" s="11">
+      <c r="G64" s="7">
         <v>0.9577</v>
       </c>
-      <c r="H64" s="12">
+      <c r="H64" s="8">
         <v>2994510.29</v>
       </c>
-      <c r="I64" s="13">
+      <c r="I64" s="9">
         <v>2867705.32</v>
       </c>
-      <c r="J64" s="12">
+      <c r="J64" s="8">
         <v>126804.9700000002</v>
       </c>
-      <c r="K64" s="14">
+      <c r="K64" s="10">
         <v>44804</v>
       </c>
-      <c r="L64" s="14">
+      <c r="L64" s="10">
         <v>45208</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A65" s="11" t="s">
+      <c r="A65" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="B65" s="11" t="s">
+      <c r="B65" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="C65" s="11" t="s">
+      <c r="C65" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="D65" s="11" t="s">
+      <c r="D65" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E65" s="11" t="s">
+      <c r="E65" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="F65" s="11" t="s">
+      <c r="F65" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="G65" s="11">
-        <v>0.8787</v>
-      </c>
-      <c r="H65" s="12">
-        <v>6519257.05</v>
-      </c>
-      <c r="I65" s="13">
-        <v>5728240.86</v>
-      </c>
-      <c r="J65" s="12">
-        <v>791016.1899999995</v>
-      </c>
-      <c r="K65" s="14">
+      <c r="G65" s="7">
+        <v>0.87870000000000004</v>
+      </c>
+      <c r="H65" s="8">
+        <v>6519257.0499999998</v>
+      </c>
+      <c r="I65" s="9">
+        <v>5728240.8600000003</v>
+      </c>
+      <c r="J65" s="8">
+        <v>791016.18999999948</v>
+      </c>
+      <c r="K65" s="10">
         <v>44804</v>
       </c>
-      <c r="L65" s="14">
+      <c r="L65" s="10">
         <v>45569</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A66" s="11" t="s">
+      <c r="A66" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="B66" s="11" t="s">
+      <c r="B66" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="C66" s="11" t="s">
+      <c r="C66" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="D66" s="11" t="s">
+      <c r="D66" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E66" s="11" t="s">
+      <c r="E66" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="F66" s="11" t="s">
+      <c r="F66" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="G66" s="11">
-        <v>0.545</v>
-      </c>
-      <c r="H66" s="12">
+      <c r="G66" s="7">
+        <v>0.54500000000000004</v>
+      </c>
+      <c r="H66" s="8">
         <v>2069000</v>
       </c>
-      <c r="I66" s="13">
+      <c r="I66" s="9">
         <v>1127516.06</v>
       </c>
-      <c r="J66" s="12">
+      <c r="J66" s="8">
         <v>941483.94</v>
       </c>
-      <c r="K66" s="14">
+      <c r="K66" s="10">
         <v>45972</v>
       </c>
-      <c r="L66" s="14">
+      <c r="L66" s="10">
         <v>46167</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A67" s="11" t="s">
+      <c r="A67" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="B67" s="11" t="s">
+      <c r="B67" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="C67" s="11" t="s">
+      <c r="C67" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="D67" s="11" t="s">
+      <c r="D67" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E67" s="11" t="s">
+      <c r="E67" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="F67" s="11" t="s">
+      <c r="F67" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G67" s="11">
+      <c r="G67" s="7">
         <v>0.6604000000000001</v>
       </c>
-      <c r="H67" s="12">
-        <v>12950372.72</v>
-      </c>
-      <c r="I67" s="13">
-        <v>8552770.91</v>
-      </c>
-      <c r="J67" s="12">
+      <c r="H67" s="8">
+        <v>12950372.720000001</v>
+      </c>
+      <c r="I67" s="9">
+        <v>8552770.9100000001</v>
+      </c>
+      <c r="J67" s="8">
         <v>4397601.8100000005</v>
       </c>
-      <c r="K67" s="14">
+      <c r="K67" s="10">
         <v>44742</v>
       </c>
-      <c r="L67" s="14">
+      <c r="L67" s="10">
         <v>46219</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A68" s="11" t="s">
+      <c r="A68" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="B68" s="11" t="s">
+      <c r="B68" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="C68" s="11" t="s">
+      <c r="C68" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="D68" s="11" t="s">
+      <c r="D68" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E68" s="11" t="s">
+      <c r="E68" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="F68" s="11" t="s">
+      <c r="F68" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="G68" s="11">
+      <c r="G68" s="7">
         <v>0.47490000000000004</v>
       </c>
-      <c r="H68" s="12">
-        <v>18996888.26</v>
-      </c>
-      <c r="I68" s="13">
+      <c r="H68" s="8">
+        <v>18996888.260000002</v>
+      </c>
+      <c r="I68" s="9">
         <v>9021796.75</v>
       </c>
-      <c r="J68" s="12">
-        <v>9975091.510000002</v>
-      </c>
-      <c r="K68" s="15" t="s">
+      <c r="J68" s="8">
+        <v>9975091.5100000016</v>
+      </c>
+      <c r="K68" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="L68" s="15" t="s">
+      <c r="L68" s="12" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A69" s="11" t="s">
+      <c r="A69" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="B69" s="11" t="s">
+      <c r="B69" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="C69" s="11" t="s">
+      <c r="C69" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="D69" s="11" t="s">
+      <c r="D69" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E69" s="11" t="s">
+      <c r="E69" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="F69" s="11" t="s">
+      <c r="F69" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="G69" s="11">
-        <v>0.9969</v>
-      </c>
-      <c r="H69" s="12">
-        <v>25179808.67</v>
-      </c>
-      <c r="I69" s="13">
-        <v>25102278.03</v>
-      </c>
-      <c r="J69" s="12">
-        <v>77530.6400000006</v>
-      </c>
-      <c r="K69" s="14">
+      <c r="G69" s="7">
+        <v>0.99690000000000001</v>
+      </c>
+      <c r="H69" s="8">
+        <v>25179808.670000002</v>
+      </c>
+      <c r="I69" s="9">
+        <v>25102278.030000001</v>
+      </c>
+      <c r="J69" s="8">
+        <v>77530.640000000596</v>
+      </c>
+      <c r="K69" s="10">
         <v>45646</v>
       </c>
-      <c r="L69" s="14">
+      <c r="L69" s="10">
         <v>46005</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A70" s="11" t="s">
+      <c r="A70" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="B70" s="11" t="s">
+      <c r="B70" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="C70" s="11" t="s">
+      <c r="C70" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="D70" s="11" t="s">
+      <c r="D70" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E70" s="11" t="s">
+      <c r="E70" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="F70" s="11" t="s">
+      <c r="F70" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="G70" s="11">
-        <v>0.8062999999999999</v>
-      </c>
-      <c r="H70" s="12">
-        <v>8811881.78</v>
-      </c>
-      <c r="I70" s="13">
-        <v>7104640.05</v>
-      </c>
-      <c r="J70" s="12">
+      <c r="G70" s="7">
+        <v>0.80629999999999991</v>
+      </c>
+      <c r="H70" s="8">
+        <v>8811881.7799999993</v>
+      </c>
+      <c r="I70" s="9">
+        <v>7104640.0499999998</v>
+      </c>
+      <c r="J70" s="8">
         <v>1707241.7299999995</v>
       </c>
-      <c r="K70" s="14">
+      <c r="K70" s="10">
         <v>45360</v>
       </c>
-      <c r="L70" s="14">
+      <c r="L70" s="10">
         <v>45566</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A71" s="11" t="s">
+      <c r="A71" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="B71" s="11" t="s">
+      <c r="B71" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="C71" s="11" t="s">
+      <c r="C71" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="D71" s="11" t="s">
+      <c r="D71" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E71" s="11" t="s">
+      <c r="E71" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="F71" s="11" t="s">
+      <c r="F71" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="G71" s="11">
+      <c r="G71" s="7">
         <v>1</v>
       </c>
-      <c r="H71" s="12">
+      <c r="H71" s="8">
         <v>724764.22</v>
       </c>
-      <c r="I71" s="13">
+      <c r="I71" s="9">
         <v>724764.22</v>
       </c>
-      <c r="J71" s="12">
+      <c r="J71" s="8">
         <v>0</v>
       </c>
-      <c r="K71" s="14">
+      <c r="K71" s="10">
         <v>44911</v>
       </c>
-      <c r="L71" s="14">
+      <c r="L71" s="10">
         <v>45182</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A72" s="11" t="s">
+      <c r="A72" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="B72" s="11" t="s">
+      <c r="B72" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="C72" s="11" t="s">
+      <c r="C72" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="D72" s="11" t="s">
+      <c r="D72" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E72" s="11" t="s">
+      <c r="E72" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="F72" s="11" t="s">
+      <c r="F72" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G72" s="11">
-        <v>0.8592</v>
-      </c>
-      <c r="H72" s="12">
-        <v>34662990.03</v>
-      </c>
-      <c r="I72" s="13">
-        <v>29783877.3</v>
-      </c>
-      <c r="J72" s="12">
-        <v>4879112.73</v>
-      </c>
-      <c r="K72" s="14">
+      <c r="G72" s="7">
+        <v>0.85919999999999996</v>
+      </c>
+      <c r="H72" s="8">
+        <v>34662990.030000001</v>
+      </c>
+      <c r="I72" s="9">
+        <v>29783877.300000001</v>
+      </c>
+      <c r="J72" s="8">
+        <v>4879112.7300000004</v>
+      </c>
+      <c r="K72" s="10">
         <v>45155</v>
       </c>
-      <c r="L72" s="14">
+      <c r="L72" s="10">
         <v>46239</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A73" s="11" t="s">
+      <c r="A73" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="B73" s="11" t="s">
+      <c r="B73" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="C73" s="11" t="s">
+      <c r="C73" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="D73" s="11" t="s">
+      <c r="D73" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="E73" s="11" t="s">
+      <c r="E73" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="F73" s="11" t="s">
+      <c r="F73" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="G73" s="11">
-        <v>0.07</v>
-      </c>
-      <c r="H73" s="12">
+      <c r="G73" s="7">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="H73" s="8">
         <v>27739392.32</v>
       </c>
-      <c r="I73" s="13">
+      <c r="I73" s="9">
         <v>1940441.71</v>
       </c>
-      <c r="J73" s="12">
-        <v>25798950.61</v>
-      </c>
-      <c r="K73" s="14">
+      <c r="J73" s="8">
+        <v>25798950.609999999</v>
+      </c>
+      <c r="K73" s="10">
         <v>45541</v>
       </c>
-      <c r="L73" s="14">
+      <c r="L73" s="10">
         <v>46081</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A74" s="11" t="s">
+      <c r="A74" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="B74" s="11" t="s">
+      <c r="B74" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="C74" s="11" t="s">
+      <c r="C74" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="D74" s="11" t="s">
+      <c r="D74" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E74" s="11" t="s">
+      <c r="E74" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="F74" s="11" t="s">
+      <c r="F74" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="G74" s="11">
-        <v>0.8991</v>
-      </c>
-      <c r="H74" s="12">
-        <v>666913.68</v>
-      </c>
-      <c r="I74" s="13">
-        <v>599641.31</v>
-      </c>
-      <c r="J74" s="12">
+      <c r="G74" s="7">
+        <v>0.89910000000000001</v>
+      </c>
+      <c r="H74" s="8">
+        <v>666913.68000000005</v>
+      </c>
+      <c r="I74" s="9">
+        <v>599641.31000000006</v>
+      </c>
+      <c r="J74" s="8">
         <v>67272.37</v>
       </c>
-      <c r="K74" s="14">
+      <c r="K74" s="10">
         <v>45783</v>
       </c>
-      <c r="L74" s="14">
+      <c r="L74" s="10">
         <v>45964</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A75" s="11" t="s">
+      <c r="A75" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="B75" s="11" t="s">
+      <c r="B75" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="C75" s="11" t="s">
+      <c r="C75" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="D75" s="11" t="s">
+      <c r="D75" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E75" s="11" t="s">
+      <c r="E75" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="F75" s="11" t="s">
+      <c r="F75" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="G75" s="11">
-        <v>0.8976000000000001</v>
-      </c>
-      <c r="H75" s="12">
+      <c r="G75" s="7">
+        <v>0.89760000000000006</v>
+      </c>
+      <c r="H75" s="8">
         <v>763285.07</v>
       </c>
-      <c r="I75" s="13">
+      <c r="I75" s="9">
         <v>685145.56</v>
       </c>
-      <c r="J75" s="12">
-        <v>78139.5099999999</v>
-      </c>
-      <c r="K75" s="14">
+      <c r="J75" s="8">
+        <v>78139.509999999893</v>
+      </c>
+      <c r="K75" s="10">
         <v>45783</v>
       </c>
-      <c r="L75" s="14">
+      <c r="L75" s="10">
         <v>46115</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A76" s="11" t="s">
+      <c r="A76" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="B76" s="11" t="s">
+      <c r="B76" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="C76" s="11" t="s">
+      <c r="C76" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="D76" s="11" t="s">
+      <c r="D76" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E76" s="11" t="s">
+      <c r="E76" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="F76" s="11" t="s">
+      <c r="F76" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="G76" s="11">
-        <v>0.9495</v>
-      </c>
-      <c r="H76" s="12">
-        <v>32836774.76</v>
-      </c>
-      <c r="I76" s="13">
-        <v>31178236.21</v>
-      </c>
-      <c r="J76" s="12">
+      <c r="G76" s="7">
+        <v>0.94950000000000001</v>
+      </c>
+      <c r="H76" s="8">
+        <v>32836774.760000002</v>
+      </c>
+      <c r="I76" s="9">
+        <v>31178236.210000001</v>
+      </c>
+      <c r="J76" s="8">
         <v>1658538.5500000007</v>
       </c>
-      <c r="K76" s="14">
+      <c r="K76" s="10">
         <v>44564</v>
       </c>
-      <c r="L76" s="14">
+      <c r="L76" s="10">
         <v>44944</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A77" s="11" t="s">
+      <c r="A77" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="B77" s="11" t="s">
+      <c r="B77" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="C77" s="11" t="s">
+      <c r="C77" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="D77" s="11" t="s">
+      <c r="D77" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E77" s="11" t="s">
+      <c r="E77" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="F77" s="11" t="s">
+      <c r="F77" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="G77" s="11">
-        <v>0.9543</v>
-      </c>
-      <c r="H77" s="12">
+      <c r="G77" s="7">
+        <v>0.95430000000000004</v>
+      </c>
+      <c r="H77" s="8">
         <v>36880209</v>
       </c>
-      <c r="I77" s="13">
+      <c r="I77" s="9">
         <v>35196032.93</v>
       </c>
-      <c r="J77" s="12">
+      <c r="J77" s="8">
         <v>1684176.0700000003</v>
       </c>
-      <c r="K77" s="14">
+      <c r="K77" s="10">
         <v>44648</v>
       </c>
-      <c r="L77" s="14">
+      <c r="L77" s="10">
         <v>45498</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A78" s="11" t="s">
+      <c r="A78" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="B78" s="11" t="s">
+      <c r="B78" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="C78" s="11" t="s">
+      <c r="C78" s="7" t="s">
         <v>316</v>
       </c>
-      <c r="D78" s="11" t="s">
+      <c r="D78" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E78" s="11" t="s">
+      <c r="E78" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="F78" s="11" t="s">
+      <c r="F78" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="G78" s="11">
-        <v>0.0134</v>
-      </c>
-      <c r="H78" s="12">
+      <c r="G78" s="7">
+        <v>1.34E-2</v>
+      </c>
+      <c r="H78" s="8">
         <v>4705907.3</v>
       </c>
-      <c r="I78" s="13">
+      <c r="I78" s="9">
         <v>63006.28</v>
       </c>
-      <c r="J78" s="12">
-        <v>4642901.02</v>
-      </c>
-      <c r="K78" s="14">
+      <c r="J78" s="8">
+        <v>4642901.0199999996</v>
+      </c>
+      <c r="K78" s="10">
         <v>46009</v>
       </c>
-      <c r="L78" s="14">
+      <c r="L78" s="10">
         <v>46189</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A79" s="11" t="s">
+      <c r="A79" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="B79" s="11" t="s">
+      <c r="B79" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="C79" s="11" t="s">
+      <c r="C79" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="D79" s="11" t="s">
+      <c r="D79" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E79" s="11" t="s">
+      <c r="E79" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="F79" s="11" t="s">
+      <c r="F79" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="G79" s="11">
+      <c r="G79" s="7">
         <v>0.5292</v>
       </c>
-      <c r="H79" s="12">
+      <c r="H79" s="8">
         <v>10349390.52</v>
       </c>
-      <c r="I79" s="13">
+      <c r="I79" s="9">
         <v>5476795.79</v>
       </c>
-      <c r="J79" s="12">
+      <c r="J79" s="8">
         <v>4872594.7299999995</v>
       </c>
-      <c r="K79" s="14">
+      <c r="K79" s="10">
         <v>45867</v>
       </c>
-      <c r="L79" s="14">
+      <c r="L79" s="10">
         <v>46227</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A80" s="11" t="s">
+      <c r="A80" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="B80" s="11" t="s">
+      <c r="B80" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="C80" s="11" t="s">
+      <c r="C80" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="D80" s="11" t="s">
+      <c r="D80" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E80" s="11" t="s">
+      <c r="E80" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="F80" s="11" t="s">
+      <c r="F80" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="G80" s="11">
+      <c r="G80" s="7">
         <v>1</v>
       </c>
-      <c r="H80" s="12">
+      <c r="H80" s="8">
         <v>1923627.23</v>
       </c>
-      <c r="I80" s="13">
+      <c r="I80" s="9">
         <v>1923627.26</v>
       </c>
-      <c r="J80" s="12">
-        <v>-0.030000000027939677</v>
-      </c>
-      <c r="K80" s="14">
+      <c r="J80" s="8">
+        <v>-3.0000000027939677E-2</v>
+      </c>
+      <c r="K80" s="10">
         <v>44708</v>
       </c>
-      <c r="L80" s="14">
+      <c r="L80" s="10">
         <v>45640</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A81" s="11" t="s">
+      <c r="A81" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="B81" s="11" t="s">
+      <c r="B81" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="C81" s="11" t="s">
+      <c r="C81" s="7" t="s">
         <v>328</v>
       </c>
-      <c r="D81" s="11" t="s">
+      <c r="D81" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E81" s="11" t="s">
+      <c r="E81" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="F81" s="11" t="s">
+      <c r="F81" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="G81" s="11">
+      <c r="G81" s="7">
         <v>1</v>
       </c>
-      <c r="H81" s="12">
+      <c r="H81" s="8">
         <v>3552093.82</v>
       </c>
-      <c r="I81" s="13">
+      <c r="I81" s="9">
         <v>3552073.13</v>
       </c>
-      <c r="J81" s="12">
-        <v>20.68999999994412</v>
-      </c>
-      <c r="K81" s="14">
+      <c r="J81" s="8">
+        <v>20.689999999944121</v>
+      </c>
+      <c r="K81" s="10">
         <v>45034</v>
       </c>
-      <c r="L81" s="14">
+      <c r="L81" s="10">
         <v>45034</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A82" s="11" t="s">
+      <c r="A82" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="B82" s="11" t="s">
+      <c r="B82" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="C82" s="11" t="s">
+      <c r="C82" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="D82" s="11" t="s">
+      <c r="D82" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E82" s="11" t="s">
+      <c r="E82" s="7" t="s">
         <v>332</v>
       </c>
-      <c r="F82" s="11" t="s">
+      <c r="F82" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G82" s="11">
-        <v>0.9723</v>
-      </c>
-      <c r="H82" s="12">
-        <v>15078640.21</v>
-      </c>
-      <c r="I82" s="13">
-        <v>14660282.37</v>
-      </c>
-      <c r="J82" s="12">
-        <v>418357.8400000017</v>
-      </c>
-      <c r="K82" s="14">
+      <c r="G82" s="7">
+        <v>0.97230000000000005</v>
+      </c>
+      <c r="H82" s="8">
+        <v>15078640.210000001</v>
+      </c>
+      <c r="I82" s="9">
+        <v>14660282.369999999</v>
+      </c>
+      <c r="J82" s="8">
+        <v>418357.84000000171</v>
+      </c>
+      <c r="K82" s="10">
         <v>45497</v>
       </c>
-      <c r="L82" s="14">
+      <c r="L82" s="10">
         <v>45301</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A83" s="11" t="s">
+      <c r="A83" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="B83" s="11" t="s">
+      <c r="B83" s="7" t="s">
         <v>333</v>
       </c>
-      <c r="C83" s="11" t="s">
+      <c r="C83" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="D83" s="11" t="s">
+      <c r="D83" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E83" s="11" t="s">
+      <c r="E83" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="F83" s="11" t="s">
+      <c r="F83" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="G83" s="11">
-        <v>0.948</v>
-      </c>
-      <c r="H83" s="12">
-        <v>59148617.81</v>
-      </c>
-      <c r="I83" s="13">
-        <v>56075178.64</v>
-      </c>
-      <c r="J83" s="12">
-        <v>3073439.170000002</v>
-      </c>
-      <c r="K83" s="14">
+      <c r="G83" s="7">
+        <v>0.94799999999999995</v>
+      </c>
+      <c r="H83" s="8">
+        <v>59148617.810000002</v>
+      </c>
+      <c r="I83" s="9">
+        <v>56075178.640000001</v>
+      </c>
+      <c r="J83" s="8">
+        <v>3073439.1700000018</v>
+      </c>
+      <c r="K83" s="10">
         <v>44726</v>
       </c>
-      <c r="L83" s="14">
+      <c r="L83" s="10">
         <v>46006</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A84" s="11" t="s">
+      <c r="A84" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="B84" s="11" t="s">
+      <c r="B84" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="C84" s="11"/>
-      <c r="D84" s="11" t="s">
+      <c r="C84" s="7"/>
+      <c r="D84" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E84" s="11" t="s">
+      <c r="E84" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="F84" s="11" t="s">
+      <c r="F84" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="G84" s="11">
+      <c r="G84" s="7">
         <v>0</v>
       </c>
-      <c r="H84" s="12">
+      <c r="H84" s="8">
         <v>62980000</v>
       </c>
-      <c r="I84" s="13">
+      <c r="I84" s="9">
         <v>62980000</v>
       </c>
-      <c r="J84" s="12">
+      <c r="J84" s="8">
         <v>0</v>
       </c>
-      <c r="K84" s="14">
+      <c r="K84" s="10">
         <v>43930</v>
       </c>
-      <c r="L84" s="14">
+      <c r="L84" s="10">
         <v>44011</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A85" s="11" t="s">
+      <c r="A85" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="B85" s="11" t="s">
+      <c r="B85" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="C85" s="11" t="s">
+      <c r="C85" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="D85" s="11" t="s">
+      <c r="D85" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E85" s="11" t="s">
+      <c r="E85" s="7" t="s">
         <v>343</v>
       </c>
-      <c r="F85" s="11" t="s">
+      <c r="F85" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="G85" s="11">
-        <v>0.9976999999999999</v>
-      </c>
-      <c r="H85" s="12">
-        <v>19451386.88</v>
-      </c>
-      <c r="I85" s="13">
-        <v>19406169.39</v>
-      </c>
-      <c r="J85" s="12">
-        <v>45217.48999999836</v>
-      </c>
-      <c r="K85" s="14">
+      <c r="G85" s="7">
+        <v>0.99769999999999992</v>
+      </c>
+      <c r="H85" s="8">
+        <v>19451386.879999999</v>
+      </c>
+      <c r="I85" s="9">
+        <v>19406169.390000001</v>
+      </c>
+      <c r="J85" s="8">
+        <v>45217.489999998361</v>
+      </c>
+      <c r="K85" s="10">
         <v>45247</v>
       </c>
-      <c r="L85" s="14">
+      <c r="L85" s="10">
         <v>46001</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A86" s="11" t="s">
+      <c r="A86" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="B86" s="11" t="s">
+      <c r="B86" s="7" t="s">
         <v>344</v>
       </c>
-      <c r="C86" s="11" t="s">
+      <c r="C86" s="7" t="s">
         <v>345</v>
       </c>
-      <c r="D86" s="11" t="s">
+      <c r="D86" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E86" s="11" t="s">
+      <c r="E86" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="F86" s="11" t="s">
+      <c r="F86" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="G86" s="11">
-        <v>0.9666</v>
-      </c>
-      <c r="H86" s="12">
-        <v>20106028.53</v>
-      </c>
-      <c r="I86" s="13">
-        <v>19434508.22</v>
-      </c>
-      <c r="J86" s="12">
-        <v>671520.3100000024</v>
-      </c>
-      <c r="K86" s="14">
+      <c r="G86" s="7">
+        <v>0.96660000000000001</v>
+      </c>
+      <c r="H86" s="8">
+        <v>20106028.530000001</v>
+      </c>
+      <c r="I86" s="9">
+        <v>19434508.219999999</v>
+      </c>
+      <c r="J86" s="8">
+        <v>671520.31000000238</v>
+      </c>
+      <c r="K86" s="10">
         <v>44991</v>
       </c>
-      <c r="L86" s="14">
+      <c r="L86" s="10">
         <v>46094</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A87" s="11" t="s">
+      <c r="A87" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="B87" s="11" t="s">
+      <c r="B87" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="C87" s="11" t="s">
+      <c r="C87" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="D87" s="11" t="s">
+      <c r="D87" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E87" s="11" t="s">
+      <c r="E87" s="7" t="s">
         <v>348</v>
       </c>
-      <c r="F87" s="11" t="s">
+      <c r="F87" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="G87" s="11">
+      <c r="G87" s="7">
         <v>0.9577</v>
       </c>
-      <c r="H87" s="12">
-        <v>34508101.15</v>
-      </c>
-      <c r="I87" s="13">
-        <v>33048630.33</v>
-      </c>
-      <c r="J87" s="12">
+      <c r="H87" s="8">
+        <v>34508101.149999999</v>
+      </c>
+      <c r="I87" s="9">
+        <v>33048630.329999998</v>
+      </c>
+      <c r="J87" s="8">
         <v>1459470.8200000003</v>
       </c>
-      <c r="K87" s="14">
+      <c r="K87" s="10">
         <v>44690</v>
       </c>
-      <c r="L87" s="14">
+      <c r="L87" s="10">
         <v>45621</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A88" s="11" t="s">
+      <c r="A88" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="B88" s="11" t="s">
+      <c r="B88" s="7" t="s">
         <v>349</v>
       </c>
-      <c r="C88" s="11" t="s">
+      <c r="C88" s="7" t="s">
         <v>350</v>
       </c>
-      <c r="D88" s="11" t="s">
+      <c r="D88" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E88" s="11" t="s">
+      <c r="E88" s="7" t="s">
         <v>351</v>
       </c>
-      <c r="F88" s="11" t="s">
+      <c r="F88" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="G88" s="11">
-        <v>0.9711</v>
-      </c>
-      <c r="H88" s="12">
-        <v>58086688.76</v>
-      </c>
-      <c r="I88" s="13">
-        <v>56408550.91</v>
-      </c>
-      <c r="J88" s="12">
+      <c r="G88" s="7">
+        <v>0.97109999999999996</v>
+      </c>
+      <c r="H88" s="8">
+        <v>58086688.759999998</v>
+      </c>
+      <c r="I88" s="9">
+        <v>56408550.909999996</v>
+      </c>
+      <c r="J88" s="8">
         <v>1678137.8500000015</v>
       </c>
-      <c r="K88" s="14">
+      <c r="K88" s="10">
         <v>44831</v>
       </c>
-      <c r="L88" s="14">
+      <c r="L88" s="10">
         <v>45619</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A89" s="11" t="s">
+      <c r="A89" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="B89" s="11" t="s">
+      <c r="B89" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="C89" s="11" t="s">
+      <c r="C89" s="7" t="s">
         <v>354</v>
       </c>
-      <c r="D89" s="11" t="s">
+      <c r="D89" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E89" s="11" t="s">
+      <c r="E89" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="F89" s="11" t="s">
+      <c r="F89" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="G89" s="11">
-        <v>0.6973</v>
-      </c>
-      <c r="H89" s="12">
+      <c r="G89" s="7">
+        <v>0.69730000000000003</v>
+      </c>
+      <c r="H89" s="8">
         <v>28459856.91</v>
       </c>
-      <c r="I89" s="13">
-        <v>19844966.58</v>
-      </c>
-      <c r="J89" s="12">
-        <v>8614890.330000002</v>
-      </c>
-      <c r="K89" s="14">
+      <c r="I89" s="9">
+        <v>19844966.579999998</v>
+      </c>
+      <c r="J89" s="8">
+        <v>8614890.3300000019</v>
+      </c>
+      <c r="K89" s="10">
         <v>45035</v>
       </c>
-      <c r="L89" s="14">
+      <c r="L89" s="10">
         <v>46205</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A90" s="11" t="s">
+      <c r="A90" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="B90" s="11" t="s">
+      <c r="B90" s="7" t="s">
         <v>356</v>
       </c>
-      <c r="C90" s="11" t="s">
+      <c r="C90" s="7" t="s">
         <v>357</v>
       </c>
-      <c r="D90" s="11" t="s">
+      <c r="D90" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E90" s="11" t="s">
+      <c r="E90" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="F90" s="11" t="s">
+      <c r="F90" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="G90" s="11">
-        <v>0.7805</v>
-      </c>
-      <c r="H90" s="12">
-        <v>45862409.69</v>
-      </c>
-      <c r="I90" s="13">
-        <v>35796161.98</v>
-      </c>
-      <c r="J90" s="12">
-        <v>10066247.71</v>
-      </c>
-      <c r="K90" s="14">
+      <c r="G90" s="7">
+        <v>0.78049999999999997</v>
+      </c>
+      <c r="H90" s="8">
+        <v>45862409.689999998</v>
+      </c>
+      <c r="I90" s="9">
+        <v>35796161.979999997</v>
+      </c>
+      <c r="J90" s="8">
+        <v>10066247.710000001</v>
+      </c>
+      <c r="K90" s="10">
         <v>45352</v>
       </c>
-      <c r="L90" s="14">
+      <c r="L90" s="10">
         <v>46255</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A91" s="11" t="s">
+      <c r="A91" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="B91" s="11" t="s">
+      <c r="B91" s="7" t="s">
         <v>359</v>
       </c>
-      <c r="C91" s="11" t="s">
+      <c r="C91" s="7" t="s">
         <v>360</v>
       </c>
-      <c r="D91" s="11" t="s">
+      <c r="D91" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E91" s="11" t="s">
+      <c r="E91" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="F91" s="11" t="s">
+      <c r="F91" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="G91" s="11">
-        <v>0.0132</v>
-      </c>
-      <c r="H91" s="12">
+      <c r="G91" s="7">
+        <v>1.32E-2</v>
+      </c>
+      <c r="H91" s="8">
         <v>11494433.26</v>
       </c>
-      <c r="I91" s="13">
+      <c r="I91" s="9">
         <v>151285.62</v>
       </c>
-      <c r="J91" s="12">
-        <v>11343147.64</v>
-      </c>
-      <c r="K91" s="14">
+      <c r="J91" s="8">
+        <v>11343147.640000001</v>
+      </c>
+      <c r="K91" s="10">
         <v>45105</v>
       </c>
-      <c r="L91" s="14">
+      <c r="L91" s="10">
         <v>45706</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A92" s="11" t="s">
+      <c r="A92" s="7" t="s">
         <v>362</v>
       </c>
-      <c r="B92" s="11" t="s">
+      <c r="B92" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="C92" s="11" t="s">
+      <c r="C92" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="D92" s="11" t="s">
+      <c r="D92" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E92" s="11" t="s">
+      <c r="E92" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="F92" s="11" t="s">
+      <c r="F92" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="G92" s="11">
-        <v>0.898</v>
-      </c>
-      <c r="H92" s="12">
+      <c r="G92" s="7">
+        <v>0.89800000000000002</v>
+      </c>
+      <c r="H92" s="8">
         <v>1212482.21</v>
       </c>
-      <c r="I92" s="13">
+      <c r="I92" s="9">
         <v>1088826.01</v>
       </c>
-      <c r="J92" s="12">
+      <c r="J92" s="8">
         <v>123656.19999999995</v>
       </c>
-      <c r="K92" s="14">
+      <c r="K92" s="10">
         <v>44326</v>
       </c>
-      <c r="L92" s="14">
+      <c r="L92" s="10">
         <v>44536</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A93" s="11" t="s">
+      <c r="A93" s="7" t="s">
         <v>362</v>
       </c>
-      <c r="B93" s="11" t="s">
+      <c r="B93" s="7" t="s">
         <v>366</v>
       </c>
-      <c r="C93" s="11" t="s">
+      <c r="C93" s="7" t="s">
         <v>367</v>
       </c>
-      <c r="D93" s="11" t="s">
+      <c r="D93" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E93" s="11" t="s">
+      <c r="E93" s="7" t="s">
         <v>368</v>
       </c>
-      <c r="F93" s="11" t="s">
+      <c r="F93" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="G93" s="11">
-        <v>0.9209</v>
-      </c>
-      <c r="H93" s="12">
-        <v>12560309.12</v>
-      </c>
-      <c r="I93" s="13">
-        <v>11566432.39</v>
-      </c>
-      <c r="J93" s="12">
-        <v>993876.7299999986</v>
-      </c>
-      <c r="K93" s="14">
+      <c r="G93" s="7">
+        <v>0.92090000000000005</v>
+      </c>
+      <c r="H93" s="8">
+        <v>12560309.119999999</v>
+      </c>
+      <c r="I93" s="9">
+        <v>11566432.390000001</v>
+      </c>
+      <c r="J93" s="8">
+        <v>993876.72999999858</v>
+      </c>
+      <c r="K93" s="10">
         <v>44831</v>
       </c>
-      <c r="L93" s="14">
+      <c r="L93" s="10">
         <v>45477</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A94" s="11" t="s">
+      <c r="A94" s="7" t="s">
         <v>369</v>
       </c>
-      <c r="B94" s="11" t="s">
+      <c r="B94" s="7" t="s">
         <v>370</v>
       </c>
-      <c r="C94" s="11" t="s">
+      <c r="C94" s="7" t="s">
         <v>371</v>
       </c>
-      <c r="D94" s="11" t="s">
+      <c r="D94" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E94" s="11" t="s">
+      <c r="E94" s="7" t="s">
         <v>372</v>
       </c>
-      <c r="F94" s="11" t="s">
+      <c r="F94" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="G94" s="11">
-        <v>0.9990000000000001</v>
-      </c>
-      <c r="H94" s="12">
+      <c r="G94" s="7">
+        <v>0.99900000000000011</v>
+      </c>
+      <c r="H94" s="8">
         <v>17695067.23</v>
       </c>
-      <c r="I94" s="13">
+      <c r="I94" s="9">
         <v>17677149.84</v>
       </c>
-      <c r="J94" s="12">
+      <c r="J94" s="8">
         <v>17917.390000000596</v>
       </c>
-      <c r="K94" s="14">
+      <c r="K94" s="10">
         <v>44994</v>
       </c>
-      <c r="L94" s="14">
+      <c r="L94" s="10">
         <v>45928</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A95" s="11" t="s">
+      <c r="A95" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="B95" s="11" t="s">
+      <c r="B95" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="C95" s="11" t="s">
+      <c r="C95" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="D95" s="11" t="s">
+      <c r="D95" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E95" s="11" t="s">
+      <c r="E95" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="F95" s="11" t="s">
+      <c r="F95" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G95" s="11">
+      <c r="G95" s="7">
         <v>1</v>
       </c>
-      <c r="H95" s="12">
-        <v>12092480.69</v>
-      </c>
-      <c r="I95" s="13">
-        <v>12092480.69</v>
-      </c>
-      <c r="J95" s="12">
+      <c r="H95" s="8">
+        <v>12092480.689999999</v>
+      </c>
+      <c r="I95" s="9">
+        <v>12092480.689999999</v>
+      </c>
+      <c r="J95" s="8">
         <v>0</v>
       </c>
-      <c r="K95" s="14">
+      <c r="K95" s="10">
         <v>44734</v>
       </c>
-      <c r="L95" s="14">
+      <c r="L95" s="10">
         <v>45202</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A96" s="11" t="s">
+      <c r="A96" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="B96" s="11" t="s">
+      <c r="B96" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="C96" s="11" t="s">
+      <c r="C96" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="D96" s="11" t="s">
+      <c r="D96" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E96" s="11" t="s">
+      <c r="E96" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="F96" s="11" t="s">
+      <c r="F96" s="7" t="s">
         <v>379</v>
       </c>
-      <c r="G96" s="11">
-        <v>0.9117000000000001</v>
-      </c>
-      <c r="H96" s="12">
-        <v>5978542.15</v>
-      </c>
-      <c r="I96" s="13">
+      <c r="G96" s="7">
+        <v>0.91170000000000007</v>
+      </c>
+      <c r="H96" s="8">
+        <v>5978542.1500000004</v>
+      </c>
+      <c r="I96" s="9">
         <v>5450477.04</v>
       </c>
-      <c r="J96" s="12">
-        <v>528065.1100000003</v>
-      </c>
-      <c r="K96" s="14">
+      <c r="J96" s="8">
+        <v>528065.11000000034</v>
+      </c>
+      <c r="K96" s="10">
         <v>44753</v>
       </c>
-      <c r="L96" s="14">
+      <c r="L96" s="10">
         <v>44933</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A97" s="11" t="s">
+      <c r="A97" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="B97" s="11" t="s">
+      <c r="B97" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="C97" s="11" t="s">
+      <c r="C97" s="7" t="s">
         <v>381</v>
       </c>
-      <c r="D97" s="11" t="s">
+      <c r="D97" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E97" s="11" t="s">
+      <c r="E97" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="F97" s="11" t="s">
+      <c r="F97" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="G97" s="11">
-        <v>0.8019</v>
-      </c>
-      <c r="H97" s="12">
-        <v>7066834.9</v>
-      </c>
-      <c r="I97" s="13">
-        <v>5666949.72</v>
-      </c>
-      <c r="J97" s="12">
+      <c r="G97" s="7">
+        <v>0.80189999999999995</v>
+      </c>
+      <c r="H97" s="8">
+        <v>7066834.9000000004</v>
+      </c>
+      <c r="I97" s="9">
+        <v>5666949.7199999997</v>
+      </c>
+      <c r="J97" s="8">
         <v>1399885.1800000006</v>
       </c>
-      <c r="K97" s="14">
+      <c r="K97" s="10">
         <v>45848</v>
       </c>
-      <c r="L97" s="14">
+      <c r="L97" s="10">
         <v>46222</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A98" s="11" t="s">
+      <c r="A98" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="B98" s="11" t="s">
+      <c r="B98" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="C98" s="11" t="s">
+      <c r="C98" s="7" t="s">
         <v>384</v>
       </c>
-      <c r="D98" s="11" t="s">
+      <c r="D98" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E98" s="11" t="s">
+      <c r="E98" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="F98" s="11" t="s">
+      <c r="F98" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="G98" s="11">
-        <v>0.8362</v>
-      </c>
-      <c r="H98" s="12">
+      <c r="G98" s="7">
+        <v>0.83620000000000005</v>
+      </c>
+      <c r="H98" s="8">
         <v>11942741.09</v>
       </c>
-      <c r="I98" s="13">
-        <v>9986334.63</v>
-      </c>
-      <c r="J98" s="12">
+      <c r="I98" s="9">
+        <v>9986334.6300000008</v>
+      </c>
+      <c r="J98" s="8">
         <v>1956406.459999999</v>
       </c>
-      <c r="K98" s="14">
+      <c r="K98" s="10">
         <v>44734</v>
       </c>
-      <c r="L98" s="14">
+      <c r="L98" s="10">
         <v>45098</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A99" s="11" t="s">
+      <c r="A99" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="B99" s="11" t="s">
+      <c r="B99" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="C99" s="11" t="s">
+      <c r="C99" s="7" t="s">
         <v>388</v>
       </c>
-      <c r="D99" s="11" t="s">
+      <c r="D99" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E99" s="11" t="s">
+      <c r="E99" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="F99" s="11" t="s">
+      <c r="F99" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="G99" s="11">
-        <v>0.9493</v>
-      </c>
-      <c r="H99" s="12">
+      <c r="G99" s="7">
+        <v>0.94930000000000003</v>
+      </c>
+      <c r="H99" s="8">
         <v>48302952.43</v>
       </c>
-      <c r="I99" s="13">
-        <v>45853223.3</v>
-      </c>
-      <c r="J99" s="12">
+      <c r="I99" s="9">
+        <v>45853223.299999997</v>
+      </c>
+      <c r="J99" s="8">
         <v>2449729.1300000027</v>
       </c>
-      <c r="K99" s="14">
+      <c r="K99" s="10">
         <v>45189</v>
       </c>
-      <c r="L99" s="14">
+      <c r="L99" s="10">
         <v>45729</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A100" s="11" t="s">
+      <c r="A100" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="B100" s="11" t="s">
+      <c r="B100" s="7" t="s">
         <v>390</v>
       </c>
-      <c r="C100" s="11" t="s">
+      <c r="C100" s="7" t="s">
         <v>391</v>
       </c>
-      <c r="D100" s="11" t="s">
+      <c r="D100" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E100" s="11" t="s">
+      <c r="E100" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="F100" s="11" t="s">
+      <c r="F100" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="G100" s="11">
-        <v>0.9181999999999999</v>
-      </c>
-      <c r="H100" s="12">
-        <v>30543662.31</v>
-      </c>
-      <c r="I100" s="13">
-        <v>28044628.6</v>
-      </c>
-      <c r="J100" s="12">
-        <v>2499033.709999997</v>
-      </c>
-      <c r="K100" s="14">
+      <c r="G100" s="7">
+        <v>0.91819999999999991</v>
+      </c>
+      <c r="H100" s="8">
+        <v>30543662.309999999</v>
+      </c>
+      <c r="I100" s="9">
+        <v>28044628.600000001</v>
+      </c>
+      <c r="J100" s="8">
+        <v>2499033.7099999972</v>
+      </c>
+      <c r="K100" s="10">
         <v>44826</v>
       </c>
-      <c r="L100" s="14">
+      <c r="L100" s="10">
         <v>45540</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A101" s="11" t="s">
+      <c r="A101" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="B101" s="11" t="s">
+      <c r="B101" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="C101" s="11" t="s">
+      <c r="C101" s="7" t="s">
         <v>395</v>
       </c>
-      <c r="D101" s="11" t="s">
+      <c r="D101" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E101" s="11" t="s">
+      <c r="E101" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="F101" s="11" t="s">
+      <c r="F101" s="7" t="s">
         <v>397</v>
       </c>
-      <c r="G101" s="11">
-        <v>0.9188</v>
-      </c>
-      <c r="H101" s="12">
-        <v>54913544.95</v>
-      </c>
-      <c r="I101" s="13">
-        <v>50454918.61</v>
-      </c>
-      <c r="J101" s="12">
-        <v>4458626.340000004</v>
-      </c>
-      <c r="K101" s="14">
+      <c r="G101" s="7">
+        <v>0.91879999999999995</v>
+      </c>
+      <c r="H101" s="8">
+        <v>54913544.950000003</v>
+      </c>
+      <c r="I101" s="9">
+        <v>50454918.609999999</v>
+      </c>
+      <c r="J101" s="8">
+        <v>4458626.3400000036</v>
+      </c>
+      <c r="K101" s="10">
         <v>44769</v>
       </c>
-      <c r="L101" s="14">
+      <c r="L101" s="10">
         <v>45174</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A102" s="11" t="s">
+      <c r="A102" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="B102" s="11" t="s">
+      <c r="B102" s="7" t="s">
         <v>398</v>
       </c>
-      <c r="C102" s="11" t="s">
+      <c r="C102" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="D102" s="11" t="s">
+      <c r="D102" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E102" s="11" t="s">
+      <c r="E102" s="7" t="s">
         <v>400</v>
       </c>
-      <c r="F102" s="11" t="s">
+      <c r="F102" s="7" t="s">
         <v>401</v>
       </c>
-      <c r="G102" s="11">
-        <v>0.7739</v>
-      </c>
-      <c r="H102" s="12">
+      <c r="G102" s="7">
+        <v>0.77390000000000003</v>
+      </c>
+      <c r="H102" s="8">
         <v>27434724</v>
       </c>
-      <c r="I102" s="13">
-        <v>21232327.94</v>
-      </c>
-      <c r="J102" s="12">
-        <v>6202396.059999999</v>
-      </c>
-      <c r="K102" s="14">
+      <c r="I102" s="9">
+        <v>21232327.940000001</v>
+      </c>
+      <c r="J102" s="8">
+        <v>6202396.0599999987</v>
+      </c>
+      <c r="K102" s="10">
         <v>46002</v>
       </c>
-      <c r="L102" s="14">
+      <c r="L102" s="10">
         <v>46242</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A103" s="11" t="s">
+      <c r="A103" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="B103" s="11" t="s">
+      <c r="B103" s="7" t="s">
         <v>402</v>
       </c>
-      <c r="C103" s="11" t="s">
+      <c r="C103" s="7" t="s">
         <v>403</v>
       </c>
-      <c r="D103" s="11" t="s">
+      <c r="D103" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E103" s="11" t="s">
+      <c r="E103" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="F103" s="11" t="s">
+      <c r="F103" s="7" t="s">
         <v>405</v>
       </c>
-      <c r="G103" s="11">
+      <c r="G103" s="7">
         <v>0.9224</v>
       </c>
-      <c r="H103" s="12">
-        <v>80552394.92</v>
-      </c>
-      <c r="I103" s="13">
-        <v>74305045.47</v>
-      </c>
-      <c r="J103" s="12">
+      <c r="H103" s="8">
+        <v>80552394.920000002</v>
+      </c>
+      <c r="I103" s="9">
+        <v>74305045.469999999</v>
+      </c>
+      <c r="J103" s="8">
         <v>6247349.450000003</v>
       </c>
-      <c r="K103" s="14">
+      <c r="K103" s="10">
         <v>44709</v>
       </c>
-      <c r="L103" s="14">
+      <c r="L103" s="10">
         <v>45114</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A104" s="11" t="s">
+      <c r="A104" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="B104" s="11" t="s">
+      <c r="B104" s="7" t="s">
         <v>406</v>
       </c>
-      <c r="C104" s="11" t="s">
+      <c r="C104" s="7" t="s">
         <v>407</v>
       </c>
-      <c r="D104" s="11" t="s">
+      <c r="D104" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E104" s="11" t="s">
+      <c r="E104" s="7" t="s">
         <v>408</v>
       </c>
-      <c r="F104" s="11" t="s">
+      <c r="F104" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="G104" s="11">
+      <c r="G104" s="7">
         <v>0.4476</v>
       </c>
-      <c r="H104" s="12">
-        <v>68148567.14</v>
-      </c>
-      <c r="I104" s="13">
+      <c r="H104" s="8">
+        <v>68148567.140000001</v>
+      </c>
+      <c r="I104" s="9">
         <v>30502735.41</v>
       </c>
-      <c r="J104" s="12">
+      <c r="J104" s="8">
         <v>37645831.730000004</v>
       </c>
-      <c r="K104" s="14">
+      <c r="K104" s="10">
         <v>44767</v>
       </c>
-      <c r="L104" s="14">
+      <c r="L104" s="10">
         <v>45173</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A105" s="11" t="s">
+      <c r="A105" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="B105" s="11" t="s">
+      <c r="B105" s="7" t="s">
         <v>411</v>
       </c>
-      <c r="C105" s="11" t="s">
+      <c r="C105" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="D105" s="11" t="s">
+      <c r="D105" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E105" s="11" t="s">
+      <c r="E105" s="7" t="s">
         <v>413</v>
       </c>
-      <c r="F105" s="11" t="s">
+      <c r="F105" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="G105" s="11">
-        <v>0.9984000000000001</v>
-      </c>
-      <c r="H105" s="12">
+      <c r="G105" s="7">
+        <v>0.99840000000000007</v>
+      </c>
+      <c r="H105" s="8">
         <v>1498793.43</v>
       </c>
-      <c r="I105" s="13">
+      <c r="I105" s="9">
         <v>1496414.32</v>
       </c>
-      <c r="J105" s="12">
+      <c r="J105" s="8">
         <v>2379.1099999998696</v>
       </c>
-      <c r="K105" s="14">
+      <c r="K105" s="10">
         <v>45195</v>
       </c>
-      <c r="L105" s="14">
+      <c r="L105" s="10">
         <v>45121</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A106" s="11" t="s">
+      <c r="A106" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="B106" s="11" t="s">
+      <c r="B106" s="7" t="s">
         <v>415</v>
       </c>
-      <c r="C106" s="11" t="s">
+      <c r="C106" s="7" t="s">
         <v>416</v>
       </c>
-      <c r="D106" s="11" t="s">
+      <c r="D106" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E106" s="11" t="s">
+      <c r="E106" s="7" t="s">
         <v>417</v>
       </c>
-      <c r="F106" s="11" t="s">
+      <c r="F106" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="G106" s="11">
-        <v>0.9718000000000001</v>
-      </c>
-      <c r="H106" s="12">
+      <c r="G106" s="7">
+        <v>0.97180000000000011</v>
+      </c>
+      <c r="H106" s="8">
         <v>1988555.07</v>
       </c>
-      <c r="I106" s="13">
+      <c r="I106" s="9">
         <v>1932548.63</v>
       </c>
-      <c r="J106" s="12">
-        <v>56006.44000000018</v>
-      </c>
-      <c r="K106" s="14">
+      <c r="J106" s="8">
+        <v>56006.440000000177</v>
+      </c>
+      <c r="K106" s="10">
         <v>44742</v>
       </c>
-      <c r="L106" s="14">
+      <c r="L106" s="10">
         <v>45412</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A107" s="11" t="s">
+      <c r="A107" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="B107" s="11" t="s">
+      <c r="B107" s="7" t="s">
         <v>418</v>
       </c>
-      <c r="C107" s="11" t="s">
+      <c r="C107" s="7" t="s">
         <v>419</v>
       </c>
-      <c r="D107" s="11" t="s">
+      <c r="D107" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E107" s="11" t="s">
+      <c r="E107" s="7" t="s">
         <v>420</v>
       </c>
-      <c r="F107" s="11" t="s">
+      <c r="F107" s="7" t="s">
         <v>397</v>
       </c>
-      <c r="G107" s="11">
-        <v>0.608</v>
-      </c>
-      <c r="H107" s="12">
+      <c r="G107" s="7">
+        <v>0.60799999999999998</v>
+      </c>
+      <c r="H107" s="8">
         <v>2860442.12</v>
       </c>
-      <c r="I107" s="13">
+      <c r="I107" s="9">
         <v>1739254.2</v>
       </c>
-      <c r="J107" s="12">
+      <c r="J107" s="8">
         <v>1121187.9200000002</v>
       </c>
-      <c r="K107" s="14">
+      <c r="K107" s="10">
         <v>45782</v>
       </c>
-      <c r="L107" s="14">
+      <c r="L107" s="10">
         <v>46083</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A108" s="11" t="s">
+      <c r="A108" s="7" t="s">
         <v>421</v>
       </c>
-      <c r="B108" s="11" t="s">
+      <c r="B108" s="7" t="s">
         <v>422</v>
       </c>
-      <c r="C108" s="11" t="s">
+      <c r="C108" s="7" t="s">
         <v>403</v>
       </c>
-      <c r="D108" s="11" t="s">
+      <c r="D108" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E108" s="11" t="s">
+      <c r="E108" s="7" t="s">
         <v>423</v>
       </c>
-      <c r="F108" s="11" t="s">
+      <c r="F108" s="7" t="s">
         <v>424</v>
       </c>
-      <c r="G108" s="11">
+      <c r="G108" s="7">
         <v>0.9998999999999999</v>
       </c>
-      <c r="H108" s="12">
+      <c r="H108" s="8">
         <v>5272095.08</v>
       </c>
-      <c r="I108" s="13">
+      <c r="I108" s="9">
         <v>5271693.21</v>
       </c>
-      <c r="J108" s="12">
+      <c r="J108" s="8">
         <v>401.87000000011176</v>
       </c>
-      <c r="K108" s="14">
+      <c r="K108" s="10">
         <v>44746</v>
       </c>
-      <c r="L108" s="14">
+      <c r="L108" s="10">
         <v>45560</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A109" s="11" t="s">
+      <c r="A109" s="7" t="s">
         <v>421</v>
       </c>
-      <c r="B109" s="11" t="s">
+      <c r="B109" s="7" t="s">
         <v>425</v>
       </c>
-      <c r="C109" s="11" t="s">
+      <c r="C109" s="7" t="s">
         <v>426</v>
       </c>
-      <c r="D109" s="11" t="s">
+      <c r="D109" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E109" s="11" t="s">
+      <c r="E109" s="7" t="s">
         <v>427</v>
       </c>
-      <c r="F109" s="11" t="s">
+      <c r="F109" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="G109" s="11">
-        <v>0.9931</v>
-      </c>
-      <c r="H109" s="12">
+      <c r="G109" s="7">
+        <v>0.99309999999999998</v>
+      </c>
+      <c r="H109" s="8">
         <v>1690234.37</v>
       </c>
-      <c r="I109" s="13">
+      <c r="I109" s="9">
         <v>1678610.19</v>
       </c>
-      <c r="J109" s="12">
+      <c r="J109" s="8">
         <v>11624.180000000168</v>
       </c>
-      <c r="K109" s="14">
+      <c r="K109" s="10">
         <v>44772</v>
       </c>
-      <c r="L109" s="14">
+      <c r="L109" s="10">
         <v>45316</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A110" s="11" t="s">
+      <c r="A110" s="7" t="s">
         <v>421</v>
       </c>
-      <c r="B110" s="11" t="s">
+      <c r="B110" s="7" t="s">
         <v>428</v>
       </c>
-      <c r="C110" s="11" t="s">
+      <c r="C110" s="7" t="s">
         <v>429</v>
       </c>
-      <c r="D110" s="11" t="s">
+      <c r="D110" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E110" s="11" t="s">
+      <c r="E110" s="7" t="s">
         <v>430</v>
       </c>
-      <c r="F110" s="11" t="s">
+      <c r="F110" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="G110" s="11">
-        <v>0.9994</v>
-      </c>
-      <c r="H110" s="12">
-        <v>26946699.36</v>
-      </c>
-      <c r="I110" s="13">
+      <c r="G110" s="7">
+        <v>0.99939999999999996</v>
+      </c>
+      <c r="H110" s="8">
+        <v>26946699.359999999</v>
+      </c>
+      <c r="I110" s="9">
         <v>26930984.02</v>
       </c>
-      <c r="J110" s="12">
+      <c r="J110" s="8">
         <v>15715.339999999851</v>
       </c>
-      <c r="K110" s="14">
+      <c r="K110" s="10">
         <v>44823</v>
       </c>
-      <c r="L110" s="14">
+      <c r="L110" s="10">
         <v>45816</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A111" s="11" t="s">
+      <c r="A111" s="7" t="s">
         <v>432</v>
       </c>
-      <c r="B111" s="11" t="s">
+      <c r="B111" s="7" t="s">
         <v>433</v>
       </c>
-      <c r="C111" s="11" t="s">
+      <c r="C111" s="7" t="s">
         <v>434</v>
       </c>
-      <c r="D111" s="11" t="s">
+      <c r="D111" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E111" s="11" t="s">
+      <c r="E111" s="7" t="s">
         <v>435</v>
       </c>
-      <c r="F111" s="11" t="s">
+      <c r="F111" s="7" t="s">
         <v>424</v>
       </c>
-      <c r="G111" s="11">
+      <c r="G111" s="7">
         <v>1</v>
       </c>
-      <c r="H111" s="12">
+      <c r="H111" s="8">
         <v>3607367.42</v>
       </c>
-      <c r="I111" s="13">
+      <c r="I111" s="9">
         <v>3607318.65</v>
       </c>
-      <c r="J111" s="12">
-        <v>48.77000000001863</v>
-      </c>
-      <c r="K111" s="14">
+      <c r="J111" s="8">
+        <v>48.770000000018626</v>
+      </c>
+      <c r="K111" s="10">
         <v>45061</v>
       </c>
-      <c r="L111" s="14">
+      <c r="L111" s="10">
         <v>45016</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A112" s="11" t="s">
+      <c r="A112" s="7" t="s">
         <v>432</v>
       </c>
-      <c r="B112" s="11" t="s">
+      <c r="B112" s="7" t="s">
         <v>436</v>
       </c>
-      <c r="C112" s="11" t="s">
+      <c r="C112" s="7" t="s">
         <v>437</v>
       </c>
-      <c r="D112" s="11" t="s">
+      <c r="D112" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E112" s="11" t="s">
+      <c r="E112" s="7" t="s">
         <v>438</v>
       </c>
-      <c r="F112" s="11" t="s">
+      <c r="F112" s="7" t="s">
         <v>424</v>
       </c>
-      <c r="G112" s="11">
-        <v>0.9958</v>
-      </c>
-      <c r="H112" s="12">
+      <c r="G112" s="7">
+        <v>0.99580000000000002</v>
+      </c>
+      <c r="H112" s="8">
         <v>4645152.25</v>
       </c>
-      <c r="I112" s="13">
+      <c r="I112" s="9">
         <v>4625557.49</v>
       </c>
-      <c r="J112" s="12">
+      <c r="J112" s="8">
         <v>19594.759999999776</v>
       </c>
-      <c r="K112" s="14">
+      <c r="K112" s="10">
         <v>44918</v>
       </c>
-      <c r="L112" s="14">
+      <c r="L112" s="10">
         <v>45485</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A113" s="11" t="s">
+      <c r="A113" s="7" t="s">
         <v>439</v>
       </c>
-      <c r="B113" s="11" t="s">
+      <c r="B113" s="7" t="s">
         <v>440</v>
       </c>
-      <c r="C113" s="11" t="s">
+      <c r="C113" s="7" t="s">
         <v>441</v>
       </c>
-      <c r="D113" s="11" t="s">
+      <c r="D113" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E113" s="11" t="s">
+      <c r="E113" s="7" t="s">
         <v>442</v>
       </c>
-      <c r="F113" s="11" t="s">
+      <c r="F113" s="7" t="s">
         <v>443</v>
       </c>
-      <c r="G113" s="11">
+      <c r="G113" s="7">
         <v>1</v>
       </c>
-      <c r="H113" s="12">
-        <v>13242425.64</v>
-      </c>
-      <c r="I113" s="13">
+      <c r="H113" s="8">
+        <v>13242425.640000001</v>
+      </c>
+      <c r="I113" s="9">
         <v>13242495.84</v>
       </c>
-      <c r="J113" s="12">
-        <v>-70.19999999925494</v>
-      </c>
-      <c r="K113" s="14">
+      <c r="J113" s="8">
+        <v>-70.199999999254942</v>
+      </c>
+      <c r="K113" s="10">
         <v>44923</v>
       </c>
-      <c r="L113" s="14">
+      <c r="L113" s="10">
         <v>45531</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A114" s="11" t="s">
+      <c r="A114" s="7" t="s">
         <v>439</v>
       </c>
-      <c r="B114" s="11" t="s">
+      <c r="B114" s="7" t="s">
         <v>444</v>
       </c>
-      <c r="C114" s="11" t="s">
+      <c r="C114" s="7" t="s">
         <v>445</v>
       </c>
-      <c r="D114" s="11" t="s">
+      <c r="D114" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E114" s="11" t="s">
+      <c r="E114" s="7" t="s">
         <v>446</v>
       </c>
-      <c r="F114" s="11" t="s">
+      <c r="F114" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G114" s="11">
+      <c r="G114" s="7">
         <v>1</v>
       </c>
-      <c r="H114" s="12">
-        <v>20859068.44</v>
-      </c>
-      <c r="I114" s="13">
-        <v>20859068.44</v>
-      </c>
-      <c r="J114" s="12">
+      <c r="H114" s="8">
+        <v>20859068.440000001</v>
+      </c>
+      <c r="I114" s="9">
+        <v>20859068.440000001</v>
+      </c>
+      <c r="J114" s="8">
         <v>0</v>
       </c>
-      <c r="K114" s="14">
+      <c r="K114" s="10">
         <v>45007</v>
       </c>
-      <c r="L114" s="14">
+      <c r="L114" s="10">
         <v>45851</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A115" s="11" t="s">
+      <c r="A115" s="7" t="s">
         <v>439</v>
       </c>
-      <c r="B115" s="11" t="s">
+      <c r="B115" s="7" t="s">
         <v>447</v>
       </c>
-      <c r="C115" s="11" t="s">
+      <c r="C115" s="7" t="s">
         <v>448</v>
       </c>
-      <c r="D115" s="11" t="s">
+      <c r="D115" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E115" s="11" t="s">
+      <c r="E115" s="7" t="s">
         <v>449</v>
       </c>
-      <c r="F115" s="11" t="s">
+      <c r="F115" s="7" t="s">
         <v>450</v>
       </c>
-      <c r="G115" s="11">
-        <v>0.9842</v>
-      </c>
-      <c r="H115" s="12">
-        <v>20229149.79</v>
-      </c>
-      <c r="I115" s="13">
-        <v>19910398.37</v>
-      </c>
-      <c r="J115" s="12">
+      <c r="G115" s="7">
+        <v>0.98419999999999996</v>
+      </c>
+      <c r="H115" s="8">
+        <v>20229149.789999999</v>
+      </c>
+      <c r="I115" s="9">
+        <v>19910398.370000001</v>
+      </c>
+      <c r="J115" s="8">
         <v>318751.41999999806</v>
       </c>
-      <c r="K115" s="14">
+      <c r="K115" s="10">
         <v>44697</v>
       </c>
-      <c r="L115" s="14">
+      <c r="L115" s="10">
         <v>45783</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A116" s="11" t="s">
+      <c r="A116" s="7" t="s">
         <v>439</v>
       </c>
-      <c r="B116" s="11" t="s">
+      <c r="B116" s="7" t="s">
         <v>451</v>
       </c>
-      <c r="C116" s="11" t="s">
+      <c r="C116" s="7" t="s">
         <v>452</v>
       </c>
-      <c r="D116" s="11" t="s">
+      <c r="D116" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E116" s="11" t="s">
+      <c r="E116" s="7" t="s">
         <v>453</v>
       </c>
-      <c r="F116" s="11" t="s">
+      <c r="F116" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="G116" s="11">
+      <c r="G116" s="7">
         <v>0</v>
       </c>
-      <c r="H116" s="12">
-        <v>6784130.44</v>
-      </c>
-      <c r="I116" s="13">
+      <c r="H116" s="8">
+        <v>6784130.4400000004</v>
+      </c>
+      <c r="I116" s="9">
         <v>0</v>
       </c>
-      <c r="J116" s="12">
-        <v>6784130.44</v>
-      </c>
-      <c r="K116" s="14">
+      <c r="J116" s="8">
+        <v>6784130.4400000004</v>
+      </c>
+      <c r="K116" s="10">
         <v>45100</v>
       </c>
-      <c r="L116" s="14">
+      <c r="L116" s="10">
         <v>45400</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A117" s="11" t="s">
+      <c r="A117" s="7" t="s">
         <v>439</v>
       </c>
-      <c r="B117" s="11" t="s">
+      <c r="B117" s="7" t="s">
         <v>454</v>
       </c>
-      <c r="C117" s="11" t="s">
+      <c r="C117" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="D117" s="11" t="s">
+      <c r="D117" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E117" s="11" t="s">
+      <c r="E117" s="7" t="s">
         <v>455</v>
       </c>
-      <c r="F117" s="11" t="s">
+      <c r="F117" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="G117" s="11">
-        <v>0.6605</v>
-      </c>
-      <c r="H117" s="12">
-        <v>20185137.81</v>
-      </c>
-      <c r="I117" s="13">
+      <c r="G117" s="7">
+        <v>0.66049999999999998</v>
+      </c>
+      <c r="H117" s="8">
+        <v>20185137.809999999</v>
+      </c>
+      <c r="I117" s="9">
         <v>13332401.6</v>
       </c>
-      <c r="J117" s="12">
+      <c r="J117" s="8">
         <v>6852736.209999999</v>
       </c>
-      <c r="K117" s="14">
+      <c r="K117" s="10">
         <v>44754</v>
       </c>
-      <c r="L117" s="14">
+      <c r="L117" s="10">
         <v>45566</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A118" s="11" t="s">
+      <c r="A118" s="7" t="s">
         <v>439</v>
       </c>
-      <c r="B118" s="11" t="s">
+      <c r="B118" s="7" t="s">
         <v>456</v>
       </c>
-      <c r="C118" s="11" t="s">
+      <c r="C118" s="7" t="s">
         <v>457</v>
       </c>
-      <c r="D118" s="11" t="s">
+      <c r="D118" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E118" s="11" t="s">
+      <c r="E118" s="7" t="s">
         <v>458</v>
       </c>
-      <c r="F118" s="11" t="s">
+      <c r="F118" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G118" s="11">
-        <v>0.0165</v>
-      </c>
-      <c r="H118" s="12">
-        <v>7430869.32</v>
-      </c>
-      <c r="I118" s="13">
+      <c r="G118" s="7">
+        <v>1.6500000000000001E-2</v>
+      </c>
+      <c r="H118" s="8">
+        <v>7430869.3200000003</v>
+      </c>
+      <c r="I118" s="9">
         <v>122778.19</v>
       </c>
-      <c r="J118" s="12">
-        <v>7308091.13</v>
-      </c>
-      <c r="K118" s="14">
+      <c r="J118" s="8">
+        <v>7308091.1299999999</v>
+      </c>
+      <c r="K118" s="10">
         <v>45865</v>
       </c>
-      <c r="L118" s="14">
+      <c r="L118" s="10">
         <v>46166</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A119" s="11" t="s">
+      <c r="A119" s="7" t="s">
         <v>459</v>
       </c>
-      <c r="B119" s="11" t="s">
+      <c r="B119" s="7" t="s">
         <v>460</v>
       </c>
-      <c r="C119" s="11" t="s">
+      <c r="C119" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="D119" s="11" t="s">
+      <c r="D119" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E119" s="11" t="s">
+      <c r="E119" s="7" t="s">
         <v>462</v>
       </c>
-      <c r="F119" s="11" t="s">
+      <c r="F119" s="7" t="s">
         <v>424</v>
       </c>
-      <c r="G119" s="11">
-        <v>0.9903</v>
-      </c>
-      <c r="H119" s="12">
+      <c r="G119" s="7">
+        <v>0.99029999999999996</v>
+      </c>
+      <c r="H119" s="8">
         <v>11046611.98</v>
       </c>
-      <c r="I119" s="13">
-        <v>10939879.39</v>
-      </c>
-      <c r="J119" s="12">
+      <c r="I119" s="9">
+        <v>10939879.390000001</v>
+      </c>
+      <c r="J119" s="8">
         <v>106732.58999999985</v>
       </c>
-      <c r="K119" s="14">
+      <c r="K119" s="10">
         <v>44663</v>
       </c>
-      <c r="L119" s="14">
+      <c r="L119" s="10">
         <v>45507</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A120" s="11" t="s">
+      <c r="A120" s="7" t="s">
         <v>459</v>
       </c>
-      <c r="B120" s="11" t="s">
+      <c r="B120" s="7" t="s">
         <v>463</v>
       </c>
-      <c r="C120" s="11" t="s">
+      <c r="C120" s="7" t="s">
         <v>464</v>
       </c>
-      <c r="D120" s="11" t="s">
+      <c r="D120" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E120" s="11" t="s">
+      <c r="E120" s="7" t="s">
         <v>465</v>
       </c>
-      <c r="F120" s="11" t="s">
+      <c r="F120" s="7" t="s">
         <v>466</v>
       </c>
-      <c r="G120" s="11">
-        <v>0.8079000000000001</v>
-      </c>
-      <c r="H120" s="12">
+      <c r="G120" s="7">
+        <v>0.80790000000000006</v>
+      </c>
+      <c r="H120" s="8">
         <v>2755604.93</v>
       </c>
-      <c r="I120" s="13">
-        <v>2226331.45</v>
-      </c>
-      <c r="J120" s="12">
+      <c r="I120" s="9">
+        <v>2226331.4500000002</v>
+      </c>
+      <c r="J120" s="8">
         <v>529273.48</v>
       </c>
-      <c r="K120" s="14">
+      <c r="K120" s="10">
         <v>45026</v>
       </c>
-      <c r="L120" s="14">
+      <c r="L120" s="10">
         <v>46023</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A121" s="11" t="s">
+      <c r="A121" s="7" t="s">
         <v>459</v>
       </c>
-      <c r="B121" s="11" t="s">
+      <c r="B121" s="7" t="s">
         <v>467</v>
       </c>
-      <c r="C121" s="11" t="s">
+      <c r="C121" s="7" t="s">
         <v>468</v>
       </c>
-      <c r="D121" s="11" t="s">
+      <c r="D121" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E121" s="11" t="s">
+      <c r="E121" s="7" t="s">
         <v>469</v>
       </c>
-      <c r="F121" s="11" t="s">
+      <c r="F121" s="7" t="s">
         <v>466</v>
       </c>
-      <c r="G121" s="11">
+      <c r="G121" s="7">
         <v>0</v>
       </c>
-      <c r="H121" s="12">
+      <c r="H121" s="8">
         <v>1712576.84</v>
       </c>
-      <c r="I121" s="13">
+      <c r="I121" s="9">
         <v>0</v>
       </c>
-      <c r="J121" s="12">
+      <c r="J121" s="8">
         <v>1712576.84</v>
       </c>
-      <c r="K121" s="14">
+      <c r="K121" s="10">
         <v>44823</v>
       </c>
-      <c r="L121" s="14">
+      <c r="L121" s="10">
         <v>44706</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A122" s="11" t="s">
+      <c r="A122" s="7" t="s">
         <v>470</v>
       </c>
-      <c r="B122" s="11" t="s">
+      <c r="B122" s="7" t="s">
         <v>471</v>
       </c>
-      <c r="C122" s="11" t="s">
+      <c r="C122" s="7" t="s">
         <v>472</v>
       </c>
-      <c r="D122" s="11" t="s">
+      <c r="D122" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E122" s="11" t="s">
+      <c r="E122" s="7" t="s">
         <v>473</v>
       </c>
-      <c r="F122" s="11" t="s">
+      <c r="F122" s="7" t="s">
         <v>474</v>
       </c>
-      <c r="G122" s="11">
+      <c r="G122" s="7">
         <v>0.9998999999999999</v>
       </c>
-      <c r="H122" s="12">
+      <c r="H122" s="8">
         <v>1612154.63</v>
       </c>
-      <c r="I122" s="13">
+      <c r="I122" s="9">
         <v>1612024.85</v>
       </c>
-      <c r="J122" s="12">
-        <v>129.7799999997951</v>
-      </c>
-      <c r="K122" s="14">
+      <c r="J122" s="8">
+        <v>129.77999999979511</v>
+      </c>
+      <c r="K122" s="10">
         <v>45776</v>
       </c>
-      <c r="L122" s="14">
+      <c r="L122" s="10">
         <v>45986</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A123" s="11" t="s">
+      <c r="A123" s="7" t="s">
         <v>475</v>
       </c>
-      <c r="B123" s="11" t="s">
+      <c r="B123" s="7" t="s">
         <v>476</v>
       </c>
-      <c r="C123" s="11" t="s">
+      <c r="C123" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="D123" s="11" t="s">
+      <c r="D123" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E123" s="11" t="s">
+      <c r="E123" s="7" t="s">
         <v>477</v>
       </c>
-      <c r="F123" s="11" t="s">
+      <c r="F123" s="7" t="s">
         <v>478</v>
       </c>
-      <c r="G123" s="11">
+      <c r="G123" s="7">
         <v>1</v>
       </c>
-      <c r="H123" s="12">
-        <v>6453162.72</v>
-      </c>
-      <c r="I123" s="13">
-        <v>6453162.72</v>
-      </c>
-      <c r="J123" s="12">
+      <c r="H123" s="8">
+        <v>6453162.7199999997</v>
+      </c>
+      <c r="I123" s="9">
+        <v>6453162.7199999997</v>
+      </c>
+      <c r="J123" s="8">
         <v>0</v>
       </c>
-      <c r="K123" s="14">
+      <c r="K123" s="10">
         <v>44760</v>
       </c>
-      <c r="L123" s="14">
+      <c r="L123" s="10">
         <v>45201</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A124" s="11" t="s">
+      <c r="A124" s="7" t="s">
         <v>475</v>
       </c>
-      <c r="B124" s="11" t="s">
+      <c r="B124" s="7" t="s">
         <v>479</v>
       </c>
-      <c r="C124" s="11" t="s">
+      <c r="C124" s="7" t="s">
         <v>480</v>
       </c>
-      <c r="D124" s="11" t="s">
+      <c r="D124" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E124" s="11" t="s">
+      <c r="E124" s="7" t="s">
         <v>481</v>
       </c>
-      <c r="F124" s="11" t="s">
+      <c r="F124" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="G124" s="11">
-        <v>0.9993000000000001</v>
-      </c>
-      <c r="H124" s="12">
+      <c r="G124" s="7">
+        <v>0.99930000000000008</v>
+      </c>
+      <c r="H124" s="8">
         <v>1741703.69</v>
       </c>
-      <c r="I124" s="13">
+      <c r="I124" s="9">
         <v>1740561.74</v>
       </c>
-      <c r="J124" s="12">
+      <c r="J124" s="8">
         <v>1141.9499999999534</v>
       </c>
-      <c r="K124" s="14">
+      <c r="K124" s="10">
         <v>44683</v>
       </c>
-      <c r="L124" s="14">
+      <c r="L124" s="10">
         <v>45889</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A125" s="11" t="s">
+      <c r="A125" s="7" t="s">
         <v>475</v>
       </c>
-      <c r="B125" s="11" t="s">
+      <c r="B125" s="7" t="s">
         <v>482</v>
       </c>
-      <c r="C125" s="11" t="s">
+      <c r="C125" s="7" t="s">
         <v>483</v>
       </c>
-      <c r="D125" s="11" t="s">
+      <c r="D125" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E125" s="11" t="s">
+      <c r="E125" s="7" t="s">
         <v>484</v>
       </c>
-      <c r="F125" s="11" t="s">
+      <c r="F125" s="7" t="s">
         <v>485</v>
       </c>
-      <c r="G125" s="11">
+      <c r="G125" s="7">
         <v>0.997</v>
       </c>
-      <c r="H125" s="12">
-        <v>6014775.77</v>
-      </c>
-      <c r="I125" s="13">
-        <v>5996889.68</v>
-      </c>
-      <c r="J125" s="12">
-        <v>17886.08999999985</v>
-      </c>
-      <c r="K125" s="14">
+      <c r="H125" s="8">
+        <v>6014775.7699999996</v>
+      </c>
+      <c r="I125" s="9">
+        <v>5996889.6799999997</v>
+      </c>
+      <c r="J125" s="8">
+        <v>17886.089999999851</v>
+      </c>
+      <c r="K125" s="10">
         <v>44708</v>
       </c>
-      <c r="L125" s="14">
+      <c r="L125" s="10">
         <v>45467</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A126" s="11" t="s">
+      <c r="A126" s="7" t="s">
         <v>475</v>
       </c>
-      <c r="B126" s="11" t="s">
+      <c r="B126" s="7" t="s">
         <v>486</v>
       </c>
-      <c r="C126" s="11" t="s">
+      <c r="C126" s="7" t="s">
         <v>487</v>
       </c>
-      <c r="D126" s="11" t="s">
+      <c r="D126" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E126" s="11" t="s">
+      <c r="E126" s="7" t="s">
         <v>488</v>
       </c>
-      <c r="F126" s="11" t="s">
+      <c r="F126" s="7" t="s">
         <v>485</v>
       </c>
-      <c r="G126" s="11">
-        <v>0.9913</v>
-      </c>
-      <c r="H126" s="12">
+      <c r="G126" s="7">
+        <v>0.99129999999999996</v>
+      </c>
+      <c r="H126" s="8">
         <v>3569195.39</v>
       </c>
-      <c r="I126" s="13">
+      <c r="I126" s="9">
         <v>3538001.16</v>
       </c>
-      <c r="J126" s="12">
-        <v>31194.22999999998</v>
-      </c>
-      <c r="K126" s="14">
+      <c r="J126" s="8">
+        <v>31194.229999999981</v>
+      </c>
+      <c r="K126" s="10">
         <v>44658</v>
       </c>
-      <c r="L126" s="14">
+      <c r="L126" s="10">
         <v>45426</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A127" s="11" t="s">
+      <c r="A127" s="7" t="s">
         <v>475</v>
       </c>
-      <c r="B127" s="11" t="s">
+      <c r="B127" s="7" t="s">
         <v>489</v>
       </c>
-      <c r="C127" s="11" t="s">
+      <c r="C127" s="7" t="s">
         <v>490</v>
       </c>
-      <c r="D127" s="11" t="s">
+      <c r="D127" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E127" s="11" t="s">
+      <c r="E127" s="7" t="s">
         <v>491</v>
       </c>
-      <c r="F127" s="11" t="s">
+      <c r="F127" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="G127" s="11">
-        <v>0.7993000000000001</v>
-      </c>
-      <c r="H127" s="12">
+      <c r="G127" s="7">
+        <v>0.79930000000000012</v>
+      </c>
+      <c r="H127" s="8">
         <v>1528883.61</v>
       </c>
-      <c r="I127" s="13">
-        <v>1222003.41</v>
-      </c>
-      <c r="J127" s="12">
-        <v>306880.2000000002</v>
-      </c>
-      <c r="K127" s="14">
+      <c r="I127" s="9">
+        <v>1222003.4099999999</v>
+      </c>
+      <c r="J127" s="8">
+        <v>306880.20000000019</v>
+      </c>
+      <c r="K127" s="10">
         <v>44655</v>
       </c>
-      <c r="L127" s="14">
+      <c r="L127" s="10">
         <v>46164</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A128" s="11" t="s">
+      <c r="A128" s="7" t="s">
         <v>475</v>
       </c>
-      <c r="B128" s="11" t="s">
+      <c r="B128" s="7" t="s">
         <v>492</v>
       </c>
-      <c r="C128" s="11" t="s">
+      <c r="C128" s="7" t="s">
         <v>493</v>
       </c>
-      <c r="D128" s="11" t="s">
+      <c r="D128" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E128" s="11" t="s">
+      <c r="E128" s="7" t="s">
         <v>494</v>
       </c>
-      <c r="F128" s="11" t="s">
+      <c r="F128" s="7" t="s">
         <v>495</v>
       </c>
-      <c r="G128" s="11">
-        <v>0.0245</v>
-      </c>
-      <c r="H128" s="12">
-        <v>2317778.22</v>
-      </c>
-      <c r="I128" s="13">
+      <c r="G128" s="7">
+        <v>2.4500000000000001E-2</v>
+      </c>
+      <c r="H128" s="8">
+        <v>2317778.2200000002</v>
+      </c>
+      <c r="I128" s="9">
         <v>56828.03</v>
       </c>
-      <c r="J128" s="12">
+      <c r="J128" s="8">
         <v>2260950.1900000004</v>
       </c>
-      <c r="K128" s="14">
+      <c r="K128" s="10">
         <v>45035</v>
       </c>
-      <c r="L128" s="14">
+      <c r="L128" s="10">
         <v>45396</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A129" s="11" t="s">
+      <c r="A129" s="7" t="s">
         <v>496</v>
       </c>
-      <c r="B129" s="11" t="s">
+      <c r="B129" s="7" t="s">
         <v>497</v>
       </c>
-      <c r="C129" s="11" t="s">
+      <c r="C129" s="7" t="s">
         <v>498</v>
       </c>
-      <c r="D129" s="11" t="s">
+      <c r="D129" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E129" s="11" t="s">
+      <c r="E129" s="7" t="s">
         <v>499</v>
       </c>
-      <c r="F129" s="11" t="s">
+      <c r="F129" s="7" t="s">
         <v>500</v>
       </c>
-      <c r="G129" s="11">
+      <c r="G129" s="7">
         <v>1</v>
       </c>
-      <c r="H129" s="12">
-        <v>6478069.43</v>
-      </c>
-      <c r="I129" s="13">
-        <v>6478029.44</v>
-      </c>
-      <c r="J129" s="12">
+      <c r="H129" s="8">
+        <v>6478069.4299999997</v>
+      </c>
+      <c r="I129" s="9">
+        <v>6478029.4400000004</v>
+      </c>
+      <c r="J129" s="8">
         <v>39.989999999292195</v>
       </c>
-      <c r="K129" s="14">
+      <c r="K129" s="10">
         <v>44827</v>
       </c>
-      <c r="L129" s="14">
+      <c r="L129" s="10">
         <v>45690</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A130" s="11" t="s">
+      <c r="A130" s="7" t="s">
         <v>496</v>
       </c>
-      <c r="B130" s="11" t="s">
+      <c r="B130" s="7" t="s">
         <v>501</v>
       </c>
-      <c r="C130" s="11" t="s">
+      <c r="C130" s="7" t="s">
         <v>502</v>
       </c>
-      <c r="D130" s="11" t="s">
+      <c r="D130" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E130" s="11" t="s">
+      <c r="E130" s="7" t="s">
         <v>503</v>
       </c>
-      <c r="F130" s="11" t="s">
+      <c r="F130" s="7" t="s">
         <v>504</v>
       </c>
-      <c r="G130" s="11">
-        <v>0.7809</v>
-      </c>
-      <c r="H130" s="12">
+      <c r="G130" s="7">
+        <v>0.78090000000000004</v>
+      </c>
+      <c r="H130" s="8">
         <v>544550.48</v>
       </c>
-      <c r="I130" s="13">
+      <c r="I130" s="9">
         <v>425261.4</v>
       </c>
-      <c r="J130" s="12">
+      <c r="J130" s="8">
         <v>119289.07999999996</v>
       </c>
-      <c r="K130" s="14">
+      <c r="K130" s="10">
         <v>45925</v>
       </c>
-      <c r="L130" s="14">
+      <c r="L130" s="10">
         <v>46165</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A131" s="11" t="s">
+      <c r="A131" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="B131" s="11" t="s">
+      <c r="B131" s="7" t="s">
         <v>506</v>
       </c>
-      <c r="C131" s="11" t="s">
+      <c r="C131" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="D131" s="11" t="s">
+      <c r="D131" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E131" s="11" t="s">
+      <c r="E131" s="7" t="s">
         <v>507</v>
       </c>
-      <c r="F131" s="11" t="s">
+      <c r="F131" s="7" t="s">
         <v>508</v>
       </c>
-      <c r="G131" s="11">
+      <c r="G131" s="7">
         <v>1</v>
       </c>
-      <c r="H131" s="12">
+      <c r="H131" s="8">
         <v>2389346</v>
       </c>
-      <c r="I131" s="13">
+      <c r="I131" s="9">
         <v>2389346</v>
       </c>
-      <c r="J131" s="12">
+      <c r="J131" s="8">
         <v>0</v>
       </c>
-      <c r="K131" s="14">
+      <c r="K131" s="10">
         <v>44693</v>
       </c>
-      <c r="L131" s="14">
+      <c r="L131" s="10">
         <v>45456</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A132" s="11" t="s">
+      <c r="A132" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="B132" s="11" t="s">
+      <c r="B132" s="7" t="s">
         <v>509</v>
       </c>
-      <c r="C132" s="11" t="s">
+      <c r="C132" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="D132" s="11" t="s">
+      <c r="D132" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E132" s="11" t="s">
+      <c r="E132" s="7" t="s">
         <v>510</v>
       </c>
-      <c r="F132" s="11" t="s">
+      <c r="F132" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="G132" s="11">
+      <c r="G132" s="7">
         <v>1</v>
       </c>
-      <c r="H132" s="12">
+      <c r="H132" s="8">
         <v>6743574.04</v>
       </c>
-      <c r="I132" s="13">
-        <v>6743573.85</v>
-      </c>
-      <c r="J132" s="12">
+      <c r="I132" s="9">
+        <v>6743573.8499999996</v>
+      </c>
+      <c r="J132" s="8">
         <v>0.19000000040978193</v>
       </c>
-      <c r="K132" s="14">
+      <c r="K132" s="10">
         <v>44693</v>
       </c>
-      <c r="L132" s="14">
+      <c r="L132" s="10">
         <v>45152</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A133" s="11" t="s">
+      <c r="A133" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="B133" s="11" t="s">
+      <c r="B133" s="7" t="s">
         <v>511</v>
       </c>
-      <c r="C133" s="11" t="s">
+      <c r="C133" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="D133" s="11" t="s">
+      <c r="D133" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E133" s="11" t="s">
+      <c r="E133" s="7" t="s">
         <v>512</v>
       </c>
-      <c r="F133" s="11" t="s">
+      <c r="F133" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="G133" s="11">
-        <v>0.9562999999999999</v>
-      </c>
-      <c r="H133" s="12">
+      <c r="G133" s="7">
+        <v>0.95629999999999993</v>
+      </c>
+      <c r="H133" s="8">
         <v>1052239.53</v>
       </c>
-      <c r="I133" s="13">
+      <c r="I133" s="9">
         <v>1006235.15</v>
       </c>
-      <c r="J133" s="12">
+      <c r="J133" s="8">
         <v>46004.380000000005</v>
       </c>
-      <c r="K133" s="14">
+      <c r="K133" s="10">
         <v>44613</v>
       </c>
-      <c r="L133" s="14">
+      <c r="L133" s="10">
         <v>45183</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A134" s="11" t="s">
+      <c r="A134" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="B134" s="11" t="s">
+      <c r="B134" s="7" t="s">
         <v>513</v>
       </c>
-      <c r="C134" s="11" t="s">
+      <c r="C134" s="7" t="s">
         <v>514</v>
       </c>
-      <c r="D134" s="11" t="s">
+      <c r="D134" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E134" s="11" t="s">
+      <c r="E134" s="7" t="s">
         <v>515</v>
       </c>
-      <c r="F134" s="11" t="s">
+      <c r="F134" s="7" t="s">
         <v>516</v>
       </c>
-      <c r="G134" s="11">
+      <c r="G134" s="7">
         <v>0.6409999999999999</v>
       </c>
-      <c r="H134" s="12">
+      <c r="H134" s="8">
         <v>256613.37</v>
       </c>
-      <c r="I134" s="13">
+      <c r="I134" s="9">
         <v>164482.69</v>
       </c>
-      <c r="J134" s="12">
+      <c r="J134" s="8">
         <v>92130.68</v>
       </c>
-      <c r="K134" s="14">
+      <c r="K134" s="10">
         <v>45915</v>
       </c>
-      <c r="L134" s="14">
+      <c r="L134" s="10">
         <v>46005</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A135" s="11" t="s">
+      <c r="A135" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="B135" s="11" t="s">
+      <c r="B135" s="7" t="s">
         <v>517</v>
       </c>
-      <c r="C135" s="11" t="s">
+      <c r="C135" s="7" t="s">
         <v>518</v>
       </c>
-      <c r="D135" s="11" t="s">
+      <c r="D135" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E135" s="11" t="s">
+      <c r="E135" s="7" t="s">
         <v>519</v>
       </c>
-      <c r="F135" s="11" t="s">
+      <c r="F135" s="7" t="s">
         <v>520</v>
       </c>
-      <c r="G135" s="11">
-        <v>0.9508</v>
-      </c>
-      <c r="H135" s="12">
+      <c r="G135" s="7">
+        <v>0.95079999999999998</v>
+      </c>
+      <c r="H135" s="8">
         <v>13554947.83</v>
       </c>
-      <c r="I135" s="13">
-        <v>12888506.56</v>
-      </c>
-      <c r="J135" s="12">
-        <v>666441.2699999996</v>
-      </c>
-      <c r="K135" s="14">
+      <c r="I135" s="9">
+        <v>12888506.560000001</v>
+      </c>
+      <c r="J135" s="8">
+        <v>666441.26999999955</v>
+      </c>
+      <c r="K135" s="10">
         <v>44537</v>
       </c>
-      <c r="L135" s="14">
+      <c r="L135" s="10">
         <v>46075</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A136" s="11" t="s">
+      <c r="A136" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="B136" s="11" t="s">
+      <c r="B136" s="7" t="s">
         <v>521</v>
       </c>
-      <c r="C136" s="11" t="s">
+      <c r="C136" s="7" t="s">
         <v>448</v>
       </c>
-      <c r="D136" s="11" t="s">
+      <c r="D136" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E136" s="11" t="s">
+      <c r="E136" s="7" t="s">
         <v>522</v>
       </c>
-      <c r="F136" s="11" t="s">
+      <c r="F136" s="7" t="s">
         <v>523</v>
       </c>
-      <c r="G136" s="11">
+      <c r="G136" s="7">
         <v>0</v>
       </c>
-      <c r="H136" s="12">
+      <c r="H136" s="8">
         <v>1305890.95</v>
       </c>
-      <c r="I136" s="13">
+      <c r="I136" s="9">
         <v>0</v>
       </c>
-      <c r="J136" s="12">
+      <c r="J136" s="8">
         <v>1305890.95</v>
       </c>
-      <c r="K136" s="14">
+      <c r="K136" s="10">
         <v>44610</v>
       </c>
-      <c r="L136" s="14">
+      <c r="L136" s="10">
         <v>45567</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A137" s="11" t="s">
+      <c r="A137" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="B137" s="11" t="s">
+      <c r="B137" s="7" t="s">
         <v>524</v>
       </c>
-      <c r="C137" s="11" t="s">
+      <c r="C137" s="7" t="s">
         <v>525</v>
       </c>
-      <c r="D137" s="11" t="s">
+      <c r="D137" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E137" s="11" t="s">
+      <c r="E137" s="7" t="s">
         <v>526</v>
       </c>
-      <c r="F137" s="11" t="s">
+      <c r="F137" s="7" t="s">
         <v>527</v>
       </c>
-      <c r="G137" s="11">
-        <v>0.9765999999999999</v>
-      </c>
-      <c r="H137" s="12">
-        <v>56185153.92</v>
-      </c>
-      <c r="I137" s="13">
-        <v>54872063.4</v>
-      </c>
-      <c r="J137" s="12">
+      <c r="G137" s="7">
+        <v>0.97659999999999991</v>
+      </c>
+      <c r="H137" s="8">
+        <v>56185153.920000002</v>
+      </c>
+      <c r="I137" s="9">
+        <v>54872063.399999999</v>
+      </c>
+      <c r="J137" s="8">
         <v>1313090.5200000033</v>
       </c>
-      <c r="K137" s="14">
+      <c r="K137" s="10">
         <v>44872</v>
       </c>
-      <c r="L137" s="14">
+      <c r="L137" s="10">
         <v>45475</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A138" s="11" t="s">
+      <c r="A138" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="B138" s="11" t="s">
+      <c r="B138" s="7" t="s">
         <v>528</v>
       </c>
-      <c r="C138" s="11" t="s">
+      <c r="C138" s="7" t="s">
         <v>529</v>
       </c>
-      <c r="D138" s="11" t="s">
+      <c r="D138" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E138" s="11" t="s">
+      <c r="E138" s="7" t="s">
         <v>530</v>
       </c>
-      <c r="F138" s="11" t="s">
+      <c r="F138" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="G138" s="11">
-        <v>0.8513</v>
-      </c>
-      <c r="H138" s="12">
+      <c r="G138" s="7">
+        <v>0.85129999999999995</v>
+      </c>
+      <c r="H138" s="8">
         <v>12100122.6</v>
       </c>
-      <c r="I138" s="13">
+      <c r="I138" s="9">
         <v>10301084.52</v>
       </c>
-      <c r="J138" s="12">
+      <c r="J138" s="8">
         <v>1799038.08</v>
       </c>
-      <c r="K138" s="14">
+      <c r="K138" s="10">
         <v>45758</v>
       </c>
-      <c r="L138" s="14">
+      <c r="L138" s="10">
         <v>46123</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A139" s="11" t="s">
+      <c r="A139" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="B139" s="11" t="s">
+      <c r="B139" s="7" t="s">
         <v>532</v>
       </c>
-      <c r="C139" s="11" t="s">
+      <c r="C139" s="7" t="s">
         <v>533</v>
       </c>
-      <c r="D139" s="11" t="s">
+      <c r="D139" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E139" s="11" t="s">
+      <c r="E139" s="7" t="s">
         <v>534</v>
       </c>
-      <c r="F139" s="11" t="s">
+      <c r="F139" s="7" t="s">
         <v>508</v>
       </c>
-      <c r="G139" s="11">
-        <v>0.8454999999999999</v>
-      </c>
-      <c r="H139" s="12">
+      <c r="G139" s="7">
+        <v>0.84549999999999992</v>
+      </c>
+      <c r="H139" s="8">
         <v>12432476.25</v>
       </c>
-      <c r="I139" s="13">
-        <v>10511270.47</v>
-      </c>
-      <c r="J139" s="12">
+      <c r="I139" s="9">
+        <v>10511270.470000001</v>
+      </c>
+      <c r="J139" s="8">
         <v>1921205.7799999993</v>
       </c>
-      <c r="K139" s="14">
+      <c r="K139" s="10">
         <v>45894</v>
       </c>
-      <c r="L139" s="14">
+      <c r="L139" s="10">
         <v>46112</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A140" s="11" t="s">
+      <c r="A140" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="B140" s="11" t="s">
+      <c r="B140" s="7" t="s">
         <v>535</v>
       </c>
-      <c r="C140" s="11" t="s">
+      <c r="C140" s="7" t="s">
         <v>434</v>
       </c>
-      <c r="D140" s="11" t="s">
+      <c r="D140" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E140" s="11" t="s">
+      <c r="E140" s="7" t="s">
         <v>536</v>
       </c>
-      <c r="F140" s="11" t="s">
+      <c r="F140" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="G140" s="11">
-        <v>0.8916</v>
-      </c>
-      <c r="H140" s="12">
+      <c r="G140" s="7">
+        <v>0.89159999999999995</v>
+      </c>
+      <c r="H140" s="8">
         <v>24590858.27</v>
       </c>
-      <c r="I140" s="13">
+      <c r="I140" s="9">
         <v>21925638.52</v>
       </c>
-      <c r="J140" s="12">
+      <c r="J140" s="8">
         <v>2665219.75</v>
       </c>
-      <c r="K140" s="14">
+      <c r="K140" s="10">
         <v>44638</v>
       </c>
-      <c r="L140" s="14">
+      <c r="L140" s="10">
         <v>45936</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A141" s="11" t="s">
+      <c r="A141" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="B141" s="11" t="s">
+      <c r="B141" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="C141" s="11" t="s">
+      <c r="C141" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="D141" s="11" t="s">
+      <c r="D141" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E141" s="11" t="s">
+      <c r="E141" s="7" t="s">
         <v>538</v>
       </c>
-      <c r="F141" s="11" t="s">
+      <c r="F141" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="G141" s="11">
-        <v>0.0707</v>
-      </c>
-      <c r="H141" s="12">
+      <c r="G141" s="7">
+        <v>7.0699999999999999E-2</v>
+      </c>
+      <c r="H141" s="8">
         <v>3615856.15</v>
       </c>
-      <c r="I141" s="13">
+      <c r="I141" s="9">
         <v>255684.47</v>
       </c>
-      <c r="J141" s="12">
+      <c r="J141" s="8">
         <v>3360171.6799999997</v>
       </c>
-      <c r="K141" s="14">
+      <c r="K141" s="10">
         <v>44791</v>
       </c>
-      <c r="L141" s="14">
+      <c r="L141" s="10">
         <v>45259</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A142" s="11" t="s">
+      <c r="A142" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="B142" s="11" t="s">
+      <c r="B142" s="7" t="s">
         <v>539</v>
       </c>
-      <c r="C142" s="11" t="s">
+      <c r="C142" s="7" t="s">
         <v>540</v>
       </c>
-      <c r="D142" s="11" t="s">
+      <c r="D142" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E142" s="11" t="s">
+      <c r="E142" s="7" t="s">
         <v>541</v>
       </c>
-      <c r="F142" s="11" t="s">
+      <c r="F142" s="7" t="s">
         <v>508</v>
       </c>
-      <c r="G142" s="11">
-        <v>0.1637</v>
-      </c>
-      <c r="H142" s="12">
-        <v>7848019.53</v>
-      </c>
-      <c r="I142" s="13">
-        <v>1284711.9</v>
-      </c>
-      <c r="J142" s="12">
-        <v>6563307.630000001</v>
-      </c>
-      <c r="K142" s="14">
+      <c r="G142" s="7">
+        <v>0.16370000000000001</v>
+      </c>
+      <c r="H142" s="8">
+        <v>7848019.5300000003</v>
+      </c>
+      <c r="I142" s="9">
+        <v>1284711.8999999999</v>
+      </c>
+      <c r="J142" s="8">
+        <v>6563307.6300000008</v>
+      </c>
+      <c r="K142" s="10">
         <v>45986</v>
       </c>
-      <c r="L142" s="14">
+      <c r="L142" s="10">
         <v>46351</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A143" s="11" t="s">
+      <c r="A143" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="B143" s="11" t="s">
+      <c r="B143" s="7" t="s">
         <v>542</v>
       </c>
-      <c r="C143" s="11" t="s">
+      <c r="C143" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="D143" s="11" t="s">
+      <c r="D143" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E143" s="11" t="s">
+      <c r="E143" s="7" t="s">
         <v>543</v>
       </c>
-      <c r="F143" s="11" t="s">
+      <c r="F143" s="7" t="s">
         <v>544</v>
       </c>
-      <c r="G143" s="11">
-        <v>0.5364</v>
-      </c>
-      <c r="H143" s="12">
-        <v>16932981.45</v>
-      </c>
-      <c r="I143" s="13">
-        <v>9082408.67</v>
-      </c>
-      <c r="J143" s="12">
-        <v>7850572.779999999</v>
-      </c>
-      <c r="K143" s="14">
+      <c r="G143" s="7">
+        <v>0.53639999999999999</v>
+      </c>
+      <c r="H143" s="8">
+        <v>16932981.449999999</v>
+      </c>
+      <c r="I143" s="9">
+        <v>9082408.6699999999</v>
+      </c>
+      <c r="J143" s="8">
+        <v>7850572.7799999993</v>
+      </c>
+      <c r="K143" s="10">
         <v>44791</v>
       </c>
-      <c r="L143" s="14">
+      <c r="L143" s="10">
         <v>45393</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A144" s="11" t="s">
+      <c r="A144" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="B144" s="11" t="s">
+      <c r="B144" s="7" t="s">
         <v>545</v>
       </c>
-      <c r="C144" s="11" t="s">
+      <c r="C144" s="7" t="s">
         <v>546</v>
       </c>
-      <c r="D144" s="11" t="s">
+      <c r="D144" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E144" s="11" t="s">
+      <c r="E144" s="7" t="s">
         <v>547</v>
       </c>
-      <c r="F144" s="11" t="s">
+      <c r="F144" s="7" t="s">
         <v>548</v>
       </c>
-      <c r="G144" s="11">
-        <v>0.6043</v>
-      </c>
-      <c r="H144" s="12">
+      <c r="G144" s="7">
+        <v>0.60429999999999995</v>
+      </c>
+      <c r="H144" s="8">
         <v>24187461.93</v>
       </c>
-      <c r="I144" s="13">
-        <v>14615806.69</v>
-      </c>
-      <c r="J144" s="12">
-        <v>9571655.24</v>
-      </c>
-      <c r="K144" s="14">
+      <c r="I144" s="9">
+        <v>14615806.689999999</v>
+      </c>
+      <c r="J144" s="8">
+        <v>9571655.2400000002</v>
+      </c>
+      <c r="K144" s="10">
         <v>45723</v>
       </c>
-      <c r="L144" s="14">
+      <c r="L144" s="10">
         <v>46203</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A145" s="11" t="s">
+      <c r="A145" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="B145" s="11" t="s">
+      <c r="B145" s="7" t="s">
         <v>549</v>
       </c>
-      <c r="C145" s="11" t="s">
+      <c r="C145" s="7" t="s">
         <v>550</v>
       </c>
-      <c r="D145" s="11" t="s">
+      <c r="D145" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E145" s="11" t="s">
+      <c r="E145" s="7" t="s">
         <v>551</v>
       </c>
-      <c r="F145" s="11" t="s">
+      <c r="F145" s="7" t="s">
         <v>552</v>
       </c>
-      <c r="G145" s="11">
-        <v>0.8298000000000001</v>
-      </c>
-      <c r="H145" s="12">
-        <v>74609626.42</v>
-      </c>
-      <c r="I145" s="13">
-        <v>61911151.04</v>
-      </c>
-      <c r="J145" s="12">
+      <c r="G145" s="7">
+        <v>0.82980000000000009</v>
+      </c>
+      <c r="H145" s="8">
+        <v>74609626.420000002</v>
+      </c>
+      <c r="I145" s="9">
+        <v>61911151.039999999</v>
+      </c>
+      <c r="J145" s="8">
         <v>12698475.380000003</v>
       </c>
-      <c r="K145" s="14">
+      <c r="K145" s="10">
         <v>45555</v>
       </c>
-      <c r="L145" s="14">
+      <c r="L145" s="10">
         <v>46112</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A146" s="11" t="s">
+      <c r="A146" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="B146" s="11" t="s">
+      <c r="B146" s="7" t="s">
         <v>553</v>
       </c>
-      <c r="C146" s="11" t="s">
+      <c r="C146" s="7" t="s">
         <v>554</v>
       </c>
-      <c r="D146" s="11" t="s">
+      <c r="D146" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E146" s="11" t="s">
+      <c r="E146" s="7" t="s">
         <v>555</v>
       </c>
-      <c r="F146" s="11" t="s">
+      <c r="F146" s="7" t="s">
         <v>520</v>
       </c>
-      <c r="G146" s="11">
+      <c r="G146" s="7">
         <v>0.15</v>
       </c>
-      <c r="H146" s="12">
-        <v>15203482.79</v>
-      </c>
-      <c r="I146" s="13">
-        <v>2279930.05</v>
-      </c>
-      <c r="J146" s="12">
+      <c r="H146" s="8">
+        <v>15203482.789999999</v>
+      </c>
+      <c r="I146" s="9">
+        <v>2279930.0499999998</v>
+      </c>
+      <c r="J146" s="8">
         <v>12923552.739999998</v>
       </c>
-      <c r="K146" s="14">
+      <c r="K146" s="10">
         <v>44757</v>
       </c>
-      <c r="L146" s="14">
+      <c r="L146" s="10">
         <v>46287</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A147" s="11" t="s">
+      <c r="A147" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="B147" s="11" t="s">
+      <c r="B147" s="7" t="s">
         <v>556</v>
       </c>
-      <c r="C147" s="11" t="s">
+      <c r="C147" s="7" t="s">
         <v>490</v>
       </c>
-      <c r="D147" s="11" t="s">
+      <c r="D147" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E147" s="11" t="s">
+      <c r="E147" s="7" t="s">
         <v>557</v>
       </c>
-      <c r="F147" s="11" t="s">
+      <c r="F147" s="7" t="s">
         <v>520</v>
       </c>
-      <c r="G147" s="11">
-        <v>0.0216</v>
-      </c>
-      <c r="H147" s="12">
+      <c r="G147" s="7">
+        <v>2.1600000000000001E-2</v>
+      </c>
+      <c r="H147" s="8">
         <v>13677862.32</v>
       </c>
-      <c r="I147" s="13">
+      <c r="I147" s="9">
         <v>296101.87</v>
       </c>
-      <c r="J147" s="12">
+      <c r="J147" s="8">
         <v>13381760.450000001</v>
       </c>
-      <c r="K147" s="14">
+      <c r="K147" s="10">
         <v>44581</v>
       </c>
-      <c r="L147" s="14">
+      <c r="L147" s="10">
         <v>45561</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A148" s="11" t="s">
+      <c r="A148" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="B148" s="11" t="s">
+      <c r="B148" s="7" t="s">
         <v>558</v>
       </c>
-      <c r="C148" s="11" t="s">
+      <c r="C148" s="7" t="s">
         <v>559</v>
       </c>
-      <c r="D148" s="11" t="s">
+      <c r="D148" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E148" s="11" t="s">
+      <c r="E148" s="7" t="s">
         <v>560</v>
       </c>
-      <c r="F148" s="11" t="s">
+      <c r="F148" s="7" t="s">
         <v>561</v>
       </c>
-      <c r="G148" s="11">
+      <c r="G148" s="7">
         <v>0</v>
       </c>
-      <c r="H148" s="12">
+      <c r="H148" s="8">
         <v>14144248.92</v>
       </c>
-      <c r="I148" s="13">
+      <c r="I148" s="9">
         <v>0</v>
       </c>
-      <c r="J148" s="12">
+      <c r="J148" s="8">
         <v>14144248.92</v>
       </c>
-      <c r="K148" s="14">
+      <c r="K148" s="10">
         <v>41443</v>
       </c>
-      <c r="L148" s="14">
+      <c r="L148" s="10">
         <v>44012</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A149" s="11" t="s">
+      <c r="A149" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="B149" s="11" t="s">
+      <c r="B149" s="7" t="s">
         <v>562</v>
       </c>
-      <c r="C149" s="11" t="s">
+      <c r="C149" s="7" t="s">
         <v>563</v>
       </c>
-      <c r="D149" s="11" t="s">
+      <c r="D149" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E149" s="11" t="s">
+      <c r="E149" s="7" t="s">
         <v>564</v>
       </c>
-      <c r="F149" s="11" t="s">
+      <c r="F149" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="G149" s="11">
-        <v>0.3475</v>
-      </c>
-      <c r="H149" s="12">
-        <v>24165422.12</v>
-      </c>
-      <c r="I149" s="13">
-        <v>8398407.23</v>
-      </c>
-      <c r="J149" s="12">
-        <v>15767014.89</v>
-      </c>
-      <c r="K149" s="14">
+      <c r="G149" s="7">
+        <v>0.34749999999999998</v>
+      </c>
+      <c r="H149" s="8">
+        <v>24165422.120000001</v>
+      </c>
+      <c r="I149" s="9">
+        <v>8398407.2300000004</v>
+      </c>
+      <c r="J149" s="8">
+        <v>15767014.890000001</v>
+      </c>
+      <c r="K149" s="10">
         <v>44538</v>
       </c>
-      <c r="L149" s="14">
+      <c r="L149" s="10">
         <v>45426</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A150" s="11" t="s">
+      <c r="A150" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="B150" s="11" t="s">
+      <c r="B150" s="7" t="s">
         <v>565</v>
       </c>
-      <c r="C150" s="11" t="s">
+      <c r="C150" s="7" t="s">
         <v>566</v>
       </c>
-      <c r="D150" s="11" t="s">
+      <c r="D150" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E150" s="11" t="s">
+      <c r="E150" s="7" t="s">
         <v>567</v>
       </c>
-      <c r="F150" s="11" t="s">
+      <c r="F150" s="7" t="s">
         <v>568</v>
       </c>
-      <c r="G150" s="11">
-        <v>0.5169</v>
-      </c>
-      <c r="H150" s="12">
+      <c r="G150" s="7">
+        <v>0.51690000000000003</v>
+      </c>
+      <c r="H150" s="8">
         <v>104939756.55</v>
       </c>
-      <c r="I150" s="13">
-        <v>54247297.54</v>
-      </c>
-      <c r="J150" s="12">
-        <v>50692459.01</v>
-      </c>
-      <c r="K150" s="14">
+      <c r="I150" s="9">
+        <v>54247297.539999999</v>
+      </c>
+      <c r="J150" s="8">
+        <v>50692459.009999998</v>
+      </c>
+      <c r="K150" s="10">
         <v>45624</v>
       </c>
-      <c r="L150" s="14">
+      <c r="L150" s="10">
         <v>46074</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A151" s="11" t="s">
+      <c r="A151" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="B151" s="11" t="s">
+      <c r="B151" s="7" t="s">
         <v>569</v>
       </c>
-      <c r="C151" s="11" t="s">
+      <c r="C151" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="D151" s="11" t="s">
+      <c r="D151" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E151" s="11" t="s">
+      <c r="E151" s="7" t="s">
         <v>571</v>
       </c>
-      <c r="F151" s="11" t="s">
+      <c r="F151" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="G151" s="11">
+      <c r="G151" s="7">
         <v>0.18899999999999997</v>
       </c>
-      <c r="H151" s="12">
+      <c r="H151" s="8">
         <v>116500000</v>
       </c>
-      <c r="I151" s="13">
-        <v>22022321.06</v>
-      </c>
-      <c r="J151" s="12">
-        <v>94477678.94</v>
-      </c>
-      <c r="K151" s="14">
+      <c r="I151" s="9">
+        <v>22022321.059999999</v>
+      </c>
+      <c r="J151" s="8">
+        <v>94477678.939999998</v>
+      </c>
+      <c r="K151" s="10">
         <v>45897</v>
       </c>
-      <c r="L151" s="14">
+      <c r="L151" s="10">
         <v>46107</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A152" s="11" t="s">
+      <c r="A152" s="7" t="s">
         <v>572</v>
       </c>
-      <c r="B152" s="11" t="s">
+      <c r="B152" s="7" t="s">
         <v>573</v>
       </c>
-      <c r="C152" s="11" t="s">
+      <c r="C152" s="7" t="s">
         <v>574</v>
       </c>
-      <c r="D152" s="11" t="s">
+      <c r="D152" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E152" s="11" t="s">
+      <c r="E152" s="7" t="s">
         <v>575</v>
       </c>
-      <c r="F152" s="11" t="s">
+      <c r="F152" s="7" t="s">
         <v>576</v>
       </c>
-      <c r="G152" s="11">
+      <c r="G152" s="7">
         <v>1</v>
       </c>
-      <c r="H152" s="12">
+      <c r="H152" s="8">
         <v>10061005.41</v>
       </c>
-      <c r="I152" s="13">
-        <v>10061005.39</v>
-      </c>
-      <c r="J152" s="12">
-        <v>0.019999999552965164</v>
-      </c>
-      <c r="K152" s="14">
+      <c r="I152" s="9">
+        <v>10061005.390000001</v>
+      </c>
+      <c r="J152" s="8">
+        <v>1.9999999552965164E-2</v>
+      </c>
+      <c r="K152" s="10">
         <v>45261</v>
       </c>
-      <c r="L152" s="14">
+      <c r="L152" s="10">
         <v>45833</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A153" s="11" t="s">
+      <c r="A153" s="7" t="s">
         <v>577</v>
       </c>
-      <c r="B153" s="11" t="s">
+      <c r="B153" s="7" t="s">
         <v>578</v>
       </c>
-      <c r="C153" s="11" t="s">
+      <c r="C153" s="7" t="s">
         <v>579</v>
       </c>
-      <c r="D153" s="11" t="s">
+      <c r="D153" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E153" s="11" t="s">
+      <c r="E153" s="7" t="s">
         <v>580</v>
       </c>
-      <c r="F153" s="11" t="s">
+      <c r="F153" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G153" s="11">
+      <c r="G153" s="7">
         <v>1</v>
       </c>
-      <c r="H153" s="12">
-        <v>81950979.23</v>
-      </c>
-      <c r="I153" s="13">
+      <c r="H153" s="8">
+        <v>81950979.230000004</v>
+      </c>
+      <c r="I153" s="9">
         <v>81950979</v>
       </c>
-      <c r="J153" s="12">
+      <c r="J153" s="8">
         <v>0.23000000417232513</v>
       </c>
-      <c r="K153" s="14">
+      <c r="K153" s="10">
         <v>44792</v>
       </c>
-      <c r="L153" s="14">
+      <c r="L153" s="10">
         <v>46022</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A154" s="11" t="s">
+      <c r="A154" s="7" t="s">
         <v>577</v>
       </c>
-      <c r="B154" s="11" t="s">
+      <c r="B154" s="7" t="s">
         <v>581</v>
       </c>
-      <c r="C154" s="11" t="s">
+      <c r="C154" s="7" t="s">
         <v>582</v>
       </c>
-      <c r="D154" s="11" t="s">
+      <c r="D154" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E154" s="11" t="s">
+      <c r="E154" s="7" t="s">
         <v>583</v>
       </c>
-      <c r="F154" s="11" t="s">
+      <c r="F154" s="7" t="s">
         <v>584</v>
       </c>
-      <c r="G154" s="11">
+      <c r="G154" s="7">
         <v>0</v>
       </c>
-      <c r="H154" s="12">
-        <v>41522873.42</v>
-      </c>
-      <c r="I154" s="13">
+      <c r="H154" s="8">
+        <v>41522873.420000002</v>
+      </c>
+      <c r="I154" s="9">
         <v>0</v>
       </c>
-      <c r="J154" s="12">
-        <v>41522873.42</v>
-      </c>
-      <c r="K154" s="14">
+      <c r="J154" s="8">
+        <v>41522873.420000002</v>
+      </c>
+      <c r="K154" s="10">
         <v>45901</v>
       </c>
-      <c r="L154" s="14">
+      <c r="L154" s="10">
         <v>46801</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A155" s="11" t="s">
+      <c r="A155" s="7" t="s">
         <v>585</v>
       </c>
-      <c r="B155" s="11" t="s">
+      <c r="B155" s="7" t="s">
         <v>586</v>
       </c>
-      <c r="C155" s="11" t="s">
+      <c r="C155" s="7" t="s">
         <v>587</v>
       </c>
-      <c r="D155" s="11" t="s">
+      <c r="D155" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E155" s="11" t="s">
+      <c r="E155" s="7" t="s">
         <v>588</v>
       </c>
-      <c r="F155" s="11" t="s">
+      <c r="F155" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="G155" s="11">
+      <c r="G155" s="7">
         <v>0.9728</v>
       </c>
-      <c r="H155" s="12">
+      <c r="H155" s="8">
         <v>4444784.22</v>
       </c>
-      <c r="I155" s="13">
-        <v>4324004.81</v>
-      </c>
-      <c r="J155" s="12">
+      <c r="I155" s="9">
+        <v>4324004.8099999996</v>
+      </c>
+      <c r="J155" s="8">
         <v>120779.41000000015</v>
       </c>
-      <c r="K155" s="14">
+      <c r="K155" s="10">
         <v>45155</v>
       </c>
-      <c r="L155" s="14">
+      <c r="L155" s="10">
         <v>45576</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A156" s="11" t="s">
+      <c r="A156" s="7" t="s">
         <v>589</v>
       </c>
-      <c r="B156" s="11" t="s">
+      <c r="B156" s="7" t="s">
         <v>590</v>
       </c>
-      <c r="C156" s="11" t="s">
+      <c r="C156" s="7" t="s">
         <v>591</v>
       </c>
-      <c r="D156" s="11" t="s">
+      <c r="D156" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E156" s="11" t="s">
+      <c r="E156" s="7" t="s">
         <v>592</v>
       </c>
-      <c r="F156" s="11" t="s">
+      <c r="F156" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="G156" s="11">
+      <c r="G156" s="7">
         <v>0</v>
       </c>
-      <c r="H156" s="12">
-        <v>8995898.05</v>
-      </c>
-      <c r="I156" s="13">
+      <c r="H156" s="8">
+        <v>8995898.0500000007</v>
+      </c>
+      <c r="I156" s="9">
         <v>266299.23</v>
       </c>
-      <c r="J156" s="12">
-        <v>8729598.82</v>
-      </c>
-      <c r="K156" s="14">
+      <c r="J156" s="8">
+        <v>8729598.8200000003</v>
+      </c>
+      <c r="K156" s="10">
         <v>44816</v>
       </c>
-      <c r="L156" s="14">
+      <c r="L156" s="10">
         <v>44996</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A157" s="11" t="s">
+      <c r="A157" s="7" t="s">
         <v>593</v>
       </c>
-      <c r="B157" s="11" t="s">
+      <c r="B157" s="7" t="s">
         <v>594</v>
       </c>
-      <c r="C157" s="11" t="s">
+      <c r="C157" s="7" t="s">
         <v>595</v>
       </c>
-      <c r="D157" s="11" t="s">
+      <c r="D157" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E157" s="11" t="s">
+      <c r="E157" s="7" t="s">
         <v>596</v>
       </c>
-      <c r="F157" s="11" t="s">
+      <c r="F157" s="7" t="s">
         <v>576</v>
       </c>
-      <c r="G157" s="11">
-        <v>0.3153</v>
-      </c>
-      <c r="H157" s="12">
+      <c r="G157" s="7">
+        <v>0.31530000000000002</v>
+      </c>
+      <c r="H157" s="8">
         <v>3294597.99</v>
       </c>
-      <c r="I157" s="13">
+      <c r="I157" s="9">
         <v>1038880.21</v>
       </c>
-      <c r="J157" s="12">
+      <c r="J157" s="8">
         <v>2255717.7800000003</v>
       </c>
-      <c r="K157" s="14">
+      <c r="K157" s="10">
         <v>45278</v>
       </c>
-      <c r="L157" s="14">
+      <c r="L157" s="10">
         <v>46122</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A158" s="11" t="s">
+      <c r="A158" s="7" t="s">
         <v>597</v>
       </c>
-      <c r="B158" s="11" t="s">
+      <c r="B158" s="7" t="s">
         <v>598</v>
       </c>
-      <c r="C158" s="11" t="s">
+      <c r="C158" s="7" t="s">
         <v>599</v>
       </c>
-      <c r="D158" s="11" t="s">
+      <c r="D158" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E158" s="11" t="s">
+      <c r="E158" s="7" t="s">
         <v>600</v>
       </c>
-      <c r="F158" s="11" t="s">
+      <c r="F158" s="7" t="s">
         <v>500</v>
       </c>
-      <c r="G158" s="11">
-        <v>0.9922</v>
-      </c>
-      <c r="H158" s="12">
-        <v>6055289.34</v>
-      </c>
-      <c r="I158" s="13">
-        <v>6007931.02</v>
-      </c>
-      <c r="J158" s="12">
-        <v>47358.3200000003</v>
-      </c>
-      <c r="K158" s="14">
+      <c r="G158" s="7">
+        <v>0.99219999999999997</v>
+      </c>
+      <c r="H158" s="8">
+        <v>6055289.3399999999</v>
+      </c>
+      <c r="I158" s="9">
+        <v>6007931.0199999996</v>
+      </c>
+      <c r="J158" s="8">
+        <v>47358.320000000298</v>
+      </c>
+      <c r="K158" s="10">
         <v>44715</v>
       </c>
-      <c r="L158" s="14">
+      <c r="L158" s="10">
         <v>45075</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A159" s="11" t="s">
+      <c r="A159" s="7" t="s">
         <v>597</v>
       </c>
-      <c r="B159" s="11" t="s">
+      <c r="B159" s="7" t="s">
         <v>601</v>
       </c>
-      <c r="C159" s="11" t="s">
+      <c r="C159" s="7" t="s">
         <v>602</v>
       </c>
-      <c r="D159" s="11" t="s">
+      <c r="D159" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E159" s="11" t="s">
+      <c r="E159" s="7" t="s">
         <v>603</v>
       </c>
-      <c r="F159" s="11" t="s">
+      <c r="F159" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G159" s="11">
+      <c r="G159" s="7">
         <v>0.22760000000000002</v>
       </c>
-      <c r="H159" s="12">
-        <v>8973983.87</v>
-      </c>
-      <c r="I159" s="13">
+      <c r="H159" s="8">
+        <v>8973983.8699999992</v>
+      </c>
+      <c r="I159" s="9">
         <v>2042159.29</v>
       </c>
-      <c r="J159" s="12">
-        <v>6931824.579999999</v>
-      </c>
-      <c r="K159" s="14">
+      <c r="J159" s="8">
+        <v>6931824.5799999991</v>
+      </c>
+      <c r="K159" s="10">
         <v>44707</v>
       </c>
-      <c r="L159" s="14">
+      <c r="L159" s="10">
         <v>45280</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A160" s="11" t="s">
+      <c r="A160" s="7" t="s">
         <v>604</v>
       </c>
-      <c r="B160" s="11" t="s">
+      <c r="B160" s="7" t="s">
         <v>605</v>
       </c>
-      <c r="C160" s="11" t="s">
+      <c r="C160" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="D160" s="11" t="s">
+      <c r="D160" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E160" s="11" t="s">
+      <c r="E160" s="7" t="s">
         <v>606</v>
       </c>
-      <c r="F160" s="11" t="s">
+      <c r="F160" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="G160" s="11">
+      <c r="G160" s="7">
         <v>1</v>
       </c>
-      <c r="H160" s="12">
-        <v>13792679.79</v>
-      </c>
-      <c r="I160" s="13">
-        <v>13792679.79</v>
-      </c>
-      <c r="J160" s="12">
+      <c r="H160" s="8">
+        <v>13792679.789999999</v>
+      </c>
+      <c r="I160" s="9">
+        <v>13792679.789999999</v>
+      </c>
+      <c r="J160" s="8">
         <v>0</v>
       </c>
-      <c r="K160" s="14">
+      <c r="K160" s="10">
         <v>44767</v>
       </c>
-      <c r="L160" s="14">
+      <c r="L160" s="10">
         <v>45411</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A161" s="11" t="s">
+      <c r="A161" s="7" t="s">
         <v>604</v>
       </c>
-      <c r="B161" s="11" t="s">
+      <c r="B161" s="7" t="s">
         <v>607</v>
       </c>
-      <c r="C161" s="11" t="s">
+      <c r="C161" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="D161" s="11" t="s">
+      <c r="D161" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E161" s="11" t="s">
+      <c r="E161" s="7" t="s">
         <v>608</v>
       </c>
-      <c r="F161" s="11" t="s">
+      <c r="F161" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="G161" s="11">
-        <v>0.9122</v>
-      </c>
-      <c r="H161" s="12">
+      <c r="G161" s="7">
+        <v>0.91220000000000001</v>
+      </c>
+      <c r="H161" s="8">
         <v>22472818</v>
       </c>
-      <c r="I161" s="13">
+      <c r="I161" s="9">
         <v>20500685.68</v>
       </c>
-      <c r="J161" s="12">
+      <c r="J161" s="8">
         <v>1972132.3200000003</v>
       </c>
-      <c r="K161" s="14">
+      <c r="K161" s="10">
         <v>44827</v>
       </c>
-      <c r="L161" s="14">
+      <c r="L161" s="10">
         <v>45460</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A162" s="11" t="s">
+      <c r="A162" s="7" t="s">
         <v>604</v>
       </c>
-      <c r="B162" s="11" t="s">
+      <c r="B162" s="7" t="s">
         <v>609</v>
       </c>
-      <c r="C162" s="11" t="s">
+      <c r="C162" s="7" t="s">
         <v>610</v>
       </c>
-      <c r="D162" s="11" t="s">
+      <c r="D162" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E162" s="11" t="s">
+      <c r="E162" s="7" t="s">
         <v>611</v>
       </c>
-      <c r="F162" s="11" t="s">
+      <c r="F162" s="7" t="s">
         <v>612</v>
       </c>
-      <c r="G162" s="11">
-        <v>0.8996</v>
-      </c>
-      <c r="H162" s="12">
-        <v>51414775.09</v>
-      </c>
-      <c r="I162" s="13">
-        <v>46254135.59</v>
-      </c>
-      <c r="J162" s="12">
+      <c r="G162" s="7">
+        <v>0.89959999999999996</v>
+      </c>
+      <c r="H162" s="8">
+        <v>51414775.090000004</v>
+      </c>
+      <c r="I162" s="9">
+        <v>46254135.590000004</v>
+      </c>
+      <c r="J162" s="8">
         <v>5160639.5</v>
       </c>
-      <c r="K162" s="14">
+      <c r="K162" s="10">
         <v>45566</v>
       </c>
-      <c r="L162" s="14">
+      <c r="L162" s="10">
         <v>46106</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A163" s="11" t="s">
+      <c r="A163" s="7" t="s">
         <v>613</v>
       </c>
-      <c r="B163" s="11" t="s">
+      <c r="B163" s="7" t="s">
         <v>614</v>
       </c>
-      <c r="C163" s="11" t="s">
+      <c r="C163" s="7" t="s">
         <v>615</v>
       </c>
-      <c r="D163" s="11" t="s">
+      <c r="D163" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E163" s="11" t="s">
+      <c r="E163" s="7" t="s">
         <v>616</v>
       </c>
-      <c r="F163" s="11" t="s">
+      <c r="F163" s="7" t="s">
         <v>617</v>
       </c>
-      <c r="G163" s="11">
+      <c r="G163" s="7">
         <v>0</v>
       </c>
-      <c r="H163" s="12">
+      <c r="H163" s="8">
         <v>1302281.25</v>
       </c>
-      <c r="I163" s="13">
+      <c r="I163" s="9">
         <v>0</v>
       </c>
-      <c r="J163" s="12">
+      <c r="J163" s="8">
         <v>1302281.25</v>
       </c>
-      <c r="K163" s="14">
+      <c r="K163" s="10">
         <v>46810</v>
       </c>
-      <c r="L163" s="14">
+      <c r="L163" s="10">
         <v>46440</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A164" s="11" t="s">
+      <c r="A164" s="7" t="s">
         <v>618</v>
       </c>
-      <c r="B164" s="11" t="s">
+      <c r="B164" s="7" t="s">
         <v>619</v>
       </c>
-      <c r="C164" s="11" t="s">
+      <c r="C164" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="D164" s="11" t="s">
+      <c r="D164" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E164" s="11" t="s">
+      <c r="E164" s="7" t="s">
         <v>620</v>
       </c>
-      <c r="F164" s="11" t="s">
+      <c r="F164" s="7" t="s">
         <v>621</v>
       </c>
-      <c r="G164" s="11">
+      <c r="G164" s="7">
         <v>1</v>
       </c>
-      <c r="H164" s="12">
-        <v>18264452.89</v>
-      </c>
-      <c r="I164" s="13">
-        <v>18264452.89</v>
-      </c>
-      <c r="J164" s="12">
+      <c r="H164" s="8">
+        <v>18264452.890000001</v>
+      </c>
+      <c r="I164" s="9">
+        <v>18264452.890000001</v>
+      </c>
+      <c r="J164" s="8">
         <v>0</v>
       </c>
-      <c r="K164" s="14">
+      <c r="K164" s="10">
         <v>44722</v>
       </c>
-      <c r="L164" s="14">
+      <c r="L164" s="10">
         <v>45723</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A165" s="11" t="s">
+      <c r="A165" s="7" t="s">
         <v>618</v>
       </c>
-      <c r="B165" s="11" t="s">
+      <c r="B165" s="7" t="s">
         <v>622</v>
       </c>
-      <c r="C165" s="11" t="s">
+      <c r="C165" s="7" t="s">
         <v>623</v>
       </c>
-      <c r="D165" s="11" t="s">
+      <c r="D165" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E165" s="11" t="s">
+      <c r="E165" s="7" t="s">
         <v>624</v>
       </c>
-      <c r="F165" s="11" t="s">
+      <c r="F165" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="G165" s="11">
-        <v>0.9953</v>
-      </c>
-      <c r="H165" s="12">
-        <v>30599999.01</v>
-      </c>
-      <c r="I165" s="13">
-        <v>30456294.33</v>
-      </c>
-      <c r="J165" s="12">
+      <c r="G165" s="7">
+        <v>0.99529999999999996</v>
+      </c>
+      <c r="H165" s="8">
+        <v>30599999.010000002</v>
+      </c>
+      <c r="I165" s="9">
+        <v>30456294.329999998</v>
+      </c>
+      <c r="J165" s="8">
         <v>143704.68000000343</v>
       </c>
-      <c r="K165" s="14">
+      <c r="K165" s="10">
         <v>45019</v>
       </c>
-      <c r="L165" s="14">
+      <c r="L165" s="10">
         <v>45743</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A166" s="11" t="s">
+      <c r="A166" s="7" t="s">
         <v>618</v>
       </c>
-      <c r="B166" s="11" t="s">
+      <c r="B166" s="7" t="s">
         <v>625</v>
       </c>
-      <c r="C166" s="11" t="s">
+      <c r="C166" s="7" t="s">
         <v>626</v>
       </c>
-      <c r="D166" s="11" t="s">
+      <c r="D166" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E166" s="11" t="s">
+      <c r="E166" s="7" t="s">
         <v>627</v>
       </c>
-      <c r="F166" s="11" t="s">
+      <c r="F166" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="G166" s="11">
-        <v>0.9601000000000001</v>
-      </c>
-      <c r="H166" s="12">
-        <v>43796954.98</v>
-      </c>
-      <c r="I166" s="13">
-        <v>42048979.52</v>
-      </c>
-      <c r="J166" s="12">
+      <c r="G166" s="7">
+        <v>0.96010000000000006</v>
+      </c>
+      <c r="H166" s="8">
+        <v>43796954.979999997</v>
+      </c>
+      <c r="I166" s="9">
+        <v>42048979.520000003</v>
+      </c>
+      <c r="J166" s="8">
         <v>1747975.4599999934</v>
       </c>
-      <c r="K166" s="14">
+      <c r="K166" s="10">
         <v>44641</v>
       </c>
-      <c r="L166" s="14">
+      <c r="L166" s="10">
         <v>46091</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A167" s="11" t="s">
+      <c r="A167" s="7" t="s">
         <v>618</v>
       </c>
-      <c r="B167" s="11" t="s">
+      <c r="B167" s="7" t="s">
         <v>628</v>
       </c>
-      <c r="C167" s="11" t="s">
+      <c r="C167" s="7" t="s">
         <v>629</v>
       </c>
-      <c r="D167" s="11" t="s">
+      <c r="D167" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E167" s="11" t="s">
+      <c r="E167" s="7" t="s">
         <v>630</v>
       </c>
-      <c r="F167" s="11" t="s">
+      <c r="F167" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="G167" s="11">
-        <v>0.7956</v>
-      </c>
-      <c r="H167" s="12">
+      <c r="G167" s="7">
+        <v>0.79559999999999997</v>
+      </c>
+      <c r="H167" s="8">
         <v>45726170.25</v>
       </c>
-      <c r="I167" s="13">
-        <v>36377601.26</v>
-      </c>
-      <c r="J167" s="12">
-        <v>9348568.990000002</v>
-      </c>
-      <c r="K167" s="14">
+      <c r="I167" s="9">
+        <v>36377601.259999998</v>
+      </c>
+      <c r="J167" s="8">
+        <v>9348568.9900000021</v>
+      </c>
+      <c r="K167" s="10">
         <v>44623</v>
       </c>
-      <c r="L167" s="14">
+      <c r="L167" s="10">
         <v>46222</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A168" s="11" t="s">
+      <c r="A168" s="7" t="s">
         <v>618</v>
       </c>
-      <c r="B168" s="11" t="s">
+      <c r="B168" s="7" t="s">
         <v>631</v>
       </c>
-      <c r="C168" s="11" t="s">
+      <c r="C168" s="7" t="s">
         <v>632</v>
       </c>
-      <c r="D168" s="11" t="s">
+      <c r="D168" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E168" s="11" t="s">
+      <c r="E168" s="7" t="s">
         <v>633</v>
       </c>
-      <c r="F168" s="11" t="s">
+      <c r="F168" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="G168" s="11">
+      <c r="G168" s="7">
         <v>0.30670000000000003</v>
       </c>
-      <c r="H168" s="12">
-        <v>65678550.13</v>
-      </c>
-      <c r="I168" s="13">
-        <v>20145177.51</v>
-      </c>
-      <c r="J168" s="12">
+      <c r="H168" s="8">
+        <v>65678550.130000003</v>
+      </c>
+      <c r="I168" s="9">
+        <v>20145177.510000002</v>
+      </c>
+      <c r="J168" s="8">
         <v>45533372.620000005</v>
       </c>
-      <c r="K168" s="14">
+      <c r="K168" s="10">
         <v>44623</v>
       </c>
-      <c r="L168" s="14">
+      <c r="L168" s="10">
         <v>46170</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:L168" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/ANALITICA.xlsx
+++ b/ANALITICA.xlsx
@@ -1,18 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D6FBC53-382A-4ACC-ABC9-CE7744161055}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="MyWorkSheet-1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="MyWorkSheet-1" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MyWorkSheet-1'!$A$1:$L$168</definedName>
-  </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
@@ -1926,24 +1919,22 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="\R\$#,##0.00;\-\R\$#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="dd\-mm\-yyyy"/>
+    <numFmt numFmtId="164" formatCode="R$#,##0.00;-R$#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="DD-MM-YYYY"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <color rgb="FF404040"/>
       <sz val="13"/>
-      <color rgb="FF404040"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -2004,60 +1995,57 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="165" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{E8B2EFBD-0C0E-4A81-AE34-F75C53EDCEE5}"/>
-  </tableStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2390,6410 +2378,6408 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L168"/>
-  <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="30.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.28515625" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="255.7109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="180.28515625" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.28515625" style="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.42578125" style="14" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20" style="15" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.5703125" style="14" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.140625" style="16" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13" style="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="11"/>
+    <col min="1" max="1" width="16.46153846153846" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.571428571428573" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.153846153846153" style="1" customWidth="1"/>
+    <col min="5" max="5" width="36.15384615384615" style="1" customWidth="1"/>
+    <col min="6" max="6" width="33.07692307692308" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.76923076923077" style="1" customWidth="1"/>
+    <col min="8" max="8" width="21.23076923076923" style="2" customWidth="1"/>
+    <col min="9" max="9" width="20.76923076923077" style="3" customWidth="1"/>
+    <col min="10" max="10" width="19.846153846153847" style="2" customWidth="1"/>
+    <col min="11" max="11" width="18.92857142857143" style="4" customWidth="1"/>
+    <col min="12" max="12" width="15.214285714285715" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="7">
-        <v>0.89159999999999995</v>
-      </c>
-      <c r="H2" s="8">
+      <c r="G2" s="11">
+        <v>0.8916</v>
+      </c>
+      <c r="H2" s="12">
         <v>14782911.98</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="13">
         <v>13180256.4</v>
       </c>
-      <c r="J2" s="8">
+      <c r="J2" s="12">
         <v>1602655.58</v>
       </c>
-      <c r="K2" s="10">
+      <c r="K2" s="14">
         <v>44917</v>
       </c>
-      <c r="L2" s="10">
+      <c r="L2" s="14">
         <v>45513</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="11">
         <v>0</v>
       </c>
-      <c r="H3" s="8">
+      <c r="H3" s="12">
         <v>10134014.66</v>
       </c>
-      <c r="I3" s="9">
+      <c r="I3" s="13">
         <v>0</v>
       </c>
-      <c r="J3" s="8">
+      <c r="J3" s="12">
         <v>10134014.66</v>
       </c>
-      <c r="K3" s="10">
+      <c r="K3" s="14">
         <v>45365</v>
       </c>
-      <c r="L3" s="10">
+      <c r="L3" s="14">
         <v>45476</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="11">
         <v>0.6744</v>
       </c>
-      <c r="H4" s="8">
-        <v>37535912.649999999</v>
-      </c>
-      <c r="I4" s="9">
-        <v>25313733.219999999</v>
-      </c>
-      <c r="J4" s="8">
+      <c r="H4" s="12">
+        <v>37535912.65</v>
+      </c>
+      <c r="I4" s="13">
+        <v>25313733.22</v>
+      </c>
+      <c r="J4" s="12">
         <v>12222179.43</v>
       </c>
-      <c r="K4" s="10">
+      <c r="K4" s="14">
         <v>44807</v>
       </c>
-      <c r="L4" s="10">
+      <c r="L4" s="14">
         <v>45208</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="11">
         <v>1</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="12">
         <v>4928388.09</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="13">
         <v>4928388.26</v>
       </c>
-      <c r="J5" s="8">
-        <v>-0.16999999992549419</v>
-      </c>
-      <c r="K5" s="10">
+      <c r="J5" s="12">
+        <v>-0.1699999999254942</v>
+      </c>
+      <c r="K5" s="14">
         <v>45478</v>
       </c>
-      <c r="L5" s="10">
+      <c r="L5" s="14">
         <v>45327</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="G6" s="7">
-        <v>0.20039999999999999</v>
-      </c>
-      <c r="H6" s="8">
-        <v>18990162.940000001</v>
-      </c>
-      <c r="I6" s="9">
+      <c r="G6" s="11">
+        <v>0.2004</v>
+      </c>
+      <c r="H6" s="12">
+        <v>18990162.94</v>
+      </c>
+      <c r="I6" s="13">
         <v>3806174.66</v>
       </c>
-      <c r="J6" s="8">
+      <c r="J6" s="12">
         <v>15183988.280000001</v>
       </c>
-      <c r="K6" s="10">
+      <c r="K6" s="14">
         <v>45868</v>
       </c>
-      <c r="L6" s="10">
+      <c r="L6" s="14">
         <v>46228</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G7" s="7">
-        <v>7.6E-3</v>
-      </c>
-      <c r="H7" s="8">
-        <v>16774604.060000001</v>
-      </c>
-      <c r="I7" s="9">
+      <c r="G7" s="11">
+        <v>0.0076</v>
+      </c>
+      <c r="H7" s="12">
+        <v>16774604.06</v>
+      </c>
+      <c r="I7" s="13">
         <v>127835.64</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J7" s="12">
         <v>16646768.42</v>
       </c>
-      <c r="K7" s="10">
+      <c r="K7" s="14">
         <v>45100</v>
       </c>
-      <c r="L7" s="10">
+      <c r="L7" s="14">
         <v>45460</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="11">
         <v>1</v>
       </c>
-      <c r="H8" s="8">
-        <v>5581731.2999999998</v>
-      </c>
-      <c r="I8" s="9">
-        <v>5581730.2999999998</v>
-      </c>
-      <c r="J8" s="8">
+      <c r="H8" s="12">
+        <v>5581731.3</v>
+      </c>
+      <c r="I8" s="13">
+        <v>5581730.3</v>
+      </c>
+      <c r="J8" s="12">
         <v>1</v>
       </c>
-      <c r="K8" s="10">
+      <c r="K8" s="14">
         <v>44777</v>
       </c>
-      <c r="L8" s="10">
+      <c r="L8" s="14">
         <v>45348</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="G9" s="7">
-        <v>0.99019999999999997</v>
-      </c>
-      <c r="H9" s="8">
+      <c r="G9" s="11">
+        <v>0.9902</v>
+      </c>
+      <c r="H9" s="12">
         <v>5312585.57</v>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="13">
         <v>5260332.26</v>
       </c>
-      <c r="J9" s="8">
-        <v>52253.310000000522</v>
-      </c>
-      <c r="K9" s="10">
+      <c r="J9" s="12">
+        <v>52253.31000000052</v>
+      </c>
+      <c r="K9" s="14">
         <v>44536</v>
       </c>
-      <c r="L9" s="10">
+      <c r="L9" s="14">
         <v>45289</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="G10" s="7">
-        <v>0.97129999999999994</v>
-      </c>
-      <c r="H10" s="8">
+      <c r="G10" s="11">
+        <v>0.9712999999999999</v>
+      </c>
+      <c r="H10" s="12">
         <v>7795660.46</v>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="13">
         <v>7571952.29</v>
       </c>
-      <c r="J10" s="8">
+      <c r="J10" s="12">
         <v>223708.16999999993</v>
       </c>
-      <c r="K10" s="10">
+      <c r="K10" s="14">
         <v>44909</v>
       </c>
-      <c r="L10" s="10">
+      <c r="L10" s="14">
         <v>46144</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="G11" s="7">
-        <v>0.89159999999999995</v>
-      </c>
-      <c r="H11" s="8">
-        <v>7234583.7699999996</v>
-      </c>
-      <c r="I11" s="9">
-        <v>6450491.3099999996</v>
-      </c>
-      <c r="J11" s="8">
+      <c r="G11" s="11">
+        <v>0.8916</v>
+      </c>
+      <c r="H11" s="12">
+        <v>7234583.77</v>
+      </c>
+      <c r="I11" s="13">
+        <v>6450491.31</v>
+      </c>
+      <c r="J11" s="12">
         <v>784092.46</v>
       </c>
-      <c r="K11" s="10">
+      <c r="K11" s="14">
         <v>45425</v>
       </c>
-      <c r="L11" s="10">
+      <c r="L11" s="14">
         <v>45999</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="11">
         <v>0.8456999999999999</v>
       </c>
-      <c r="H12" s="8">
-        <v>36782151.810000002</v>
-      </c>
-      <c r="I12" s="9">
+      <c r="H12" s="12">
+        <v>36782151.81</v>
+      </c>
+      <c r="I12" s="13">
         <v>31106158.75</v>
       </c>
-      <c r="J12" s="8">
-        <v>5675993.0600000024</v>
-      </c>
-      <c r="K12" s="10">
+      <c r="J12" s="12">
+        <v>5675993.060000002</v>
+      </c>
+      <c r="K12" s="14">
         <v>45566</v>
       </c>
-      <c r="L12" s="10">
+      <c r="L12" s="14">
         <v>46228</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="G13" s="7">
-        <v>0.40670000000000001</v>
-      </c>
-      <c r="H13" s="8">
+      <c r="G13" s="11">
+        <v>0.4067</v>
+      </c>
+      <c r="H13" s="12">
         <v>11928823.02</v>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="13">
         <v>4852042.8</v>
       </c>
-      <c r="J13" s="8">
-        <v>7076780.2199999997</v>
-      </c>
-      <c r="K13" s="10">
+      <c r="J13" s="12">
+        <v>7076780.22</v>
+      </c>
+      <c r="K13" s="14">
         <v>44903</v>
       </c>
-      <c r="L13" s="10">
+      <c r="L13" s="14">
         <v>45239</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="11">
         <v>0.5746</v>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="12">
         <v>22825141.32</v>
       </c>
-      <c r="I14" s="9">
-        <v>13115141.810000001</v>
-      </c>
-      <c r="J14" s="8">
-        <v>9709999.5099999998</v>
-      </c>
-      <c r="K14" s="10">
+      <c r="I14" s="13">
+        <v>13115141.81</v>
+      </c>
+      <c r="J14" s="12">
+        <v>9709999.51</v>
+      </c>
+      <c r="K14" s="14">
         <v>45019</v>
       </c>
-      <c r="L14" s="10">
+      <c r="L14" s="14">
         <v>46193</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="G15" s="7">
-        <v>0.99900000000000011</v>
-      </c>
-      <c r="H15" s="8">
-        <v>7155724.3899999997</v>
-      </c>
-      <c r="I15" s="9">
-        <v>7148655.5999999996</v>
-      </c>
-      <c r="J15" s="8">
-        <v>7068.7900000000373</v>
-      </c>
-      <c r="K15" s="10">
+      <c r="G15" s="11">
+        <v>0.9990000000000001</v>
+      </c>
+      <c r="H15" s="12">
+        <v>7155724.39</v>
+      </c>
+      <c r="I15" s="13">
+        <v>7148655.6</v>
+      </c>
+      <c r="J15" s="12">
+        <v>7068.790000000037</v>
+      </c>
+      <c r="K15" s="14">
         <v>45314</v>
       </c>
-      <c r="L15" s="10">
+      <c r="L15" s="14">
         <v>45617</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="G16" s="7">
-        <v>0.88560000000000005</v>
-      </c>
-      <c r="H16" s="8">
+      <c r="G16" s="11">
+        <v>0.8856</v>
+      </c>
+      <c r="H16" s="12">
         <v>6765672.29</v>
       </c>
-      <c r="I16" s="9">
-        <v>5991696.5800000001</v>
-      </c>
-      <c r="J16" s="8">
+      <c r="I16" s="13">
+        <v>5991696.58</v>
+      </c>
+      <c r="J16" s="12">
         <v>773975.71</v>
       </c>
-      <c r="K16" s="10">
+      <c r="K16" s="14">
         <v>45398</v>
       </c>
-      <c r="L16" s="10">
+      <c r="L16" s="14">
         <v>46062</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G17" s="11">
         <v>0</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H17" s="12">
         <v>2742607.66</v>
       </c>
-      <c r="I17" s="9">
+      <c r="I17" s="13">
         <v>0</v>
       </c>
-      <c r="J17" s="8">
+      <c r="J17" s="12">
         <v>2742607.66</v>
       </c>
-      <c r="K17" s="10">
+      <c r="K17" s="14">
         <v>45917</v>
       </c>
-      <c r="L17" s="10">
+      <c r="L17" s="14">
         <v>46097</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="G18" s="7">
-        <v>0.99540000000000006</v>
-      </c>
-      <c r="H18" s="8">
-        <v>32464769.579999998</v>
-      </c>
-      <c r="I18" s="9">
-        <v>32314427.699999999</v>
-      </c>
-      <c r="J18" s="8">
+      <c r="G18" s="11">
+        <v>0.9954000000000001</v>
+      </c>
+      <c r="H18" s="12">
+        <v>32464769.58</v>
+      </c>
+      <c r="I18" s="13">
+        <v>32314427.7</v>
+      </c>
+      <c r="J18" s="12">
         <v>150341.87999999896</v>
       </c>
-      <c r="K18" s="10">
+      <c r="K18" s="14">
         <v>44697</v>
       </c>
-      <c r="L18" s="10">
+      <c r="L18" s="14">
         <v>45972</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G19" s="11">
         <v>0.94</v>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="12">
         <v>44149151.5</v>
       </c>
-      <c r="I19" s="9">
-        <v>41500959.490000002</v>
-      </c>
-      <c r="J19" s="8">
-        <v>2648192.0099999979</v>
-      </c>
-      <c r="K19" s="10">
+      <c r="I19" s="13">
+        <v>41500959.49</v>
+      </c>
+      <c r="J19" s="12">
+        <v>2648192.009999998</v>
+      </c>
+      <c r="K19" s="14">
         <v>44763</v>
       </c>
-      <c r="L19" s="10">
+      <c r="L19" s="14">
         <v>45999</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="G20" s="7">
-        <v>0.77300000000000002</v>
-      </c>
-      <c r="H20" s="8">
+      <c r="G20" s="11">
+        <v>0.773</v>
+      </c>
+      <c r="H20" s="12">
         <v>16880240</v>
       </c>
-      <c r="I20" s="9">
-        <v>13048536.539999999</v>
-      </c>
-      <c r="J20" s="8">
-        <v>3831703.4600000009</v>
-      </c>
-      <c r="K20" s="10">
+      <c r="I20" s="13">
+        <v>13048536.54</v>
+      </c>
+      <c r="J20" s="12">
+        <v>3831703.460000001</v>
+      </c>
+      <c r="K20" s="14">
         <v>45034</v>
       </c>
-      <c r="L20" s="10">
+      <c r="L20" s="14">
         <v>45253</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F21" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="G21" s="7">
-        <v>0.51629999999999998</v>
-      </c>
-      <c r="H21" s="8">
-        <v>31022838.120000001</v>
-      </c>
-      <c r="I21" s="9">
+      <c r="G21" s="11">
+        <v>0.5163</v>
+      </c>
+      <c r="H21" s="12">
+        <v>31022838.12</v>
+      </c>
+      <c r="I21" s="13">
         <v>16018051.23</v>
       </c>
-      <c r="J21" s="8">
-        <v>15004786.890000001</v>
-      </c>
-      <c r="K21" s="10">
+      <c r="J21" s="12">
+        <v>15004786.89</v>
+      </c>
+      <c r="K21" s="14">
         <v>45309</v>
       </c>
-      <c r="L21" s="10">
+      <c r="L21" s="14">
         <v>46392</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="G22" s="7">
-        <v>0.66079999999999994</v>
-      </c>
-      <c r="H22" s="8">
-        <v>48872552.259999998</v>
-      </c>
-      <c r="I22" s="9">
-        <v>32294745.039999999</v>
-      </c>
-      <c r="J22" s="8">
+      <c r="G22" s="11">
+        <v>0.6607999999999999</v>
+      </c>
+      <c r="H22" s="12">
+        <v>48872552.26</v>
+      </c>
+      <c r="I22" s="13">
+        <v>32294745.04</v>
+      </c>
+      <c r="J22" s="12">
         <v>16577807.219999999</v>
       </c>
-      <c r="K22" s="10">
+      <c r="K22" s="14">
         <v>44875</v>
       </c>
-      <c r="L22" s="10">
+      <c r="L22" s="14">
         <v>46375</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="G23" s="7">
-        <v>0.71930000000000005</v>
-      </c>
-      <c r="H23" s="8">
-        <v>89008310.650000006</v>
-      </c>
-      <c r="I23" s="9">
-        <v>64026819.340000004</v>
-      </c>
-      <c r="J23" s="8">
+      <c r="G23" s="11">
+        <v>0.7193</v>
+      </c>
+      <c r="H23" s="12">
+        <v>89008310.65</v>
+      </c>
+      <c r="I23" s="13">
+        <v>64026819.34</v>
+      </c>
+      <c r="J23" s="12">
         <v>24981491.310000002</v>
       </c>
-      <c r="K23" s="10">
+      <c r="K23" s="14">
         <v>44789</v>
       </c>
-      <c r="L23" s="10">
+      <c r="L23" s="14">
         <v>45510</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="G24" s="7">
-        <v>0.43520000000000003</v>
-      </c>
-      <c r="H24" s="8">
-        <v>60543657.329999998</v>
-      </c>
-      <c r="I24" s="9">
-        <v>26345865.469999999</v>
-      </c>
-      <c r="J24" s="8">
-        <v>34197791.859999999</v>
-      </c>
-      <c r="K24" s="10">
+      <c r="G24" s="11">
+        <v>0.44920000000000004</v>
+      </c>
+      <c r="H24" s="12">
+        <v>62211091.02</v>
+      </c>
+      <c r="I24" s="13">
+        <v>27948056.39</v>
+      </c>
+      <c r="J24" s="12">
+        <v>34263034.63</v>
+      </c>
+      <c r="K24" s="14">
         <v>44883</v>
       </c>
-      <c r="L24" s="10">
+      <c r="L24" s="14">
         <v>46144</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="F25" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="G25" s="7">
-        <v>0.99219999999999997</v>
-      </c>
-      <c r="H25" s="8">
+      <c r="G25" s="11">
+        <v>0.9922</v>
+      </c>
+      <c r="H25" s="12">
         <v>5361446.28</v>
       </c>
-      <c r="I25" s="9">
+      <c r="I25" s="13">
         <v>5319761.7</v>
       </c>
-      <c r="J25" s="8">
+      <c r="J25" s="12">
         <v>41684.580000000075</v>
       </c>
-      <c r="K25" s="10">
+      <c r="K25" s="14">
         <v>44637</v>
       </c>
-      <c r="L25" s="10">
+      <c r="L25" s="14">
         <v>45484</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="G26" s="7">
-        <v>0.87860000000000005</v>
-      </c>
-      <c r="H26" s="8">
-        <v>2601911.3199999998</v>
-      </c>
-      <c r="I26" s="9">
+      <c r="G26" s="11">
+        <v>0.8786</v>
+      </c>
+      <c r="H26" s="12">
+        <v>2601911.32</v>
+      </c>
+      <c r="I26" s="13">
         <v>2286080.42</v>
       </c>
-      <c r="J26" s="8">
-        <v>315830.89999999991</v>
-      </c>
-      <c r="K26" s="10">
+      <c r="J26" s="12">
+        <v>315830.8999999999</v>
+      </c>
+      <c r="K26" s="14">
         <v>45624</v>
       </c>
-      <c r="L26" s="10">
+      <c r="L26" s="14">
         <v>46106</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F27" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="G27" s="7">
+      <c r="G27" s="11">
         <v>0.1104</v>
       </c>
-      <c r="H27" s="8">
-        <v>2394811.9500000002</v>
-      </c>
-      <c r="I27" s="9">
-        <v>264324.59999999998</v>
-      </c>
-      <c r="J27" s="8">
+      <c r="H27" s="12">
+        <v>2394811.95</v>
+      </c>
+      <c r="I27" s="13">
+        <v>264324.6</v>
+      </c>
+      <c r="J27" s="12">
         <v>2130487.35</v>
       </c>
-      <c r="K27" s="10">
+      <c r="K27" s="14">
         <v>44840</v>
       </c>
-      <c r="L27" s="10">
+      <c r="L27" s="14">
         <v>45390</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="F28" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="G28" s="7">
+      <c r="G28" s="11">
         <v>0.9998999999999999</v>
       </c>
-      <c r="H28" s="8">
+      <c r="H28" s="12">
         <v>2975474.34</v>
       </c>
-      <c r="I28" s="9">
+      <c r="I28" s="13">
         <v>2975297.32</v>
       </c>
-      <c r="J28" s="8">
+      <c r="J28" s="12">
         <v>177.02000000001863</v>
       </c>
-      <c r="K28" s="10">
+      <c r="K28" s="14">
         <v>44883</v>
       </c>
-      <c r="L28" s="10">
+      <c r="L28" s="14">
         <v>45411</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="F29" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="G29" s="7">
+      <c r="G29" s="11">
         <v>1</v>
       </c>
-      <c r="H29" s="8">
+      <c r="H29" s="12">
         <v>4808707.09</v>
       </c>
-      <c r="I29" s="9">
+      <c r="I29" s="13">
         <v>4808707.09</v>
       </c>
-      <c r="J29" s="8">
+      <c r="J29" s="12">
         <v>0</v>
       </c>
-      <c r="K29" s="10">
+      <c r="K29" s="14">
         <v>44743</v>
       </c>
-      <c r="L29" s="10">
+      <c r="L29" s="14">
         <v>45341</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E30" s="7" t="s">
+      <c r="E30" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F30" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G30" s="7">
-        <v>0.91099999999999992</v>
-      </c>
-      <c r="H30" s="8">
-        <v>13208831.359999999</v>
-      </c>
-      <c r="I30" s="9">
+      <c r="G30" s="11">
+        <v>0.9109999999999999</v>
+      </c>
+      <c r="H30" s="12">
+        <v>13208831.36</v>
+      </c>
+      <c r="I30" s="13">
         <v>12032786.93</v>
       </c>
-      <c r="J30" s="8">
+      <c r="J30" s="12">
         <v>1176044.4299999997</v>
       </c>
-      <c r="K30" s="10">
+      <c r="K30" s="14">
         <v>44708</v>
       </c>
-      <c r="L30" s="10">
+      <c r="L30" s="14">
         <v>45398</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="E31" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="F31" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="G31" s="7">
+      <c r="G31" s="11">
         <v>1</v>
       </c>
-      <c r="H31" s="8">
-        <v>11551184.439999999</v>
-      </c>
-      <c r="I31" s="9">
+      <c r="H31" s="12">
+        <v>11551184.44</v>
+      </c>
+      <c r="I31" s="13">
         <v>11551184.4</v>
       </c>
-      <c r="J31" s="8">
-        <v>3.9999999105930328E-2</v>
-      </c>
-      <c r="K31" s="10">
+      <c r="J31" s="12">
+        <v>0.03999999910593033</v>
+      </c>
+      <c r="K31" s="14">
         <v>44733</v>
       </c>
-      <c r="L31" s="10">
+      <c r="L31" s="14">
         <v>45953</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B32" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D32" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E32" s="7" t="s">
+      <c r="E32" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="F32" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="G32" s="7">
-        <v>0.99080000000000001</v>
-      </c>
-      <c r="H32" s="8">
-        <v>9751616.3699999992</v>
-      </c>
-      <c r="I32" s="9">
-        <v>9661616.3699999992</v>
-      </c>
-      <c r="J32" s="8">
+      <c r="G32" s="11">
+        <v>0.9908</v>
+      </c>
+      <c r="H32" s="12">
+        <v>9751616.37</v>
+      </c>
+      <c r="I32" s="13">
+        <v>9661616.37</v>
+      </c>
+      <c r="J32" s="12">
         <v>90000</v>
       </c>
-      <c r="K32" s="10">
+      <c r="K32" s="14">
         <v>44873</v>
       </c>
-      <c r="L32" s="10">
+      <c r="L32" s="14">
         <v>45485</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="E33" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="F33" s="7" t="s">
+      <c r="F33" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="G33" s="7">
+      <c r="G33" s="11">
         <v>0.5958</v>
       </c>
-      <c r="H33" s="8">
-        <v>6016602.4800000004</v>
-      </c>
-      <c r="I33" s="9">
+      <c r="H33" s="12">
+        <v>6016602.48</v>
+      </c>
+      <c r="I33" s="13">
         <v>3584685.32</v>
       </c>
-      <c r="J33" s="8">
+      <c r="J33" s="12">
         <v>2431917.1600000006</v>
       </c>
-      <c r="K33" s="10">
+      <c r="K33" s="14">
         <v>45133</v>
       </c>
-      <c r="L33" s="10">
+      <c r="L33" s="14">
         <v>46128</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D34" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="E34" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="F34" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="G34" s="7">
-        <v>0.99980000000000002</v>
-      </c>
-      <c r="H34" s="8">
-        <v>8396309.7599999998</v>
-      </c>
-      <c r="I34" s="9">
-        <v>8394769.0199999996</v>
-      </c>
-      <c r="J34" s="8">
+      <c r="G34" s="11">
+        <v>0.9998</v>
+      </c>
+      <c r="H34" s="12">
+        <v>8396309.76</v>
+      </c>
+      <c r="I34" s="13">
+        <v>8394769.02</v>
+      </c>
+      <c r="J34" s="12">
         <v>1540.7400000002235</v>
       </c>
-      <c r="K34" s="10">
+      <c r="K34" s="14">
         <v>44868</v>
       </c>
-      <c r="L34" s="10">
+      <c r="L34" s="14">
         <v>45560</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="D35" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="E35" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="F35" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="G35" s="7">
-        <v>0.98650000000000004</v>
-      </c>
-      <c r="H35" s="8">
-        <v>45237596.810000002</v>
-      </c>
-      <c r="I35" s="9">
-        <v>44626728.200000003</v>
-      </c>
-      <c r="J35" s="8">
+      <c r="G35" s="11">
+        <v>0.9865</v>
+      </c>
+      <c r="H35" s="12">
+        <v>45237596.81</v>
+      </c>
+      <c r="I35" s="13">
+        <v>44626728.2</v>
+      </c>
+      <c r="J35" s="12">
         <v>610868.6099999994</v>
       </c>
-      <c r="K35" s="10">
+      <c r="K35" s="14">
         <v>44769</v>
       </c>
-      <c r="L35" s="10">
+      <c r="L35" s="14">
         <v>45701</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C36" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="D36" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E36" s="7" t="s">
+      <c r="E36" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="F36" s="7" t="s">
+      <c r="F36" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G36" s="7">
+      <c r="G36" s="11">
         <v>0.9899</v>
       </c>
-      <c r="H36" s="8">
-        <v>148784461.49000001</v>
-      </c>
-      <c r="I36" s="9">
+      <c r="H36" s="12">
+        <v>148784461.49</v>
+      </c>
+      <c r="I36" s="13">
         <v>147280622.62</v>
       </c>
-      <c r="J36" s="8">
+      <c r="J36" s="12">
         <v>1503838.8700000048</v>
       </c>
-      <c r="K36" s="10">
+      <c r="K36" s="14">
         <v>45503</v>
       </c>
-      <c r="L36" s="10">
+      <c r="L36" s="14">
         <v>46043</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" s="7" t="s">
+      <c r="A37" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B37" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="D37" s="7" t="s">
+      <c r="D37" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E37" s="7" t="s">
+      <c r="E37" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="F37" s="7" t="s">
+      <c r="F37" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="G37" s="7">
-        <v>0.97809999999999997</v>
-      </c>
-      <c r="H37" s="8">
-        <v>90986818.170000002</v>
-      </c>
-      <c r="I37" s="9">
-        <v>88995375.530000001</v>
-      </c>
-      <c r="J37" s="8">
+      <c r="G37" s="11">
+        <v>0.9781</v>
+      </c>
+      <c r="H37" s="12">
+        <v>90986818.17</v>
+      </c>
+      <c r="I37" s="13">
+        <v>88995375.53</v>
+      </c>
+      <c r="J37" s="12">
         <v>1991442.6400000006</v>
       </c>
-      <c r="K37" s="10">
+      <c r="K37" s="14">
         <v>44986</v>
       </c>
-      <c r="L37" s="10">
+      <c r="L37" s="14">
         <v>45589</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="B38" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="D38" s="7" t="s">
+      <c r="D38" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E38" s="7" t="s">
+      <c r="E38" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="F38" s="7" t="s">
+      <c r="F38" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G38" s="7">
-        <v>0.97860000000000003</v>
-      </c>
-      <c r="H38" s="8">
-        <v>113557951.65000001</v>
-      </c>
-      <c r="I38" s="9">
-        <v>111133195.68000001</v>
-      </c>
-      <c r="J38" s="8">
-        <v>2424755.9699999988</v>
-      </c>
-      <c r="K38" s="10">
+      <c r="G38" s="11">
+        <v>0.9786</v>
+      </c>
+      <c r="H38" s="12">
+        <v>113557951.65</v>
+      </c>
+      <c r="I38" s="13">
+        <v>111133195.68</v>
+      </c>
+      <c r="J38" s="12">
+        <v>2424755.969999999</v>
+      </c>
+      <c r="K38" s="14">
         <v>45498</v>
       </c>
-      <c r="L38" s="10">
+      <c r="L38" s="14">
         <v>46038</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="7" t="s">
+      <c r="A39" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="B39" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C39" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="D39" s="7" t="s">
+      <c r="D39" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E39" s="7" t="s">
+      <c r="E39" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="F39" s="7" t="s">
+      <c r="F39" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G39" s="7">
-        <v>0.93010000000000004</v>
-      </c>
-      <c r="H39" s="8">
-        <v>41651255.979999997</v>
-      </c>
-      <c r="I39" s="9">
-        <v>38738669.020000003</v>
-      </c>
-      <c r="J39" s="8">
+      <c r="G39" s="11">
+        <v>0.9301</v>
+      </c>
+      <c r="H39" s="12">
+        <v>41651255.98</v>
+      </c>
+      <c r="I39" s="13">
+        <v>38738669.02</v>
+      </c>
+      <c r="J39" s="12">
         <v>2912586.9599999934</v>
       </c>
-      <c r="K39" s="10">
+      <c r="K39" s="14">
         <v>45391</v>
       </c>
-      <c r="L39" s="10">
+      <c r="L39" s="14">
         <v>46057</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B40" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="D40" s="7" t="s">
+      <c r="D40" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E40" s="7" t="s">
+      <c r="E40" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="F40" s="7" t="s">
+      <c r="F40" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G40" s="7">
-        <v>0.55259999999999998</v>
-      </c>
-      <c r="H40" s="8">
+      <c r="G40" s="11">
+        <v>0.5526</v>
+      </c>
+      <c r="H40" s="12">
         <v>22759968.59</v>
       </c>
-      <c r="I40" s="9">
+      <c r="I40" s="13">
         <v>12576165.07</v>
       </c>
-      <c r="J40" s="8">
+      <c r="J40" s="12">
         <v>10183803.52</v>
       </c>
-      <c r="K40" s="10">
+      <c r="K40" s="14">
         <v>44511</v>
       </c>
-      <c r="L40" s="10">
+      <c r="L40" s="14">
         <v>44958</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41" s="7" t="s">
+      <c r="A41" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="B41" s="7" t="s">
+      <c r="B41" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C41" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="D41" s="7" t="s">
+      <c r="D41" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E41" s="7" t="s">
+      <c r="E41" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="F41" s="7" t="s">
+      <c r="F41" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G41" s="7">
-        <v>0.54139999999999999</v>
-      </c>
-      <c r="H41" s="8">
+      <c r="G41" s="11">
+        <v>0.5414</v>
+      </c>
+      <c r="H41" s="12">
         <v>26504288.68</v>
       </c>
-      <c r="I41" s="9">
+      <c r="I41" s="13">
         <v>14348711.09</v>
       </c>
-      <c r="J41" s="8">
+      <c r="J41" s="12">
         <v>12155577.59</v>
       </c>
-      <c r="K41" s="10">
+      <c r="K41" s="14">
         <v>45190</v>
       </c>
-      <c r="L41" s="10">
+      <c r="L41" s="14">
         <v>46153</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="7" t="s">
+      <c r="A42" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="B42" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="C42" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="D42" s="7" t="s">
+      <c r="D42" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E42" s="7" t="s">
+      <c r="E42" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="F42" s="7" t="s">
+      <c r="F42" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="G42" s="7">
-        <v>1.0500000000000001E-2</v>
-      </c>
-      <c r="H42" s="8">
+      <c r="G42" s="11">
+        <v>0.0105</v>
+      </c>
+      <c r="H42" s="12">
         <v>12679339.18</v>
       </c>
-      <c r="I42" s="9">
-        <v>133236.57999999999</v>
-      </c>
-      <c r="J42" s="8">
+      <c r="I42" s="13">
+        <v>133236.58</v>
+      </c>
+      <c r="J42" s="12">
         <v>12546102.6</v>
       </c>
-      <c r="K42" s="10">
+      <c r="K42" s="14">
         <v>44753</v>
       </c>
-      <c r="L42" s="10">
+      <c r="L42" s="14">
         <v>44984</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43" s="7" t="s">
+      <c r="A43" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="B43" s="7" t="s">
+      <c r="B43" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C43" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="D43" s="7" t="s">
+      <c r="D43" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E43" s="7" t="s">
+      <c r="E43" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="F43" s="7" t="s">
+      <c r="F43" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="G43" s="7">
-        <v>6.3E-3</v>
-      </c>
-      <c r="H43" s="8">
-        <v>21672861.460000001</v>
-      </c>
-      <c r="I43" s="9">
+      <c r="G43" s="11">
+        <v>0.0063</v>
+      </c>
+      <c r="H43" s="12">
+        <v>21672861.46</v>
+      </c>
+      <c r="I43" s="13">
         <v>137475.09</v>
       </c>
-      <c r="J43" s="8">
-        <v>21535386.370000001</v>
-      </c>
-      <c r="K43" s="10">
+      <c r="J43" s="12">
+        <v>21535386.37</v>
+      </c>
+      <c r="K43" s="14">
         <v>44783</v>
       </c>
-      <c r="L43" s="10">
+      <c r="L43" s="14">
         <v>44998</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44" s="7" t="s">
+      <c r="A44" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="B44" s="7" t="s">
+      <c r="B44" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C44" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="D44" s="7" t="s">
+      <c r="D44" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E44" s="7" t="s">
+      <c r="E44" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="F44" s="7" t="s">
+      <c r="F44" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="G44" s="7">
+      <c r="G44" s="11">
         <v>0.2034</v>
       </c>
-      <c r="H44" s="8">
+      <c r="H44" s="12">
         <v>30334596.91</v>
       </c>
-      <c r="I44" s="9">
-        <v>6171237.7800000003</v>
-      </c>
-      <c r="J44" s="8">
-        <v>24163359.129999999</v>
-      </c>
-      <c r="K44" s="10">
+      <c r="I44" s="13">
+        <v>6171237.78</v>
+      </c>
+      <c r="J44" s="12">
+        <v>24163359.13</v>
+      </c>
+      <c r="K44" s="14">
         <v>44753</v>
       </c>
-      <c r="L44" s="10">
+      <c r="L44" s="14">
         <v>45505</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45" s="7" t="s">
+      <c r="A45" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="B45" s="7" t="s">
+      <c r="B45" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="C45" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="D45" s="7" t="s">
+      <c r="D45" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E45" s="7" t="s">
+      <c r="E45" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="F45" s="7" t="s">
+      <c r="F45" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G45" s="7">
+      <c r="G45" s="11">
         <v>0.38670000000000004</v>
       </c>
-      <c r="H45" s="8">
-        <v>58032411.710000001</v>
-      </c>
-      <c r="I45" s="9">
-        <v>22442987.530000001</v>
-      </c>
-      <c r="J45" s="8">
+      <c r="H45" s="12">
+        <v>58032411.71</v>
+      </c>
+      <c r="I45" s="13">
+        <v>22442987.53</v>
+      </c>
+      <c r="J45" s="12">
         <v>35589424.18</v>
       </c>
-      <c r="K45" s="10">
+      <c r="K45" s="14">
         <v>44753</v>
       </c>
-      <c r="L45" s="10">
+      <c r="L45" s="14">
         <v>46077</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" s="7" t="s">
+      <c r="A46" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="B46" s="7" t="s">
+      <c r="B46" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="C46" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="D46" s="7" t="s">
+      <c r="D46" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E46" s="7" t="s">
+      <c r="E46" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="F46" s="7" t="s">
+      <c r="F46" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="G46" s="7">
+      <c r="G46" s="11">
         <v>0.25579999999999997</v>
       </c>
-      <c r="H46" s="8">
-        <v>51119038.920000002</v>
-      </c>
-      <c r="I46" s="9">
+      <c r="H46" s="12">
+        <v>51119038.92</v>
+      </c>
+      <c r="I46" s="13">
         <v>13076598.15</v>
       </c>
-      <c r="J46" s="8">
-        <v>38042440.770000003</v>
-      </c>
-      <c r="K46" s="10">
+      <c r="J46" s="12">
+        <v>38042440.77</v>
+      </c>
+      <c r="K46" s="14">
         <v>44753</v>
       </c>
-      <c r="L46" s="10">
+      <c r="L46" s="14">
         <v>46209</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="7" t="s">
+      <c r="A47" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="B47" s="7" t="s">
+      <c r="B47" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="C47" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="D47" s="7" t="s">
+      <c r="D47" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E47" s="7" t="s">
+      <c r="E47" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="F47" s="7" t="s">
+      <c r="F47" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="G47" s="7">
+      <c r="G47" s="11">
         <v>0.4456</v>
       </c>
-      <c r="H47" s="8">
+      <c r="H47" s="12">
         <v>69450000</v>
       </c>
-      <c r="I47" s="9">
+      <c r="I47" s="13">
         <v>30949430.48</v>
       </c>
-      <c r="J47" s="8">
+      <c r="J47" s="12">
         <v>38500569.519999996</v>
       </c>
-      <c r="K47" s="10">
+      <c r="K47" s="14">
         <v>44449</v>
       </c>
-      <c r="L47" s="10">
+      <c r="L47" s="14">
         <v>45329</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48" s="7" t="s">
+      <c r="A48" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="B48" s="7" t="s">
+      <c r="B48" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="C48" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="D48" s="7" t="s">
+      <c r="D48" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E48" s="7" t="s">
+      <c r="E48" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="F48" s="7" t="s">
+      <c r="F48" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="G48" s="7">
-        <v>0.44950000000000001</v>
-      </c>
-      <c r="H48" s="8">
-        <v>84484346.709999993</v>
-      </c>
-      <c r="I48" s="9">
-        <v>37978980.670000002</v>
-      </c>
-      <c r="J48" s="8">
-        <v>46505366.039999992</v>
-      </c>
-      <c r="K48" s="10">
+      <c r="G48" s="11">
+        <v>0.4495</v>
+      </c>
+      <c r="H48" s="12">
+        <v>84484346.71</v>
+      </c>
+      <c r="I48" s="13">
+        <v>37978980.67</v>
+      </c>
+      <c r="J48" s="12">
+        <v>46505366.03999999</v>
+      </c>
+      <c r="K48" s="14">
         <v>44449</v>
       </c>
-      <c r="L48" s="10">
+      <c r="L48" s="14">
         <v>45329</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A49" s="7" t="s">
+      <c r="A49" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="B49" s="7" t="s">
+      <c r="B49" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="C49" s="7" t="s">
+      <c r="C49" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="D49" s="7" t="s">
+      <c r="D49" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E49" s="7" t="s">
+      <c r="E49" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="F49" s="7" t="s">
+      <c r="F49" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="G49" s="7">
-        <v>2.8000000000000004E-3</v>
-      </c>
-      <c r="H49" s="8">
-        <v>47996411.380000003</v>
-      </c>
-      <c r="I49" s="9">
-        <v>133579.45000000001</v>
-      </c>
-      <c r="J49" s="8">
+      <c r="G49" s="11">
+        <v>0.0028000000000000004</v>
+      </c>
+      <c r="H49" s="12">
+        <v>47996411.38</v>
+      </c>
+      <c r="I49" s="13">
+        <v>133579.45</v>
+      </c>
+      <c r="J49" s="12">
         <v>47862831.93</v>
       </c>
-      <c r="K49" s="10">
+      <c r="K49" s="14">
         <v>44887</v>
       </c>
-      <c r="L49" s="10">
+      <c r="L49" s="14">
         <v>45187</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50" s="7" t="s">
+      <c r="A50" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="B50" s="7" t="s">
+      <c r="B50" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="C50" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="D50" s="7" t="s">
+      <c r="D50" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E50" s="7" t="s">
+      <c r="E50" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="F50" s="7" t="s">
+      <c r="F50" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="G50" s="7">
-        <v>3.7699999999999997E-2</v>
-      </c>
-      <c r="H50" s="8">
+      <c r="G50" s="11">
+        <v>0.0377</v>
+      </c>
+      <c r="H50" s="12">
         <v>54283415</v>
       </c>
-      <c r="I50" s="9">
+      <c r="I50" s="13">
         <v>2045374.39</v>
       </c>
-      <c r="J50" s="8">
-        <v>52238040.609999999</v>
-      </c>
-      <c r="K50" s="10">
+      <c r="J50" s="12">
+        <v>52238040.61</v>
+      </c>
+      <c r="K50" s="14">
         <v>44753</v>
       </c>
-      <c r="L50" s="10">
+      <c r="L50" s="14">
         <v>46195</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51" s="7" t="s">
+      <c r="A51" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="B51" s="7" t="s">
+      <c r="B51" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="C51" s="7" t="s">
+      <c r="C51" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="D51" s="7" t="s">
+      <c r="D51" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E51" s="7" t="s">
+      <c r="E51" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="F51" s="7" t="s">
+      <c r="F51" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="G51" s="7">
-        <v>0.96439999999999992</v>
-      </c>
-      <c r="H51" s="8">
-        <v>1332580.8600000001</v>
-      </c>
-      <c r="I51" s="9">
-        <v>1285178.3600000001</v>
-      </c>
-      <c r="J51" s="8">
+      <c r="G51" s="11">
+        <v>0.9643999999999999</v>
+      </c>
+      <c r="H51" s="12">
+        <v>1332580.86</v>
+      </c>
+      <c r="I51" s="13">
+        <v>1285178.36</v>
+      </c>
+      <c r="J51" s="12">
         <v>47402.5</v>
       </c>
-      <c r="K51" s="10">
+      <c r="K51" s="14">
         <v>44536</v>
       </c>
-      <c r="L51" s="10">
+      <c r="L51" s="14">
         <v>45230</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A52" s="7" t="s">
+      <c r="A52" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="B52" s="7" t="s">
+      <c r="B52" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="C52" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="D52" s="7" t="s">
+      <c r="D52" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E52" s="7" t="s">
+      <c r="E52" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="F52" s="7" t="s">
+      <c r="F52" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="G52" s="7">
+      <c r="G52" s="11">
         <v>1</v>
       </c>
-      <c r="H52" s="8">
-        <v>8156656.1900000004</v>
-      </c>
-      <c r="I52" s="9">
-        <v>8156656.1299999999</v>
-      </c>
-      <c r="J52" s="8">
-        <v>6.0000000521540642E-2</v>
-      </c>
-      <c r="K52" s="10">
+      <c r="H52" s="12">
+        <v>8156656.19</v>
+      </c>
+      <c r="I52" s="13">
+        <v>8156656.13</v>
+      </c>
+      <c r="J52" s="12">
+        <v>0.06000000052154064</v>
+      </c>
+      <c r="K52" s="14">
         <v>44832</v>
       </c>
-      <c r="L52" s="10">
+      <c r="L52" s="14">
         <v>45378</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A53" s="7" t="s">
+      <c r="A53" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="B53" s="7" t="s">
+      <c r="B53" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="C53" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="D53" s="7" t="s">
+      <c r="D53" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E53" s="7" t="s">
+      <c r="E53" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="F53" s="7" t="s">
+      <c r="F53" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="G53" s="7">
-        <v>0.84209999999999996</v>
-      </c>
-      <c r="H53" s="8">
-        <v>7704834.9100000001</v>
-      </c>
-      <c r="I53" s="9">
-        <v>6488132.9400000004</v>
-      </c>
-      <c r="J53" s="8">
+      <c r="G53" s="11">
+        <v>0.8421</v>
+      </c>
+      <c r="H53" s="12">
+        <v>7704834.91</v>
+      </c>
+      <c r="I53" s="13">
+        <v>6488132.94</v>
+      </c>
+      <c r="J53" s="12">
         <v>1216701.9699999997</v>
       </c>
-      <c r="K53" s="10">
+      <c r="K53" s="14">
         <v>45286</v>
       </c>
-      <c r="L53" s="10">
+      <c r="L53" s="14">
         <v>46098</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A54" s="7" t="s">
+      <c r="A54" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="B54" s="7" t="s">
+      <c r="B54" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="C54" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="D54" s="7" t="s">
+      <c r="D54" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E54" s="7" t="s">
+      <c r="E54" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="F54" s="7" t="s">
+      <c r="F54" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="G54" s="7">
+      <c r="G54" s="11">
         <v>0</v>
       </c>
-      <c r="H54" s="8">
-        <v>11620104.779999999</v>
-      </c>
-      <c r="I54" s="9">
+      <c r="H54" s="12">
+        <v>11620104.78</v>
+      </c>
+      <c r="I54" s="13">
         <v>0</v>
       </c>
-      <c r="J54" s="8">
-        <v>11620104.779999999</v>
-      </c>
-      <c r="K54" s="12" t="s">
+      <c r="J54" s="12">
+        <v>11620104.78</v>
+      </c>
+      <c r="K54" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="L54" s="12" t="s">
+      <c r="L54" s="15" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A55" s="7" t="s">
+      <c r="A55" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="B55" s="7" t="s">
+      <c r="B55" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="C55" s="7" t="s">
+      <c r="C55" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="D55" s="7" t="s">
+      <c r="D55" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E55" s="7" t="s">
+      <c r="E55" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="F55" s="7" t="s">
+      <c r="F55" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="G55" s="7">
-        <v>0.97540000000000004</v>
-      </c>
-      <c r="H55" s="8">
-        <v>56189486.280000001</v>
-      </c>
-      <c r="I55" s="9">
+      <c r="G55" s="11">
+        <v>0.9754</v>
+      </c>
+      <c r="H55" s="12">
+        <v>56189486.28</v>
+      </c>
+      <c r="I55" s="13">
         <v>54809333.5</v>
       </c>
-      <c r="J55" s="8">
+      <c r="J55" s="12">
         <v>1380152.7800000012</v>
       </c>
-      <c r="K55" s="10">
+      <c r="K55" s="14">
         <v>45035</v>
       </c>
-      <c r="L55" s="10">
+      <c r="L55" s="14">
         <v>46360</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A56" s="7" t="s">
+      <c r="A56" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="B56" s="7" t="s">
+      <c r="B56" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="C56" s="7" t="s">
+      <c r="C56" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="D56" s="7" t="s">
+      <c r="D56" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E56" s="7" t="s">
+      <c r="E56" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="F56" s="7" t="s">
+      <c r="F56" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="G56" s="7">
+      <c r="G56" s="11">
         <v>1</v>
       </c>
-      <c r="H56" s="8">
+      <c r="H56" s="12">
         <v>4374443.78</v>
       </c>
-      <c r="I56" s="9">
+      <c r="I56" s="13">
         <v>4374443.78</v>
       </c>
-      <c r="J56" s="8">
+      <c r="J56" s="12">
         <v>0</v>
       </c>
-      <c r="K56" s="10">
+      <c r="K56" s="14">
         <v>44707</v>
       </c>
-      <c r="L56" s="10">
+      <c r="L56" s="14">
         <v>45488</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A57" s="7" t="s">
+      <c r="A57" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="B57" s="7" t="s">
+      <c r="B57" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="C57" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="D57" s="7" t="s">
+      <c r="D57" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E57" s="7" t="s">
+      <c r="E57" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="F57" s="7" t="s">
+      <c r="F57" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G57" s="7">
-        <v>0.99939999999999996</v>
-      </c>
-      <c r="H57" s="8">
-        <v>14995089.279999999</v>
-      </c>
-      <c r="I57" s="9">
-        <v>14985558.449999999</v>
-      </c>
-      <c r="J57" s="8">
-        <v>9530.8300000000745</v>
-      </c>
-      <c r="K57" s="10">
+      <c r="G57" s="11">
+        <v>0.9994</v>
+      </c>
+      <c r="H57" s="12">
+        <v>14995089.28</v>
+      </c>
+      <c r="I57" s="13">
+        <v>14985558.45</v>
+      </c>
+      <c r="J57" s="12">
+        <v>9530.830000000075</v>
+      </c>
+      <c r="K57" s="14">
         <v>44719</v>
       </c>
-      <c r="L57" s="10">
+      <c r="L57" s="14">
         <v>45476</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A58" s="7" t="s">
+      <c r="A58" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="B58" s="7" t="s">
+      <c r="B58" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="C58" s="7" t="s">
+      <c r="C58" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="D58" s="7" t="s">
+      <c r="D58" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="E58" s="7" t="s">
+      <c r="E58" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="F58" s="7" t="s">
+      <c r="F58" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="G58" s="7">
-        <v>0.86519999999999997</v>
-      </c>
-      <c r="H58" s="8">
-        <v>8463890.9399999995</v>
-      </c>
-      <c r="I58" s="9">
-        <v>7322834.1200000001</v>
-      </c>
-      <c r="J58" s="8">
+      <c r="G58" s="11">
+        <v>0.8652</v>
+      </c>
+      <c r="H58" s="12">
+        <v>8463890.94</v>
+      </c>
+      <c r="I58" s="13">
+        <v>7322834.12</v>
+      </c>
+      <c r="J58" s="12">
         <v>1141056.8199999994</v>
       </c>
-      <c r="K58" s="10">
+      <c r="K58" s="14">
         <v>44688</v>
       </c>
-      <c r="L58" s="10">
+      <c r="L58" s="14">
         <v>46045</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A59" s="7" t="s">
+      <c r="A59" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="B59" s="7" t="s">
+      <c r="B59" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C59" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="D59" s="7" t="s">
+      <c r="D59" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E59" s="7" t="s">
+      <c r="E59" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="F59" s="7" t="s">
+      <c r="F59" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="G59" s="7">
+      <c r="G59" s="11">
         <v>0.4113</v>
       </c>
-      <c r="H59" s="8">
+      <c r="H59" s="12">
         <v>30477728.43</v>
       </c>
-      <c r="I59" s="9">
-        <v>12534756.699999999</v>
-      </c>
-      <c r="J59" s="8">
+      <c r="I59" s="13">
+        <v>12534756.7</v>
+      </c>
+      <c r="J59" s="12">
         <v>17942971.73</v>
       </c>
-      <c r="K59" s="10">
+      <c r="K59" s="14">
         <v>44708</v>
       </c>
-      <c r="L59" s="10">
+      <c r="L59" s="14">
         <v>45437</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A60" s="7" t="s">
+      <c r="A60" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="B60" s="7" t="s">
+      <c r="B60" s="11" t="s">
         <v>248</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="C60" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="D60" s="7" t="s">
+      <c r="D60" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E60" s="7" t="s">
+      <c r="E60" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="F60" s="7" t="s">
+      <c r="F60" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="G60" s="7">
+      <c r="G60" s="11">
         <v>0.97</v>
       </c>
-      <c r="H60" s="8">
-        <v>5722613.8700000001</v>
-      </c>
-      <c r="I60" s="9">
+      <c r="H60" s="12">
+        <v>5722613.87</v>
+      </c>
+      <c r="I60" s="13">
         <v>5551029.21</v>
       </c>
-      <c r="J60" s="8">
+      <c r="J60" s="12">
         <v>171584.66000000015</v>
       </c>
-      <c r="K60" s="10">
+      <c r="K60" s="14">
         <v>44727</v>
       </c>
-      <c r="L60" s="10">
+      <c r="L60" s="14">
         <v>45489</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A61" s="7" t="s">
+      <c r="A61" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="B61" s="7" t="s">
+      <c r="B61" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="C61" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="D61" s="7" t="s">
+      <c r="D61" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E61" s="7" t="s">
+      <c r="E61" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="F61" s="7" t="s">
+      <c r="F61" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="G61" s="7">
-        <v>0.80920000000000003</v>
-      </c>
-      <c r="H61" s="8">
+      <c r="G61" s="11">
+        <v>0.8092</v>
+      </c>
+      <c r="H61" s="12">
         <v>51359899.57</v>
       </c>
-      <c r="I61" s="9">
-        <v>41562191.240000002</v>
-      </c>
-      <c r="J61" s="8">
-        <v>9797708.3299999982</v>
-      </c>
-      <c r="K61" s="10">
+      <c r="I61" s="13">
+        <v>41562191.24</v>
+      </c>
+      <c r="J61" s="12">
+        <v>9797708.329999998</v>
+      </c>
+      <c r="K61" s="14">
         <v>45105</v>
       </c>
-      <c r="L61" s="10">
+      <c r="L61" s="14">
         <v>45769</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A62" s="7" t="s">
+      <c r="A62" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="B62" s="7" t="s">
+      <c r="B62" s="11" t="s">
         <v>258</v>
       </c>
-      <c r="C62" s="7" t="s">
+      <c r="C62" s="11" t="s">
         <v>259</v>
       </c>
-      <c r="D62" s="7" t="s">
+      <c r="D62" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E62" s="7" t="s">
+      <c r="E62" s="11" t="s">
         <v>260</v>
       </c>
-      <c r="F62" s="7" t="s">
+      <c r="F62" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="G62" s="7">
+      <c r="G62" s="11">
         <v>1</v>
       </c>
-      <c r="H62" s="8">
-        <v>6948720.1900000004</v>
-      </c>
-      <c r="I62" s="9">
-        <v>6948720.1900000004</v>
-      </c>
-      <c r="J62" s="8">
+      <c r="H62" s="12">
+        <v>6948720.19</v>
+      </c>
+      <c r="I62" s="13">
+        <v>6948720.19</v>
+      </c>
+      <c r="J62" s="12">
         <v>0</v>
       </c>
-      <c r="K62" s="10">
+      <c r="K62" s="14">
         <v>44882</v>
       </c>
-      <c r="L62" s="10">
+      <c r="L62" s="14">
         <v>45147</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A63" s="7" t="s">
+      <c r="A63" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="B63" s="7" t="s">
+      <c r="B63" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="C63" s="7" t="s">
+      <c r="C63" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="D63" s="7" t="s">
+      <c r="D63" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E63" s="7" t="s">
+      <c r="E63" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="F63" s="7" t="s">
+      <c r="F63" s="11" t="s">
         <v>264</v>
       </c>
-      <c r="G63" s="7">
-        <v>0.97659999999999991</v>
-      </c>
-      <c r="H63" s="8">
+      <c r="G63" s="11">
+        <v>0.9765999999999999</v>
+      </c>
+      <c r="H63" s="12">
         <v>3107538.75</v>
       </c>
-      <c r="I63" s="9">
+      <c r="I63" s="13">
         <v>3034704.58</v>
       </c>
-      <c r="J63" s="8">
-        <v>72834.169999999925</v>
-      </c>
-      <c r="K63" s="10">
+      <c r="J63" s="12">
+        <v>72834.16999999993</v>
+      </c>
+      <c r="K63" s="14">
         <v>44536</v>
       </c>
-      <c r="L63" s="10">
+      <c r="L63" s="14">
         <v>45386</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A64" s="7" t="s">
+      <c r="A64" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="B64" s="7" t="s">
+      <c r="B64" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="C64" s="7" t="s">
+      <c r="C64" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="D64" s="7" t="s">
+      <c r="D64" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E64" s="7" t="s">
+      <c r="E64" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="F64" s="7" t="s">
+      <c r="F64" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="G64" s="7">
+      <c r="G64" s="11">
         <v>0.9577</v>
       </c>
-      <c r="H64" s="8">
+      <c r="H64" s="12">
         <v>2994510.29</v>
       </c>
-      <c r="I64" s="9">
+      <c r="I64" s="13">
         <v>2867705.32</v>
       </c>
-      <c r="J64" s="8">
+      <c r="J64" s="12">
         <v>126804.9700000002</v>
       </c>
-      <c r="K64" s="10">
+      <c r="K64" s="14">
         <v>44804</v>
       </c>
-      <c r="L64" s="10">
+      <c r="L64" s="14">
         <v>45208</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A65" s="7" t="s">
+      <c r="A65" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="B65" s="7" t="s">
+      <c r="B65" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="C65" s="7" t="s">
+      <c r="C65" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="D65" s="7" t="s">
+      <c r="D65" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E65" s="7" t="s">
+      <c r="E65" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="F65" s="7" t="s">
+      <c r="F65" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="G65" s="7">
-        <v>0.87870000000000004</v>
-      </c>
-      <c r="H65" s="8">
-        <v>6519257.0499999998</v>
-      </c>
-      <c r="I65" s="9">
-        <v>5728240.8600000003</v>
-      </c>
-      <c r="J65" s="8">
-        <v>791016.18999999948</v>
-      </c>
-      <c r="K65" s="10">
+      <c r="G65" s="11">
+        <v>0.8787</v>
+      </c>
+      <c r="H65" s="12">
+        <v>6519257.05</v>
+      </c>
+      <c r="I65" s="13">
+        <v>5728240.86</v>
+      </c>
+      <c r="J65" s="12">
+        <v>791016.1899999995</v>
+      </c>
+      <c r="K65" s="14">
         <v>44804</v>
       </c>
-      <c r="L65" s="10">
+      <c r="L65" s="14">
         <v>45569</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A66" s="7" t="s">
+      <c r="A66" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="B66" s="7" t="s">
+      <c r="B66" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="C66" s="7" t="s">
+      <c r="C66" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="D66" s="7" t="s">
+      <c r="D66" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E66" s="7" t="s">
+      <c r="E66" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="F66" s="7" t="s">
+      <c r="F66" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="G66" s="7">
-        <v>0.54500000000000004</v>
-      </c>
-      <c r="H66" s="8">
+      <c r="G66" s="11">
+        <v>0.545</v>
+      </c>
+      <c r="H66" s="12">
         <v>2069000</v>
       </c>
-      <c r="I66" s="9">
+      <c r="I66" s="13">
         <v>1127516.06</v>
       </c>
-      <c r="J66" s="8">
+      <c r="J66" s="12">
         <v>941483.94</v>
       </c>
-      <c r="K66" s="10">
+      <c r="K66" s="14">
         <v>45972</v>
       </c>
-      <c r="L66" s="10">
+      <c r="L66" s="14">
         <v>46167</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A67" s="7" t="s">
+      <c r="A67" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="B67" s="7" t="s">
+      <c r="B67" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="C67" s="7" t="s">
+      <c r="C67" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="D67" s="7" t="s">
+      <c r="D67" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E67" s="7" t="s">
+      <c r="E67" s="11" t="s">
         <v>276</v>
       </c>
-      <c r="F67" s="7" t="s">
+      <c r="F67" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G67" s="7">
+      <c r="G67" s="11">
         <v>0.6604000000000001</v>
       </c>
-      <c r="H67" s="8">
-        <v>12950372.720000001</v>
-      </c>
-      <c r="I67" s="9">
-        <v>8552770.9100000001</v>
-      </c>
-      <c r="J67" s="8">
+      <c r="H67" s="12">
+        <v>12950372.72</v>
+      </c>
+      <c r="I67" s="13">
+        <v>8552770.91</v>
+      </c>
+      <c r="J67" s="12">
         <v>4397601.8100000005</v>
       </c>
-      <c r="K67" s="10">
+      <c r="K67" s="14">
         <v>44742</v>
       </c>
-      <c r="L67" s="10">
+      <c r="L67" s="14">
         <v>46219</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A68" s="7" t="s">
+      <c r="A68" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="B68" s="7" t="s">
+      <c r="B68" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="C68" s="7" t="s">
+      <c r="C68" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="D68" s="7" t="s">
+      <c r="D68" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E68" s="7" t="s">
+      <c r="E68" s="11" t="s">
         <v>279</v>
       </c>
-      <c r="F68" s="7" t="s">
+      <c r="F68" s="11" t="s">
         <v>280</v>
       </c>
-      <c r="G68" s="7">
+      <c r="G68" s="11">
         <v>0.47490000000000004</v>
       </c>
-      <c r="H68" s="8">
-        <v>18996888.260000002</v>
-      </c>
-      <c r="I68" s="9">
+      <c r="H68" s="12">
+        <v>18996888.26</v>
+      </c>
+      <c r="I68" s="13">
         <v>9021796.75</v>
       </c>
-      <c r="J68" s="8">
-        <v>9975091.5100000016</v>
-      </c>
-      <c r="K68" s="12" t="s">
+      <c r="J68" s="12">
+        <v>9975091.510000002</v>
+      </c>
+      <c r="K68" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="L68" s="12" t="s">
+      <c r="L68" s="15" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A69" s="7" t="s">
+      <c r="A69" s="11" t="s">
         <v>281</v>
       </c>
-      <c r="B69" s="7" t="s">
+      <c r="B69" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="C69" s="7" t="s">
+      <c r="C69" s="11" t="s">
         <v>283</v>
       </c>
-      <c r="D69" s="7" t="s">
+      <c r="D69" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E69" s="7" t="s">
+      <c r="E69" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="F69" s="7" t="s">
+      <c r="F69" s="11" t="s">
         <v>285</v>
       </c>
-      <c r="G69" s="7">
-        <v>0.99690000000000001</v>
-      </c>
-      <c r="H69" s="8">
-        <v>25179808.670000002</v>
-      </c>
-      <c r="I69" s="9">
-        <v>25102278.030000001</v>
-      </c>
-      <c r="J69" s="8">
-        <v>77530.640000000596</v>
-      </c>
-      <c r="K69" s="10">
+      <c r="G69" s="11">
+        <v>0.9969</v>
+      </c>
+      <c r="H69" s="12">
+        <v>25179808.67</v>
+      </c>
+      <c r="I69" s="13">
+        <v>25102278.03</v>
+      </c>
+      <c r="J69" s="12">
+        <v>77530.6400000006</v>
+      </c>
+      <c r="K69" s="14">
         <v>45646</v>
       </c>
-      <c r="L69" s="10">
+      <c r="L69" s="14">
         <v>46005</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A70" s="7" t="s">
+      <c r="A70" s="11" t="s">
         <v>281</v>
       </c>
-      <c r="B70" s="7" t="s">
+      <c r="B70" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="C70" s="7" t="s">
+      <c r="C70" s="11" t="s">
         <v>287</v>
       </c>
-      <c r="D70" s="7" t="s">
+      <c r="D70" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E70" s="7" t="s">
+      <c r="E70" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="F70" s="7" t="s">
+      <c r="F70" s="11" t="s">
         <v>289</v>
       </c>
-      <c r="G70" s="7">
-        <v>0.80629999999999991</v>
-      </c>
-      <c r="H70" s="8">
-        <v>8811881.7799999993</v>
-      </c>
-      <c r="I70" s="9">
-        <v>7104640.0499999998</v>
-      </c>
-      <c r="J70" s="8">
+      <c r="G70" s="11">
+        <v>0.8062999999999999</v>
+      </c>
+      <c r="H70" s="12">
+        <v>8811881.78</v>
+      </c>
+      <c r="I70" s="13">
+        <v>7104640.05</v>
+      </c>
+      <c r="J70" s="12">
         <v>1707241.7299999995</v>
       </c>
-      <c r="K70" s="10">
+      <c r="K70" s="14">
         <v>45360</v>
       </c>
-      <c r="L70" s="10">
+      <c r="L70" s="14">
         <v>45566</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A71" s="7" t="s">
+      <c r="A71" s="11" t="s">
         <v>290</v>
       </c>
-      <c r="B71" s="7" t="s">
+      <c r="B71" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="C71" s="7" t="s">
+      <c r="C71" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="D71" s="7" t="s">
+      <c r="D71" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E71" s="7" t="s">
+      <c r="E71" s="11" t="s">
         <v>293</v>
       </c>
-      <c r="F71" s="7" t="s">
+      <c r="F71" s="11" t="s">
         <v>294</v>
       </c>
-      <c r="G71" s="7">
+      <c r="G71" s="11">
         <v>1</v>
       </c>
-      <c r="H71" s="8">
+      <c r="H71" s="12">
         <v>724764.22</v>
       </c>
-      <c r="I71" s="9">
+      <c r="I71" s="13">
         <v>724764.22</v>
       </c>
-      <c r="J71" s="8">
+      <c r="J71" s="12">
         <v>0</v>
       </c>
-      <c r="K71" s="10">
+      <c r="K71" s="14">
         <v>44911</v>
       </c>
-      <c r="L71" s="10">
+      <c r="L71" s="14">
         <v>45182</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A72" s="7" t="s">
+      <c r="A72" s="11" t="s">
         <v>290</v>
       </c>
-      <c r="B72" s="7" t="s">
+      <c r="B72" s="11" t="s">
         <v>295</v>
       </c>
-      <c r="C72" s="7" t="s">
+      <c r="C72" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="D72" s="7" t="s">
+      <c r="D72" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E72" s="7" t="s">
+      <c r="E72" s="11" t="s">
         <v>297</v>
       </c>
-      <c r="F72" s="7" t="s">
+      <c r="F72" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G72" s="7">
-        <v>0.85919999999999996</v>
-      </c>
-      <c r="H72" s="8">
-        <v>34662990.030000001</v>
-      </c>
-      <c r="I72" s="9">
-        <v>29783877.300000001</v>
-      </c>
-      <c r="J72" s="8">
-        <v>4879112.7300000004</v>
-      </c>
-      <c r="K72" s="10">
+      <c r="G72" s="11">
+        <v>0.8592</v>
+      </c>
+      <c r="H72" s="12">
+        <v>34662990.03</v>
+      </c>
+      <c r="I72" s="13">
+        <v>29783877.3</v>
+      </c>
+      <c r="J72" s="12">
+        <v>4879112.73</v>
+      </c>
+      <c r="K72" s="14">
         <v>45155</v>
       </c>
-      <c r="L72" s="10">
+      <c r="L72" s="14">
         <v>46239</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A73" s="7" t="s">
+      <c r="A73" s="11" t="s">
         <v>290</v>
       </c>
-      <c r="B73" s="7" t="s">
+      <c r="B73" s="11" t="s">
         <v>298</v>
       </c>
-      <c r="C73" s="7" t="s">
+      <c r="C73" s="11" t="s">
         <v>299</v>
       </c>
-      <c r="D73" s="7" t="s">
+      <c r="D73" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="E73" s="7" t="s">
+      <c r="E73" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="F73" s="7" t="s">
+      <c r="F73" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="G73" s="7">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="H73" s="8">
+      <c r="G73" s="11">
+        <v>0.07</v>
+      </c>
+      <c r="H73" s="12">
         <v>27739392.32</v>
       </c>
-      <c r="I73" s="9">
+      <c r="I73" s="13">
         <v>1940441.71</v>
       </c>
-      <c r="J73" s="8">
-        <v>25798950.609999999</v>
-      </c>
-      <c r="K73" s="10">
+      <c r="J73" s="12">
+        <v>25798950.61</v>
+      </c>
+      <c r="K73" s="14">
         <v>45541</v>
       </c>
-      <c r="L73" s="10">
+      <c r="L73" s="14">
         <v>46081</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A74" s="7" t="s">
+      <c r="A74" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="B74" s="7" t="s">
+      <c r="B74" s="11" t="s">
         <v>302</v>
       </c>
-      <c r="C74" s="7" t="s">
+      <c r="C74" s="11" t="s">
         <v>303</v>
       </c>
-      <c r="D74" s="7" t="s">
+      <c r="D74" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E74" s="7" t="s">
+      <c r="E74" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="F74" s="7" t="s">
+      <c r="F74" s="11" t="s">
         <v>305</v>
       </c>
-      <c r="G74" s="7">
-        <v>0.89910000000000001</v>
-      </c>
-      <c r="H74" s="8">
-        <v>666913.68000000005</v>
-      </c>
-      <c r="I74" s="9">
-        <v>599641.31000000006</v>
-      </c>
-      <c r="J74" s="8">
+      <c r="G74" s="11">
+        <v>0.8991</v>
+      </c>
+      <c r="H74" s="12">
+        <v>666913.68</v>
+      </c>
+      <c r="I74" s="13">
+        <v>599641.31</v>
+      </c>
+      <c r="J74" s="12">
         <v>67272.37</v>
       </c>
-      <c r="K74" s="10">
+      <c r="K74" s="14">
         <v>45783</v>
       </c>
-      <c r="L74" s="10">
+      <c r="L74" s="14">
         <v>45964</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A75" s="7" t="s">
+      <c r="A75" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="B75" s="7" t="s">
+      <c r="B75" s="11" t="s">
         <v>306</v>
       </c>
-      <c r="C75" s="7" t="s">
+      <c r="C75" s="11" t="s">
         <v>307</v>
       </c>
-      <c r="D75" s="7" t="s">
+      <c r="D75" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E75" s="7" t="s">
+      <c r="E75" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="F75" s="7" t="s">
+      <c r="F75" s="11" t="s">
         <v>305</v>
       </c>
-      <c r="G75" s="7">
-        <v>0.89760000000000006</v>
-      </c>
-      <c r="H75" s="8">
+      <c r="G75" s="11">
+        <v>0.8976000000000001</v>
+      </c>
+      <c r="H75" s="12">
         <v>763285.07</v>
       </c>
-      <c r="I75" s="9">
+      <c r="I75" s="13">
         <v>685145.56</v>
       </c>
-      <c r="J75" s="8">
-        <v>78139.509999999893</v>
-      </c>
-      <c r="K75" s="10">
+      <c r="J75" s="12">
+        <v>78139.5099999999</v>
+      </c>
+      <c r="K75" s="14">
         <v>45783</v>
       </c>
-      <c r="L75" s="10">
+      <c r="L75" s="14">
         <v>46115</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A76" s="7" t="s">
+      <c r="A76" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="B76" s="7" t="s">
+      <c r="B76" s="11" t="s">
         <v>309</v>
       </c>
-      <c r="C76" s="7" t="s">
+      <c r="C76" s="11" t="s">
         <v>310</v>
       </c>
-      <c r="D76" s="7" t="s">
+      <c r="D76" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E76" s="7" t="s">
+      <c r="E76" s="11" t="s">
         <v>311</v>
       </c>
-      <c r="F76" s="7" t="s">
+      <c r="F76" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="G76" s="7">
-        <v>0.94950000000000001</v>
-      </c>
-      <c r="H76" s="8">
-        <v>32836774.760000002</v>
-      </c>
-      <c r="I76" s="9">
-        <v>31178236.210000001</v>
-      </c>
-      <c r="J76" s="8">
+      <c r="G76" s="11">
+        <v>0.9495</v>
+      </c>
+      <c r="H76" s="12">
+        <v>32836774.76</v>
+      </c>
+      <c r="I76" s="13">
+        <v>31178236.21</v>
+      </c>
+      <c r="J76" s="12">
         <v>1658538.5500000007</v>
       </c>
-      <c r="K76" s="10">
+      <c r="K76" s="14">
         <v>44564</v>
       </c>
-      <c r="L76" s="10">
+      <c r="L76" s="14">
         <v>44944</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A77" s="7" t="s">
+      <c r="A77" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="B77" s="7" t="s">
+      <c r="B77" s="11" t="s">
         <v>312</v>
       </c>
-      <c r="C77" s="7" t="s">
+      <c r="C77" s="11" t="s">
         <v>313</v>
       </c>
-      <c r="D77" s="7" t="s">
+      <c r="D77" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E77" s="7" t="s">
+      <c r="E77" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="F77" s="7" t="s">
+      <c r="F77" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="G77" s="7">
-        <v>0.95430000000000004</v>
-      </c>
-      <c r="H77" s="8">
+      <c r="G77" s="11">
+        <v>0.9543</v>
+      </c>
+      <c r="H77" s="12">
         <v>36880209</v>
       </c>
-      <c r="I77" s="9">
+      <c r="I77" s="13">
         <v>35196032.93</v>
       </c>
-      <c r="J77" s="8">
+      <c r="J77" s="12">
         <v>1684176.0700000003</v>
       </c>
-      <c r="K77" s="10">
+      <c r="K77" s="14">
         <v>44648</v>
       </c>
-      <c r="L77" s="10">
+      <c r="L77" s="14">
         <v>45498</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A78" s="7" t="s">
+      <c r="A78" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="B78" s="7" t="s">
+      <c r="B78" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="C78" s="7" t="s">
+      <c r="C78" s="11" t="s">
         <v>316</v>
       </c>
-      <c r="D78" s="7" t="s">
+      <c r="D78" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E78" s="7" t="s">
+      <c r="E78" s="11" t="s">
         <v>317</v>
       </c>
-      <c r="F78" s="7" t="s">
+      <c r="F78" s="11" t="s">
         <v>318</v>
       </c>
-      <c r="G78" s="7">
-        <v>1.34E-2</v>
-      </c>
-      <c r="H78" s="8">
+      <c r="G78" s="11">
+        <v>0.0134</v>
+      </c>
+      <c r="H78" s="12">
         <v>4705907.3</v>
       </c>
-      <c r="I78" s="9">
+      <c r="I78" s="13">
         <v>63006.28</v>
       </c>
-      <c r="J78" s="8">
-        <v>4642901.0199999996</v>
-      </c>
-      <c r="K78" s="10">
+      <c r="J78" s="12">
+        <v>4642901.02</v>
+      </c>
+      <c r="K78" s="14">
         <v>46009</v>
       </c>
-      <c r="L78" s="10">
+      <c r="L78" s="14">
         <v>46189</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A79" s="7" t="s">
+      <c r="A79" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="B79" s="7" t="s">
+      <c r="B79" s="11" t="s">
         <v>319</v>
       </c>
-      <c r="C79" s="7" t="s">
+      <c r="C79" s="11" t="s">
         <v>320</v>
       </c>
-      <c r="D79" s="7" t="s">
+      <c r="D79" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E79" s="7" t="s">
+      <c r="E79" s="11" t="s">
         <v>321</v>
       </c>
-      <c r="F79" s="7" t="s">
+      <c r="F79" s="11" t="s">
         <v>322</v>
       </c>
-      <c r="G79" s="7">
+      <c r="G79" s="11">
         <v>0.5292</v>
       </c>
-      <c r="H79" s="8">
+      <c r="H79" s="12">
         <v>10349390.52</v>
       </c>
-      <c r="I79" s="9">
+      <c r="I79" s="13">
         <v>5476795.79</v>
       </c>
-      <c r="J79" s="8">
+      <c r="J79" s="12">
         <v>4872594.7299999995</v>
       </c>
-      <c r="K79" s="10">
+      <c r="K79" s="14">
         <v>45867</v>
       </c>
-      <c r="L79" s="10">
+      <c r="L79" s="14">
         <v>46227</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A80" s="7" t="s">
+      <c r="A80" s="11" t="s">
         <v>323</v>
       </c>
-      <c r="B80" s="7" t="s">
+      <c r="B80" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="C80" s="7" t="s">
+      <c r="C80" s="11" t="s">
         <v>325</v>
       </c>
-      <c r="D80" s="7" t="s">
+      <c r="D80" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E80" s="7" t="s">
+      <c r="E80" s="11" t="s">
         <v>326</v>
       </c>
-      <c r="F80" s="7" t="s">
+      <c r="F80" s="11" t="s">
         <v>305</v>
       </c>
-      <c r="G80" s="7">
+      <c r="G80" s="11">
         <v>1</v>
       </c>
-      <c r="H80" s="8">
+      <c r="H80" s="12">
         <v>1923627.23</v>
       </c>
-      <c r="I80" s="9">
+      <c r="I80" s="13">
         <v>1923627.26</v>
       </c>
-      <c r="J80" s="8">
-        <v>-3.0000000027939677E-2</v>
-      </c>
-      <c r="K80" s="10">
+      <c r="J80" s="12">
+        <v>-0.030000000027939677</v>
+      </c>
+      <c r="K80" s="14">
         <v>44708</v>
       </c>
-      <c r="L80" s="10">
+      <c r="L80" s="14">
         <v>45640</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A81" s="7" t="s">
+      <c r="A81" s="11" t="s">
         <v>323</v>
       </c>
-      <c r="B81" s="7" t="s">
+      <c r="B81" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="C81" s="7" t="s">
+      <c r="C81" s="11" t="s">
         <v>328</v>
       </c>
-      <c r="D81" s="7" t="s">
+      <c r="D81" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E81" s="7" t="s">
+      <c r="E81" s="11" t="s">
         <v>329</v>
       </c>
-      <c r="F81" s="7" t="s">
+      <c r="F81" s="11" t="s">
         <v>330</v>
       </c>
-      <c r="G81" s="7">
+      <c r="G81" s="11">
         <v>1</v>
       </c>
-      <c r="H81" s="8">
+      <c r="H81" s="12">
         <v>3552093.82</v>
       </c>
-      <c r="I81" s="9">
+      <c r="I81" s="13">
         <v>3552073.13</v>
       </c>
-      <c r="J81" s="8">
-        <v>20.689999999944121</v>
-      </c>
-      <c r="K81" s="10">
+      <c r="J81" s="12">
+        <v>20.68999999994412</v>
+      </c>
+      <c r="K81" s="14">
         <v>45034</v>
       </c>
-      <c r="L81" s="10">
+      <c r="L81" s="14">
         <v>45034</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A82" s="7" t="s">
+      <c r="A82" s="11" t="s">
         <v>323</v>
       </c>
-      <c r="B82" s="7" t="s">
+      <c r="B82" s="11" t="s">
         <v>331</v>
       </c>
-      <c r="C82" s="7" t="s">
+      <c r="C82" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="D82" s="7" t="s">
+      <c r="D82" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E82" s="7" t="s">
+      <c r="E82" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="F82" s="7" t="s">
+      <c r="F82" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G82" s="7">
-        <v>0.97230000000000005</v>
-      </c>
-      <c r="H82" s="8">
-        <v>15078640.210000001</v>
-      </c>
-      <c r="I82" s="9">
-        <v>14660282.369999999</v>
-      </c>
-      <c r="J82" s="8">
-        <v>418357.84000000171</v>
-      </c>
-      <c r="K82" s="10">
+      <c r="G82" s="11">
+        <v>0.9723</v>
+      </c>
+      <c r="H82" s="12">
+        <v>15078640.21</v>
+      </c>
+      <c r="I82" s="13">
+        <v>14660282.37</v>
+      </c>
+      <c r="J82" s="12">
+        <v>418357.8400000017</v>
+      </c>
+      <c r="K82" s="14">
         <v>45497</v>
       </c>
-      <c r="L82" s="10">
+      <c r="L82" s="14">
         <v>45301</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A83" s="7" t="s">
+      <c r="A83" s="11" t="s">
         <v>323</v>
       </c>
-      <c r="B83" s="7" t="s">
+      <c r="B83" s="11" t="s">
         <v>333</v>
       </c>
-      <c r="C83" s="7" t="s">
+      <c r="C83" s="11" t="s">
         <v>334</v>
       </c>
-      <c r="D83" s="7" t="s">
+      <c r="D83" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E83" s="7" t="s">
+      <c r="E83" s="11" t="s">
         <v>335</v>
       </c>
-      <c r="F83" s="7" t="s">
+      <c r="F83" s="11" t="s">
         <v>336</v>
       </c>
-      <c r="G83" s="7">
-        <v>0.94799999999999995</v>
-      </c>
-      <c r="H83" s="8">
-        <v>59148617.810000002</v>
-      </c>
-      <c r="I83" s="9">
-        <v>56075178.640000001</v>
-      </c>
-      <c r="J83" s="8">
-        <v>3073439.1700000018</v>
-      </c>
-      <c r="K83" s="10">
+      <c r="G83" s="11">
+        <v>0.948</v>
+      </c>
+      <c r="H83" s="12">
+        <v>59148617.81</v>
+      </c>
+      <c r="I83" s="13">
+        <v>56075178.64</v>
+      </c>
+      <c r="J83" s="12">
+        <v>3073439.170000002</v>
+      </c>
+      <c r="K83" s="14">
         <v>44726</v>
       </c>
-      <c r="L83" s="10">
+      <c r="L83" s="14">
         <v>46006</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A84" s="7" t="s">
+      <c r="A84" s="11" t="s">
         <v>337</v>
       </c>
-      <c r="B84" s="7" t="s">
+      <c r="B84" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="C84" s="7"/>
-      <c r="D84" s="7" t="s">
+      <c r="C84" s="11"/>
+      <c r="D84" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E84" s="7" t="s">
+      <c r="E84" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="F84" s="7" t="s">
+      <c r="F84" s="11" t="s">
         <v>340</v>
       </c>
-      <c r="G84" s="7">
+      <c r="G84" s="11">
         <v>0</v>
       </c>
-      <c r="H84" s="8">
+      <c r="H84" s="12">
         <v>62980000</v>
       </c>
-      <c r="I84" s="9">
+      <c r="I84" s="13">
         <v>62980000</v>
       </c>
-      <c r="J84" s="8">
+      <c r="J84" s="12">
         <v>0</v>
       </c>
-      <c r="K84" s="10">
+      <c r="K84" s="14">
         <v>43930</v>
       </c>
-      <c r="L84" s="10">
+      <c r="L84" s="14">
         <v>44011</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A85" s="7" t="s">
+      <c r="A85" s="11" t="s">
         <v>337</v>
       </c>
-      <c r="B85" s="7" t="s">
+      <c r="B85" s="11" t="s">
         <v>341</v>
       </c>
-      <c r="C85" s="7" t="s">
+      <c r="C85" s="11" t="s">
         <v>342</v>
       </c>
-      <c r="D85" s="7" t="s">
+      <c r="D85" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E85" s="7" t="s">
+      <c r="E85" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="F85" s="7" t="s">
+      <c r="F85" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="G85" s="7">
-        <v>0.99769999999999992</v>
-      </c>
-      <c r="H85" s="8">
-        <v>19451386.879999999</v>
-      </c>
-      <c r="I85" s="9">
-        <v>19406169.390000001</v>
-      </c>
-      <c r="J85" s="8">
-        <v>45217.489999998361</v>
-      </c>
-      <c r="K85" s="10">
+      <c r="G85" s="11">
+        <v>0.9976999999999999</v>
+      </c>
+      <c r="H85" s="12">
+        <v>19451386.88</v>
+      </c>
+      <c r="I85" s="13">
+        <v>19406169.39</v>
+      </c>
+      <c r="J85" s="12">
+        <v>45217.48999999836</v>
+      </c>
+      <c r="K85" s="14">
         <v>45247</v>
       </c>
-      <c r="L85" s="10">
+      <c r="L85" s="14">
         <v>46001</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A86" s="7" t="s">
+      <c r="A86" s="11" t="s">
         <v>337</v>
       </c>
-      <c r="B86" s="7" t="s">
+      <c r="B86" s="11" t="s">
         <v>344</v>
       </c>
-      <c r="C86" s="7" t="s">
+      <c r="C86" s="11" t="s">
         <v>345</v>
       </c>
-      <c r="D86" s="7" t="s">
+      <c r="D86" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E86" s="7" t="s">
+      <c r="E86" s="11" t="s">
         <v>346</v>
       </c>
-      <c r="F86" s="7" t="s">
+      <c r="F86" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G86" s="7">
-        <v>0.96660000000000001</v>
-      </c>
-      <c r="H86" s="8">
-        <v>20106028.530000001</v>
-      </c>
-      <c r="I86" s="9">
-        <v>19434508.219999999</v>
-      </c>
-      <c r="J86" s="8">
-        <v>671520.31000000238</v>
-      </c>
-      <c r="K86" s="10">
+      <c r="G86" s="11">
+        <v>0.9666</v>
+      </c>
+      <c r="H86" s="12">
+        <v>20106028.53</v>
+      </c>
+      <c r="I86" s="13">
+        <v>19434508.22</v>
+      </c>
+      <c r="J86" s="12">
+        <v>671520.3100000024</v>
+      </c>
+      <c r="K86" s="14">
         <v>44991</v>
       </c>
-      <c r="L86" s="10">
+      <c r="L86" s="14">
         <v>46094</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A87" s="7" t="s">
+      <c r="A87" s="11" t="s">
         <v>337</v>
       </c>
-      <c r="B87" s="7" t="s">
+      <c r="B87" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="C87" s="7" t="s">
+      <c r="C87" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="D87" s="7" t="s">
+      <c r="D87" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E87" s="7" t="s">
+      <c r="E87" s="11" t="s">
         <v>348</v>
       </c>
-      <c r="F87" s="7" t="s">
+      <c r="F87" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="G87" s="7">
+      <c r="G87" s="11">
         <v>0.9577</v>
       </c>
-      <c r="H87" s="8">
-        <v>34508101.149999999</v>
-      </c>
-      <c r="I87" s="9">
-        <v>33048630.329999998</v>
-      </c>
-      <c r="J87" s="8">
+      <c r="H87" s="12">
+        <v>34508101.15</v>
+      </c>
+      <c r="I87" s="13">
+        <v>33048630.33</v>
+      </c>
+      <c r="J87" s="12">
         <v>1459470.8200000003</v>
       </c>
-      <c r="K87" s="10">
+      <c r="K87" s="14">
         <v>44690</v>
       </c>
-      <c r="L87" s="10">
+      <c r="L87" s="14">
         <v>45621</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A88" s="7" t="s">
+      <c r="A88" s="11" t="s">
         <v>337</v>
       </c>
-      <c r="B88" s="7" t="s">
+      <c r="B88" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="C88" s="7" t="s">
+      <c r="C88" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="D88" s="7" t="s">
+      <c r="D88" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E88" s="7" t="s">
+      <c r="E88" s="11" t="s">
         <v>351</v>
       </c>
-      <c r="F88" s="7" t="s">
+      <c r="F88" s="11" t="s">
         <v>352</v>
       </c>
-      <c r="G88" s="7">
-        <v>0.97109999999999996</v>
-      </c>
-      <c r="H88" s="8">
-        <v>58086688.759999998</v>
-      </c>
-      <c r="I88" s="9">
-        <v>56408550.909999996</v>
-      </c>
-      <c r="J88" s="8">
+      <c r="G88" s="11">
+        <v>0.9711</v>
+      </c>
+      <c r="H88" s="12">
+        <v>58086688.76</v>
+      </c>
+      <c r="I88" s="13">
+        <v>56408550.91</v>
+      </c>
+      <c r="J88" s="12">
         <v>1678137.8500000015</v>
       </c>
-      <c r="K88" s="10">
+      <c r="K88" s="14">
         <v>44831</v>
       </c>
-      <c r="L88" s="10">
+      <c r="L88" s="14">
         <v>45619</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A89" s="7" t="s">
+      <c r="A89" s="11" t="s">
         <v>337</v>
       </c>
-      <c r="B89" s="7" t="s">
+      <c r="B89" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="C89" s="7" t="s">
+      <c r="C89" s="11" t="s">
         <v>354</v>
       </c>
-      <c r="D89" s="7" t="s">
+      <c r="D89" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E89" s="7" t="s">
+      <c r="E89" s="11" t="s">
         <v>355</v>
       </c>
-      <c r="F89" s="7" t="s">
+      <c r="F89" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="G89" s="7">
-        <v>0.69730000000000003</v>
-      </c>
-      <c r="H89" s="8">
+      <c r="G89" s="11">
+        <v>0.6973</v>
+      </c>
+      <c r="H89" s="12">
         <v>28459856.91</v>
       </c>
-      <c r="I89" s="9">
-        <v>19844966.579999998</v>
-      </c>
-      <c r="J89" s="8">
-        <v>8614890.3300000019</v>
-      </c>
-      <c r="K89" s="10">
+      <c r="I89" s="13">
+        <v>19844966.58</v>
+      </c>
+      <c r="J89" s="12">
+        <v>8614890.330000002</v>
+      </c>
+      <c r="K89" s="14">
         <v>45035</v>
       </c>
-      <c r="L89" s="10">
+      <c r="L89" s="14">
         <v>46205</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A90" s="7" t="s">
+      <c r="A90" s="11" t="s">
         <v>337</v>
       </c>
-      <c r="B90" s="7" t="s">
+      <c r="B90" s="11" t="s">
         <v>356</v>
       </c>
-      <c r="C90" s="7" t="s">
+      <c r="C90" s="11" t="s">
         <v>357</v>
       </c>
-      <c r="D90" s="7" t="s">
+      <c r="D90" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E90" s="7" t="s">
+      <c r="E90" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="F90" s="7" t="s">
+      <c r="F90" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="G90" s="7">
-        <v>0.78049999999999997</v>
-      </c>
-      <c r="H90" s="8">
-        <v>45862409.689999998</v>
-      </c>
-      <c r="I90" s="9">
-        <v>35796161.979999997</v>
-      </c>
-      <c r="J90" s="8">
-        <v>10066247.710000001</v>
-      </c>
-      <c r="K90" s="10">
+      <c r="G90" s="11">
+        <v>0.7805</v>
+      </c>
+      <c r="H90" s="12">
+        <v>45862409.69</v>
+      </c>
+      <c r="I90" s="13">
+        <v>35796161.98</v>
+      </c>
+      <c r="J90" s="12">
+        <v>10066247.71</v>
+      </c>
+      <c r="K90" s="14">
         <v>45352</v>
       </c>
-      <c r="L90" s="10">
+      <c r="L90" s="14">
         <v>46255</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A91" s="7" t="s">
+      <c r="A91" s="11" t="s">
         <v>337</v>
       </c>
-      <c r="B91" s="7" t="s">
+      <c r="B91" s="11" t="s">
         <v>359</v>
       </c>
-      <c r="C91" s="7" t="s">
+      <c r="C91" s="11" t="s">
         <v>360</v>
       </c>
-      <c r="D91" s="7" t="s">
+      <c r="D91" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E91" s="7" t="s">
+      <c r="E91" s="11" t="s">
         <v>361</v>
       </c>
-      <c r="F91" s="7" t="s">
+      <c r="F91" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="G91" s="7">
-        <v>1.32E-2</v>
-      </c>
-      <c r="H91" s="8">
+      <c r="G91" s="11">
+        <v>0.0132</v>
+      </c>
+      <c r="H91" s="12">
         <v>11494433.26</v>
       </c>
-      <c r="I91" s="9">
+      <c r="I91" s="13">
         <v>151285.62</v>
       </c>
-      <c r="J91" s="8">
-        <v>11343147.640000001</v>
-      </c>
-      <c r="K91" s="10">
+      <c r="J91" s="12">
+        <v>11343147.64</v>
+      </c>
+      <c r="K91" s="14">
         <v>45105</v>
       </c>
-      <c r="L91" s="10">
+      <c r="L91" s="14">
         <v>45706</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A92" s="7" t="s">
+      <c r="A92" s="11" t="s">
         <v>362</v>
       </c>
-      <c r="B92" s="7" t="s">
+      <c r="B92" s="11" t="s">
         <v>363</v>
       </c>
-      <c r="C92" s="7" t="s">
+      <c r="C92" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="D92" s="7" t="s">
+      <c r="D92" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E92" s="7" t="s">
+      <c r="E92" s="11" t="s">
         <v>364</v>
       </c>
-      <c r="F92" s="7" t="s">
+      <c r="F92" s="11" t="s">
         <v>365</v>
       </c>
-      <c r="G92" s="7">
-        <v>0.89800000000000002</v>
-      </c>
-      <c r="H92" s="8">
+      <c r="G92" s="11">
+        <v>0.898</v>
+      </c>
+      <c r="H92" s="12">
         <v>1212482.21</v>
       </c>
-      <c r="I92" s="9">
+      <c r="I92" s="13">
         <v>1088826.01</v>
       </c>
-      <c r="J92" s="8">
+      <c r="J92" s="12">
         <v>123656.19999999995</v>
       </c>
-      <c r="K92" s="10">
+      <c r="K92" s="14">
         <v>44326</v>
       </c>
-      <c r="L92" s="10">
+      <c r="L92" s="14">
         <v>44536</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A93" s="7" t="s">
+      <c r="A93" s="11" t="s">
         <v>362</v>
       </c>
-      <c r="B93" s="7" t="s">
+      <c r="B93" s="11" t="s">
         <v>366</v>
       </c>
-      <c r="C93" s="7" t="s">
+      <c r="C93" s="11" t="s">
         <v>367</v>
       </c>
-      <c r="D93" s="7" t="s">
+      <c r="D93" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E93" s="7" t="s">
+      <c r="E93" s="11" t="s">
         <v>368</v>
       </c>
-      <c r="F93" s="7" t="s">
+      <c r="F93" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="G93" s="7">
-        <v>0.92090000000000005</v>
-      </c>
-      <c r="H93" s="8">
-        <v>12560309.119999999</v>
-      </c>
-      <c r="I93" s="9">
-        <v>11566432.390000001</v>
-      </c>
-      <c r="J93" s="8">
-        <v>993876.72999999858</v>
-      </c>
-      <c r="K93" s="10">
+      <c r="G93" s="11">
+        <v>0.9209</v>
+      </c>
+      <c r="H93" s="12">
+        <v>12560309.12</v>
+      </c>
+      <c r="I93" s="13">
+        <v>11566432.39</v>
+      </c>
+      <c r="J93" s="12">
+        <v>993876.7299999986</v>
+      </c>
+      <c r="K93" s="14">
         <v>44831</v>
       </c>
-      <c r="L93" s="10">
+      <c r="L93" s="14">
         <v>45477</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A94" s="7" t="s">
+      <c r="A94" s="11" t="s">
         <v>369</v>
       </c>
-      <c r="B94" s="7" t="s">
+      <c r="B94" s="11" t="s">
         <v>370</v>
       </c>
-      <c r="C94" s="7" t="s">
+      <c r="C94" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="D94" s="7" t="s">
+      <c r="D94" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E94" s="7" t="s">
+      <c r="E94" s="11" t="s">
         <v>372</v>
       </c>
-      <c r="F94" s="7" t="s">
+      <c r="F94" s="11" t="s">
         <v>373</v>
       </c>
-      <c r="G94" s="7">
-        <v>0.99900000000000011</v>
-      </c>
-      <c r="H94" s="8">
+      <c r="G94" s="11">
+        <v>0.9990000000000001</v>
+      </c>
+      <c r="H94" s="12">
         <v>17695067.23</v>
       </c>
-      <c r="I94" s="9">
+      <c r="I94" s="13">
         <v>17677149.84</v>
       </c>
-      <c r="J94" s="8">
+      <c r="J94" s="12">
         <v>17917.390000000596</v>
       </c>
-      <c r="K94" s="10">
+      <c r="K94" s="14">
         <v>44994</v>
       </c>
-      <c r="L94" s="10">
+      <c r="L94" s="14">
         <v>45928</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A95" s="7" t="s">
+      <c r="A95" s="11" t="s">
         <v>374</v>
       </c>
-      <c r="B95" s="7" t="s">
+      <c r="B95" s="11" t="s">
         <v>375</v>
       </c>
-      <c r="C95" s="7" t="s">
+      <c r="C95" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="D95" s="7" t="s">
+      <c r="D95" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E95" s="7" t="s">
+      <c r="E95" s="11" t="s">
         <v>376</v>
       </c>
-      <c r="F95" s="7" t="s">
+      <c r="F95" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="G95" s="7">
+      <c r="G95" s="11">
         <v>1</v>
       </c>
-      <c r="H95" s="8">
-        <v>12092480.689999999</v>
-      </c>
-      <c r="I95" s="9">
-        <v>12092480.689999999</v>
-      </c>
-      <c r="J95" s="8">
+      <c r="H95" s="12">
+        <v>12092480.69</v>
+      </c>
+      <c r="I95" s="13">
+        <v>12092480.69</v>
+      </c>
+      <c r="J95" s="12">
         <v>0</v>
       </c>
-      <c r="K95" s="10">
+      <c r="K95" s="14">
         <v>44734</v>
       </c>
-      <c r="L95" s="10">
+      <c r="L95" s="14">
         <v>45202</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A96" s="7" t="s">
+      <c r="A96" s="11" t="s">
         <v>374</v>
       </c>
-      <c r="B96" s="7" t="s">
+      <c r="B96" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="C96" s="7" t="s">
+      <c r="C96" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="D96" s="7" t="s">
+      <c r="D96" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E96" s="7" t="s">
+      <c r="E96" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="F96" s="7" t="s">
+      <c r="F96" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="G96" s="7">
-        <v>0.91170000000000007</v>
-      </c>
-      <c r="H96" s="8">
-        <v>5978542.1500000004</v>
-      </c>
-      <c r="I96" s="9">
+      <c r="G96" s="11">
+        <v>0.9117000000000001</v>
+      </c>
+      <c r="H96" s="12">
+        <v>5978542.15</v>
+      </c>
+      <c r="I96" s="13">
         <v>5450477.04</v>
       </c>
-      <c r="J96" s="8">
-        <v>528065.11000000034</v>
-      </c>
-      <c r="K96" s="10">
+      <c r="J96" s="12">
+        <v>528065.1100000003</v>
+      </c>
+      <c r="K96" s="14">
         <v>44753</v>
       </c>
-      <c r="L96" s="10">
+      <c r="L96" s="14">
         <v>44933</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A97" s="7" t="s">
+      <c r="A97" s="11" t="s">
         <v>374</v>
       </c>
-      <c r="B97" s="7" t="s">
+      <c r="B97" s="11" t="s">
         <v>380</v>
       </c>
-      <c r="C97" s="7" t="s">
+      <c r="C97" s="11" t="s">
         <v>381</v>
       </c>
-      <c r="D97" s="7" t="s">
+      <c r="D97" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E97" s="7" t="s">
+      <c r="E97" s="11" t="s">
         <v>382</v>
       </c>
-      <c r="F97" s="7" t="s">
+      <c r="F97" s="11" t="s">
         <v>280</v>
       </c>
-      <c r="G97" s="7">
-        <v>0.80189999999999995</v>
-      </c>
-      <c r="H97" s="8">
-        <v>7066834.9000000004</v>
-      </c>
-      <c r="I97" s="9">
-        <v>5666949.7199999997</v>
-      </c>
-      <c r="J97" s="8">
+      <c r="G97" s="11">
+        <v>0.8019</v>
+      </c>
+      <c r="H97" s="12">
+        <v>7066834.9</v>
+      </c>
+      <c r="I97" s="13">
+        <v>5666949.72</v>
+      </c>
+      <c r="J97" s="12">
         <v>1399885.1800000006</v>
       </c>
-      <c r="K97" s="10">
+      <c r="K97" s="14">
         <v>45848</v>
       </c>
-      <c r="L97" s="10">
+      <c r="L97" s="14">
         <v>46222</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A98" s="7" t="s">
+      <c r="A98" s="11" t="s">
         <v>374</v>
       </c>
-      <c r="B98" s="7" t="s">
+      <c r="B98" s="11" t="s">
         <v>383</v>
       </c>
-      <c r="C98" s="7" t="s">
+      <c r="C98" s="11" t="s">
         <v>384</v>
       </c>
-      <c r="D98" s="7" t="s">
+      <c r="D98" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E98" s="7" t="s">
+      <c r="E98" s="11" t="s">
         <v>385</v>
       </c>
-      <c r="F98" s="7" t="s">
+      <c r="F98" s="11" t="s">
         <v>386</v>
       </c>
-      <c r="G98" s="7">
-        <v>0.83620000000000005</v>
-      </c>
-      <c r="H98" s="8">
+      <c r="G98" s="11">
+        <v>0.8362</v>
+      </c>
+      <c r="H98" s="12">
         <v>11942741.09</v>
       </c>
-      <c r="I98" s="9">
-        <v>9986334.6300000008</v>
-      </c>
-      <c r="J98" s="8">
+      <c r="I98" s="13">
+        <v>9986334.63</v>
+      </c>
+      <c r="J98" s="12">
         <v>1956406.459999999</v>
       </c>
-      <c r="K98" s="10">
+      <c r="K98" s="14">
         <v>44734</v>
       </c>
-      <c r="L98" s="10">
+      <c r="L98" s="14">
         <v>45098</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A99" s="7" t="s">
+      <c r="A99" s="11" t="s">
         <v>374</v>
       </c>
-      <c r="B99" s="7" t="s">
+      <c r="B99" s="11" t="s">
         <v>387</v>
       </c>
-      <c r="C99" s="7" t="s">
+      <c r="C99" s="11" t="s">
         <v>388</v>
       </c>
-      <c r="D99" s="7" t="s">
+      <c r="D99" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E99" s="7" t="s">
+      <c r="E99" s="11" t="s">
         <v>389</v>
       </c>
-      <c r="F99" s="7" t="s">
+      <c r="F99" s="11" t="s">
         <v>386</v>
       </c>
-      <c r="G99" s="7">
-        <v>0.94930000000000003</v>
-      </c>
-      <c r="H99" s="8">
+      <c r="G99" s="11">
+        <v>0.9493</v>
+      </c>
+      <c r="H99" s="12">
         <v>48302952.43</v>
       </c>
-      <c r="I99" s="9">
-        <v>45853223.299999997</v>
-      </c>
-      <c r="J99" s="8">
+      <c r="I99" s="13">
+        <v>45853223.3</v>
+      </c>
+      <c r="J99" s="12">
         <v>2449729.1300000027</v>
       </c>
-      <c r="K99" s="10">
+      <c r="K99" s="14">
         <v>45189</v>
       </c>
-      <c r="L99" s="10">
+      <c r="L99" s="14">
         <v>45729</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A100" s="7" t="s">
+      <c r="A100" s="11" t="s">
         <v>374</v>
       </c>
-      <c r="B100" s="7" t="s">
+      <c r="B100" s="11" t="s">
         <v>390</v>
       </c>
-      <c r="C100" s="7" t="s">
+      <c r="C100" s="11" t="s">
         <v>391</v>
       </c>
-      <c r="D100" s="7" t="s">
+      <c r="D100" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E100" s="7" t="s">
+      <c r="E100" s="11" t="s">
         <v>392</v>
       </c>
-      <c r="F100" s="7" t="s">
+      <c r="F100" s="11" t="s">
         <v>393</v>
       </c>
-      <c r="G100" s="7">
-        <v>0.91819999999999991</v>
-      </c>
-      <c r="H100" s="8">
-        <v>30543662.309999999</v>
-      </c>
-      <c r="I100" s="9">
-        <v>28044628.600000001</v>
-      </c>
-      <c r="J100" s="8">
-        <v>2499033.7099999972</v>
-      </c>
-      <c r="K100" s="10">
+      <c r="G100" s="11">
+        <v>0.9181999999999999</v>
+      </c>
+      <c r="H100" s="12">
+        <v>30543662.31</v>
+      </c>
+      <c r="I100" s="13">
+        <v>28044628.6</v>
+      </c>
+      <c r="J100" s="12">
+        <v>2499033.709999997</v>
+      </c>
+      <c r="K100" s="14">
         <v>44826</v>
       </c>
-      <c r="L100" s="10">
+      <c r="L100" s="14">
         <v>45540</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A101" s="7" t="s">
+      <c r="A101" s="11" t="s">
         <v>374</v>
       </c>
-      <c r="B101" s="7" t="s">
+      <c r="B101" s="11" t="s">
         <v>394</v>
       </c>
-      <c r="C101" s="7" t="s">
+      <c r="C101" s="11" t="s">
         <v>395</v>
       </c>
-      <c r="D101" s="7" t="s">
+      <c r="D101" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E101" s="7" t="s">
+      <c r="E101" s="11" t="s">
         <v>396</v>
       </c>
-      <c r="F101" s="7" t="s">
+      <c r="F101" s="11" t="s">
         <v>397</v>
       </c>
-      <c r="G101" s="7">
-        <v>0.91879999999999995</v>
-      </c>
-      <c r="H101" s="8">
-        <v>54913544.950000003</v>
-      </c>
-      <c r="I101" s="9">
-        <v>50454918.609999999</v>
-      </c>
-      <c r="J101" s="8">
-        <v>4458626.3400000036</v>
-      </c>
-      <c r="K101" s="10">
+      <c r="G101" s="11">
+        <v>0.9188</v>
+      </c>
+      <c r="H101" s="12">
+        <v>54913544.95</v>
+      </c>
+      <c r="I101" s="13">
+        <v>50454918.61</v>
+      </c>
+      <c r="J101" s="12">
+        <v>4458626.340000004</v>
+      </c>
+      <c r="K101" s="14">
         <v>44769</v>
       </c>
-      <c r="L101" s="10">
+      <c r="L101" s="14">
         <v>45174</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A102" s="7" t="s">
+      <c r="A102" s="11" t="s">
         <v>374</v>
       </c>
-      <c r="B102" s="7" t="s">
+      <c r="B102" s="11" t="s">
         <v>398</v>
       </c>
-      <c r="C102" s="7" t="s">
+      <c r="C102" s="11" t="s">
         <v>399</v>
       </c>
-      <c r="D102" s="7" t="s">
+      <c r="D102" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E102" s="7" t="s">
+      <c r="E102" s="11" t="s">
         <v>400</v>
       </c>
-      <c r="F102" s="7" t="s">
+      <c r="F102" s="11" t="s">
         <v>401</v>
       </c>
-      <c r="G102" s="7">
-        <v>0.77390000000000003</v>
-      </c>
-      <c r="H102" s="8">
+      <c r="G102" s="11">
+        <v>0.7739</v>
+      </c>
+      <c r="H102" s="12">
         <v>27434724</v>
       </c>
-      <c r="I102" s="9">
-        <v>21232327.940000001</v>
-      </c>
-      <c r="J102" s="8">
-        <v>6202396.0599999987</v>
-      </c>
-      <c r="K102" s="10">
+      <c r="I102" s="13">
+        <v>21232327.94</v>
+      </c>
+      <c r="J102" s="12">
+        <v>6202396.059999999</v>
+      </c>
+      <c r="K102" s="14">
         <v>46002</v>
       </c>
-      <c r="L102" s="10">
+      <c r="L102" s="14">
         <v>46242</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A103" s="7" t="s">
+      <c r="A103" s="11" t="s">
         <v>374</v>
       </c>
-      <c r="B103" s="7" t="s">
+      <c r="B103" s="11" t="s">
         <v>402</v>
       </c>
-      <c r="C103" s="7" t="s">
+      <c r="C103" s="11" t="s">
         <v>403</v>
       </c>
-      <c r="D103" s="7" t="s">
+      <c r="D103" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E103" s="7" t="s">
+      <c r="E103" s="11" t="s">
         <v>404</v>
       </c>
-      <c r="F103" s="7" t="s">
+      <c r="F103" s="11" t="s">
         <v>405</v>
       </c>
-      <c r="G103" s="7">
+      <c r="G103" s="11">
         <v>0.9224</v>
       </c>
-      <c r="H103" s="8">
-        <v>80552394.920000002</v>
-      </c>
-      <c r="I103" s="9">
-        <v>74305045.469999999</v>
-      </c>
-      <c r="J103" s="8">
+      <c r="H103" s="12">
+        <v>80552394.92</v>
+      </c>
+      <c r="I103" s="13">
+        <v>74305045.47</v>
+      </c>
+      <c r="J103" s="12">
         <v>6247349.450000003</v>
       </c>
-      <c r="K103" s="10">
+      <c r="K103" s="14">
         <v>44709</v>
       </c>
-      <c r="L103" s="10">
+      <c r="L103" s="14">
         <v>45114</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A104" s="7" t="s">
+      <c r="A104" s="11" t="s">
         <v>374</v>
       </c>
-      <c r="B104" s="7" t="s">
+      <c r="B104" s="11" t="s">
         <v>406</v>
       </c>
-      <c r="C104" s="7" t="s">
+      <c r="C104" s="11" t="s">
         <v>407</v>
       </c>
-      <c r="D104" s="7" t="s">
+      <c r="D104" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E104" s="7" t="s">
+      <c r="E104" s="11" t="s">
         <v>408</v>
       </c>
-      <c r="F104" s="7" t="s">
+      <c r="F104" s="11" t="s">
         <v>409</v>
       </c>
-      <c r="G104" s="7">
+      <c r="G104" s="11">
         <v>0.4476</v>
       </c>
-      <c r="H104" s="8">
-        <v>68148567.140000001</v>
-      </c>
-      <c r="I104" s="9">
+      <c r="H104" s="12">
+        <v>68148567.14</v>
+      </c>
+      <c r="I104" s="13">
         <v>30502735.41</v>
       </c>
-      <c r="J104" s="8">
+      <c r="J104" s="12">
         <v>37645831.730000004</v>
       </c>
-      <c r="K104" s="10">
+      <c r="K104" s="14">
         <v>44767</v>
       </c>
-      <c r="L104" s="10">
+      <c r="L104" s="14">
         <v>45173</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A105" s="7" t="s">
+      <c r="A105" s="11" t="s">
         <v>410</v>
       </c>
-      <c r="B105" s="7" t="s">
+      <c r="B105" s="11" t="s">
         <v>411</v>
       </c>
-      <c r="C105" s="7" t="s">
+      <c r="C105" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="D105" s="7" t="s">
+      <c r="D105" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E105" s="7" t="s">
+      <c r="E105" s="11" t="s">
         <v>413</v>
       </c>
-      <c r="F105" s="7" t="s">
+      <c r="F105" s="11" t="s">
         <v>414</v>
       </c>
-      <c r="G105" s="7">
-        <v>0.99840000000000007</v>
-      </c>
-      <c r="H105" s="8">
+      <c r="G105" s="11">
+        <v>0.9984000000000001</v>
+      </c>
+      <c r="H105" s="12">
         <v>1498793.43</v>
       </c>
-      <c r="I105" s="9">
+      <c r="I105" s="13">
         <v>1496414.32</v>
       </c>
-      <c r="J105" s="8">
+      <c r="J105" s="12">
         <v>2379.1099999998696</v>
       </c>
-      <c r="K105" s="10">
+      <c r="K105" s="14">
         <v>45195</v>
       </c>
-      <c r="L105" s="10">
+      <c r="L105" s="14">
         <v>45121</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A106" s="7" t="s">
+      <c r="A106" s="11" t="s">
         <v>410</v>
       </c>
-      <c r="B106" s="7" t="s">
+      <c r="B106" s="11" t="s">
         <v>415</v>
       </c>
-      <c r="C106" s="7" t="s">
+      <c r="C106" s="11" t="s">
         <v>416</v>
       </c>
-      <c r="D106" s="7" t="s">
+      <c r="D106" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E106" s="7" t="s">
+      <c r="E106" s="11" t="s">
         <v>417</v>
       </c>
-      <c r="F106" s="7" t="s">
+      <c r="F106" s="11" t="s">
         <v>294</v>
       </c>
-      <c r="G106" s="7">
-        <v>0.97180000000000011</v>
-      </c>
-      <c r="H106" s="8">
+      <c r="G106" s="11">
+        <v>0.9718000000000001</v>
+      </c>
+      <c r="H106" s="12">
         <v>1988555.07</v>
       </c>
-      <c r="I106" s="9">
+      <c r="I106" s="13">
         <v>1932548.63</v>
       </c>
-      <c r="J106" s="8">
-        <v>56006.440000000177</v>
-      </c>
-      <c r="K106" s="10">
+      <c r="J106" s="12">
+        <v>56006.44000000018</v>
+      </c>
+      <c r="K106" s="14">
         <v>44742</v>
       </c>
-      <c r="L106" s="10">
+      <c r="L106" s="14">
         <v>45412</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A107" s="7" t="s">
+      <c r="A107" s="11" t="s">
         <v>410</v>
       </c>
-      <c r="B107" s="7" t="s">
+      <c r="B107" s="11" t="s">
         <v>418</v>
       </c>
-      <c r="C107" s="7" t="s">
+      <c r="C107" s="11" t="s">
         <v>419</v>
       </c>
-      <c r="D107" s="7" t="s">
+      <c r="D107" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E107" s="7" t="s">
+      <c r="E107" s="11" t="s">
         <v>420</v>
       </c>
-      <c r="F107" s="7" t="s">
+      <c r="F107" s="11" t="s">
         <v>397</v>
       </c>
-      <c r="G107" s="7">
-        <v>0.60799999999999998</v>
-      </c>
-      <c r="H107" s="8">
+      <c r="G107" s="11">
+        <v>0.608</v>
+      </c>
+      <c r="H107" s="12">
         <v>2860442.12</v>
       </c>
-      <c r="I107" s="9">
+      <c r="I107" s="13">
         <v>1739254.2</v>
       </c>
-      <c r="J107" s="8">
+      <c r="J107" s="12">
         <v>1121187.9200000002</v>
       </c>
-      <c r="K107" s="10">
+      <c r="K107" s="14">
         <v>45782</v>
       </c>
-      <c r="L107" s="10">
+      <c r="L107" s="14">
         <v>46083</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A108" s="7" t="s">
+      <c r="A108" s="11" t="s">
         <v>421</v>
       </c>
-      <c r="B108" s="7" t="s">
+      <c r="B108" s="11" t="s">
         <v>422</v>
       </c>
-      <c r="C108" s="7" t="s">
+      <c r="C108" s="11" t="s">
         <v>403</v>
       </c>
-      <c r="D108" s="7" t="s">
+      <c r="D108" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E108" s="7" t="s">
+      <c r="E108" s="11" t="s">
         <v>423</v>
       </c>
-      <c r="F108" s="7" t="s">
+      <c r="F108" s="11" t="s">
         <v>424</v>
       </c>
-      <c r="G108" s="7">
+      <c r="G108" s="11">
         <v>0.9998999999999999</v>
       </c>
-      <c r="H108" s="8">
+      <c r="H108" s="12">
         <v>5272095.08</v>
       </c>
-      <c r="I108" s="9">
+      <c r="I108" s="13">
         <v>5271693.21</v>
       </c>
-      <c r="J108" s="8">
+      <c r="J108" s="12">
         <v>401.87000000011176</v>
       </c>
-      <c r="K108" s="10">
+      <c r="K108" s="14">
         <v>44746</v>
       </c>
-      <c r="L108" s="10">
+      <c r="L108" s="14">
         <v>45560</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A109" s="7" t="s">
+      <c r="A109" s="11" t="s">
         <v>421</v>
       </c>
-      <c r="B109" s="7" t="s">
+      <c r="B109" s="11" t="s">
         <v>425</v>
       </c>
-      <c r="C109" s="7" t="s">
+      <c r="C109" s="11" t="s">
         <v>426</v>
       </c>
-      <c r="D109" s="7" t="s">
+      <c r="D109" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E109" s="7" t="s">
+      <c r="E109" s="11" t="s">
         <v>427</v>
       </c>
-      <c r="F109" s="7" t="s">
+      <c r="F109" s="11" t="s">
         <v>294</v>
       </c>
-      <c r="G109" s="7">
-        <v>0.99309999999999998</v>
-      </c>
-      <c r="H109" s="8">
+      <c r="G109" s="11">
+        <v>0.9931</v>
+      </c>
+      <c r="H109" s="12">
         <v>1690234.37</v>
       </c>
-      <c r="I109" s="9">
+      <c r="I109" s="13">
         <v>1678610.19</v>
       </c>
-      <c r="J109" s="8">
+      <c r="J109" s="12">
         <v>11624.180000000168</v>
       </c>
-      <c r="K109" s="10">
+      <c r="K109" s="14">
         <v>44772</v>
       </c>
-      <c r="L109" s="10">
+      <c r="L109" s="14">
         <v>45316</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A110" s="7" t="s">
+      <c r="A110" s="11" t="s">
         <v>421</v>
       </c>
-      <c r="B110" s="7" t="s">
+      <c r="B110" s="11" t="s">
         <v>428</v>
       </c>
-      <c r="C110" s="7" t="s">
+      <c r="C110" s="11" t="s">
         <v>429</v>
       </c>
-      <c r="D110" s="7" t="s">
+      <c r="D110" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E110" s="7" t="s">
+      <c r="E110" s="11" t="s">
         <v>430</v>
       </c>
-      <c r="F110" s="7" t="s">
+      <c r="F110" s="11" t="s">
         <v>431</v>
       </c>
-      <c r="G110" s="7">
-        <v>0.99939999999999996</v>
-      </c>
-      <c r="H110" s="8">
-        <v>26946699.359999999</v>
-      </c>
-      <c r="I110" s="9">
+      <c r="G110" s="11">
+        <v>0.9994</v>
+      </c>
+      <c r="H110" s="12">
+        <v>26946699.36</v>
+      </c>
+      <c r="I110" s="13">
         <v>26930984.02</v>
       </c>
-      <c r="J110" s="8">
+      <c r="J110" s="12">
         <v>15715.339999999851</v>
       </c>
-      <c r="K110" s="10">
+      <c r="K110" s="14">
         <v>44823</v>
       </c>
-      <c r="L110" s="10">
+      <c r="L110" s="14">
         <v>45816</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A111" s="7" t="s">
+      <c r="A111" s="11" t="s">
         <v>432</v>
       </c>
-      <c r="B111" s="7" t="s">
+      <c r="B111" s="11" t="s">
         <v>433</v>
       </c>
-      <c r="C111" s="7" t="s">
+      <c r="C111" s="11" t="s">
         <v>434</v>
       </c>
-      <c r="D111" s="7" t="s">
+      <c r="D111" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E111" s="7" t="s">
+      <c r="E111" s="11" t="s">
         <v>435</v>
       </c>
-      <c r="F111" s="7" t="s">
+      <c r="F111" s="11" t="s">
         <v>424</v>
       </c>
-      <c r="G111" s="7">
+      <c r="G111" s="11">
         <v>1</v>
       </c>
-      <c r="H111" s="8">
+      <c r="H111" s="12">
         <v>3607367.42</v>
       </c>
-      <c r="I111" s="9">
+      <c r="I111" s="13">
         <v>3607318.65</v>
       </c>
-      <c r="J111" s="8">
-        <v>48.770000000018626</v>
-      </c>
-      <c r="K111" s="10">
+      <c r="J111" s="12">
+        <v>48.77000000001863</v>
+      </c>
+      <c r="K111" s="14">
         <v>45061</v>
       </c>
-      <c r="L111" s="10">
+      <c r="L111" s="14">
         <v>45016</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A112" s="7" t="s">
+      <c r="A112" s="11" t="s">
         <v>432</v>
       </c>
-      <c r="B112" s="7" t="s">
+      <c r="B112" s="11" t="s">
         <v>436</v>
       </c>
-      <c r="C112" s="7" t="s">
+      <c r="C112" s="11" t="s">
         <v>437</v>
       </c>
-      <c r="D112" s="7" t="s">
+      <c r="D112" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E112" s="7" t="s">
+      <c r="E112" s="11" t="s">
         <v>438</v>
       </c>
-      <c r="F112" s="7" t="s">
+      <c r="F112" s="11" t="s">
         <v>424</v>
       </c>
-      <c r="G112" s="7">
-        <v>0.99580000000000002</v>
-      </c>
-      <c r="H112" s="8">
+      <c r="G112" s="11">
+        <v>0.9958</v>
+      </c>
+      <c r="H112" s="12">
         <v>4645152.25</v>
       </c>
-      <c r="I112" s="9">
+      <c r="I112" s="13">
         <v>4625557.49</v>
       </c>
-      <c r="J112" s="8">
+      <c r="J112" s="12">
         <v>19594.759999999776</v>
       </c>
-      <c r="K112" s="10">
+      <c r="K112" s="14">
         <v>44918</v>
       </c>
-      <c r="L112" s="10">
+      <c r="L112" s="14">
         <v>45485</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A113" s="7" t="s">
+      <c r="A113" s="11" t="s">
         <v>439</v>
       </c>
-      <c r="B113" s="7" t="s">
+      <c r="B113" s="11" t="s">
         <v>440</v>
       </c>
-      <c r="C113" s="7" t="s">
+      <c r="C113" s="11" t="s">
         <v>441</v>
       </c>
-      <c r="D113" s="7" t="s">
+      <c r="D113" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E113" s="7" t="s">
+      <c r="E113" s="11" t="s">
         <v>442</v>
       </c>
-      <c r="F113" s="7" t="s">
+      <c r="F113" s="11" t="s">
         <v>443</v>
       </c>
-      <c r="G113" s="7">
+      <c r="G113" s="11">
         <v>1</v>
       </c>
-      <c r="H113" s="8">
-        <v>13242425.640000001</v>
-      </c>
-      <c r="I113" s="9">
+      <c r="H113" s="12">
+        <v>13242425.64</v>
+      </c>
+      <c r="I113" s="13">
         <v>13242495.84</v>
       </c>
-      <c r="J113" s="8">
-        <v>-70.199999999254942</v>
-      </c>
-      <c r="K113" s="10">
+      <c r="J113" s="12">
+        <v>-70.19999999925494</v>
+      </c>
+      <c r="K113" s="14">
         <v>44923</v>
       </c>
-      <c r="L113" s="10">
+      <c r="L113" s="14">
         <v>45531</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A114" s="7" t="s">
+      <c r="A114" s="11" t="s">
         <v>439</v>
       </c>
-      <c r="B114" s="7" t="s">
+      <c r="B114" s="11" t="s">
         <v>444</v>
       </c>
-      <c r="C114" s="7" t="s">
+      <c r="C114" s="11" t="s">
         <v>445</v>
       </c>
-      <c r="D114" s="7" t="s">
+      <c r="D114" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E114" s="7" t="s">
+      <c r="E114" s="11" t="s">
         <v>446</v>
       </c>
-      <c r="F114" s="7" t="s">
+      <c r="F114" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G114" s="7">
+      <c r="G114" s="11">
         <v>1</v>
       </c>
-      <c r="H114" s="8">
-        <v>20859068.440000001</v>
-      </c>
-      <c r="I114" s="9">
-        <v>20859068.440000001</v>
-      </c>
-      <c r="J114" s="8">
+      <c r="H114" s="12">
+        <v>20859068.44</v>
+      </c>
+      <c r="I114" s="13">
+        <v>20859068.44</v>
+      </c>
+      <c r="J114" s="12">
         <v>0</v>
       </c>
-      <c r="K114" s="10">
+      <c r="K114" s="14">
         <v>45007</v>
       </c>
-      <c r="L114" s="10">
+      <c r="L114" s="14">
         <v>45851</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A115" s="7" t="s">
+      <c r="A115" s="11" t="s">
         <v>439</v>
       </c>
-      <c r="B115" s="7" t="s">
+      <c r="B115" s="11" t="s">
         <v>447</v>
       </c>
-      <c r="C115" s="7" t="s">
+      <c r="C115" s="11" t="s">
         <v>448</v>
       </c>
-      <c r="D115" s="7" t="s">
+      <c r="D115" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E115" s="7" t="s">
+      <c r="E115" s="11" t="s">
         <v>449</v>
       </c>
-      <c r="F115" s="7" t="s">
+      <c r="F115" s="11" t="s">
         <v>450</v>
       </c>
-      <c r="G115" s="7">
-        <v>0.98419999999999996</v>
-      </c>
-      <c r="H115" s="8">
-        <v>20229149.789999999</v>
-      </c>
-      <c r="I115" s="9">
-        <v>19910398.370000001</v>
-      </c>
-      <c r="J115" s="8">
+      <c r="G115" s="11">
+        <v>0.9842</v>
+      </c>
+      <c r="H115" s="12">
+        <v>20229149.79</v>
+      </c>
+      <c r="I115" s="13">
+        <v>19910398.37</v>
+      </c>
+      <c r="J115" s="12">
         <v>318751.41999999806</v>
       </c>
-      <c r="K115" s="10">
+      <c r="K115" s="14">
         <v>44697</v>
       </c>
-      <c r="L115" s="10">
+      <c r="L115" s="14">
         <v>45783</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A116" s="7" t="s">
+      <c r="A116" s="11" t="s">
         <v>439</v>
       </c>
-      <c r="B116" s="7" t="s">
+      <c r="B116" s="11" t="s">
         <v>451</v>
       </c>
-      <c r="C116" s="7" t="s">
+      <c r="C116" s="11" t="s">
         <v>452</v>
       </c>
-      <c r="D116" s="7" t="s">
+      <c r="D116" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E116" s="7" t="s">
+      <c r="E116" s="11" t="s">
         <v>453</v>
       </c>
-      <c r="F116" s="7" t="s">
+      <c r="F116" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G116" s="7">
+      <c r="G116" s="11">
         <v>0</v>
       </c>
-      <c r="H116" s="8">
-        <v>6784130.4400000004</v>
-      </c>
-      <c r="I116" s="9">
+      <c r="H116" s="12">
+        <v>6784130.44</v>
+      </c>
+      <c r="I116" s="13">
         <v>0</v>
       </c>
-      <c r="J116" s="8">
-        <v>6784130.4400000004</v>
-      </c>
-      <c r="K116" s="10">
+      <c r="J116" s="12">
+        <v>6784130.44</v>
+      </c>
+      <c r="K116" s="14">
         <v>45100</v>
       </c>
-      <c r="L116" s="10">
+      <c r="L116" s="14">
         <v>45400</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A117" s="7" t="s">
+      <c r="A117" s="11" t="s">
         <v>439</v>
       </c>
-      <c r="B117" s="7" t="s">
+      <c r="B117" s="11" t="s">
         <v>454</v>
       </c>
-      <c r="C117" s="7" t="s">
+      <c r="C117" s="11" t="s">
         <v>334</v>
       </c>
-      <c r="D117" s="7" t="s">
+      <c r="D117" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E117" s="7" t="s">
+      <c r="E117" s="11" t="s">
         <v>455</v>
       </c>
-      <c r="F117" s="7" t="s">
+      <c r="F117" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="G117" s="7">
-        <v>0.66049999999999998</v>
-      </c>
-      <c r="H117" s="8">
-        <v>20185137.809999999</v>
-      </c>
-      <c r="I117" s="9">
+      <c r="G117" s="11">
+        <v>0.6605</v>
+      </c>
+      <c r="H117" s="12">
+        <v>20185137.81</v>
+      </c>
+      <c r="I117" s="13">
         <v>13332401.6</v>
       </c>
-      <c r="J117" s="8">
+      <c r="J117" s="12">
         <v>6852736.209999999</v>
       </c>
-      <c r="K117" s="10">
+      <c r="K117" s="14">
         <v>44754</v>
       </c>
-      <c r="L117" s="10">
+      <c r="L117" s="14">
         <v>45566</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A118" s="7" t="s">
+      <c r="A118" s="11" t="s">
         <v>439</v>
       </c>
-      <c r="B118" s="7" t="s">
+      <c r="B118" s="11" t="s">
         <v>456</v>
       </c>
-      <c r="C118" s="7" t="s">
+      <c r="C118" s="11" t="s">
         <v>457</v>
       </c>
-      <c r="D118" s="7" t="s">
+      <c r="D118" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E118" s="7" t="s">
+      <c r="E118" s="11" t="s">
         <v>458</v>
       </c>
-      <c r="F118" s="7" t="s">
+      <c r="F118" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G118" s="7">
-        <v>1.6500000000000001E-2</v>
-      </c>
-      <c r="H118" s="8">
-        <v>7430869.3200000003</v>
-      </c>
-      <c r="I118" s="9">
+      <c r="G118" s="11">
+        <v>0.0165</v>
+      </c>
+      <c r="H118" s="12">
+        <v>7430869.32</v>
+      </c>
+      <c r="I118" s="13">
         <v>122778.19</v>
       </c>
-      <c r="J118" s="8">
-        <v>7308091.1299999999</v>
-      </c>
-      <c r="K118" s="10">
+      <c r="J118" s="12">
+        <v>7308091.13</v>
+      </c>
+      <c r="K118" s="14">
         <v>45865</v>
       </c>
-      <c r="L118" s="10">
+      <c r="L118" s="14">
         <v>46166</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A119" s="7" t="s">
+      <c r="A119" s="11" t="s">
         <v>459</v>
       </c>
-      <c r="B119" s="7" t="s">
+      <c r="B119" s="11" t="s">
         <v>460</v>
       </c>
-      <c r="C119" s="7" t="s">
+      <c r="C119" s="11" t="s">
         <v>461</v>
       </c>
-      <c r="D119" s="7" t="s">
+      <c r="D119" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E119" s="7" t="s">
+      <c r="E119" s="11" t="s">
         <v>462</v>
       </c>
-      <c r="F119" s="7" t="s">
+      <c r="F119" s="11" t="s">
         <v>424</v>
       </c>
-      <c r="G119" s="7">
-        <v>0.99029999999999996</v>
-      </c>
-      <c r="H119" s="8">
+      <c r="G119" s="11">
+        <v>0.9903</v>
+      </c>
+      <c r="H119" s="12">
         <v>11046611.98</v>
       </c>
-      <c r="I119" s="9">
-        <v>10939879.390000001</v>
-      </c>
-      <c r="J119" s="8">
+      <c r="I119" s="13">
+        <v>10939879.39</v>
+      </c>
+      <c r="J119" s="12">
         <v>106732.58999999985</v>
       </c>
-      <c r="K119" s="10">
+      <c r="K119" s="14">
         <v>44663</v>
       </c>
-      <c r="L119" s="10">
+      <c r="L119" s="14">
         <v>45507</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A120" s="7" t="s">
+      <c r="A120" s="11" t="s">
         <v>459</v>
       </c>
-      <c r="B120" s="7" t="s">
+      <c r="B120" s="11" t="s">
         <v>463</v>
       </c>
-      <c r="C120" s="7" t="s">
+      <c r="C120" s="11" t="s">
         <v>464</v>
       </c>
-      <c r="D120" s="7" t="s">
+      <c r="D120" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E120" s="7" t="s">
+      <c r="E120" s="11" t="s">
         <v>465</v>
       </c>
-      <c r="F120" s="7" t="s">
+      <c r="F120" s="11" t="s">
         <v>466</v>
       </c>
-      <c r="G120" s="7">
-        <v>0.80790000000000006</v>
-      </c>
-      <c r="H120" s="8">
+      <c r="G120" s="11">
+        <v>0.8079000000000001</v>
+      </c>
+      <c r="H120" s="12">
         <v>2755604.93</v>
       </c>
-      <c r="I120" s="9">
-        <v>2226331.4500000002</v>
-      </c>
-      <c r="J120" s="8">
+      <c r="I120" s="13">
+        <v>2226331.45</v>
+      </c>
+      <c r="J120" s="12">
         <v>529273.48</v>
       </c>
-      <c r="K120" s="10">
+      <c r="K120" s="14">
         <v>45026</v>
       </c>
-      <c r="L120" s="10">
+      <c r="L120" s="14">
         <v>46023</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A121" s="7" t="s">
+      <c r="A121" s="11" t="s">
         <v>459</v>
       </c>
-      <c r="B121" s="7" t="s">
+      <c r="B121" s="11" t="s">
         <v>467</v>
       </c>
-      <c r="C121" s="7" t="s">
+      <c r="C121" s="11" t="s">
         <v>468</v>
       </c>
-      <c r="D121" s="7" t="s">
+      <c r="D121" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E121" s="7" t="s">
+      <c r="E121" s="11" t="s">
         <v>469</v>
       </c>
-      <c r="F121" s="7" t="s">
+      <c r="F121" s="11" t="s">
         <v>466</v>
       </c>
-      <c r="G121" s="7">
+      <c r="G121" s="11">
         <v>0</v>
       </c>
-      <c r="H121" s="8">
+      <c r="H121" s="12">
         <v>1712576.84</v>
       </c>
-      <c r="I121" s="9">
+      <c r="I121" s="13">
         <v>0</v>
       </c>
-      <c r="J121" s="8">
+      <c r="J121" s="12">
         <v>1712576.84</v>
       </c>
-      <c r="K121" s="10">
+      <c r="K121" s="14">
         <v>44823</v>
       </c>
-      <c r="L121" s="10">
+      <c r="L121" s="14">
         <v>44706</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A122" s="7" t="s">
+      <c r="A122" s="11" t="s">
         <v>470</v>
       </c>
-      <c r="B122" s="7" t="s">
+      <c r="B122" s="11" t="s">
         <v>471</v>
       </c>
-      <c r="C122" s="7" t="s">
+      <c r="C122" s="11" t="s">
         <v>472</v>
       </c>
-      <c r="D122" s="7" t="s">
+      <c r="D122" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E122" s="7" t="s">
+      <c r="E122" s="11" t="s">
         <v>473</v>
       </c>
-      <c r="F122" s="7" t="s">
+      <c r="F122" s="11" t="s">
         <v>474</v>
       </c>
-      <c r="G122" s="7">
+      <c r="G122" s="11">
         <v>0.9998999999999999</v>
       </c>
-      <c r="H122" s="8">
+      <c r="H122" s="12">
         <v>1612154.63</v>
       </c>
-      <c r="I122" s="9">
+      <c r="I122" s="13">
         <v>1612024.85</v>
       </c>
-      <c r="J122" s="8">
-        <v>129.77999999979511</v>
-      </c>
-      <c r="K122" s="10">
+      <c r="J122" s="12">
+        <v>129.7799999997951</v>
+      </c>
+      <c r="K122" s="14">
         <v>45776</v>
       </c>
-      <c r="L122" s="10">
+      <c r="L122" s="14">
         <v>45986</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A123" s="7" t="s">
+      <c r="A123" s="11" t="s">
         <v>475</v>
       </c>
-      <c r="B123" s="7" t="s">
+      <c r="B123" s="11" t="s">
         <v>476</v>
       </c>
-      <c r="C123" s="7" t="s">
+      <c r="C123" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="D123" s="7" t="s">
+      <c r="D123" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E123" s="7" t="s">
+      <c r="E123" s="11" t="s">
         <v>477</v>
       </c>
-      <c r="F123" s="7" t="s">
+      <c r="F123" s="11" t="s">
         <v>478</v>
       </c>
-      <c r="G123" s="7">
+      <c r="G123" s="11">
         <v>1</v>
       </c>
-      <c r="H123" s="8">
-        <v>6453162.7199999997</v>
-      </c>
-      <c r="I123" s="9">
-        <v>6453162.7199999997</v>
-      </c>
-      <c r="J123" s="8">
+      <c r="H123" s="12">
+        <v>6453162.72</v>
+      </c>
+      <c r="I123" s="13">
+        <v>6453162.72</v>
+      </c>
+      <c r="J123" s="12">
         <v>0</v>
       </c>
-      <c r="K123" s="10">
+      <c r="K123" s="14">
         <v>44760</v>
       </c>
-      <c r="L123" s="10">
+      <c r="L123" s="14">
         <v>45201</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A124" s="7" t="s">
+      <c r="A124" s="11" t="s">
         <v>475</v>
       </c>
-      <c r="B124" s="7" t="s">
+      <c r="B124" s="11" t="s">
         <v>479</v>
       </c>
-      <c r="C124" s="7" t="s">
+      <c r="C124" s="11" t="s">
         <v>480</v>
       </c>
-      <c r="D124" s="7" t="s">
+      <c r="D124" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E124" s="7" t="s">
+      <c r="E124" s="11" t="s">
         <v>481</v>
       </c>
-      <c r="F124" s="7" t="s">
+      <c r="F124" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="G124" s="7">
-        <v>0.99930000000000008</v>
-      </c>
-      <c r="H124" s="8">
+      <c r="G124" s="11">
+        <v>0.9993000000000001</v>
+      </c>
+      <c r="H124" s="12">
         <v>1741703.69</v>
       </c>
-      <c r="I124" s="9">
+      <c r="I124" s="13">
         <v>1740561.74</v>
       </c>
-      <c r="J124" s="8">
+      <c r="J124" s="12">
         <v>1141.9499999999534</v>
       </c>
-      <c r="K124" s="10">
+      <c r="K124" s="14">
         <v>44683</v>
       </c>
-      <c r="L124" s="10">
+      <c r="L124" s="14">
         <v>45889</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A125" s="7" t="s">
+      <c r="A125" s="11" t="s">
         <v>475</v>
       </c>
-      <c r="B125" s="7" t="s">
+      <c r="B125" s="11" t="s">
         <v>482</v>
       </c>
-      <c r="C125" s="7" t="s">
+      <c r="C125" s="11" t="s">
         <v>483</v>
       </c>
-      <c r="D125" s="7" t="s">
+      <c r="D125" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E125" s="7" t="s">
+      <c r="E125" s="11" t="s">
         <v>484</v>
       </c>
-      <c r="F125" s="7" t="s">
+      <c r="F125" s="11" t="s">
         <v>485</v>
       </c>
-      <c r="G125" s="7">
+      <c r="G125" s="11">
         <v>0.997</v>
       </c>
-      <c r="H125" s="8">
-        <v>6014775.7699999996</v>
-      </c>
-      <c r="I125" s="9">
-        <v>5996889.6799999997</v>
-      </c>
-      <c r="J125" s="8">
-        <v>17886.089999999851</v>
-      </c>
-      <c r="K125" s="10">
+      <c r="H125" s="12">
+        <v>6014775.77</v>
+      </c>
+      <c r="I125" s="13">
+        <v>5996889.68</v>
+      </c>
+      <c r="J125" s="12">
+        <v>17886.08999999985</v>
+      </c>
+      <c r="K125" s="14">
         <v>44708</v>
       </c>
-      <c r="L125" s="10">
+      <c r="L125" s="14">
         <v>45467</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A126" s="7" t="s">
+      <c r="A126" s="11" t="s">
         <v>475</v>
       </c>
-      <c r="B126" s="7" t="s">
+      <c r="B126" s="11" t="s">
         <v>486</v>
       </c>
-      <c r="C126" s="7" t="s">
+      <c r="C126" s="11" t="s">
         <v>487</v>
       </c>
-      <c r="D126" s="7" t="s">
+      <c r="D126" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E126" s="7" t="s">
+      <c r="E126" s="11" t="s">
         <v>488</v>
       </c>
-      <c r="F126" s="7" t="s">
+      <c r="F126" s="11" t="s">
         <v>485</v>
       </c>
-      <c r="G126" s="7">
-        <v>0.99129999999999996</v>
-      </c>
-      <c r="H126" s="8">
+      <c r="G126" s="11">
+        <v>0.9913</v>
+      </c>
+      <c r="H126" s="12">
         <v>3569195.39</v>
       </c>
-      <c r="I126" s="9">
+      <c r="I126" s="13">
         <v>3538001.16</v>
       </c>
-      <c r="J126" s="8">
-        <v>31194.229999999981</v>
-      </c>
-      <c r="K126" s="10">
+      <c r="J126" s="12">
+        <v>31194.22999999998</v>
+      </c>
+      <c r="K126" s="14">
         <v>44658</v>
       </c>
-      <c r="L126" s="10">
+      <c r="L126" s="14">
         <v>45426</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A127" s="7" t="s">
+      <c r="A127" s="11" t="s">
         <v>475</v>
       </c>
-      <c r="B127" s="7" t="s">
+      <c r="B127" s="11" t="s">
         <v>489</v>
       </c>
-      <c r="C127" s="7" t="s">
+      <c r="C127" s="11" t="s">
         <v>490</v>
       </c>
-      <c r="D127" s="7" t="s">
+      <c r="D127" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E127" s="7" t="s">
+      <c r="E127" s="11" t="s">
         <v>491</v>
       </c>
-      <c r="F127" s="7" t="s">
+      <c r="F127" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="G127" s="7">
-        <v>0.79930000000000012</v>
-      </c>
-      <c r="H127" s="8">
+      <c r="G127" s="11">
+        <v>0.7993000000000001</v>
+      </c>
+      <c r="H127" s="12">
         <v>1528883.61</v>
       </c>
-      <c r="I127" s="9">
-        <v>1222003.4099999999</v>
-      </c>
-      <c r="J127" s="8">
-        <v>306880.20000000019</v>
-      </c>
-      <c r="K127" s="10">
+      <c r="I127" s="13">
+        <v>1222003.41</v>
+      </c>
+      <c r="J127" s="12">
+        <v>306880.2000000002</v>
+      </c>
+      <c r="K127" s="14">
         <v>44655</v>
       </c>
-      <c r="L127" s="10">
+      <c r="L127" s="14">
         <v>46164</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A128" s="7" t="s">
+      <c r="A128" s="11" t="s">
         <v>475</v>
       </c>
-      <c r="B128" s="7" t="s">
+      <c r="B128" s="11" t="s">
         <v>492</v>
       </c>
-      <c r="C128" s="7" t="s">
+      <c r="C128" s="11" t="s">
         <v>493</v>
       </c>
-      <c r="D128" s="7" t="s">
+      <c r="D128" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E128" s="7" t="s">
+      <c r="E128" s="11" t="s">
         <v>494</v>
       </c>
-      <c r="F128" s="7" t="s">
+      <c r="F128" s="11" t="s">
         <v>495</v>
       </c>
-      <c r="G128" s="7">
-        <v>2.4500000000000001E-2</v>
-      </c>
-      <c r="H128" s="8">
-        <v>2317778.2200000002</v>
-      </c>
-      <c r="I128" s="9">
+      <c r="G128" s="11">
+        <v>0.0245</v>
+      </c>
+      <c r="H128" s="12">
+        <v>2317778.22</v>
+      </c>
+      <c r="I128" s="13">
         <v>56828.03</v>
       </c>
-      <c r="J128" s="8">
+      <c r="J128" s="12">
         <v>2260950.1900000004</v>
       </c>
-      <c r="K128" s="10">
+      <c r="K128" s="14">
         <v>45035</v>
       </c>
-      <c r="L128" s="10">
+      <c r="L128" s="14">
         <v>45396</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A129" s="7" t="s">
+      <c r="A129" s="11" t="s">
         <v>496</v>
       </c>
-      <c r="B129" s="7" t="s">
+      <c r="B129" s="11" t="s">
         <v>497</v>
       </c>
-      <c r="C129" s="7" t="s">
+      <c r="C129" s="11" t="s">
         <v>498</v>
       </c>
-      <c r="D129" s="7" t="s">
+      <c r="D129" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E129" s="7" t="s">
+      <c r="E129" s="11" t="s">
         <v>499</v>
       </c>
-      <c r="F129" s="7" t="s">
+      <c r="F129" s="11" t="s">
         <v>500</v>
       </c>
-      <c r="G129" s="7">
+      <c r="G129" s="11">
         <v>1</v>
       </c>
-      <c r="H129" s="8">
-        <v>6478069.4299999997</v>
-      </c>
-      <c r="I129" s="9">
-        <v>6478029.4400000004</v>
-      </c>
-      <c r="J129" s="8">
+      <c r="H129" s="12">
+        <v>6478069.43</v>
+      </c>
+      <c r="I129" s="13">
+        <v>6478029.44</v>
+      </c>
+      <c r="J129" s="12">
         <v>39.989999999292195</v>
       </c>
-      <c r="K129" s="10">
+      <c r="K129" s="14">
         <v>44827</v>
       </c>
-      <c r="L129" s="10">
+      <c r="L129" s="14">
         <v>45690</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A130" s="7" t="s">
+      <c r="A130" s="11" t="s">
         <v>496</v>
       </c>
-      <c r="B130" s="7" t="s">
+      <c r="B130" s="11" t="s">
         <v>501</v>
       </c>
-      <c r="C130" s="7" t="s">
+      <c r="C130" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="D130" s="7" t="s">
+      <c r="D130" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E130" s="7" t="s">
+      <c r="E130" s="11" t="s">
         <v>503</v>
       </c>
-      <c r="F130" s="7" t="s">
+      <c r="F130" s="11" t="s">
         <v>504</v>
       </c>
-      <c r="G130" s="7">
-        <v>0.78090000000000004</v>
-      </c>
-      <c r="H130" s="8">
+      <c r="G130" s="11">
+        <v>0.7809</v>
+      </c>
+      <c r="H130" s="12">
         <v>544550.48</v>
       </c>
-      <c r="I130" s="9">
+      <c r="I130" s="13">
         <v>425261.4</v>
       </c>
-      <c r="J130" s="8">
+      <c r="J130" s="12">
         <v>119289.07999999996</v>
       </c>
-      <c r="K130" s="10">
+      <c r="K130" s="14">
         <v>45925</v>
       </c>
-      <c r="L130" s="10">
+      <c r="L130" s="14">
         <v>46165</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A131" s="7" t="s">
+      <c r="A131" s="11" t="s">
         <v>505</v>
       </c>
-      <c r="B131" s="7" t="s">
+      <c r="B131" s="11" t="s">
         <v>506</v>
       </c>
-      <c r="C131" s="7" t="s">
+      <c r="C131" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="D131" s="7" t="s">
+      <c r="D131" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E131" s="7" t="s">
+      <c r="E131" s="11" t="s">
         <v>507</v>
       </c>
-      <c r="F131" s="7" t="s">
+      <c r="F131" s="11" t="s">
         <v>508</v>
       </c>
-      <c r="G131" s="7">
+      <c r="G131" s="11">
         <v>1</v>
       </c>
-      <c r="H131" s="8">
+      <c r="H131" s="12">
         <v>2389346</v>
       </c>
-      <c r="I131" s="9">
+      <c r="I131" s="13">
         <v>2389346</v>
       </c>
-      <c r="J131" s="8">
+      <c r="J131" s="12">
         <v>0</v>
       </c>
-      <c r="K131" s="10">
+      <c r="K131" s="14">
         <v>44693</v>
       </c>
-      <c r="L131" s="10">
+      <c r="L131" s="14">
         <v>45456</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A132" s="7" t="s">
+      <c r="A132" s="11" t="s">
         <v>505</v>
       </c>
-      <c r="B132" s="7" t="s">
+      <c r="B132" s="11" t="s">
         <v>509</v>
       </c>
-      <c r="C132" s="7" t="s">
+      <c r="C132" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="D132" s="7" t="s">
+      <c r="D132" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E132" s="7" t="s">
+      <c r="E132" s="11" t="s">
         <v>510</v>
       </c>
-      <c r="F132" s="7" t="s">
+      <c r="F132" s="11" t="s">
         <v>340</v>
       </c>
-      <c r="G132" s="7">
+      <c r="G132" s="11">
         <v>1</v>
       </c>
-      <c r="H132" s="8">
+      <c r="H132" s="12">
         <v>6743574.04</v>
       </c>
-      <c r="I132" s="9">
-        <v>6743573.8499999996</v>
-      </c>
-      <c r="J132" s="8">
+      <c r="I132" s="13">
+        <v>6743573.85</v>
+      </c>
+      <c r="J132" s="12">
         <v>0.19000000040978193</v>
       </c>
-      <c r="K132" s="10">
+      <c r="K132" s="14">
         <v>44693</v>
       </c>
-      <c r="L132" s="10">
+      <c r="L132" s="14">
         <v>45152</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A133" s="7" t="s">
+      <c r="A133" s="11" t="s">
         <v>505</v>
       </c>
-      <c r="B133" s="7" t="s">
+      <c r="B133" s="11" t="s">
         <v>511</v>
       </c>
-      <c r="C133" s="7" t="s">
+      <c r="C133" s="11" t="s">
         <v>313</v>
       </c>
-      <c r="D133" s="7" t="s">
+      <c r="D133" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E133" s="7" t="s">
+      <c r="E133" s="11" t="s">
         <v>512</v>
       </c>
-      <c r="F133" s="7" t="s">
+      <c r="F133" s="11" t="s">
         <v>365</v>
       </c>
-      <c r="G133" s="7">
-        <v>0.95629999999999993</v>
-      </c>
-      <c r="H133" s="8">
+      <c r="G133" s="11">
+        <v>0.9562999999999999</v>
+      </c>
+      <c r="H133" s="12">
         <v>1052239.53</v>
       </c>
-      <c r="I133" s="9">
+      <c r="I133" s="13">
         <v>1006235.15</v>
       </c>
-      <c r="J133" s="8">
+      <c r="J133" s="12">
         <v>46004.380000000005</v>
       </c>
-      <c r="K133" s="10">
+      <c r="K133" s="14">
         <v>44613</v>
       </c>
-      <c r="L133" s="10">
+      <c r="L133" s="14">
         <v>45183</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A134" s="7" t="s">
+      <c r="A134" s="11" t="s">
         <v>505</v>
       </c>
-      <c r="B134" s="7" t="s">
+      <c r="B134" s="11" t="s">
         <v>513</v>
       </c>
-      <c r="C134" s="7" t="s">
+      <c r="C134" s="11" t="s">
         <v>514</v>
       </c>
-      <c r="D134" s="7" t="s">
+      <c r="D134" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E134" s="7" t="s">
+      <c r="E134" s="11" t="s">
         <v>515</v>
       </c>
-      <c r="F134" s="7" t="s">
+      <c r="F134" s="11" t="s">
         <v>516</v>
       </c>
-      <c r="G134" s="7">
+      <c r="G134" s="11">
         <v>0.6409999999999999</v>
       </c>
-      <c r="H134" s="8">
+      <c r="H134" s="12">
         <v>256613.37</v>
       </c>
-      <c r="I134" s="9">
+      <c r="I134" s="13">
         <v>164482.69</v>
       </c>
-      <c r="J134" s="8">
+      <c r="J134" s="12">
         <v>92130.68</v>
       </c>
-      <c r="K134" s="10">
+      <c r="K134" s="14">
         <v>45915</v>
       </c>
-      <c r="L134" s="10">
+      <c r="L134" s="14">
         <v>46005</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A135" s="7" t="s">
+      <c r="A135" s="11" t="s">
         <v>505</v>
       </c>
-      <c r="B135" s="7" t="s">
+      <c r="B135" s="11" t="s">
         <v>517</v>
       </c>
-      <c r="C135" s="7" t="s">
+      <c r="C135" s="11" t="s">
         <v>518</v>
       </c>
-      <c r="D135" s="7" t="s">
+      <c r="D135" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E135" s="7" t="s">
+      <c r="E135" s="11" t="s">
         <v>519</v>
       </c>
-      <c r="F135" s="7" t="s">
+      <c r="F135" s="11" t="s">
         <v>520</v>
       </c>
-      <c r="G135" s="7">
-        <v>0.95079999999999998</v>
-      </c>
-      <c r="H135" s="8">
+      <c r="G135" s="11">
+        <v>0.9508</v>
+      </c>
+      <c r="H135" s="12">
         <v>13554947.83</v>
       </c>
-      <c r="I135" s="9">
-        <v>12888506.560000001</v>
-      </c>
-      <c r="J135" s="8">
-        <v>666441.26999999955</v>
-      </c>
-      <c r="K135" s="10">
+      <c r="I135" s="13">
+        <v>12888506.56</v>
+      </c>
+      <c r="J135" s="12">
+        <v>666441.2699999996</v>
+      </c>
+      <c r="K135" s="14">
         <v>44537</v>
       </c>
-      <c r="L135" s="10">
+      <c r="L135" s="14">
         <v>46075</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A136" s="7" t="s">
+      <c r="A136" s="11" t="s">
         <v>505</v>
       </c>
-      <c r="B136" s="7" t="s">
+      <c r="B136" s="11" t="s">
         <v>521</v>
       </c>
-      <c r="C136" s="7" t="s">
+      <c r="C136" s="11" t="s">
         <v>448</v>
       </c>
-      <c r="D136" s="7" t="s">
+      <c r="D136" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E136" s="7" t="s">
+      <c r="E136" s="11" t="s">
         <v>522</v>
       </c>
-      <c r="F136" s="7" t="s">
+      <c r="F136" s="11" t="s">
         <v>523</v>
       </c>
-      <c r="G136" s="7">
+      <c r="G136" s="11">
         <v>0</v>
       </c>
-      <c r="H136" s="8">
+      <c r="H136" s="12">
         <v>1305890.95</v>
       </c>
-      <c r="I136" s="9">
+      <c r="I136" s="13">
         <v>0</v>
       </c>
-      <c r="J136" s="8">
+      <c r="J136" s="12">
         <v>1305890.95</v>
       </c>
-      <c r="K136" s="10">
+      <c r="K136" s="14">
         <v>44610</v>
       </c>
-      <c r="L136" s="10">
+      <c r="L136" s="14">
         <v>45567</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A137" s="7" t="s">
+      <c r="A137" s="11" t="s">
         <v>505</v>
       </c>
-      <c r="B137" s="7" t="s">
+      <c r="B137" s="11" t="s">
         <v>524</v>
       </c>
-      <c r="C137" s="7" t="s">
+      <c r="C137" s="11" t="s">
         <v>525</v>
       </c>
-      <c r="D137" s="7" t="s">
+      <c r="D137" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E137" s="7" t="s">
+      <c r="E137" s="11" t="s">
         <v>526</v>
       </c>
-      <c r="F137" s="7" t="s">
+      <c r="F137" s="11" t="s">
         <v>527</v>
       </c>
-      <c r="G137" s="7">
-        <v>0.97659999999999991</v>
-      </c>
-      <c r="H137" s="8">
-        <v>56185153.920000002</v>
-      </c>
-      <c r="I137" s="9">
-        <v>54872063.399999999</v>
-      </c>
-      <c r="J137" s="8">
+      <c r="G137" s="11">
+        <v>0.9765999999999999</v>
+      </c>
+      <c r="H137" s="12">
+        <v>56185153.92</v>
+      </c>
+      <c r="I137" s="13">
+        <v>54872063.4</v>
+      </c>
+      <c r="J137" s="12">
         <v>1313090.5200000033</v>
       </c>
-      <c r="K137" s="10">
+      <c r="K137" s="14">
         <v>44872</v>
       </c>
-      <c r="L137" s="10">
+      <c r="L137" s="14">
         <v>45475</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A138" s="7" t="s">
+      <c r="A138" s="11" t="s">
         <v>505</v>
       </c>
-      <c r="B138" s="7" t="s">
+      <c r="B138" s="11" t="s">
         <v>528</v>
       </c>
-      <c r="C138" s="7" t="s">
+      <c r="C138" s="11" t="s">
         <v>529</v>
       </c>
-      <c r="D138" s="7" t="s">
+      <c r="D138" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E138" s="7" t="s">
+      <c r="E138" s="11" t="s">
         <v>530</v>
       </c>
-      <c r="F138" s="7" t="s">
+      <c r="F138" s="11" t="s">
         <v>531</v>
       </c>
-      <c r="G138" s="7">
-        <v>0.85129999999999995</v>
-      </c>
-      <c r="H138" s="8">
+      <c r="G138" s="11">
+        <v>0.8513</v>
+      </c>
+      <c r="H138" s="12">
         <v>12100122.6</v>
       </c>
-      <c r="I138" s="9">
+      <c r="I138" s="13">
         <v>10301084.52</v>
       </c>
-      <c r="J138" s="8">
+      <c r="J138" s="12">
         <v>1799038.08</v>
       </c>
-      <c r="K138" s="10">
+      <c r="K138" s="14">
         <v>45758</v>
       </c>
-      <c r="L138" s="10">
+      <c r="L138" s="14">
         <v>46123</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A139" s="7" t="s">
+      <c r="A139" s="11" t="s">
         <v>505</v>
       </c>
-      <c r="B139" s="7" t="s">
+      <c r="B139" s="11" t="s">
         <v>532</v>
       </c>
-      <c r="C139" s="7" t="s">
+      <c r="C139" s="11" t="s">
         <v>533</v>
       </c>
-      <c r="D139" s="7" t="s">
+      <c r="D139" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E139" s="7" t="s">
+      <c r="E139" s="11" t="s">
         <v>534</v>
       </c>
-      <c r="F139" s="7" t="s">
+      <c r="F139" s="11" t="s">
         <v>508</v>
       </c>
-      <c r="G139" s="7">
-        <v>0.84549999999999992</v>
-      </c>
-      <c r="H139" s="8">
+      <c r="G139" s="11">
+        <v>0.8454999999999999</v>
+      </c>
+      <c r="H139" s="12">
         <v>12432476.25</v>
       </c>
-      <c r="I139" s="9">
-        <v>10511270.470000001</v>
-      </c>
-      <c r="J139" s="8">
+      <c r="I139" s="13">
+        <v>10511270.47</v>
+      </c>
+      <c r="J139" s="12">
         <v>1921205.7799999993</v>
       </c>
-      <c r="K139" s="10">
+      <c r="K139" s="14">
         <v>45894</v>
       </c>
-      <c r="L139" s="10">
+      <c r="L139" s="14">
         <v>46112</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A140" s="7" t="s">
+      <c r="A140" s="11" t="s">
         <v>505</v>
       </c>
-      <c r="B140" s="7" t="s">
+      <c r="B140" s="11" t="s">
         <v>535</v>
       </c>
-      <c r="C140" s="7" t="s">
+      <c r="C140" s="11" t="s">
         <v>434</v>
       </c>
-      <c r="D140" s="7" t="s">
+      <c r="D140" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E140" s="7" t="s">
+      <c r="E140" s="11" t="s">
         <v>536</v>
       </c>
-      <c r="F140" s="7" t="s">
+      <c r="F140" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="G140" s="7">
-        <v>0.89159999999999995</v>
-      </c>
-      <c r="H140" s="8">
+      <c r="G140" s="11">
+        <v>0.8916</v>
+      </c>
+      <c r="H140" s="12">
         <v>24590858.27</v>
       </c>
-      <c r="I140" s="9">
+      <c r="I140" s="13">
         <v>21925638.52</v>
       </c>
-      <c r="J140" s="8">
+      <c r="J140" s="12">
         <v>2665219.75</v>
       </c>
-      <c r="K140" s="10">
+      <c r="K140" s="14">
         <v>44638</v>
       </c>
-      <c r="L140" s="10">
+      <c r="L140" s="14">
         <v>45936</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A141" s="7" t="s">
+      <c r="A141" s="11" t="s">
         <v>505</v>
       </c>
-      <c r="B141" s="7" t="s">
+      <c r="B141" s="11" t="s">
         <v>537</v>
       </c>
-      <c r="C141" s="7" t="s">
+      <c r="C141" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="D141" s="7" t="s">
+      <c r="D141" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E141" s="7" t="s">
+      <c r="E141" s="11" t="s">
         <v>538</v>
       </c>
-      <c r="F141" s="7" t="s">
+      <c r="F141" s="11" t="s">
         <v>336</v>
       </c>
-      <c r="G141" s="7">
-        <v>7.0699999999999999E-2</v>
-      </c>
-      <c r="H141" s="8">
+      <c r="G141" s="11">
+        <v>0.0707</v>
+      </c>
+      <c r="H141" s="12">
         <v>3615856.15</v>
       </c>
-      <c r="I141" s="9">
+      <c r="I141" s="13">
         <v>255684.47</v>
       </c>
-      <c r="J141" s="8">
+      <c r="J141" s="12">
         <v>3360171.6799999997</v>
       </c>
-      <c r="K141" s="10">
+      <c r="K141" s="14">
         <v>44791</v>
       </c>
-      <c r="L141" s="10">
+      <c r="L141" s="14">
         <v>45259</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A142" s="7" t="s">
+      <c r="A142" s="11" t="s">
         <v>505</v>
       </c>
-      <c r="B142" s="7" t="s">
+      <c r="B142" s="11" t="s">
         <v>539</v>
       </c>
-      <c r="C142" s="7" t="s">
+      <c r="C142" s="11" t="s">
         <v>540</v>
       </c>
-      <c r="D142" s="7" t="s">
+      <c r="D142" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E142" s="7" t="s">
+      <c r="E142" s="11" t="s">
         <v>541</v>
       </c>
-      <c r="F142" s="7" t="s">
+      <c r="F142" s="11" t="s">
         <v>508</v>
       </c>
-      <c r="G142" s="7">
-        <v>0.16370000000000001</v>
-      </c>
-      <c r="H142" s="8">
-        <v>7848019.5300000003</v>
-      </c>
-      <c r="I142" s="9">
-        <v>1284711.8999999999</v>
-      </c>
-      <c r="J142" s="8">
-        <v>6563307.6300000008</v>
-      </c>
-      <c r="K142" s="10">
+      <c r="G142" s="11">
+        <v>0.1637</v>
+      </c>
+      <c r="H142" s="12">
+        <v>7848019.53</v>
+      </c>
+      <c r="I142" s="13">
+        <v>1284711.9</v>
+      </c>
+      <c r="J142" s="12">
+        <v>6563307.630000001</v>
+      </c>
+      <c r="K142" s="14">
         <v>45986</v>
       </c>
-      <c r="L142" s="10">
+      <c r="L142" s="14">
         <v>46351</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A143" s="7" t="s">
+      <c r="A143" s="11" t="s">
         <v>505</v>
       </c>
-      <c r="B143" s="7" t="s">
+      <c r="B143" s="11" t="s">
         <v>542</v>
       </c>
-      <c r="C143" s="7" t="s">
+      <c r="C143" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="D143" s="7" t="s">
+      <c r="D143" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E143" s="7" t="s">
+      <c r="E143" s="11" t="s">
         <v>543</v>
       </c>
-      <c r="F143" s="7" t="s">
+      <c r="F143" s="11" t="s">
         <v>544</v>
       </c>
-      <c r="G143" s="7">
-        <v>0.53639999999999999</v>
-      </c>
-      <c r="H143" s="8">
-        <v>16932981.449999999</v>
-      </c>
-      <c r="I143" s="9">
-        <v>9082408.6699999999</v>
-      </c>
-      <c r="J143" s="8">
-        <v>7850572.7799999993</v>
-      </c>
-      <c r="K143" s="10">
+      <c r="G143" s="11">
+        <v>0.5364</v>
+      </c>
+      <c r="H143" s="12">
+        <v>16932981.45</v>
+      </c>
+      <c r="I143" s="13">
+        <v>9082408.67</v>
+      </c>
+      <c r="J143" s="12">
+        <v>7850572.779999999</v>
+      </c>
+      <c r="K143" s="14">
         <v>44791</v>
       </c>
-      <c r="L143" s="10">
+      <c r="L143" s="14">
         <v>45393</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A144" s="7" t="s">
+      <c r="A144" s="11" t="s">
         <v>505</v>
       </c>
-      <c r="B144" s="7" t="s">
+      <c r="B144" s="11" t="s">
         <v>545</v>
       </c>
-      <c r="C144" s="7" t="s">
+      <c r="C144" s="11" t="s">
         <v>546</v>
       </c>
-      <c r="D144" s="7" t="s">
+      <c r="D144" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E144" s="7" t="s">
+      <c r="E144" s="11" t="s">
         <v>547</v>
       </c>
-      <c r="F144" s="7" t="s">
+      <c r="F144" s="11" t="s">
         <v>548</v>
       </c>
-      <c r="G144" s="7">
-        <v>0.60429999999999995</v>
-      </c>
-      <c r="H144" s="8">
+      <c r="G144" s="11">
+        <v>0.6043</v>
+      </c>
+      <c r="H144" s="12">
         <v>24187461.93</v>
       </c>
-      <c r="I144" s="9">
-        <v>14615806.689999999</v>
-      </c>
-      <c r="J144" s="8">
-        <v>9571655.2400000002</v>
-      </c>
-      <c r="K144" s="10">
+      <c r="I144" s="13">
+        <v>14615806.69</v>
+      </c>
+      <c r="J144" s="12">
+        <v>9571655.24</v>
+      </c>
+      <c r="K144" s="14">
         <v>45723</v>
       </c>
-      <c r="L144" s="10">
+      <c r="L144" s="14">
         <v>46203</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A145" s="7" t="s">
+      <c r="A145" s="11" t="s">
         <v>505</v>
       </c>
-      <c r="B145" s="7" t="s">
+      <c r="B145" s="11" t="s">
         <v>549</v>
       </c>
-      <c r="C145" s="7" t="s">
+      <c r="C145" s="11" t="s">
         <v>550</v>
       </c>
-      <c r="D145" s="7" t="s">
+      <c r="D145" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E145" s="7" t="s">
+      <c r="E145" s="11" t="s">
         <v>551</v>
       </c>
-      <c r="F145" s="7" t="s">
+      <c r="F145" s="11" t="s">
         <v>552</v>
       </c>
-      <c r="G145" s="7">
-        <v>0.82980000000000009</v>
-      </c>
-      <c r="H145" s="8">
-        <v>74609626.420000002</v>
-      </c>
-      <c r="I145" s="9">
-        <v>61911151.039999999</v>
-      </c>
-      <c r="J145" s="8">
-        <v>12698475.380000003</v>
-      </c>
-      <c r="K145" s="10">
+      <c r="G145" s="11">
+        <v>0.8504</v>
+      </c>
+      <c r="H145" s="12">
+        <v>74609626.42</v>
+      </c>
+      <c r="I145" s="13">
+        <v>63449041.49</v>
+      </c>
+      <c r="J145" s="12">
+        <v>11160584.93</v>
+      </c>
+      <c r="K145" s="14">
         <v>45555</v>
       </c>
-      <c r="L145" s="10">
+      <c r="L145" s="14">
         <v>46112</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A146" s="7" t="s">
+      <c r="A146" s="11" t="s">
         <v>505</v>
       </c>
-      <c r="B146" s="7" t="s">
+      <c r="B146" s="11" t="s">
         <v>553</v>
       </c>
-      <c r="C146" s="7" t="s">
+      <c r="C146" s="11" t="s">
         <v>554</v>
       </c>
-      <c r="D146" s="7" t="s">
+      <c r="D146" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E146" s="7" t="s">
+      <c r="E146" s="11" t="s">
         <v>555</v>
       </c>
-      <c r="F146" s="7" t="s">
+      <c r="F146" s="11" t="s">
         <v>520</v>
       </c>
-      <c r="G146" s="7">
+      <c r="G146" s="11">
         <v>0.15</v>
       </c>
-      <c r="H146" s="8">
-        <v>15203482.789999999</v>
-      </c>
-      <c r="I146" s="9">
-        <v>2279930.0499999998</v>
-      </c>
-      <c r="J146" s="8">
+      <c r="H146" s="12">
+        <v>15203482.79</v>
+      </c>
+      <c r="I146" s="13">
+        <v>2279930.05</v>
+      </c>
+      <c r="J146" s="12">
         <v>12923552.739999998</v>
       </c>
-      <c r="K146" s="10">
+      <c r="K146" s="14">
         <v>44757</v>
       </c>
-      <c r="L146" s="10">
+      <c r="L146" s="14">
         <v>46287</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A147" s="7" t="s">
+      <c r="A147" s="11" t="s">
         <v>505</v>
       </c>
-      <c r="B147" s="7" t="s">
+      <c r="B147" s="11" t="s">
         <v>556</v>
       </c>
-      <c r="C147" s="7" t="s">
+      <c r="C147" s="11" t="s">
         <v>490</v>
       </c>
-      <c r="D147" s="7" t="s">
+      <c r="D147" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E147" s="7" t="s">
+      <c r="E147" s="11" t="s">
         <v>557</v>
       </c>
-      <c r="F147" s="7" t="s">
+      <c r="F147" s="11" t="s">
         <v>520</v>
       </c>
-      <c r="G147" s="7">
-        <v>2.1600000000000001E-2</v>
-      </c>
-      <c r="H147" s="8">
+      <c r="G147" s="11">
+        <v>0.0216</v>
+      </c>
+      <c r="H147" s="12">
         <v>13677862.32</v>
       </c>
-      <c r="I147" s="9">
+      <c r="I147" s="13">
         <v>296101.87</v>
       </c>
-      <c r="J147" s="8">
+      <c r="J147" s="12">
         <v>13381760.450000001</v>
       </c>
-      <c r="K147" s="10">
+      <c r="K147" s="14">
         <v>44581</v>
       </c>
-      <c r="L147" s="10">
+      <c r="L147" s="14">
         <v>45561</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A148" s="7" t="s">
+      <c r="A148" s="11" t="s">
         <v>505</v>
       </c>
-      <c r="B148" s="7" t="s">
+      <c r="B148" s="11" t="s">
         <v>558</v>
       </c>
-      <c r="C148" s="7" t="s">
+      <c r="C148" s="11" t="s">
         <v>559</v>
       </c>
-      <c r="D148" s="7" t="s">
+      <c r="D148" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E148" s="7" t="s">
+      <c r="E148" s="11" t="s">
         <v>560</v>
       </c>
-      <c r="F148" s="7" t="s">
+      <c r="F148" s="11" t="s">
         <v>561</v>
       </c>
-      <c r="G148" s="7">
+      <c r="G148" s="11">
         <v>0</v>
       </c>
-      <c r="H148" s="8">
+      <c r="H148" s="12">
         <v>14144248.92</v>
       </c>
-      <c r="I148" s="9">
+      <c r="I148" s="13">
         <v>0</v>
       </c>
-      <c r="J148" s="8">
+      <c r="J148" s="12">
         <v>14144248.92</v>
       </c>
-      <c r="K148" s="10">
+      <c r="K148" s="14">
         <v>41443</v>
       </c>
-      <c r="L148" s="10">
+      <c r="L148" s="14">
         <v>44012</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A149" s="7" t="s">
+      <c r="A149" s="11" t="s">
         <v>505</v>
       </c>
-      <c r="B149" s="7" t="s">
+      <c r="B149" s="11" t="s">
         <v>562</v>
       </c>
-      <c r="C149" s="7" t="s">
+      <c r="C149" s="11" t="s">
         <v>563</v>
       </c>
-      <c r="D149" s="7" t="s">
+      <c r="D149" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E149" s="7" t="s">
+      <c r="E149" s="11" t="s">
         <v>564</v>
       </c>
-      <c r="F149" s="7" t="s">
+      <c r="F149" s="11" t="s">
         <v>336</v>
       </c>
-      <c r="G149" s="7">
-        <v>0.34749999999999998</v>
-      </c>
-      <c r="H149" s="8">
-        <v>24165422.120000001</v>
-      </c>
-      <c r="I149" s="9">
-        <v>8398407.2300000004</v>
-      </c>
-      <c r="J149" s="8">
-        <v>15767014.890000001</v>
-      </c>
-      <c r="K149" s="10">
+      <c r="G149" s="11">
+        <v>0.3475</v>
+      </c>
+      <c r="H149" s="12">
+        <v>24165422.12</v>
+      </c>
+      <c r="I149" s="13">
+        <v>8398407.23</v>
+      </c>
+      <c r="J149" s="12">
+        <v>15767014.89</v>
+      </c>
+      <c r="K149" s="14">
         <v>44538</v>
       </c>
-      <c r="L149" s="10">
+      <c r="L149" s="14">
         <v>45426</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A150" s="7" t="s">
+      <c r="A150" s="11" t="s">
         <v>505</v>
       </c>
-      <c r="B150" s="7" t="s">
+      <c r="B150" s="11" t="s">
         <v>565</v>
       </c>
-      <c r="C150" s="7" t="s">
+      <c r="C150" s="11" t="s">
         <v>566</v>
       </c>
-      <c r="D150" s="7" t="s">
+      <c r="D150" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E150" s="7" t="s">
+      <c r="E150" s="11" t="s">
         <v>567</v>
       </c>
-      <c r="F150" s="7" t="s">
+      <c r="F150" s="11" t="s">
         <v>568</v>
       </c>
-      <c r="G150" s="7">
-        <v>0.51690000000000003</v>
-      </c>
-      <c r="H150" s="8">
+      <c r="G150" s="11">
+        <v>0.5169</v>
+      </c>
+      <c r="H150" s="12">
         <v>104939756.55</v>
       </c>
-      <c r="I150" s="9">
-        <v>54247297.539999999</v>
-      </c>
-      <c r="J150" s="8">
-        <v>50692459.009999998</v>
-      </c>
-      <c r="K150" s="10">
+      <c r="I150" s="13">
+        <v>54247297.54</v>
+      </c>
+      <c r="J150" s="12">
+        <v>50692459.01</v>
+      </c>
+      <c r="K150" s="14">
         <v>45624</v>
       </c>
-      <c r="L150" s="10">
+      <c r="L150" s="14">
         <v>46074</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A151" s="7" t="s">
+      <c r="A151" s="11" t="s">
         <v>505</v>
       </c>
-      <c r="B151" s="7" t="s">
+      <c r="B151" s="11" t="s">
         <v>569</v>
       </c>
-      <c r="C151" s="7" t="s">
+      <c r="C151" s="11" t="s">
         <v>570</v>
       </c>
-      <c r="D151" s="7" t="s">
+      <c r="D151" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E151" s="7" t="s">
+      <c r="E151" s="11" t="s">
         <v>571</v>
       </c>
-      <c r="F151" s="7" t="s">
+      <c r="F151" s="11" t="s">
         <v>336</v>
       </c>
-      <c r="G151" s="7">
+      <c r="G151" s="11">
         <v>0.18899999999999997</v>
       </c>
-      <c r="H151" s="8">
+      <c r="H151" s="12">
         <v>116500000</v>
       </c>
-      <c r="I151" s="9">
-        <v>22022321.059999999</v>
-      </c>
-      <c r="J151" s="8">
-        <v>94477678.939999998</v>
-      </c>
-      <c r="K151" s="10">
+      <c r="I151" s="13">
+        <v>22022321.06</v>
+      </c>
+      <c r="J151" s="12">
+        <v>94477678.94</v>
+      </c>
+      <c r="K151" s="14">
         <v>45897</v>
       </c>
-      <c r="L151" s="10">
+      <c r="L151" s="14">
         <v>46107</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A152" s="7" t="s">
+      <c r="A152" s="11" t="s">
         <v>572</v>
       </c>
-      <c r="B152" s="7" t="s">
+      <c r="B152" s="11" t="s">
         <v>573</v>
       </c>
-      <c r="C152" s="7" t="s">
+      <c r="C152" s="11" t="s">
         <v>574</v>
       </c>
-      <c r="D152" s="7" t="s">
+      <c r="D152" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E152" s="7" t="s">
+      <c r="E152" s="11" t="s">
         <v>575</v>
       </c>
-      <c r="F152" s="7" t="s">
+      <c r="F152" s="11" t="s">
         <v>576</v>
       </c>
-      <c r="G152" s="7">
+      <c r="G152" s="11">
         <v>1</v>
       </c>
-      <c r="H152" s="8">
+      <c r="H152" s="12">
         <v>10061005.41</v>
       </c>
-      <c r="I152" s="9">
-        <v>10061005.390000001</v>
-      </c>
-      <c r="J152" s="8">
-        <v>1.9999999552965164E-2</v>
-      </c>
-      <c r="K152" s="10">
+      <c r="I152" s="13">
+        <v>10061005.39</v>
+      </c>
+      <c r="J152" s="12">
+        <v>0.019999999552965164</v>
+      </c>
+      <c r="K152" s="14">
         <v>45261</v>
       </c>
-      <c r="L152" s="10">
+      <c r="L152" s="14">
         <v>45833</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A153" s="7" t="s">
+      <c r="A153" s="11" t="s">
         <v>577</v>
       </c>
-      <c r="B153" s="7" t="s">
+      <c r="B153" s="11" t="s">
         <v>578</v>
       </c>
-      <c r="C153" s="7" t="s">
+      <c r="C153" s="11" t="s">
         <v>579</v>
       </c>
-      <c r="D153" s="7" t="s">
+      <c r="D153" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E153" s="7" t="s">
+      <c r="E153" s="11" t="s">
         <v>580</v>
       </c>
-      <c r="F153" s="7" t="s">
+      <c r="F153" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G153" s="7">
+      <c r="G153" s="11">
         <v>1</v>
       </c>
-      <c r="H153" s="8">
-        <v>81950979.230000004</v>
-      </c>
-      <c r="I153" s="9">
+      <c r="H153" s="12">
+        <v>81950979.23</v>
+      </c>
+      <c r="I153" s="13">
         <v>81950979</v>
       </c>
-      <c r="J153" s="8">
+      <c r="J153" s="12">
         <v>0.23000000417232513</v>
       </c>
-      <c r="K153" s="10">
+      <c r="K153" s="14">
         <v>44792</v>
       </c>
-      <c r="L153" s="10">
+      <c r="L153" s="14">
         <v>46022</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A154" s="7" t="s">
+      <c r="A154" s="11" t="s">
         <v>577</v>
       </c>
-      <c r="B154" s="7" t="s">
+      <c r="B154" s="11" t="s">
         <v>581</v>
       </c>
-      <c r="C154" s="7" t="s">
+      <c r="C154" s="11" t="s">
         <v>582</v>
       </c>
-      <c r="D154" s="7" t="s">
+      <c r="D154" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E154" s="7" t="s">
+      <c r="E154" s="11" t="s">
         <v>583</v>
       </c>
-      <c r="F154" s="7" t="s">
+      <c r="F154" s="11" t="s">
         <v>584</v>
       </c>
-      <c r="G154" s="7">
+      <c r="G154" s="11">
         <v>0</v>
       </c>
-      <c r="H154" s="8">
-        <v>41522873.420000002</v>
-      </c>
-      <c r="I154" s="9">
+      <c r="H154" s="12">
+        <v>41522873.42</v>
+      </c>
+      <c r="I154" s="13">
         <v>0</v>
       </c>
-      <c r="J154" s="8">
-        <v>41522873.420000002</v>
-      </c>
-      <c r="K154" s="10">
+      <c r="J154" s="12">
+        <v>41522873.42</v>
+      </c>
+      <c r="K154" s="14">
         <v>45901</v>
       </c>
-      <c r="L154" s="10">
+      <c r="L154" s="14">
         <v>46801</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A155" s="7" t="s">
+      <c r="A155" s="11" t="s">
         <v>585</v>
       </c>
-      <c r="B155" s="7" t="s">
+      <c r="B155" s="11" t="s">
         <v>586</v>
       </c>
-      <c r="C155" s="7" t="s">
+      <c r="C155" s="11" t="s">
         <v>587</v>
       </c>
-      <c r="D155" s="7" t="s">
+      <c r="D155" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E155" s="7" t="s">
+      <c r="E155" s="11" t="s">
         <v>588</v>
       </c>
-      <c r="F155" s="7" t="s">
+      <c r="F155" s="11" t="s">
         <v>318</v>
       </c>
-      <c r="G155" s="7">
+      <c r="G155" s="11">
         <v>0.9728</v>
       </c>
-      <c r="H155" s="8">
+      <c r="H155" s="12">
         <v>4444784.22</v>
       </c>
-      <c r="I155" s="9">
-        <v>4324004.8099999996</v>
-      </c>
-      <c r="J155" s="8">
+      <c r="I155" s="13">
+        <v>4324004.81</v>
+      </c>
+      <c r="J155" s="12">
         <v>120779.41000000015</v>
       </c>
-      <c r="K155" s="10">
+      <c r="K155" s="14">
         <v>45155</v>
       </c>
-      <c r="L155" s="10">
+      <c r="L155" s="14">
         <v>45576</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A156" s="7" t="s">
+      <c r="A156" s="11" t="s">
         <v>589</v>
       </c>
-      <c r="B156" s="7" t="s">
+      <c r="B156" s="11" t="s">
         <v>590</v>
       </c>
-      <c r="C156" s="7" t="s">
+      <c r="C156" s="11" t="s">
         <v>591</v>
       </c>
-      <c r="D156" s="7" t="s">
+      <c r="D156" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E156" s="7" t="s">
+      <c r="E156" s="11" t="s">
         <v>592</v>
       </c>
-      <c r="F156" s="7" t="s">
+      <c r="F156" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="G156" s="7">
+      <c r="G156" s="11">
         <v>0</v>
       </c>
-      <c r="H156" s="8">
-        <v>8995898.0500000007</v>
-      </c>
-      <c r="I156" s="9">
+      <c r="H156" s="12">
+        <v>8995898.05</v>
+      </c>
+      <c r="I156" s="13">
         <v>266299.23</v>
       </c>
-      <c r="J156" s="8">
-        <v>8729598.8200000003</v>
-      </c>
-      <c r="K156" s="10">
+      <c r="J156" s="12">
+        <v>8729598.82</v>
+      </c>
+      <c r="K156" s="14">
         <v>44816</v>
       </c>
-      <c r="L156" s="10">
+      <c r="L156" s="14">
         <v>44996</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A157" s="7" t="s">
+      <c r="A157" s="11" t="s">
         <v>593</v>
       </c>
-      <c r="B157" s="7" t="s">
+      <c r="B157" s="11" t="s">
         <v>594</v>
       </c>
-      <c r="C157" s="7" t="s">
+      <c r="C157" s="11" t="s">
         <v>595</v>
       </c>
-      <c r="D157" s="7" t="s">
+      <c r="D157" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E157" s="7" t="s">
+      <c r="E157" s="11" t="s">
         <v>596</v>
       </c>
-      <c r="F157" s="7" t="s">
+      <c r="F157" s="11" t="s">
         <v>576</v>
       </c>
-      <c r="G157" s="7">
-        <v>0.31530000000000002</v>
-      </c>
-      <c r="H157" s="8">
+      <c r="G157" s="11">
+        <v>0.3153</v>
+      </c>
+      <c r="H157" s="12">
         <v>3294597.99</v>
       </c>
-      <c r="I157" s="9">
+      <c r="I157" s="13">
         <v>1038880.21</v>
       </c>
-      <c r="J157" s="8">
+      <c r="J157" s="12">
         <v>2255717.7800000003</v>
       </c>
-      <c r="K157" s="10">
+      <c r="K157" s="14">
         <v>45278</v>
       </c>
-      <c r="L157" s="10">
+      <c r="L157" s="14">
         <v>46122</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A158" s="7" t="s">
+      <c r="A158" s="11" t="s">
         <v>597</v>
       </c>
-      <c r="B158" s="7" t="s">
+      <c r="B158" s="11" t="s">
         <v>598</v>
       </c>
-      <c r="C158" s="7" t="s">
+      <c r="C158" s="11" t="s">
         <v>599</v>
       </c>
-      <c r="D158" s="7" t="s">
+      <c r="D158" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E158" s="7" t="s">
+      <c r="E158" s="11" t="s">
         <v>600</v>
       </c>
-      <c r="F158" s="7" t="s">
+      <c r="F158" s="11" t="s">
         <v>500</v>
       </c>
-      <c r="G158" s="7">
-        <v>0.99219999999999997</v>
-      </c>
-      <c r="H158" s="8">
-        <v>6055289.3399999999</v>
-      </c>
-      <c r="I158" s="9">
-        <v>6007931.0199999996</v>
-      </c>
-      <c r="J158" s="8">
-        <v>47358.320000000298</v>
-      </c>
-      <c r="K158" s="10">
+      <c r="G158" s="11">
+        <v>0.9922</v>
+      </c>
+      <c r="H158" s="12">
+        <v>6055289.34</v>
+      </c>
+      <c r="I158" s="13">
+        <v>6007931.02</v>
+      </c>
+      <c r="J158" s="12">
+        <v>47358.3200000003</v>
+      </c>
+      <c r="K158" s="14">
         <v>44715</v>
       </c>
-      <c r="L158" s="10">
+      <c r="L158" s="14">
         <v>45075</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A159" s="7" t="s">
+      <c r="A159" s="11" t="s">
         <v>597</v>
       </c>
-      <c r="B159" s="7" t="s">
+      <c r="B159" s="11" t="s">
         <v>601</v>
       </c>
-      <c r="C159" s="7" t="s">
+      <c r="C159" s="11" t="s">
         <v>602</v>
       </c>
-      <c r="D159" s="7" t="s">
+      <c r="D159" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E159" s="7" t="s">
+      <c r="E159" s="11" t="s">
         <v>603</v>
       </c>
-      <c r="F159" s="7" t="s">
+      <c r="F159" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G159" s="7">
+      <c r="G159" s="11">
         <v>0.22760000000000002</v>
       </c>
-      <c r="H159" s="8">
-        <v>8973983.8699999992</v>
-      </c>
-      <c r="I159" s="9">
+      <c r="H159" s="12">
+        <v>8973983.87</v>
+      </c>
+      <c r="I159" s="13">
         <v>2042159.29</v>
       </c>
-      <c r="J159" s="8">
-        <v>6931824.5799999991</v>
-      </c>
-      <c r="K159" s="10">
+      <c r="J159" s="12">
+        <v>6931824.579999999</v>
+      </c>
+      <c r="K159" s="14">
         <v>44707</v>
       </c>
-      <c r="L159" s="10">
+      <c r="L159" s="14">
         <v>45280</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A160" s="7" t="s">
+      <c r="A160" s="11" t="s">
         <v>604</v>
       </c>
-      <c r="B160" s="7" t="s">
+      <c r="B160" s="11" t="s">
         <v>605</v>
       </c>
-      <c r="C160" s="7" t="s">
+      <c r="C160" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="D160" s="7" t="s">
+      <c r="D160" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E160" s="7" t="s">
+      <c r="E160" s="11" t="s">
         <v>606</v>
       </c>
-      <c r="F160" s="7" t="s">
+      <c r="F160" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="G160" s="7">
+      <c r="G160" s="11">
         <v>1</v>
       </c>
-      <c r="H160" s="8">
-        <v>13792679.789999999</v>
-      </c>
-      <c r="I160" s="9">
-        <v>13792679.789999999</v>
-      </c>
-      <c r="J160" s="8">
+      <c r="H160" s="12">
+        <v>13792679.79</v>
+      </c>
+      <c r="I160" s="13">
+        <v>13792679.79</v>
+      </c>
+      <c r="J160" s="12">
         <v>0</v>
       </c>
-      <c r="K160" s="10">
+      <c r="K160" s="14">
         <v>44767</v>
       </c>
-      <c r="L160" s="10">
+      <c r="L160" s="14">
         <v>45411</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A161" s="7" t="s">
+      <c r="A161" s="11" t="s">
         <v>604</v>
       </c>
-      <c r="B161" s="7" t="s">
+      <c r="B161" s="11" t="s">
         <v>607</v>
       </c>
-      <c r="C161" s="7" t="s">
+      <c r="C161" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="D161" s="7" t="s">
+      <c r="D161" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E161" s="7" t="s">
+      <c r="E161" s="11" t="s">
         <v>608</v>
       </c>
-      <c r="F161" s="7" t="s">
+      <c r="F161" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="G161" s="7">
-        <v>0.91220000000000001</v>
-      </c>
-      <c r="H161" s="8">
+      <c r="G161" s="11">
+        <v>0.9122</v>
+      </c>
+      <c r="H161" s="12">
         <v>22472818</v>
       </c>
-      <c r="I161" s="9">
+      <c r="I161" s="13">
         <v>20500685.68</v>
       </c>
-      <c r="J161" s="8">
+      <c r="J161" s="12">
         <v>1972132.3200000003</v>
       </c>
-      <c r="K161" s="10">
+      <c r="K161" s="14">
         <v>44827</v>
       </c>
-      <c r="L161" s="10">
+      <c r="L161" s="14">
         <v>45460</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A162" s="7" t="s">
+      <c r="A162" s="11" t="s">
         <v>604</v>
       </c>
-      <c r="B162" s="7" t="s">
+      <c r="B162" s="11" t="s">
         <v>609</v>
       </c>
-      <c r="C162" s="7" t="s">
+      <c r="C162" s="11" t="s">
         <v>610</v>
       </c>
-      <c r="D162" s="7" t="s">
+      <c r="D162" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E162" s="7" t="s">
+      <c r="E162" s="11" t="s">
         <v>611</v>
       </c>
-      <c r="F162" s="7" t="s">
+      <c r="F162" s="11" t="s">
         <v>612</v>
       </c>
-      <c r="G162" s="7">
-        <v>0.89959999999999996</v>
-      </c>
-      <c r="H162" s="8">
-        <v>51414775.090000004</v>
-      </c>
-      <c r="I162" s="9">
-        <v>46254135.590000004</v>
-      </c>
-      <c r="J162" s="8">
+      <c r="G162" s="11">
+        <v>0.8996</v>
+      </c>
+      <c r="H162" s="12">
+        <v>51414775.09</v>
+      </c>
+      <c r="I162" s="13">
+        <v>46254135.59</v>
+      </c>
+      <c r="J162" s="12">
         <v>5160639.5</v>
       </c>
-      <c r="K162" s="10">
+      <c r="K162" s="14">
         <v>45566</v>
       </c>
-      <c r="L162" s="10">
+      <c r="L162" s="14">
         <v>46106</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A163" s="7" t="s">
+      <c r="A163" s="11" t="s">
         <v>613</v>
       </c>
-      <c r="B163" s="7" t="s">
+      <c r="B163" s="11" t="s">
         <v>614</v>
       </c>
-      <c r="C163" s="7" t="s">
+      <c r="C163" s="11" t="s">
         <v>615</v>
       </c>
-      <c r="D163" s="7" t="s">
+      <c r="D163" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E163" s="7" t="s">
+      <c r="E163" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="F163" s="7" t="s">
+      <c r="F163" s="11" t="s">
         <v>617</v>
       </c>
-      <c r="G163" s="7">
+      <c r="G163" s="11">
         <v>0</v>
       </c>
-      <c r="H163" s="8">
+      <c r="H163" s="12">
         <v>1302281.25</v>
       </c>
-      <c r="I163" s="9">
+      <c r="I163" s="13">
         <v>0</v>
       </c>
-      <c r="J163" s="8">
+      <c r="J163" s="12">
         <v>1302281.25</v>
       </c>
-      <c r="K163" s="10">
-        <v>46810</v>
-      </c>
-      <c r="L163" s="10">
+      <c r="K163" s="14">
+        <v>46080</v>
+      </c>
+      <c r="L163" s="14">
         <v>46440</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A164" s="7" t="s">
+      <c r="A164" s="11" t="s">
         <v>618</v>
       </c>
-      <c r="B164" s="7" t="s">
+      <c r="B164" s="11" t="s">
         <v>619</v>
       </c>
-      <c r="C164" s="7" t="s">
+      <c r="C164" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="D164" s="7" t="s">
+      <c r="D164" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E164" s="7" t="s">
+      <c r="E164" s="11" t="s">
         <v>620</v>
       </c>
-      <c r="F164" s="7" t="s">
+      <c r="F164" s="11" t="s">
         <v>621</v>
       </c>
-      <c r="G164" s="7">
+      <c r="G164" s="11">
         <v>1</v>
       </c>
-      <c r="H164" s="8">
-        <v>18264452.890000001</v>
-      </c>
-      <c r="I164" s="9">
-        <v>18264452.890000001</v>
-      </c>
-      <c r="J164" s="8">
+      <c r="H164" s="12">
+        <v>18264452.89</v>
+      </c>
+      <c r="I164" s="13">
+        <v>18264452.89</v>
+      </c>
+      <c r="J164" s="12">
         <v>0</v>
       </c>
-      <c r="K164" s="10">
+      <c r="K164" s="14">
         <v>44722</v>
       </c>
-      <c r="L164" s="10">
+      <c r="L164" s="14">
         <v>45723</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A165" s="7" t="s">
+      <c r="A165" s="11" t="s">
         <v>618</v>
       </c>
-      <c r="B165" s="7" t="s">
+      <c r="B165" s="11" t="s">
         <v>622</v>
       </c>
-      <c r="C165" s="7" t="s">
+      <c r="C165" s="11" t="s">
         <v>623</v>
       </c>
-      <c r="D165" s="7" t="s">
+      <c r="D165" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E165" s="7" t="s">
+      <c r="E165" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="F165" s="7" t="s">
+      <c r="F165" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G165" s="7">
-        <v>0.99529999999999996</v>
-      </c>
-      <c r="H165" s="8">
-        <v>30599999.010000002</v>
-      </c>
-      <c r="I165" s="9">
-        <v>30456294.329999998</v>
-      </c>
-      <c r="J165" s="8">
+      <c r="G165" s="11">
+        <v>0.9953</v>
+      </c>
+      <c r="H165" s="12">
+        <v>30599999.01</v>
+      </c>
+      <c r="I165" s="13">
+        <v>30456294.33</v>
+      </c>
+      <c r="J165" s="12">
         <v>143704.68000000343</v>
       </c>
-      <c r="K165" s="10">
+      <c r="K165" s="14">
         <v>45019</v>
       </c>
-      <c r="L165" s="10">
+      <c r="L165" s="14">
         <v>45743</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A166" s="7" t="s">
+      <c r="A166" s="11" t="s">
         <v>618</v>
       </c>
-      <c r="B166" s="7" t="s">
+      <c r="B166" s="11" t="s">
         <v>625</v>
       </c>
-      <c r="C166" s="7" t="s">
+      <c r="C166" s="11" t="s">
         <v>626</v>
       </c>
-      <c r="D166" s="7" t="s">
+      <c r="D166" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E166" s="7" t="s">
+      <c r="E166" s="11" t="s">
         <v>627</v>
       </c>
-      <c r="F166" s="7" t="s">
+      <c r="F166" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="G166" s="7">
-        <v>0.96010000000000006</v>
-      </c>
-      <c r="H166" s="8">
-        <v>43796954.979999997</v>
-      </c>
-      <c r="I166" s="9">
-        <v>42048979.520000003</v>
-      </c>
-      <c r="J166" s="8">
+      <c r="G166" s="11">
+        <v>0.9601000000000001</v>
+      </c>
+      <c r="H166" s="12">
+        <v>43796954.98</v>
+      </c>
+      <c r="I166" s="13">
+        <v>42048979.52</v>
+      </c>
+      <c r="J166" s="12">
         <v>1747975.4599999934</v>
       </c>
-      <c r="K166" s="10">
+      <c r="K166" s="14">
         <v>44641</v>
       </c>
-      <c r="L166" s="10">
+      <c r="L166" s="14">
         <v>46091</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A167" s="7" t="s">
+      <c r="A167" s="11" t="s">
         <v>618</v>
       </c>
-      <c r="B167" s="7" t="s">
+      <c r="B167" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="C167" s="7" t="s">
+      <c r="C167" s="11" t="s">
         <v>629</v>
       </c>
-      <c r="D167" s="7" t="s">
+      <c r="D167" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E167" s="7" t="s">
+      <c r="E167" s="11" t="s">
         <v>630</v>
       </c>
-      <c r="F167" s="7" t="s">
+      <c r="F167" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="G167" s="7">
-        <v>0.79559999999999997</v>
-      </c>
-      <c r="H167" s="8">
+      <c r="G167" s="11">
+        <v>0.7956</v>
+      </c>
+      <c r="H167" s="12">
         <v>45726170.25</v>
       </c>
-      <c r="I167" s="9">
-        <v>36377601.259999998</v>
-      </c>
-      <c r="J167" s="8">
-        <v>9348568.9900000021</v>
-      </c>
-      <c r="K167" s="10">
+      <c r="I167" s="13">
+        <v>36377601.26</v>
+      </c>
+      <c r="J167" s="12">
+        <v>9348568.990000002</v>
+      </c>
+      <c r="K167" s="14">
         <v>44623</v>
       </c>
-      <c r="L167" s="10">
+      <c r="L167" s="14">
         <v>46222</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A168" s="7" t="s">
+      <c r="A168" s="11" t="s">
         <v>618</v>
       </c>
-      <c r="B168" s="7" t="s">
+      <c r="B168" s="11" t="s">
         <v>631</v>
       </c>
-      <c r="C168" s="7" t="s">
+      <c r="C168" s="11" t="s">
         <v>632</v>
       </c>
-      <c r="D168" s="7" t="s">
+      <c r="D168" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E168" s="7" t="s">
+      <c r="E168" s="11" t="s">
         <v>633</v>
       </c>
-      <c r="F168" s="7" t="s">
+      <c r="F168" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="G168" s="7">
+      <c r="G168" s="11">
         <v>0.30670000000000003</v>
       </c>
-      <c r="H168" s="8">
-        <v>65678550.130000003</v>
-      </c>
-      <c r="I168" s="9">
-        <v>20145177.510000002</v>
-      </c>
-      <c r="J168" s="8">
+      <c r="H168" s="12">
+        <v>65678550.13</v>
+      </c>
+      <c r="I168" s="13">
+        <v>20145177.51</v>
+      </c>
+      <c r="J168" s="12">
         <v>45533372.620000005</v>
       </c>
-      <c r="K168" s="10">
+      <c r="K168" s="14">
         <v>44623</v>
       </c>
-      <c r="L168" s="10">
+      <c r="L168" s="14">
         <v>46170</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L168" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/ANALITICA.xlsx
+++ b/ANALITICA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="638">
   <si>
     <t>Municipio</t>
   </si>
@@ -296,6 +296,24 @@
     <t>DRV ENGENHARIA - EIRELI</t>
   </si>
   <si>
+    <t>330001/001345/2025</t>
+  </si>
+  <si>
+    <t>025/2025</t>
+  </si>
+  <si>
+    <t>ATA DE REGISTRO</t>
+  </si>
+  <si>
+    <t>ADESÃO DE ATA DE REGISTRO DE PREÇO PARA SERVIÇOS DE URBANIZAÇÃO, DIVIDIDOS EM 4 LOTES POR REGIÕES, (EXECUÇÃO DE CONSTRUÇÃO/RECUPERAÇÃO DE CALÇADAS, CICLOVIAS E PAVIMENTOS DE DIVERSOS TRECHOS DESCONTÍNUOS DE VIAS NÃO CADASTRADAS EM LOGRADOUROS PÚBLICOS MUNICIPAIS) A SER IMPLEMENTADO NAS IMEDIAÇÕES DAS HABITAÇÕES DE INTERESSE SOCIAL OU EM ÁREAS CONFIGURADAS COMO DE ESPECIAL INTERESSE SOCIAL - LOTE IV (SERRANA e CENTRO NORTE)</t>
+  </si>
+  <si>
+    <t>FAB MIX CONCRETOS LTDA</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
     <t>330018/000695/2021</t>
   </si>
   <si>
@@ -692,9 +710,6 @@
     <t>CRATER CONSTRUÇÕES LTDA.</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>Itaperuna</t>
   </si>
   <si>
@@ -1536,9 +1551,6 @@
   </si>
   <si>
     <t>PROJETO E OBRAS DE RESTAURANTE DO POVO, RIO DE JANEIRO/RJ (LOTE 02)</t>
-  </si>
-  <si>
-    <t>FAB MIX CONCRETOS LTDA</t>
   </si>
   <si>
     <t>e-17/026/1892/2019-1</t>
@@ -2379,7 +2391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L168"/>
+  <dimension ref="A1:L169"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16.46153846153846" style="1" customWidth="1"/>
@@ -3167,31 +3179,31 @@
         <v>95</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G21" s="11">
-        <v>0.5163</v>
+        <v>0</v>
       </c>
       <c r="H21" s="12">
-        <v>31022838.12</v>
+        <v>5054505.24</v>
       </c>
       <c r="I21" s="13">
-        <v>16018051.23</v>
+        <v>0</v>
       </c>
       <c r="J21" s="12">
-        <v>15004786.89</v>
-      </c>
-      <c r="K21" s="14">
-        <v>45309</v>
+        <v>5054505.24</v>
+      </c>
+      <c r="K21" s="15" t="s">
+        <v>99</v>
       </c>
       <c r="L21" s="14">
-        <v>46392</v>
+        <v>46312</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -3199,37 +3211,37 @@
         <v>82</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G22" s="11">
-        <v>0.6607999999999999</v>
+        <v>0.5163</v>
       </c>
       <c r="H22" s="12">
-        <v>48872552.26</v>
+        <v>31022838.12</v>
       </c>
       <c r="I22" s="13">
-        <v>32294745.04</v>
+        <v>16018051.23</v>
       </c>
       <c r="J22" s="12">
-        <v>16577807.219999999</v>
+        <v>15004786.89</v>
       </c>
       <c r="K22" s="14">
-        <v>44875</v>
+        <v>45309</v>
       </c>
       <c r="L22" s="14">
-        <v>46375</v>
+        <v>46392</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -3237,37 +3249,37 @@
         <v>82</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G23" s="11">
-        <v>0.7193</v>
+        <v>0.6607999999999999</v>
       </c>
       <c r="H23" s="12">
-        <v>89008310.65</v>
+        <v>48872552.26</v>
       </c>
       <c r="I23" s="13">
-        <v>64026819.34</v>
+        <v>32294745.04</v>
       </c>
       <c r="J23" s="12">
-        <v>24981491.310000002</v>
+        <v>16577807.219999999</v>
       </c>
       <c r="K23" s="14">
-        <v>44789</v>
+        <v>44875</v>
       </c>
       <c r="L23" s="14">
-        <v>45510</v>
+        <v>46375</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -3275,943 +3287,943 @@
         <v>82</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G24" s="11">
-        <v>0.44920000000000004</v>
+        <v>0.7193</v>
       </c>
       <c r="H24" s="12">
-        <v>62211091.02</v>
+        <v>89008310.65</v>
       </c>
       <c r="I24" s="13">
-        <v>27948056.39</v>
+        <v>64026819.34</v>
       </c>
       <c r="J24" s="12">
-        <v>34263034.63</v>
+        <v>24981491.310000002</v>
       </c>
       <c r="K24" s="14">
-        <v>44883</v>
+        <v>44789</v>
       </c>
       <c r="L24" s="14">
-        <v>46144</v>
+        <v>45510</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G25" s="11">
-        <v>0.9922</v>
+        <v>0.44920000000000004</v>
       </c>
       <c r="H25" s="12">
-        <v>5361446.28</v>
+        <v>62211091.02</v>
       </c>
       <c r="I25" s="13">
-        <v>5319761.7</v>
+        <v>27948056.39</v>
       </c>
       <c r="J25" s="12">
-        <v>41684.580000000075</v>
+        <v>34263034.63</v>
       </c>
       <c r="K25" s="14">
-        <v>44637</v>
+        <v>44883</v>
       </c>
       <c r="L25" s="14">
-        <v>45484</v>
+        <v>46144</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G26" s="11">
-        <v>0.8786</v>
+        <v>0.9922</v>
       </c>
       <c r="H26" s="12">
-        <v>2601911.32</v>
+        <v>5361446.28</v>
       </c>
       <c r="I26" s="13">
-        <v>2286080.42</v>
+        <v>5319761.7</v>
       </c>
       <c r="J26" s="12">
-        <v>315830.8999999999</v>
+        <v>41684.580000000075</v>
       </c>
       <c r="K26" s="14">
-        <v>45624</v>
+        <v>44637</v>
       </c>
       <c r="L26" s="14">
-        <v>46106</v>
+        <v>45484</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G27" s="11">
-        <v>0.1104</v>
+        <v>0.8786</v>
       </c>
       <c r="H27" s="12">
-        <v>2394811.95</v>
+        <v>2601911.32</v>
       </c>
       <c r="I27" s="13">
-        <v>264324.6</v>
+        <v>2286080.42</v>
       </c>
       <c r="J27" s="12">
-        <v>2130487.35</v>
+        <v>315830.8999999999</v>
       </c>
       <c r="K27" s="14">
-        <v>44840</v>
+        <v>45624</v>
       </c>
       <c r="L27" s="14">
-        <v>45390</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G28" s="11">
-        <v>0.9998999999999999</v>
+        <v>0.1104</v>
       </c>
       <c r="H28" s="12">
-        <v>2975474.34</v>
+        <v>2394811.95</v>
       </c>
       <c r="I28" s="13">
-        <v>2975297.32</v>
+        <v>264324.6</v>
       </c>
       <c r="J28" s="12">
-        <v>177.02000000001863</v>
+        <v>2130487.35</v>
       </c>
       <c r="K28" s="14">
-        <v>44883</v>
+        <v>44840</v>
       </c>
       <c r="L28" s="14">
-        <v>45411</v>
+        <v>45390</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D29" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G29" s="11">
-        <v>1</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="H29" s="12">
-        <v>4808707.09</v>
+        <v>2975474.34</v>
       </c>
       <c r="I29" s="13">
-        <v>4808707.09</v>
+        <v>2975297.32</v>
       </c>
       <c r="J29" s="12">
-        <v>0</v>
+        <v>177.02000000001863</v>
       </c>
       <c r="K29" s="14">
-        <v>44743</v>
+        <v>44883</v>
       </c>
       <c r="L29" s="14">
-        <v>45341</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D30" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>45</v>
+        <v>138</v>
       </c>
       <c r="G30" s="11">
-        <v>0.9109999999999999</v>
+        <v>1</v>
       </c>
       <c r="H30" s="12">
-        <v>13208831.36</v>
+        <v>4808707.09</v>
       </c>
       <c r="I30" s="13">
-        <v>12032786.93</v>
+        <v>4808707.09</v>
       </c>
       <c r="J30" s="12">
-        <v>1176044.4299999997</v>
+        <v>0</v>
       </c>
       <c r="K30" s="14">
-        <v>44708</v>
+        <v>44743</v>
       </c>
       <c r="L30" s="14">
-        <v>45398</v>
+        <v>45341</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D31" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="G31" s="11">
-        <v>1</v>
+        <v>0.9109999999999999</v>
       </c>
       <c r="H31" s="12">
-        <v>11551184.44</v>
+        <v>13208831.36</v>
       </c>
       <c r="I31" s="13">
-        <v>11551184.4</v>
+        <v>12032786.93</v>
       </c>
       <c r="J31" s="12">
-        <v>0.03999999910593033</v>
+        <v>1176044.4299999997</v>
       </c>
       <c r="K31" s="14">
-        <v>44733</v>
+        <v>44708</v>
       </c>
       <c r="L31" s="14">
-        <v>45953</v>
+        <v>45398</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>143</v>
+        <v>65</v>
       </c>
       <c r="G32" s="11">
-        <v>0.9908</v>
+        <v>1</v>
       </c>
       <c r="H32" s="12">
-        <v>9751616.37</v>
+        <v>11551184.44</v>
       </c>
       <c r="I32" s="13">
-        <v>9661616.37</v>
+        <v>11551184.4</v>
       </c>
       <c r="J32" s="12">
-        <v>90000</v>
+        <v>0.03999999910593033</v>
       </c>
       <c r="K32" s="14">
-        <v>44873</v>
+        <v>44733</v>
       </c>
       <c r="L32" s="14">
-        <v>45485</v>
+        <v>45953</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G33" s="11">
-        <v>0.5958</v>
+        <v>0.9908</v>
       </c>
       <c r="H33" s="12">
-        <v>6016602.48</v>
+        <v>9751616.37</v>
       </c>
       <c r="I33" s="13">
-        <v>3584685.32</v>
+        <v>9661616.37</v>
       </c>
       <c r="J33" s="12">
-        <v>2431917.1600000006</v>
+        <v>90000</v>
       </c>
       <c r="K33" s="14">
-        <v>45133</v>
+        <v>44873</v>
       </c>
       <c r="L33" s="14">
-        <v>46128</v>
+        <v>45485</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G34" s="11">
-        <v>0.9998</v>
+        <v>0.5958</v>
       </c>
       <c r="H34" s="12">
-        <v>8396309.76</v>
+        <v>6016602.48</v>
       </c>
       <c r="I34" s="13">
-        <v>8394769.02</v>
+        <v>3584685.32</v>
       </c>
       <c r="J34" s="12">
-        <v>1540.7400000002235</v>
+        <v>2431917.1600000006</v>
       </c>
       <c r="K34" s="14">
-        <v>44868</v>
+        <v>45133</v>
       </c>
       <c r="L34" s="14">
-        <v>45560</v>
+        <v>46128</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D35" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G35" s="11">
-        <v>0.9865</v>
+        <v>0.9998</v>
       </c>
       <c r="H35" s="12">
-        <v>45237596.81</v>
+        <v>8396309.76</v>
       </c>
       <c r="I35" s="13">
-        <v>44626728.2</v>
+        <v>8394769.02</v>
       </c>
       <c r="J35" s="12">
-        <v>610868.6099999994</v>
+        <v>1540.7400000002235</v>
       </c>
       <c r="K35" s="14">
-        <v>44769</v>
+        <v>44868</v>
       </c>
       <c r="L35" s="14">
-        <v>45701</v>
+        <v>45560</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>22</v>
+        <v>163</v>
       </c>
       <c r="G36" s="11">
-        <v>0.9899</v>
+        <v>0.9865</v>
       </c>
       <c r="H36" s="12">
-        <v>148784461.49</v>
+        <v>45237596.81</v>
       </c>
       <c r="I36" s="13">
-        <v>147280622.62</v>
+        <v>44626728.2</v>
       </c>
       <c r="J36" s="12">
-        <v>1503838.8700000048</v>
+        <v>610868.6099999994</v>
       </c>
       <c r="K36" s="14">
-        <v>45503</v>
+        <v>44769</v>
       </c>
       <c r="L36" s="14">
-        <v>46043</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>164</v>
+        <v>22</v>
       </c>
       <c r="G37" s="11">
-        <v>0.9781</v>
+        <v>0.9899</v>
       </c>
       <c r="H37" s="12">
-        <v>90986818.17</v>
+        <v>148784461.49</v>
       </c>
       <c r="I37" s="13">
-        <v>88995375.53</v>
+        <v>147280622.62</v>
       </c>
       <c r="J37" s="12">
-        <v>1991442.6400000006</v>
+        <v>1503838.8700000048</v>
       </c>
       <c r="K37" s="14">
-        <v>44986</v>
+        <v>45503</v>
       </c>
       <c r="L37" s="14">
-        <v>45589</v>
+        <v>46043</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>45</v>
+        <v>170</v>
       </c>
       <c r="G38" s="11">
-        <v>0.9786</v>
+        <v>0.9781</v>
       </c>
       <c r="H38" s="12">
-        <v>113557951.65</v>
+        <v>90986818.17</v>
       </c>
       <c r="I38" s="13">
-        <v>111133195.68</v>
+        <v>88995375.53</v>
       </c>
       <c r="J38" s="12">
-        <v>2424755.969999999</v>
+        <v>1991442.6400000006</v>
       </c>
       <c r="K38" s="14">
-        <v>45498</v>
+        <v>44986</v>
       </c>
       <c r="L38" s="14">
-        <v>46038</v>
+        <v>45589</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D39" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="G39" s="11">
-        <v>0.9301</v>
+        <v>0.9786</v>
       </c>
       <c r="H39" s="12">
-        <v>41651255.98</v>
+        <v>113557951.65</v>
       </c>
       <c r="I39" s="13">
-        <v>38738669.02</v>
+        <v>111133195.68</v>
       </c>
       <c r="J39" s="12">
-        <v>2912586.9599999934</v>
+        <v>2424755.969999999</v>
       </c>
       <c r="K39" s="14">
-        <v>45391</v>
+        <v>45498</v>
       </c>
       <c r="L39" s="14">
-        <v>46057</v>
+        <v>46038</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F40" s="11" t="s">
         <v>22</v>
       </c>
       <c r="G40" s="11">
-        <v>0.5526</v>
+        <v>0.9301</v>
       </c>
       <c r="H40" s="12">
-        <v>22759968.59</v>
+        <v>41651255.98</v>
       </c>
       <c r="I40" s="13">
-        <v>12576165.07</v>
+        <v>38738669.02</v>
       </c>
       <c r="J40" s="12">
-        <v>10183803.52</v>
+        <v>2912586.9599999934</v>
       </c>
       <c r="K40" s="14">
-        <v>44511</v>
+        <v>45391</v>
       </c>
       <c r="L40" s="14">
-        <v>44958</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="G41" s="11">
-        <v>0.5414</v>
+        <v>0.5526</v>
       </c>
       <c r="H41" s="12">
-        <v>26504288.68</v>
+        <v>22759968.59</v>
       </c>
       <c r="I41" s="13">
-        <v>14348711.09</v>
+        <v>12576165.07</v>
       </c>
       <c r="J41" s="12">
-        <v>12155577.59</v>
+        <v>10183803.52</v>
       </c>
       <c r="K41" s="14">
-        <v>45190</v>
+        <v>44511</v>
       </c>
       <c r="L41" s="14">
-        <v>46153</v>
+        <v>44958</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>157</v>
+        <v>40</v>
       </c>
       <c r="G42" s="11">
-        <v>0.0105</v>
+        <v>0.5414</v>
       </c>
       <c r="H42" s="12">
-        <v>12679339.18</v>
+        <v>26504288.68</v>
       </c>
       <c r="I42" s="13">
-        <v>133236.58</v>
+        <v>14348711.09</v>
       </c>
       <c r="J42" s="12">
-        <v>12546102.6</v>
+        <v>12155577.59</v>
       </c>
       <c r="K42" s="14">
-        <v>44753</v>
+        <v>45190</v>
       </c>
       <c r="L42" s="14">
-        <v>44984</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D43" s="11" t="s">
         <v>20</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>73</v>
+        <v>163</v>
       </c>
       <c r="G43" s="11">
-        <v>0.0063</v>
+        <v>0.0105</v>
       </c>
       <c r="H43" s="12">
-        <v>21672861.46</v>
+        <v>12679339.18</v>
       </c>
       <c r="I43" s="13">
-        <v>137475.09</v>
+        <v>133236.58</v>
       </c>
       <c r="J43" s="12">
-        <v>21535386.37</v>
+        <v>12546102.6</v>
       </c>
       <c r="K43" s="14">
-        <v>44783</v>
+        <v>44753</v>
       </c>
       <c r="L43" s="14">
-        <v>44998</v>
+        <v>44984</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D44" s="11" t="s">
         <v>20</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>186</v>
+        <v>73</v>
       </c>
       <c r="G44" s="11">
-        <v>0.2034</v>
+        <v>0.0063</v>
       </c>
       <c r="H44" s="12">
-        <v>30334596.91</v>
+        <v>21672861.46</v>
       </c>
       <c r="I44" s="13">
-        <v>6171237.78</v>
+        <v>137475.09</v>
       </c>
       <c r="J44" s="12">
-        <v>24163359.13</v>
+        <v>21535386.37</v>
       </c>
       <c r="K44" s="14">
-        <v>44753</v>
+        <v>44783</v>
       </c>
       <c r="L44" s="14">
-        <v>45505</v>
+        <v>44998</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>22</v>
+        <v>192</v>
       </c>
       <c r="G45" s="11">
-        <v>0.38670000000000004</v>
+        <v>0.2034</v>
       </c>
       <c r="H45" s="12">
-        <v>58032411.71</v>
+        <v>30334596.91</v>
       </c>
       <c r="I45" s="13">
-        <v>22442987.53</v>
+        <v>6171237.78</v>
       </c>
       <c r="J45" s="12">
-        <v>35589424.18</v>
+        <v>24163359.13</v>
       </c>
       <c r="K45" s="14">
         <v>44753</v>
       </c>
       <c r="L45" s="14">
-        <v>46077</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D46" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="G46" s="11">
-        <v>0.25579999999999997</v>
+        <v>0.38670000000000004</v>
       </c>
       <c r="H46" s="12">
-        <v>51119038.92</v>
+        <v>58032411.71</v>
       </c>
       <c r="I46" s="13">
-        <v>13076598.15</v>
+        <v>22442987.53</v>
       </c>
       <c r="J46" s="12">
-        <v>38042440.77</v>
+        <v>35589424.18</v>
       </c>
       <c r="K46" s="14">
         <v>44753</v>
       </c>
       <c r="L46" s="14">
-        <v>46209</v>
+        <v>46077</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G47" s="11">
-        <v>0.4456</v>
+        <v>0.25579999999999997</v>
       </c>
       <c r="H47" s="12">
-        <v>69450000</v>
+        <v>51119038.92</v>
       </c>
       <c r="I47" s="13">
-        <v>30949430.48</v>
+        <v>13076598.15</v>
       </c>
       <c r="J47" s="12">
-        <v>38500569.519999996</v>
+        <v>38042440.77</v>
       </c>
       <c r="K47" s="14">
-        <v>44449</v>
+        <v>44753</v>
       </c>
       <c r="L47" s="14">
-        <v>45329</v>
+        <v>46209</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D48" s="11" t="s">
         <v>20</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G48" s="11">
-        <v>0.4495</v>
+        <v>0.4456</v>
       </c>
       <c r="H48" s="12">
-        <v>84484346.71</v>
+        <v>69450000</v>
       </c>
       <c r="I48" s="13">
-        <v>37978980.67</v>
+        <v>30949430.48</v>
       </c>
       <c r="J48" s="12">
-        <v>46505366.03999999</v>
+        <v>38500569.519999996</v>
       </c>
       <c r="K48" s="14">
         <v>44449</v>
@@ -4222,230 +4234,230 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D49" s="11" t="s">
         <v>20</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>202</v>
+        <v>103</v>
       </c>
       <c r="G49" s="11">
-        <v>0.0028000000000000004</v>
+        <v>0.4495</v>
       </c>
       <c r="H49" s="12">
-        <v>47996411.38</v>
+        <v>84484346.71</v>
       </c>
       <c r="I49" s="13">
-        <v>133579.45</v>
+        <v>37978980.67</v>
       </c>
       <c r="J49" s="12">
-        <v>47862831.93</v>
+        <v>46505366.03999999</v>
       </c>
       <c r="K49" s="14">
-        <v>44887</v>
+        <v>44449</v>
       </c>
       <c r="L49" s="14">
-        <v>45187</v>
+        <v>45329</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G50" s="11">
-        <v>0.0377</v>
+        <v>0.0028000000000000004</v>
       </c>
       <c r="H50" s="12">
-        <v>54283415</v>
+        <v>47996411.38</v>
       </c>
       <c r="I50" s="13">
-        <v>2045374.39</v>
+        <v>133579.45</v>
       </c>
       <c r="J50" s="12">
-        <v>52238040.61</v>
+        <v>47862831.93</v>
       </c>
       <c r="K50" s="14">
-        <v>44753</v>
+        <v>44887</v>
       </c>
       <c r="L50" s="14">
-        <v>46195</v>
+        <v>45187</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
-        <v>207</v>
+        <v>155</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G51" s="11">
-        <v>0.9643999999999999</v>
+        <v>0.0377</v>
       </c>
       <c r="H51" s="12">
-        <v>1332580.86</v>
+        <v>54283415</v>
       </c>
       <c r="I51" s="13">
-        <v>1285178.36</v>
+        <v>2045374.39</v>
       </c>
       <c r="J51" s="12">
-        <v>47402.5</v>
+        <v>52238040.61</v>
       </c>
       <c r="K51" s="14">
-        <v>44536</v>
+        <v>44753</v>
       </c>
       <c r="L51" s="14">
-        <v>45230</v>
+        <v>46195</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D52" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G52" s="11">
-        <v>1</v>
+        <v>0.9643999999999999</v>
       </c>
       <c r="H52" s="12">
-        <v>8156656.19</v>
+        <v>1332580.86</v>
       </c>
       <c r="I52" s="13">
-        <v>8156656.13</v>
+        <v>1285178.36</v>
       </c>
       <c r="J52" s="12">
-        <v>0.06000000052154064</v>
+        <v>47402.5</v>
       </c>
       <c r="K52" s="14">
-        <v>44832</v>
+        <v>44536</v>
       </c>
       <c r="L52" s="14">
-        <v>45378</v>
+        <v>45230</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="11" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G53" s="11">
-        <v>0.8421</v>
+        <v>1</v>
       </c>
       <c r="H53" s="12">
-        <v>7704834.91</v>
+        <v>8156656.19</v>
       </c>
       <c r="I53" s="13">
-        <v>6488132.94</v>
+        <v>8156656.13</v>
       </c>
       <c r="J53" s="12">
-        <v>1216701.9699999997</v>
+        <v>0.06000000052154064</v>
       </c>
       <c r="K53" s="14">
-        <v>45286</v>
+        <v>44832</v>
       </c>
       <c r="L53" s="14">
-        <v>46098</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="11" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G54" s="11">
-        <v>0</v>
+        <v>0.8421</v>
       </c>
       <c r="H54" s="12">
-        <v>11620104.78</v>
+        <v>7704834.91</v>
       </c>
       <c r="I54" s="13">
-        <v>0</v>
+        <v>6488132.94</v>
       </c>
       <c r="J54" s="12">
-        <v>11620104.78</v>
-      </c>
-      <c r="K54" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="L54" s="15" t="s">
-        <v>226</v>
+        <v>1216701.9699999997</v>
+      </c>
+      <c r="K54" s="14">
+        <v>45286</v>
+      </c>
+      <c r="L54" s="14">
+        <v>46098</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
@@ -4459,7 +4471,7 @@
         <v>229</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E55" s="11" t="s">
         <v>230</v>
@@ -4468,22 +4480,22 @@
         <v>231</v>
       </c>
       <c r="G55" s="11">
-        <v>0.9754</v>
+        <v>0</v>
       </c>
       <c r="H55" s="12">
-        <v>56189486.28</v>
+        <v>11620104.78</v>
       </c>
       <c r="I55" s="13">
-        <v>54809333.5</v>
+        <v>0</v>
       </c>
       <c r="J55" s="12">
-        <v>1380152.7800000012</v>
-      </c>
-      <c r="K55" s="14">
-        <v>45035</v>
-      </c>
-      <c r="L55" s="14">
-        <v>46360</v>
+        <v>11620104.78</v>
+      </c>
+      <c r="K55" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="L55" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
@@ -4497,7 +4509,7 @@
         <v>234</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E56" s="11" t="s">
         <v>235</v>
@@ -4506,141 +4518,141 @@
         <v>236</v>
       </c>
       <c r="G56" s="11">
-        <v>1</v>
+        <v>0.9754</v>
       </c>
       <c r="H56" s="12">
-        <v>4374443.78</v>
+        <v>56189486.28</v>
       </c>
       <c r="I56" s="13">
-        <v>4374443.78</v>
+        <v>54809333.5</v>
       </c>
       <c r="J56" s="12">
-        <v>0</v>
+        <v>1380152.7800000012</v>
       </c>
       <c r="K56" s="14">
-        <v>44707</v>
+        <v>45035</v>
       </c>
       <c r="L56" s="14">
-        <v>45488</v>
+        <v>46360</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>112</v>
+        <v>239</v>
       </c>
       <c r="D57" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>22</v>
+        <v>241</v>
       </c>
       <c r="G57" s="11">
-        <v>0.9994</v>
+        <v>1</v>
       </c>
       <c r="H57" s="12">
-        <v>14995089.28</v>
+        <v>4374443.78</v>
       </c>
       <c r="I57" s="13">
-        <v>14985558.45</v>
+        <v>4374443.78</v>
       </c>
       <c r="J57" s="12">
-        <v>9530.830000000075</v>
+        <v>0</v>
       </c>
       <c r="K57" s="14">
-        <v>44719</v>
+        <v>44707</v>
       </c>
       <c r="L57" s="14">
-        <v>45476</v>
+        <v>45488</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="11" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>240</v>
+        <v>118</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>241</v>
+        <v>15</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>236</v>
+        <v>22</v>
       </c>
       <c r="G58" s="11">
-        <v>0.8652</v>
+        <v>0.9994</v>
       </c>
       <c r="H58" s="12">
-        <v>8463890.94</v>
+        <v>14995089.28</v>
       </c>
       <c r="I58" s="13">
-        <v>7322834.12</v>
+        <v>14985558.45</v>
       </c>
       <c r="J58" s="12">
-        <v>1141056.8199999994</v>
+        <v>9530.830000000075</v>
       </c>
       <c r="K58" s="14">
-        <v>44688</v>
+        <v>44719</v>
       </c>
       <c r="L58" s="14">
-        <v>46045</v>
+        <v>45476</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="11" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G59" s="11">
-        <v>0.4113</v>
+        <v>0.8652</v>
       </c>
       <c r="H59" s="12">
-        <v>30477728.43</v>
+        <v>8463890.94</v>
       </c>
       <c r="I59" s="13">
-        <v>12534756.7</v>
+        <v>7322834.12</v>
       </c>
       <c r="J59" s="12">
-        <v>17942971.73</v>
+        <v>1141056.8199999994</v>
       </c>
       <c r="K59" s="14">
-        <v>44708</v>
+        <v>44688</v>
       </c>
       <c r="L59" s="14">
-        <v>45437</v>
+        <v>46045</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="11" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>248</v>
@@ -4649,7 +4661,7 @@
         <v>249</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E60" s="11" t="s">
         <v>250</v>
@@ -4658,22 +4670,22 @@
         <v>251</v>
       </c>
       <c r="G60" s="11">
-        <v>0.97</v>
+        <v>0.4113</v>
       </c>
       <c r="H60" s="12">
-        <v>5722613.87</v>
+        <v>30477728.43</v>
       </c>
       <c r="I60" s="13">
-        <v>5551029.21</v>
+        <v>12534756.7</v>
       </c>
       <c r="J60" s="12">
-        <v>171584.66000000015</v>
+        <v>17942971.73</v>
       </c>
       <c r="K60" s="14">
-        <v>44727</v>
+        <v>44708</v>
       </c>
       <c r="L60" s="14">
-        <v>45489</v>
+        <v>45437</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -4687,7 +4699,7 @@
         <v>254</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E61" s="11" t="s">
         <v>255</v>
@@ -4696,22 +4708,22 @@
         <v>256</v>
       </c>
       <c r="G61" s="11">
-        <v>0.8092</v>
+        <v>0.97</v>
       </c>
       <c r="H61" s="12">
-        <v>51359899.57</v>
+        <v>5722613.87</v>
       </c>
       <c r="I61" s="13">
-        <v>41562191.24</v>
+        <v>5551029.21</v>
       </c>
       <c r="J61" s="12">
-        <v>9797708.329999998</v>
+        <v>171584.66000000015</v>
       </c>
       <c r="K61" s="14">
-        <v>45105</v>
+        <v>44727</v>
       </c>
       <c r="L61" s="14">
-        <v>45769</v>
+        <v>45489</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -4725,264 +4737,264 @@
         <v>259</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E62" s="11" t="s">
         <v>260</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>17</v>
+        <v>261</v>
       </c>
       <c r="G62" s="11">
-        <v>1</v>
+        <v>0.8092</v>
       </c>
       <c r="H62" s="12">
-        <v>6948720.19</v>
+        <v>51359899.57</v>
       </c>
       <c r="I62" s="13">
-        <v>6948720.19</v>
+        <v>41562191.24</v>
       </c>
       <c r="J62" s="12">
-        <v>0</v>
+        <v>9797708.329999998</v>
       </c>
       <c r="K62" s="14">
-        <v>44882</v>
+        <v>45105</v>
       </c>
       <c r="L62" s="14">
-        <v>45147</v>
+        <v>45769</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="11" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D63" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>264</v>
+        <v>17</v>
       </c>
       <c r="G63" s="11">
-        <v>0.9765999999999999</v>
+        <v>1</v>
       </c>
       <c r="H63" s="12">
-        <v>3107538.75</v>
+        <v>6948720.19</v>
       </c>
       <c r="I63" s="13">
-        <v>3034704.58</v>
+        <v>6948720.19</v>
       </c>
       <c r="J63" s="12">
-        <v>72834.16999999993</v>
+        <v>0</v>
       </c>
       <c r="K63" s="14">
-        <v>44536</v>
+        <v>44882</v>
       </c>
       <c r="L63" s="14">
-        <v>45386</v>
+        <v>45147</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="11" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D64" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G64" s="11">
-        <v>0.9577</v>
+        <v>0.9765999999999999</v>
       </c>
       <c r="H64" s="12">
-        <v>2994510.29</v>
+        <v>3107538.75</v>
       </c>
       <c r="I64" s="13">
-        <v>2867705.32</v>
+        <v>3034704.58</v>
       </c>
       <c r="J64" s="12">
-        <v>126804.9700000002</v>
+        <v>72834.16999999993</v>
       </c>
       <c r="K64" s="14">
-        <v>44804</v>
+        <v>44536</v>
       </c>
       <c r="L64" s="14">
-        <v>45208</v>
+        <v>45386</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="11" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>63</v>
+        <v>271</v>
       </c>
       <c r="D65" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>93</v>
+        <v>273</v>
       </c>
       <c r="G65" s="11">
-        <v>0.8787</v>
+        <v>0.9577</v>
       </c>
       <c r="H65" s="12">
-        <v>6519257.05</v>
+        <v>2994510.29</v>
       </c>
       <c r="I65" s="13">
-        <v>5728240.86</v>
+        <v>2867705.32</v>
       </c>
       <c r="J65" s="12">
-        <v>791016.1899999995</v>
+        <v>126804.9700000002</v>
       </c>
       <c r="K65" s="14">
         <v>44804</v>
       </c>
       <c r="L65" s="14">
-        <v>45569</v>
+        <v>45208</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="11" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>272</v>
+        <v>63</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="G66" s="11">
-        <v>0.545</v>
+        <v>0.8787</v>
       </c>
       <c r="H66" s="12">
-        <v>2069000</v>
+        <v>6519257.05</v>
       </c>
       <c r="I66" s="13">
-        <v>1127516.06</v>
+        <v>5728240.86</v>
       </c>
       <c r="J66" s="12">
-        <v>941483.94</v>
+        <v>791016.1899999995</v>
       </c>
       <c r="K66" s="14">
-        <v>45972</v>
+        <v>44804</v>
       </c>
       <c r="L66" s="14">
-        <v>46167</v>
+        <v>45569</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="11" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D67" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G67" s="11">
-        <v>0.6604000000000001</v>
+        <v>0.545</v>
       </c>
       <c r="H67" s="12">
-        <v>12950372.72</v>
+        <v>2069000</v>
       </c>
       <c r="I67" s="13">
-        <v>8552770.91</v>
+        <v>1127516.06</v>
       </c>
       <c r="J67" s="12">
-        <v>4397601.8100000005</v>
+        <v>941483.94</v>
       </c>
       <c r="K67" s="14">
-        <v>44742</v>
+        <v>45972</v>
       </c>
       <c r="L67" s="14">
-        <v>46219</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" s="11" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>280</v>
+        <v>45</v>
       </c>
       <c r="G68" s="11">
-        <v>0.47490000000000004</v>
+        <v>0.6604000000000001</v>
       </c>
       <c r="H68" s="12">
-        <v>18996888.26</v>
+        <v>12950372.72</v>
       </c>
       <c r="I68" s="13">
-        <v>9021796.75</v>
+        <v>8552770.91</v>
       </c>
       <c r="J68" s="12">
-        <v>9975091.510000002</v>
-      </c>
-      <c r="K68" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="L68" s="15" t="s">
-        <v>226</v>
+        <v>4397601.8100000005</v>
+      </c>
+      <c r="K68" s="14">
+        <v>44742</v>
+      </c>
+      <c r="L68" s="14">
+        <v>46219</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="11" t="s">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>282</v>
@@ -4991,7 +5003,7 @@
         <v>283</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E69" s="11" t="s">
         <v>284</v>
@@ -5000,65 +5012,65 @@
         <v>285</v>
       </c>
       <c r="G69" s="11">
-        <v>0.9969</v>
+        <v>0.47490000000000004</v>
       </c>
       <c r="H69" s="12">
-        <v>25179808.67</v>
+        <v>18996888.26</v>
       </c>
       <c r="I69" s="13">
-        <v>25102278.03</v>
+        <v>9021796.75</v>
       </c>
       <c r="J69" s="12">
-        <v>77530.6400000006</v>
-      </c>
-      <c r="K69" s="14">
-        <v>45646</v>
-      </c>
-      <c r="L69" s="14">
-        <v>46005</v>
+        <v>9975091.510000002</v>
+      </c>
+      <c r="K69" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="L69" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" s="11" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D70" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G70" s="11">
-        <v>0.8062999999999999</v>
+        <v>0.9969</v>
       </c>
       <c r="H70" s="12">
-        <v>8811881.78</v>
+        <v>25179808.67</v>
       </c>
       <c r="I70" s="13">
-        <v>7104640.05</v>
+        <v>25102278.03</v>
       </c>
       <c r="J70" s="12">
-        <v>1707241.7299999995</v>
+        <v>77530.6400000006</v>
       </c>
       <c r="K70" s="14">
-        <v>45360</v>
+        <v>45646</v>
       </c>
       <c r="L70" s="14">
-        <v>45566</v>
+        <v>46005</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" s="11" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>291</v>
@@ -5076,331 +5088,331 @@
         <v>294</v>
       </c>
       <c r="G71" s="11">
-        <v>1</v>
+        <v>0.8062999999999999</v>
       </c>
       <c r="H71" s="12">
-        <v>724764.22</v>
+        <v>8811881.78</v>
       </c>
       <c r="I71" s="13">
-        <v>724764.22</v>
+        <v>7104640.05</v>
       </c>
       <c r="J71" s="12">
-        <v>0</v>
+        <v>1707241.7299999995</v>
       </c>
       <c r="K71" s="14">
-        <v>44911</v>
+        <v>45360</v>
       </c>
       <c r="L71" s="14">
-        <v>45182</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" s="11" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>45</v>
+        <v>299</v>
       </c>
       <c r="G72" s="11">
-        <v>0.8592</v>
+        <v>1</v>
       </c>
       <c r="H72" s="12">
-        <v>34662990.03</v>
+        <v>724764.22</v>
       </c>
       <c r="I72" s="13">
-        <v>29783877.3</v>
+        <v>724764.22</v>
       </c>
       <c r="J72" s="12">
-        <v>4879112.73</v>
+        <v>0</v>
       </c>
       <c r="K72" s="14">
-        <v>45155</v>
+        <v>44911</v>
       </c>
       <c r="L72" s="14">
-        <v>46239</v>
+        <v>45182</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" s="11" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>241</v>
+        <v>34</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>148</v>
+        <v>45</v>
       </c>
       <c r="G73" s="11">
-        <v>0.07</v>
+        <v>0.8592</v>
       </c>
       <c r="H73" s="12">
-        <v>27739392.32</v>
+        <v>34662990.03</v>
       </c>
       <c r="I73" s="13">
-        <v>1940441.71</v>
+        <v>29783877.3</v>
       </c>
       <c r="J73" s="12">
-        <v>25798950.61</v>
+        <v>4879112.73</v>
       </c>
       <c r="K73" s="14">
-        <v>45541</v>
+        <v>45155</v>
       </c>
       <c r="L73" s="14">
-        <v>46081</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" s="11" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>15</v>
+        <v>246</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>305</v>
+        <v>154</v>
       </c>
       <c r="G74" s="11">
-        <v>0.8991</v>
+        <v>0.07</v>
       </c>
       <c r="H74" s="12">
-        <v>666913.68</v>
+        <v>27739392.32</v>
       </c>
       <c r="I74" s="13">
-        <v>599641.31</v>
+        <v>1940441.71</v>
       </c>
       <c r="J74" s="12">
-        <v>67272.37</v>
+        <v>25798950.61</v>
       </c>
       <c r="K74" s="14">
-        <v>45783</v>
+        <v>45541</v>
       </c>
       <c r="L74" s="14">
-        <v>45964</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" s="11" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E75" s="11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="G75" s="11">
-        <v>0.8976000000000001</v>
+        <v>0.8991</v>
       </c>
       <c r="H75" s="12">
-        <v>763285.07</v>
+        <v>666913.68</v>
       </c>
       <c r="I75" s="13">
-        <v>685145.56</v>
+        <v>599641.31</v>
       </c>
       <c r="J75" s="12">
-        <v>78139.5099999999</v>
+        <v>67272.37</v>
       </c>
       <c r="K75" s="14">
         <v>45783</v>
       </c>
       <c r="L75" s="14">
-        <v>46115</v>
+        <v>45964</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="11" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C76" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="D76" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E76" s="11" t="s">
+        <v>313</v>
+      </c>
+      <c r="F76" s="11" t="s">
         <v>310</v>
       </c>
-      <c r="D76" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E76" s="11" t="s">
-        <v>311</v>
-      </c>
-      <c r="F76" s="11" t="s">
-        <v>73</v>
-      </c>
       <c r="G76" s="11">
-        <v>0.9495</v>
+        <v>0.8976000000000001</v>
       </c>
       <c r="H76" s="12">
-        <v>32836774.76</v>
+        <v>763285.07</v>
       </c>
       <c r="I76" s="13">
-        <v>31178236.21</v>
+        <v>685145.56</v>
       </c>
       <c r="J76" s="12">
-        <v>1658538.5500000007</v>
+        <v>78139.5099999999</v>
       </c>
       <c r="K76" s="14">
-        <v>44564</v>
+        <v>45783</v>
       </c>
       <c r="L76" s="14">
-        <v>44944</v>
+        <v>46115</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="11" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D77" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E77" s="11" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F77" s="11" t="s">
-        <v>164</v>
+        <v>73</v>
       </c>
       <c r="G77" s="11">
-        <v>0.9543</v>
+        <v>0.9495</v>
       </c>
       <c r="H77" s="12">
-        <v>36880209</v>
+        <v>32836774.76</v>
       </c>
       <c r="I77" s="13">
-        <v>35196032.93</v>
+        <v>31178236.21</v>
       </c>
       <c r="J77" s="12">
-        <v>1684176.0700000003</v>
+        <v>1658538.5500000007</v>
       </c>
       <c r="K77" s="14">
-        <v>44648</v>
+        <v>44564</v>
       </c>
       <c r="L77" s="14">
-        <v>45498</v>
+        <v>44944</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="11" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E78" s="11" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F78" s="11" t="s">
-        <v>318</v>
+        <v>170</v>
       </c>
       <c r="G78" s="11">
-        <v>0.0134</v>
+        <v>0.9543</v>
       </c>
       <c r="H78" s="12">
-        <v>4705907.3</v>
+        <v>36880209</v>
       </c>
       <c r="I78" s="13">
-        <v>63006.28</v>
+        <v>35196032.93</v>
       </c>
       <c r="J78" s="12">
-        <v>4642901.02</v>
+        <v>1684176.0700000003</v>
       </c>
       <c r="K78" s="14">
-        <v>46009</v>
+        <v>44648</v>
       </c>
       <c r="L78" s="14">
-        <v>46189</v>
+        <v>45498</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="11" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D79" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E79" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F79" s="11" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G79" s="11">
-        <v>0.5292</v>
+        <v>0.0134</v>
       </c>
       <c r="H79" s="12">
-        <v>10349390.52</v>
+        <v>4705907.3</v>
       </c>
       <c r="I79" s="13">
-        <v>5476795.79</v>
+        <v>63006.28</v>
       </c>
       <c r="J79" s="12">
-        <v>4872594.7299999995</v>
+        <v>4642901.02</v>
       </c>
       <c r="K79" s="14">
-        <v>45867</v>
+        <v>46009</v>
       </c>
       <c r="L79" s="14">
-        <v>46227</v>
+        <v>46189</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" s="11" t="s">
-        <v>323</v>
+        <v>306</v>
       </c>
       <c r="B80" s="11" t="s">
         <v>324</v>
@@ -5409,561 +5421,561 @@
         <v>325</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E80" s="11" t="s">
         <v>326</v>
       </c>
       <c r="F80" s="11" t="s">
-        <v>305</v>
+        <v>327</v>
       </c>
       <c r="G80" s="11">
-        <v>1</v>
+        <v>0.5292</v>
       </c>
       <c r="H80" s="12">
-        <v>1923627.23</v>
+        <v>10349390.52</v>
       </c>
       <c r="I80" s="13">
-        <v>1923627.26</v>
+        <v>5476795.79</v>
       </c>
       <c r="J80" s="12">
-        <v>-0.030000000027939677</v>
+        <v>4872594.7299999995</v>
       </c>
       <c r="K80" s="14">
-        <v>44708</v>
+        <v>45867</v>
       </c>
       <c r="L80" s="14">
-        <v>45640</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" s="11" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D81" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E81" s="11" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F81" s="11" t="s">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="G81" s="11">
         <v>1</v>
       </c>
       <c r="H81" s="12">
-        <v>3552093.82</v>
+        <v>1923627.23</v>
       </c>
       <c r="I81" s="13">
-        <v>3552073.13</v>
+        <v>1923627.26</v>
       </c>
       <c r="J81" s="12">
-        <v>20.68999999994412</v>
+        <v>-0.030000000027939677</v>
       </c>
       <c r="K81" s="14">
-        <v>45034</v>
+        <v>44708</v>
       </c>
       <c r="L81" s="14">
-        <v>45034</v>
+        <v>45640</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" s="11" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>249</v>
+        <v>333</v>
       </c>
       <c r="D82" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E82" s="11" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>22</v>
+        <v>335</v>
       </c>
       <c r="G82" s="11">
-        <v>0.9723</v>
+        <v>1</v>
       </c>
       <c r="H82" s="12">
-        <v>15078640.21</v>
+        <v>3552093.82</v>
       </c>
       <c r="I82" s="13">
-        <v>14660282.37</v>
+        <v>3552073.13</v>
       </c>
       <c r="J82" s="12">
-        <v>418357.8400000017</v>
+        <v>20.68999999994412</v>
       </c>
       <c r="K82" s="14">
-        <v>45497</v>
+        <v>45034</v>
       </c>
       <c r="L82" s="14">
-        <v>45301</v>
+        <v>45034</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" s="11" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>334</v>
+        <v>254</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E83" s="11" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F83" s="11" t="s">
-        <v>336</v>
+        <v>22</v>
       </c>
       <c r="G83" s="11">
-        <v>0.948</v>
+        <v>0.9723</v>
       </c>
       <c r="H83" s="12">
-        <v>59148617.81</v>
+        <v>15078640.21</v>
       </c>
       <c r="I83" s="13">
-        <v>56075178.64</v>
+        <v>14660282.37</v>
       </c>
       <c r="J83" s="12">
-        <v>3073439.170000002</v>
+        <v>418357.8400000017</v>
       </c>
       <c r="K83" s="14">
-        <v>44726</v>
+        <v>45497</v>
       </c>
       <c r="L83" s="14">
-        <v>46006</v>
+        <v>45301</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" s="11" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="B84" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="C84" s="11"/>
+      <c r="C84" s="11" t="s">
+        <v>339</v>
+      </c>
       <c r="D84" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E84" s="11" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F84" s="11" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G84" s="11">
-        <v>0</v>
+        <v>0.948</v>
       </c>
       <c r="H84" s="12">
-        <v>62980000</v>
+        <v>59148617.81</v>
       </c>
       <c r="I84" s="13">
-        <v>62980000</v>
+        <v>56075178.64</v>
       </c>
       <c r="J84" s="12">
-        <v>0</v>
+        <v>3073439.170000002</v>
       </c>
       <c r="K84" s="14">
-        <v>43930</v>
+        <v>44726</v>
       </c>
       <c r="L84" s="14">
-        <v>44011</v>
+        <v>46006</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" s="11" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>341</v>
-      </c>
-      <c r="C85" s="11" t="s">
-        <v>342</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="C85" s="11"/>
       <c r="D85" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E85" s="11" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F85" s="11" t="s">
-        <v>202</v>
+        <v>345</v>
       </c>
       <c r="G85" s="11">
-        <v>0.9976999999999999</v>
+        <v>0</v>
       </c>
       <c r="H85" s="12">
-        <v>19451386.88</v>
+        <v>62980000</v>
       </c>
       <c r="I85" s="13">
-        <v>19406169.39</v>
+        <v>62980000</v>
       </c>
       <c r="J85" s="12">
-        <v>45217.48999999836</v>
+        <v>0</v>
       </c>
       <c r="K85" s="14">
-        <v>45247</v>
+        <v>43930</v>
       </c>
       <c r="L85" s="14">
-        <v>46001</v>
+        <v>44011</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" s="11" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D86" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E86" s="11" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F86" s="11" t="s">
-        <v>40</v>
+        <v>208</v>
       </c>
       <c r="G86" s="11">
-        <v>0.9666</v>
+        <v>0.9976999999999999</v>
       </c>
       <c r="H86" s="12">
-        <v>20106028.53</v>
+        <v>19451386.88</v>
       </c>
       <c r="I86" s="13">
-        <v>19434508.22</v>
+        <v>19406169.39</v>
       </c>
       <c r="J86" s="12">
-        <v>671520.3100000024</v>
+        <v>45217.48999999836</v>
       </c>
       <c r="K86" s="14">
-        <v>44991</v>
+        <v>45247</v>
       </c>
       <c r="L86" s="14">
-        <v>46094</v>
+        <v>46001</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" s="11" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>138</v>
+        <v>350</v>
       </c>
       <c r="D87" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E87" s="11" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F87" s="11" t="s">
-        <v>157</v>
+        <v>40</v>
       </c>
       <c r="G87" s="11">
-        <v>0.9577</v>
+        <v>0.9666</v>
       </c>
       <c r="H87" s="12">
-        <v>34508101.15</v>
+        <v>20106028.53</v>
       </c>
       <c r="I87" s="13">
-        <v>33048630.33</v>
+        <v>19434508.22</v>
       </c>
       <c r="J87" s="12">
-        <v>1459470.8200000003</v>
+        <v>671520.3100000024</v>
       </c>
       <c r="K87" s="14">
-        <v>44690</v>
+        <v>44991</v>
       </c>
       <c r="L87" s="14">
-        <v>45621</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" s="11" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>350</v>
+        <v>144</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E88" s="11" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F88" s="11" t="s">
-        <v>352</v>
+        <v>163</v>
       </c>
       <c r="G88" s="11">
-        <v>0.9711</v>
+        <v>0.9577</v>
       </c>
       <c r="H88" s="12">
-        <v>58086688.76</v>
+        <v>34508101.15</v>
       </c>
       <c r="I88" s="13">
-        <v>56408550.91</v>
+        <v>33048630.33</v>
       </c>
       <c r="J88" s="12">
-        <v>1678137.8500000015</v>
+        <v>1459470.8200000003</v>
       </c>
       <c r="K88" s="14">
-        <v>44831</v>
+        <v>44690</v>
       </c>
       <c r="L88" s="14">
-        <v>45619</v>
+        <v>45621</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" s="11" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D89" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E89" s="11" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F89" s="11" t="s">
-        <v>216</v>
+        <v>357</v>
       </c>
       <c r="G89" s="11">
-        <v>0.6973</v>
+        <v>0.9711</v>
       </c>
       <c r="H89" s="12">
-        <v>28459856.91</v>
+        <v>58086688.76</v>
       </c>
       <c r="I89" s="13">
-        <v>19844966.58</v>
+        <v>56408550.91</v>
       </c>
       <c r="J89" s="12">
-        <v>8614890.330000002</v>
+        <v>1678137.8500000015</v>
       </c>
       <c r="K89" s="14">
-        <v>45035</v>
+        <v>44831</v>
       </c>
       <c r="L89" s="14">
-        <v>46205</v>
+        <v>45619</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" s="11" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D90" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E90" s="11" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F90" s="11" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="G90" s="11">
-        <v>0.7805</v>
+        <v>0.6973</v>
       </c>
       <c r="H90" s="12">
-        <v>45862409.69</v>
+        <v>28459856.91</v>
       </c>
       <c r="I90" s="13">
-        <v>35796161.98</v>
+        <v>19844966.58</v>
       </c>
       <c r="J90" s="12">
-        <v>10066247.71</v>
+        <v>8614890.330000002</v>
       </c>
       <c r="K90" s="14">
-        <v>45352</v>
+        <v>45035</v>
       </c>
       <c r="L90" s="14">
-        <v>46255</v>
+        <v>46205</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" s="11" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D91" s="11" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E91" s="11" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F91" s="11" t="s">
-        <v>157</v>
+        <v>212</v>
       </c>
       <c r="G91" s="11">
-        <v>0.0132</v>
+        <v>0.7805</v>
       </c>
       <c r="H91" s="12">
-        <v>11494433.26</v>
+        <v>45862409.69</v>
       </c>
       <c r="I91" s="13">
-        <v>151285.62</v>
+        <v>35796161.98</v>
       </c>
       <c r="J91" s="12">
-        <v>11343147.64</v>
+        <v>10066247.71</v>
       </c>
       <c r="K91" s="14">
-        <v>45105</v>
+        <v>45352</v>
       </c>
       <c r="L91" s="14">
-        <v>45706</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" s="11" t="s">
-        <v>362</v>
+        <v>342</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>172</v>
+        <v>365</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E92" s="11" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F92" s="11" t="s">
-        <v>365</v>
+        <v>163</v>
       </c>
       <c r="G92" s="11">
-        <v>0.898</v>
+        <v>0.0132</v>
       </c>
       <c r="H92" s="12">
-        <v>1212482.21</v>
+        <v>11494433.26</v>
       </c>
       <c r="I92" s="13">
-        <v>1088826.01</v>
+        <v>151285.62</v>
       </c>
       <c r="J92" s="12">
-        <v>123656.19999999995</v>
+        <v>11343147.64</v>
       </c>
       <c r="K92" s="14">
-        <v>44326</v>
+        <v>45105</v>
       </c>
       <c r="L92" s="14">
-        <v>44536</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" s="11" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>367</v>
+        <v>178</v>
       </c>
       <c r="D93" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E93" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F93" s="11" t="s">
-        <v>57</v>
+        <v>370</v>
       </c>
       <c r="G93" s="11">
-        <v>0.9209</v>
+        <v>0.898</v>
       </c>
       <c r="H93" s="12">
-        <v>12560309.12</v>
+        <v>1212482.21</v>
       </c>
       <c r="I93" s="13">
-        <v>11566432.39</v>
+        <v>1088826.01</v>
       </c>
       <c r="J93" s="12">
-        <v>993876.7299999986</v>
+        <v>123656.19999999995</v>
       </c>
       <c r="K93" s="14">
-        <v>44831</v>
+        <v>44326</v>
       </c>
       <c r="L93" s="14">
-        <v>45477</v>
+        <v>44536</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" s="11" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D94" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E94" s="11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F94" s="11" t="s">
-        <v>373</v>
+        <v>57</v>
       </c>
       <c r="G94" s="11">
-        <v>0.9990000000000001</v>
+        <v>0.9209</v>
       </c>
       <c r="H94" s="12">
-        <v>17695067.23</v>
+        <v>12560309.12</v>
       </c>
       <c r="I94" s="13">
-        <v>17677149.84</v>
+        <v>11566432.39</v>
       </c>
       <c r="J94" s="12">
-        <v>17917.390000000596</v>
+        <v>993876.7299999986</v>
       </c>
       <c r="K94" s="14">
-        <v>44994</v>
+        <v>44831</v>
       </c>
       <c r="L94" s="14">
-        <v>45928</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -5974,381 +5986,381 @@
         <v>375</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>95</v>
+        <v>376</v>
       </c>
       <c r="D95" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E95" s="11" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F95" s="11" t="s">
-        <v>17</v>
+        <v>378</v>
       </c>
       <c r="G95" s="11">
-        <v>1</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="H95" s="12">
-        <v>12092480.69</v>
+        <v>17695067.23</v>
       </c>
       <c r="I95" s="13">
-        <v>12092480.69</v>
+        <v>17677149.84</v>
       </c>
       <c r="J95" s="12">
-        <v>0</v>
+        <v>17917.390000000596</v>
       </c>
       <c r="K95" s="14">
-        <v>44734</v>
+        <v>44994</v>
       </c>
       <c r="L95" s="14">
-        <v>45202</v>
+        <v>45928</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" s="11" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="D96" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E96" s="11" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="F96" s="11" t="s">
-        <v>379</v>
+        <v>17</v>
       </c>
       <c r="G96" s="11">
-        <v>0.9117000000000001</v>
+        <v>1</v>
       </c>
       <c r="H96" s="12">
-        <v>5978542.15</v>
+        <v>12092480.69</v>
       </c>
       <c r="I96" s="13">
-        <v>5450477.04</v>
+        <v>12092480.69</v>
       </c>
       <c r="J96" s="12">
-        <v>528065.1100000003</v>
+        <v>0</v>
       </c>
       <c r="K96" s="14">
-        <v>44753</v>
+        <v>44734</v>
       </c>
       <c r="L96" s="14">
-        <v>44933</v>
+        <v>45202</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" s="11" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>381</v>
+        <v>126</v>
       </c>
       <c r="D97" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E97" s="11" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F97" s="11" t="s">
-        <v>280</v>
+        <v>384</v>
       </c>
       <c r="G97" s="11">
-        <v>0.8019</v>
+        <v>0.9117000000000001</v>
       </c>
       <c r="H97" s="12">
-        <v>7066834.9</v>
+        <v>5978542.15</v>
       </c>
       <c r="I97" s="13">
-        <v>5666949.72</v>
+        <v>5450477.04</v>
       </c>
       <c r="J97" s="12">
-        <v>1399885.1800000006</v>
+        <v>528065.1100000003</v>
       </c>
       <c r="K97" s="14">
-        <v>45848</v>
+        <v>44753</v>
       </c>
       <c r="L97" s="14">
-        <v>46222</v>
+        <v>44933</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" s="11" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D98" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E98" s="11" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F98" s="11" t="s">
-        <v>386</v>
+        <v>285</v>
       </c>
       <c r="G98" s="11">
-        <v>0.8362</v>
+        <v>0.8019</v>
       </c>
       <c r="H98" s="12">
-        <v>11942741.09</v>
+        <v>7066834.9</v>
       </c>
       <c r="I98" s="13">
-        <v>9986334.63</v>
+        <v>5666949.72</v>
       </c>
       <c r="J98" s="12">
-        <v>1956406.459999999</v>
+        <v>1399885.1800000006</v>
       </c>
       <c r="K98" s="14">
-        <v>44734</v>
+        <v>45848</v>
       </c>
       <c r="L98" s="14">
-        <v>45098</v>
+        <v>46222</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" s="11" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D99" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E99" s="11" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F99" s="11" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="G99" s="11">
-        <v>0.9493</v>
+        <v>0.8362</v>
       </c>
       <c r="H99" s="12">
-        <v>48302952.43</v>
+        <v>11942741.09</v>
       </c>
       <c r="I99" s="13">
-        <v>45853223.3</v>
+        <v>9986334.63</v>
       </c>
       <c r="J99" s="12">
-        <v>2449729.1300000027</v>
+        <v>1956406.459999999</v>
       </c>
       <c r="K99" s="14">
-        <v>45189</v>
+        <v>44734</v>
       </c>
       <c r="L99" s="14">
-        <v>45729</v>
+        <v>45098</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" s="11" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D100" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E100" s="11" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F100" s="11" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G100" s="11">
-        <v>0.9181999999999999</v>
+        <v>0.9493</v>
       </c>
       <c r="H100" s="12">
-        <v>30543662.31</v>
+        <v>48302952.43</v>
       </c>
       <c r="I100" s="13">
-        <v>28044628.6</v>
+        <v>45853223.3</v>
       </c>
       <c r="J100" s="12">
-        <v>2499033.709999997</v>
+        <v>2449729.1300000027</v>
       </c>
       <c r="K100" s="14">
-        <v>44826</v>
+        <v>45189</v>
       </c>
       <c r="L100" s="14">
-        <v>45540</v>
+        <v>45729</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" s="11" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D101" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E101" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F101" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G101" s="11">
-        <v>0.9188</v>
+        <v>0.9181999999999999</v>
       </c>
       <c r="H101" s="12">
-        <v>54913544.95</v>
+        <v>30543662.31</v>
       </c>
       <c r="I101" s="13">
-        <v>50454918.61</v>
+        <v>28044628.6</v>
       </c>
       <c r="J101" s="12">
-        <v>4458626.340000004</v>
+        <v>2499033.709999997</v>
       </c>
       <c r="K101" s="14">
-        <v>44769</v>
+        <v>44826</v>
       </c>
       <c r="L101" s="14">
-        <v>45174</v>
+        <v>45540</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" s="11" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D102" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E102" s="11" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F102" s="11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G102" s="11">
-        <v>0.7739</v>
+        <v>0.9188</v>
       </c>
       <c r="H102" s="12">
-        <v>27434724</v>
+        <v>54913544.95</v>
       </c>
       <c r="I102" s="13">
-        <v>21232327.94</v>
+        <v>50454918.61</v>
       </c>
       <c r="J102" s="12">
-        <v>6202396.059999999</v>
+        <v>4458626.340000004</v>
       </c>
       <c r="K102" s="14">
-        <v>46002</v>
+        <v>44769</v>
       </c>
       <c r="L102" s="14">
-        <v>46242</v>
+        <v>45174</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" s="11" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D103" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E103" s="11" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F103" s="11" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="G103" s="11">
-        <v>0.9224</v>
+        <v>0.7739</v>
       </c>
       <c r="H103" s="12">
-        <v>80552394.92</v>
+        <v>27434724</v>
       </c>
       <c r="I103" s="13">
-        <v>74305045.47</v>
+        <v>21232327.94</v>
       </c>
       <c r="J103" s="12">
-        <v>6247349.450000003</v>
+        <v>6202396.059999999</v>
       </c>
       <c r="K103" s="14">
-        <v>44709</v>
+        <v>46002</v>
       </c>
       <c r="L103" s="14">
-        <v>45114</v>
+        <v>46242</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" s="11" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D104" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E104" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F104" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G104" s="11">
-        <v>0.4476</v>
+        <v>0.9224</v>
       </c>
       <c r="H104" s="12">
-        <v>68148567.14</v>
+        <v>80552394.92</v>
       </c>
       <c r="I104" s="13">
-        <v>30502735.41</v>
+        <v>74305045.47</v>
       </c>
       <c r="J104" s="12">
-        <v>37645831.730000004</v>
+        <v>6247349.450000003</v>
       </c>
       <c r="K104" s="14">
-        <v>44767</v>
+        <v>44709</v>
       </c>
       <c r="L104" s="14">
-        <v>45173</v>
+        <v>45114</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" s="11" t="s">
-        <v>410</v>
+        <v>379</v>
       </c>
       <c r="B105" s="11" t="s">
         <v>411</v>
@@ -6366,217 +6378,217 @@
         <v>414</v>
       </c>
       <c r="G105" s="11">
-        <v>0.9984000000000001</v>
+        <v>0.4476</v>
       </c>
       <c r="H105" s="12">
-        <v>1498793.43</v>
+        <v>68148567.14</v>
       </c>
       <c r="I105" s="13">
-        <v>1496414.32</v>
+        <v>30502735.41</v>
       </c>
       <c r="J105" s="12">
-        <v>2379.1099999998696</v>
+        <v>37645831.730000004</v>
       </c>
       <c r="K105" s="14">
-        <v>45195</v>
+        <v>44767</v>
       </c>
       <c r="L105" s="14">
-        <v>45121</v>
+        <v>45173</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" s="11" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D106" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E106" s="11" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F106" s="11" t="s">
-        <v>294</v>
+        <v>419</v>
       </c>
       <c r="G106" s="11">
-        <v>0.9718000000000001</v>
+        <v>0.9984000000000001</v>
       </c>
       <c r="H106" s="12">
-        <v>1988555.07</v>
+        <v>1498793.43</v>
       </c>
       <c r="I106" s="13">
-        <v>1932548.63</v>
+        <v>1496414.32</v>
       </c>
       <c r="J106" s="12">
-        <v>56006.44000000018</v>
+        <v>2379.1099999998696</v>
       </c>
       <c r="K106" s="14">
-        <v>44742</v>
+        <v>45195</v>
       </c>
       <c r="L106" s="14">
-        <v>45412</v>
+        <v>45121</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107" s="11" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D107" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E107" s="11" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F107" s="11" t="s">
-        <v>397</v>
+        <v>299</v>
       </c>
       <c r="G107" s="11">
-        <v>0.608</v>
+        <v>0.9718000000000001</v>
       </c>
       <c r="H107" s="12">
-        <v>2860442.12</v>
+        <v>1988555.07</v>
       </c>
       <c r="I107" s="13">
-        <v>1739254.2</v>
+        <v>1932548.63</v>
       </c>
       <c r="J107" s="12">
-        <v>1121187.9200000002</v>
+        <v>56006.44000000018</v>
       </c>
       <c r="K107" s="14">
-        <v>45782</v>
+        <v>44742</v>
       </c>
       <c r="L107" s="14">
-        <v>46083</v>
+        <v>45412</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108" s="11" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C108" s="11" t="s">
-        <v>403</v>
+        <v>424</v>
       </c>
       <c r="D108" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E108" s="11" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="F108" s="11" t="s">
-        <v>424</v>
+        <v>402</v>
       </c>
       <c r="G108" s="11">
-        <v>0.9998999999999999</v>
+        <v>0.608</v>
       </c>
       <c r="H108" s="12">
-        <v>5272095.08</v>
+        <v>2860442.12</v>
       </c>
       <c r="I108" s="13">
-        <v>5271693.21</v>
+        <v>1739254.2</v>
       </c>
       <c r="J108" s="12">
-        <v>401.87000000011176</v>
+        <v>1121187.9200000002</v>
       </c>
       <c r="K108" s="14">
-        <v>44746</v>
+        <v>45782</v>
       </c>
       <c r="L108" s="14">
-        <v>45560</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109" s="11" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>426</v>
+        <v>408</v>
       </c>
       <c r="D109" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E109" s="11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F109" s="11" t="s">
-        <v>294</v>
+        <v>429</v>
       </c>
       <c r="G109" s="11">
-        <v>0.9931</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="H109" s="12">
-        <v>1690234.37</v>
+        <v>5272095.08</v>
       </c>
       <c r="I109" s="13">
-        <v>1678610.19</v>
+        <v>5271693.21</v>
       </c>
       <c r="J109" s="12">
-        <v>11624.180000000168</v>
+        <v>401.87000000011176</v>
       </c>
       <c r="K109" s="14">
-        <v>44772</v>
+        <v>44746</v>
       </c>
       <c r="L109" s="14">
-        <v>45316</v>
+        <v>45560</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A110" s="11" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D110" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E110" s="11" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F110" s="11" t="s">
-        <v>431</v>
+        <v>299</v>
       </c>
       <c r="G110" s="11">
-        <v>0.9994</v>
+        <v>0.9931</v>
       </c>
       <c r="H110" s="12">
-        <v>26946699.36</v>
+        <v>1690234.37</v>
       </c>
       <c r="I110" s="13">
-        <v>26930984.02</v>
+        <v>1678610.19</v>
       </c>
       <c r="J110" s="12">
-        <v>15715.339999999851</v>
+        <v>11624.180000000168</v>
       </c>
       <c r="K110" s="14">
-        <v>44823</v>
+        <v>44772</v>
       </c>
       <c r="L110" s="14">
-        <v>45816</v>
+        <v>45316</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111" s="11" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="B111" s="11" t="s">
         <v>433</v>
@@ -6591,443 +6603,443 @@
         <v>435</v>
       </c>
       <c r="F111" s="11" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="G111" s="11">
-        <v>1</v>
+        <v>0.9994</v>
       </c>
       <c r="H111" s="12">
-        <v>3607367.42</v>
+        <v>26946699.36</v>
       </c>
       <c r="I111" s="13">
-        <v>3607318.65</v>
+        <v>26930984.02</v>
       </c>
       <c r="J111" s="12">
-        <v>48.77000000001863</v>
+        <v>15715.339999999851</v>
       </c>
       <c r="K111" s="14">
-        <v>45061</v>
+        <v>44823</v>
       </c>
       <c r="L111" s="14">
-        <v>45016</v>
+        <v>45816</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112" s="11" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C112" s="11" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D112" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E112" s="11" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="F112" s="11" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="G112" s="11">
-        <v>0.9958</v>
+        <v>1</v>
       </c>
       <c r="H112" s="12">
-        <v>4645152.25</v>
+        <v>3607367.42</v>
       </c>
       <c r="I112" s="13">
-        <v>4625557.49</v>
+        <v>3607318.65</v>
       </c>
       <c r="J112" s="12">
-        <v>19594.759999999776</v>
+        <v>48.77000000001863</v>
       </c>
       <c r="K112" s="14">
-        <v>44918</v>
+        <v>45061</v>
       </c>
       <c r="L112" s="14">
-        <v>45485</v>
+        <v>45016</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113" s="11" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D113" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E113" s="11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F113" s="11" t="s">
-        <v>443</v>
+        <v>429</v>
       </c>
       <c r="G113" s="11">
-        <v>1</v>
+        <v>0.9958</v>
       </c>
       <c r="H113" s="12">
-        <v>13242425.64</v>
+        <v>4645152.25</v>
       </c>
       <c r="I113" s="13">
-        <v>13242495.84</v>
+        <v>4625557.49</v>
       </c>
       <c r="J113" s="12">
-        <v>-70.19999999925494</v>
+        <v>19594.759999999776</v>
       </c>
       <c r="K113" s="14">
-        <v>44923</v>
+        <v>44918</v>
       </c>
       <c r="L113" s="14">
-        <v>45531</v>
+        <v>45485</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" s="11" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D114" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E114" s="11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F114" s="11" t="s">
-        <v>45</v>
+        <v>448</v>
       </c>
       <c r="G114" s="11">
         <v>1</v>
       </c>
       <c r="H114" s="12">
-        <v>20859068.44</v>
+        <v>13242425.64</v>
       </c>
       <c r="I114" s="13">
-        <v>20859068.44</v>
+        <v>13242495.84</v>
       </c>
       <c r="J114" s="12">
-        <v>0</v>
+        <v>-70.19999999925494</v>
       </c>
       <c r="K114" s="14">
-        <v>45007</v>
+        <v>44923</v>
       </c>
       <c r="L114" s="14">
-        <v>45851</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" s="11" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D115" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E115" s="11" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="F115" s="11" t="s">
-        <v>450</v>
+        <v>45</v>
       </c>
       <c r="G115" s="11">
-        <v>0.9842</v>
+        <v>1</v>
       </c>
       <c r="H115" s="12">
-        <v>20229149.79</v>
+        <v>20859068.44</v>
       </c>
       <c r="I115" s="13">
-        <v>19910398.37</v>
+        <v>20859068.44</v>
       </c>
       <c r="J115" s="12">
-        <v>318751.41999999806</v>
+        <v>0</v>
       </c>
       <c r="K115" s="14">
-        <v>44697</v>
+        <v>45007</v>
       </c>
       <c r="L115" s="14">
-        <v>45783</v>
+        <v>45851</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116" s="11" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E116" s="11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F116" s="11" t="s">
-        <v>40</v>
+        <v>455</v>
       </c>
       <c r="G116" s="11">
-        <v>0</v>
+        <v>0.9842</v>
       </c>
       <c r="H116" s="12">
-        <v>6784130.44</v>
+        <v>20229149.79</v>
       </c>
       <c r="I116" s="13">
-        <v>0</v>
+        <v>19910398.37</v>
       </c>
       <c r="J116" s="12">
-        <v>6784130.44</v>
+        <v>318751.41999999806</v>
       </c>
       <c r="K116" s="14">
-        <v>45100</v>
+        <v>44697</v>
       </c>
       <c r="L116" s="14">
-        <v>45400</v>
+        <v>45783</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117" s="11" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>334</v>
+        <v>457</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E117" s="11" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="F117" s="11" t="s">
-        <v>157</v>
+        <v>40</v>
       </c>
       <c r="G117" s="11">
-        <v>0.6605</v>
+        <v>0</v>
       </c>
       <c r="H117" s="12">
-        <v>20185137.81</v>
+        <v>6784130.44</v>
       </c>
       <c r="I117" s="13">
-        <v>13332401.6</v>
+        <v>0</v>
       </c>
       <c r="J117" s="12">
-        <v>6852736.209999999</v>
+        <v>6784130.44</v>
       </c>
       <c r="K117" s="14">
-        <v>44754</v>
+        <v>45100</v>
       </c>
       <c r="L117" s="14">
-        <v>45566</v>
+        <v>45400</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118" s="11" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C118" s="11" t="s">
-        <v>457</v>
+        <v>339</v>
       </c>
       <c r="D118" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E118" s="11" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="F118" s="11" t="s">
-        <v>45</v>
+        <v>163</v>
       </c>
       <c r="G118" s="11">
-        <v>0.0165</v>
+        <v>0.6605</v>
       </c>
       <c r="H118" s="12">
-        <v>7430869.32</v>
+        <v>20185137.81</v>
       </c>
       <c r="I118" s="13">
-        <v>122778.19</v>
+        <v>13332401.6</v>
       </c>
       <c r="J118" s="12">
-        <v>7308091.13</v>
+        <v>6852736.209999999</v>
       </c>
       <c r="K118" s="14">
-        <v>45865</v>
+        <v>44754</v>
       </c>
       <c r="L118" s="14">
-        <v>46166</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119" s="11" t="s">
-        <v>459</v>
+        <v>444</v>
       </c>
       <c r="B119" s="11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C119" s="11" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D119" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E119" s="11" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F119" s="11" t="s">
-        <v>424</v>
+        <v>45</v>
       </c>
       <c r="G119" s="11">
-        <v>0.9903</v>
+        <v>0.0165</v>
       </c>
       <c r="H119" s="12">
-        <v>11046611.98</v>
+        <v>7430869.32</v>
       </c>
       <c r="I119" s="13">
-        <v>10939879.39</v>
+        <v>122778.19</v>
       </c>
       <c r="J119" s="12">
-        <v>106732.58999999985</v>
+        <v>7308091.13</v>
       </c>
       <c r="K119" s="14">
-        <v>44663</v>
+        <v>45865</v>
       </c>
       <c r="L119" s="14">
-        <v>45507</v>
+        <v>46166</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120" s="11" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="B120" s="11" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C120" s="11" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D120" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E120" s="11" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="F120" s="11" t="s">
-        <v>466</v>
+        <v>429</v>
       </c>
       <c r="G120" s="11">
-        <v>0.8079000000000001</v>
+        <v>0.9903</v>
       </c>
       <c r="H120" s="12">
-        <v>2755604.93</v>
+        <v>11046611.98</v>
       </c>
       <c r="I120" s="13">
-        <v>2226331.45</v>
+        <v>10939879.39</v>
       </c>
       <c r="J120" s="12">
-        <v>529273.48</v>
+        <v>106732.58999999985</v>
       </c>
       <c r="K120" s="14">
-        <v>45026</v>
+        <v>44663</v>
       </c>
       <c r="L120" s="14">
-        <v>46023</v>
+        <v>45507</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121" s="11" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="B121" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C121" s="11" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D121" s="11" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E121" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F121" s="11" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="G121" s="11">
-        <v>0</v>
+        <v>0.8079000000000001</v>
       </c>
       <c r="H121" s="12">
-        <v>1712576.84</v>
+        <v>2755604.93</v>
       </c>
       <c r="I121" s="13">
-        <v>0</v>
+        <v>2226331.45</v>
       </c>
       <c r="J121" s="12">
-        <v>1712576.84</v>
+        <v>529273.48</v>
       </c>
       <c r="K121" s="14">
-        <v>44823</v>
+        <v>45026</v>
       </c>
       <c r="L121" s="14">
-        <v>44706</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122" s="11" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="B122" s="11" t="s">
+        <v>472</v>
+      </c>
+      <c r="C122" s="11" t="s">
+        <v>473</v>
+      </c>
+      <c r="D122" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E122" s="11" t="s">
+        <v>474</v>
+      </c>
+      <c r="F122" s="11" t="s">
         <v>471</v>
       </c>
-      <c r="C122" s="11" t="s">
-        <v>472</v>
-      </c>
-      <c r="D122" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E122" s="11" t="s">
-        <v>473</v>
-      </c>
-      <c r="F122" s="11" t="s">
-        <v>474</v>
-      </c>
       <c r="G122" s="11">
-        <v>0.9998999999999999</v>
+        <v>0</v>
       </c>
       <c r="H122" s="12">
-        <v>1612154.63</v>
+        <v>1712576.84</v>
       </c>
       <c r="I122" s="13">
-        <v>1612024.85</v>
+        <v>0</v>
       </c>
       <c r="J122" s="12">
-        <v>129.7799999997951</v>
+        <v>1712576.84</v>
       </c>
       <c r="K122" s="14">
-        <v>45776</v>
+        <v>44823</v>
       </c>
       <c r="L122" s="14">
-        <v>45986</v>
+        <v>44706</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
@@ -7038,229 +7050,229 @@
         <v>476</v>
       </c>
       <c r="C123" s="11" t="s">
-        <v>151</v>
+        <v>477</v>
       </c>
       <c r="D123" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E123" s="11" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F123" s="11" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="G123" s="11">
-        <v>1</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="H123" s="12">
-        <v>6453162.72</v>
+        <v>1612154.63</v>
       </c>
       <c r="I123" s="13">
-        <v>6453162.72</v>
+        <v>1612024.85</v>
       </c>
       <c r="J123" s="12">
-        <v>0</v>
+        <v>129.7799999997951</v>
       </c>
       <c r="K123" s="14">
-        <v>44760</v>
+        <v>45776</v>
       </c>
       <c r="L123" s="14">
-        <v>45201</v>
+        <v>45986</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124" s="11" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B124" s="11" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C124" s="11" t="s">
-        <v>480</v>
+        <v>157</v>
       </c>
       <c r="D124" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E124" s="11" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F124" s="11" t="s">
-        <v>236</v>
+        <v>483</v>
       </c>
       <c r="G124" s="11">
-        <v>0.9993000000000001</v>
+        <v>1</v>
       </c>
       <c r="H124" s="12">
-        <v>1741703.69</v>
+        <v>6453162.72</v>
       </c>
       <c r="I124" s="13">
-        <v>1740561.74</v>
+        <v>6453162.72</v>
       </c>
       <c r="J124" s="12">
-        <v>1141.9499999999534</v>
+        <v>0</v>
       </c>
       <c r="K124" s="14">
-        <v>44683</v>
+        <v>44760</v>
       </c>
       <c r="L124" s="14">
-        <v>45889</v>
+        <v>45201</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" s="11" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B125" s="11" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C125" s="11" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D125" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E125" s="11" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="F125" s="11" t="s">
-        <v>485</v>
+        <v>241</v>
       </c>
       <c r="G125" s="11">
-        <v>0.997</v>
+        <v>0.9993000000000001</v>
       </c>
       <c r="H125" s="12">
-        <v>6014775.77</v>
+        <v>1741703.69</v>
       </c>
       <c r="I125" s="13">
-        <v>5996889.68</v>
+        <v>1740561.74</v>
       </c>
       <c r="J125" s="12">
-        <v>17886.08999999985</v>
+        <v>1141.9499999999534</v>
       </c>
       <c r="K125" s="14">
-        <v>44708</v>
+        <v>44683</v>
       </c>
       <c r="L125" s="14">
-        <v>45467</v>
+        <v>45889</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126" s="11" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B126" s="11" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C126" s="11" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D126" s="11" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E126" s="11" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F126" s="11" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="G126" s="11">
-        <v>0.9913</v>
+        <v>0.997</v>
       </c>
       <c r="H126" s="12">
-        <v>3569195.39</v>
+        <v>6014775.77</v>
       </c>
       <c r="I126" s="13">
-        <v>3538001.16</v>
+        <v>5996889.68</v>
       </c>
       <c r="J126" s="12">
-        <v>31194.22999999998</v>
+        <v>17886.08999999985</v>
       </c>
       <c r="K126" s="14">
-        <v>44658</v>
+        <v>44708</v>
       </c>
       <c r="L126" s="14">
-        <v>45426</v>
+        <v>45467</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127" s="11" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B127" s="11" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C127" s="11" t="s">
+        <v>492</v>
+      </c>
+      <c r="D127" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E127" s="11" t="s">
+        <v>493</v>
+      </c>
+      <c r="F127" s="11" t="s">
         <v>490</v>
       </c>
-      <c r="D127" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E127" s="11" t="s">
-        <v>491</v>
-      </c>
-      <c r="F127" s="11" t="s">
-        <v>236</v>
-      </c>
       <c r="G127" s="11">
-        <v>0.7993000000000001</v>
+        <v>0.9913</v>
       </c>
       <c r="H127" s="12">
-        <v>1528883.61</v>
+        <v>3569195.39</v>
       </c>
       <c r="I127" s="13">
-        <v>1222003.41</v>
+        <v>3538001.16</v>
       </c>
       <c r="J127" s="12">
-        <v>306880.2000000002</v>
+        <v>31194.22999999998</v>
       </c>
       <c r="K127" s="14">
-        <v>44655</v>
+        <v>44658</v>
       </c>
       <c r="L127" s="14">
-        <v>46164</v>
+        <v>45426</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" s="11" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B128" s="11" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C128" s="11" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D128" s="11" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E128" s="11" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="F128" s="11" t="s">
-        <v>495</v>
+        <v>241</v>
       </c>
       <c r="G128" s="11">
-        <v>0.0245</v>
+        <v>0.7993000000000001</v>
       </c>
       <c r="H128" s="12">
-        <v>2317778.22</v>
+        <v>1528883.61</v>
       </c>
       <c r="I128" s="13">
-        <v>56828.03</v>
+        <v>1222003.41</v>
       </c>
       <c r="J128" s="12">
-        <v>2260950.1900000004</v>
+        <v>306880.2000000002</v>
       </c>
       <c r="K128" s="14">
-        <v>45035</v>
+        <v>44655</v>
       </c>
       <c r="L128" s="14">
-        <v>45396</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129" s="11" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
       <c r="B129" s="11" t="s">
         <v>497</v>
@@ -7269,7 +7281,7 @@
         <v>498</v>
       </c>
       <c r="D129" s="11" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E129" s="11" t="s">
         <v>499</v>
@@ -7278,217 +7290,217 @@
         <v>500</v>
       </c>
       <c r="G129" s="11">
-        <v>1</v>
+        <v>0.0245</v>
       </c>
       <c r="H129" s="12">
-        <v>6478069.43</v>
+        <v>2317778.22</v>
       </c>
       <c r="I129" s="13">
-        <v>6478029.44</v>
+        <v>56828.03</v>
       </c>
       <c r="J129" s="12">
-        <v>39.989999999292195</v>
+        <v>2260950.1900000004</v>
       </c>
       <c r="K129" s="14">
-        <v>44827</v>
+        <v>45035</v>
       </c>
       <c r="L129" s="14">
-        <v>45690</v>
+        <v>45396</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130" s="11" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="B130" s="11" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C130" s="11" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D130" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E130" s="11" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F130" s="11" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="G130" s="11">
-        <v>0.7809</v>
+        <v>1</v>
       </c>
       <c r="H130" s="12">
-        <v>544550.48</v>
+        <v>6478069.43</v>
       </c>
       <c r="I130" s="13">
-        <v>425261.4</v>
+        <v>6478029.44</v>
       </c>
       <c r="J130" s="12">
-        <v>119289.07999999996</v>
+        <v>39.989999999292195</v>
       </c>
       <c r="K130" s="14">
-        <v>45925</v>
+        <v>44827</v>
       </c>
       <c r="L130" s="14">
-        <v>46165</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131" s="11" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="B131" s="11" t="s">
         <v>506</v>
       </c>
       <c r="C131" s="11" t="s">
-        <v>178</v>
+        <v>507</v>
       </c>
       <c r="D131" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E131" s="11" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F131" s="11" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="G131" s="11">
-        <v>1</v>
+        <v>0.7809</v>
       </c>
       <c r="H131" s="12">
-        <v>2389346</v>
+        <v>544550.48</v>
       </c>
       <c r="I131" s="13">
-        <v>2389346</v>
+        <v>425261.4</v>
       </c>
       <c r="J131" s="12">
-        <v>0</v>
+        <v>119289.07999999996</v>
       </c>
       <c r="K131" s="14">
-        <v>44693</v>
+        <v>45925</v>
       </c>
       <c r="L131" s="14">
-        <v>45456</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B132" s="11" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C132" s="11" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D132" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E132" s="11" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="F132" s="11" t="s">
-        <v>340</v>
+        <v>98</v>
       </c>
       <c r="G132" s="11">
         <v>1</v>
       </c>
       <c r="H132" s="12">
-        <v>6743574.04</v>
+        <v>2389346</v>
       </c>
       <c r="I132" s="13">
-        <v>6743573.85</v>
+        <v>2389346</v>
       </c>
       <c r="J132" s="12">
-        <v>0.19000000040978193</v>
+        <v>0</v>
       </c>
       <c r="K132" s="14">
         <v>44693</v>
       </c>
       <c r="L132" s="14">
-        <v>45152</v>
+        <v>45456</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B133" s="11" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C133" s="11" t="s">
-        <v>313</v>
+        <v>194</v>
       </c>
       <c r="D133" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E133" s="11" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="F133" s="11" t="s">
-        <v>365</v>
+        <v>345</v>
       </c>
       <c r="G133" s="11">
-        <v>0.9562999999999999</v>
+        <v>1</v>
       </c>
       <c r="H133" s="12">
-        <v>1052239.53</v>
+        <v>6743574.04</v>
       </c>
       <c r="I133" s="13">
-        <v>1006235.15</v>
+        <v>6743573.85</v>
       </c>
       <c r="J133" s="12">
-        <v>46004.380000000005</v>
+        <v>0.19000000040978193</v>
       </c>
       <c r="K133" s="14">
-        <v>44613</v>
+        <v>44693</v>
       </c>
       <c r="L133" s="14">
-        <v>45183</v>
+        <v>45152</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B134" s="11" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C134" s="11" t="s">
-        <v>514</v>
+        <v>318</v>
       </c>
       <c r="D134" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E134" s="11" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F134" s="11" t="s">
-        <v>516</v>
+        <v>370</v>
       </c>
       <c r="G134" s="11">
-        <v>0.6409999999999999</v>
+        <v>0.9562999999999999</v>
       </c>
       <c r="H134" s="12">
-        <v>256613.37</v>
+        <v>1052239.53</v>
       </c>
       <c r="I134" s="13">
-        <v>164482.69</v>
+        <v>1006235.15</v>
       </c>
       <c r="J134" s="12">
-        <v>92130.68</v>
+        <v>46004.380000000005</v>
       </c>
       <c r="K134" s="14">
-        <v>45915</v>
+        <v>44613</v>
       </c>
       <c r="L134" s="14">
-        <v>46005</v>
+        <v>45183</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B135" s="11" t="s">
         <v>517</v>
@@ -7506,74 +7518,74 @@
         <v>520</v>
       </c>
       <c r="G135" s="11">
-        <v>0.9508</v>
+        <v>0.6409999999999999</v>
       </c>
       <c r="H135" s="12">
-        <v>13554947.83</v>
+        <v>256613.37</v>
       </c>
       <c r="I135" s="13">
-        <v>12888506.56</v>
+        <v>164482.69</v>
       </c>
       <c r="J135" s="12">
-        <v>666441.2699999996</v>
+        <v>92130.68</v>
       </c>
       <c r="K135" s="14">
-        <v>44537</v>
+        <v>45915</v>
       </c>
       <c r="L135" s="14">
-        <v>46075</v>
+        <v>46005</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B136" s="11" t="s">
         <v>521</v>
       </c>
       <c r="C136" s="11" t="s">
-        <v>448</v>
+        <v>522</v>
       </c>
       <c r="D136" s="11" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E136" s="11" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F136" s="11" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="G136" s="11">
-        <v>0</v>
+        <v>0.9508</v>
       </c>
       <c r="H136" s="12">
-        <v>1305890.95</v>
+        <v>13554947.83</v>
       </c>
       <c r="I136" s="13">
-        <v>0</v>
+        <v>12888506.56</v>
       </c>
       <c r="J136" s="12">
-        <v>1305890.95</v>
+        <v>666441.2699999996</v>
       </c>
       <c r="K136" s="14">
-        <v>44610</v>
+        <v>44537</v>
       </c>
       <c r="L136" s="14">
-        <v>45567</v>
+        <v>46075</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B137" s="11" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C137" s="11" t="s">
-        <v>525</v>
+        <v>453</v>
       </c>
       <c r="D137" s="11" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E137" s="11" t="s">
         <v>526</v>
@@ -7582,27 +7594,27 @@
         <v>527</v>
       </c>
       <c r="G137" s="11">
-        <v>0.9765999999999999</v>
+        <v>0</v>
       </c>
       <c r="H137" s="12">
-        <v>56185153.92</v>
+        <v>1305890.95</v>
       </c>
       <c r="I137" s="13">
-        <v>54872063.4</v>
+        <v>0</v>
       </c>
       <c r="J137" s="12">
-        <v>1313090.5200000033</v>
+        <v>1305890.95</v>
       </c>
       <c r="K137" s="14">
-        <v>44872</v>
+        <v>44610</v>
       </c>
       <c r="L137" s="14">
-        <v>45475</v>
+        <v>45567</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B138" s="11" t="s">
         <v>528</v>
@@ -7611,7 +7623,7 @@
         <v>529</v>
       </c>
       <c r="D138" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E138" s="11" t="s">
         <v>530</v>
@@ -7620,27 +7632,27 @@
         <v>531</v>
       </c>
       <c r="G138" s="11">
-        <v>0.8513</v>
+        <v>0.9765999999999999</v>
       </c>
       <c r="H138" s="12">
-        <v>12100122.6</v>
+        <v>56185153.92</v>
       </c>
       <c r="I138" s="13">
-        <v>10301084.52</v>
+        <v>54872063.4</v>
       </c>
       <c r="J138" s="12">
-        <v>1799038.08</v>
+        <v>1313090.5200000033</v>
       </c>
       <c r="K138" s="14">
-        <v>45758</v>
+        <v>44872</v>
       </c>
       <c r="L138" s="14">
-        <v>46123</v>
+        <v>45475</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B139" s="11" t="s">
         <v>532</v>
@@ -7655,191 +7667,191 @@
         <v>534</v>
       </c>
       <c r="F139" s="11" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="G139" s="11">
-        <v>0.8454999999999999</v>
+        <v>0.8513</v>
       </c>
       <c r="H139" s="12">
-        <v>12432476.25</v>
+        <v>12100122.6</v>
       </c>
       <c r="I139" s="13">
-        <v>10511270.47</v>
+        <v>10301084.52</v>
       </c>
       <c r="J139" s="12">
-        <v>1921205.7799999993</v>
+        <v>1799038.08</v>
       </c>
       <c r="K139" s="14">
-        <v>45894</v>
+        <v>45758</v>
       </c>
       <c r="L139" s="14">
-        <v>46112</v>
+        <v>46123</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B140" s="11" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C140" s="11" t="s">
-        <v>434</v>
+        <v>537</v>
       </c>
       <c r="D140" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E140" s="11" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="F140" s="11" t="s">
-        <v>148</v>
+        <v>98</v>
       </c>
       <c r="G140" s="11">
-        <v>0.8916</v>
+        <v>0.8454999999999999</v>
       </c>
       <c r="H140" s="12">
-        <v>24590858.27</v>
+        <v>12432476.25</v>
       </c>
       <c r="I140" s="13">
-        <v>21925638.52</v>
+        <v>10511270.47</v>
       </c>
       <c r="J140" s="12">
-        <v>2665219.75</v>
+        <v>1921205.7799999993</v>
       </c>
       <c r="K140" s="14">
-        <v>44638</v>
+        <v>45894</v>
       </c>
       <c r="L140" s="14">
-        <v>45936</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B141" s="11" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C141" s="11" t="s">
-        <v>141</v>
+        <v>439</v>
       </c>
       <c r="D141" s="11" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E141" s="11" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="F141" s="11" t="s">
-        <v>336</v>
+        <v>154</v>
       </c>
       <c r="G141" s="11">
-        <v>0.0707</v>
+        <v>0.8916</v>
       </c>
       <c r="H141" s="12">
-        <v>3615856.15</v>
+        <v>24590858.27</v>
       </c>
       <c r="I141" s="13">
-        <v>255684.47</v>
+        <v>21925638.52</v>
       </c>
       <c r="J141" s="12">
-        <v>3360171.6799999997</v>
+        <v>2665219.75</v>
       </c>
       <c r="K141" s="14">
-        <v>44791</v>
+        <v>44638</v>
       </c>
       <c r="L141" s="14">
-        <v>45259</v>
+        <v>45936</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B142" s="11" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C142" s="11" t="s">
-        <v>540</v>
+        <v>147</v>
       </c>
       <c r="D142" s="11" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E142" s="11" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F142" s="11" t="s">
-        <v>508</v>
+        <v>341</v>
       </c>
       <c r="G142" s="11">
-        <v>0.1637</v>
+        <v>0.0707</v>
       </c>
       <c r="H142" s="12">
-        <v>7848019.53</v>
+        <v>3615856.15</v>
       </c>
       <c r="I142" s="13">
-        <v>1284711.9</v>
+        <v>255684.47</v>
       </c>
       <c r="J142" s="12">
-        <v>6563307.630000001</v>
+        <v>3360171.6799999997</v>
       </c>
       <c r="K142" s="14">
-        <v>45986</v>
+        <v>44791</v>
       </c>
       <c r="L142" s="14">
-        <v>46351</v>
+        <v>45259</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B143" s="11" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C143" s="11" t="s">
-        <v>99</v>
+        <v>544</v>
       </c>
       <c r="D143" s="11" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E143" s="11" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="F143" s="11" t="s">
-        <v>544</v>
+        <v>98</v>
       </c>
       <c r="G143" s="11">
-        <v>0.5364</v>
+        <v>0.1637</v>
       </c>
       <c r="H143" s="12">
-        <v>16932981.45</v>
+        <v>7848019.53</v>
       </c>
       <c r="I143" s="13">
-        <v>9082408.67</v>
+        <v>1284711.9</v>
       </c>
       <c r="J143" s="12">
-        <v>7850572.779999999</v>
+        <v>6563307.630000001</v>
       </c>
       <c r="K143" s="14">
-        <v>44791</v>
+        <v>45986</v>
       </c>
       <c r="L143" s="14">
-        <v>45393</v>
+        <v>46351</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B144" s="11" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C144" s="11" t="s">
-        <v>546</v>
+        <v>105</v>
       </c>
       <c r="D144" s="11" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E144" s="11" t="s">
         <v>547</v>
@@ -7848,27 +7860,27 @@
         <v>548</v>
       </c>
       <c r="G144" s="11">
-        <v>0.6043</v>
+        <v>0.5364</v>
       </c>
       <c r="H144" s="12">
-        <v>24187461.93</v>
+        <v>16932981.45</v>
       </c>
       <c r="I144" s="13">
-        <v>14615806.69</v>
+        <v>9082408.67</v>
       </c>
       <c r="J144" s="12">
-        <v>9571655.24</v>
+        <v>7850572.779999999</v>
       </c>
       <c r="K144" s="14">
-        <v>45723</v>
+        <v>44791</v>
       </c>
       <c r="L144" s="14">
-        <v>46203</v>
+        <v>45393</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B145" s="11" t="s">
         <v>549</v>
@@ -7886,27 +7898,27 @@
         <v>552</v>
       </c>
       <c r="G145" s="11">
-        <v>0.8504</v>
+        <v>0.6043</v>
       </c>
       <c r="H145" s="12">
-        <v>74609626.42</v>
+        <v>24187461.93</v>
       </c>
       <c r="I145" s="13">
-        <v>63449041.49</v>
+        <v>14615806.69</v>
       </c>
       <c r="J145" s="12">
-        <v>11160584.93</v>
+        <v>9571655.24</v>
       </c>
       <c r="K145" s="14">
-        <v>45555</v>
+        <v>45723</v>
       </c>
       <c r="L145" s="14">
-        <v>46112</v>
+        <v>46203</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A146" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B146" s="11" t="s">
         <v>553</v>
@@ -7921,106 +7933,106 @@
         <v>555</v>
       </c>
       <c r="F146" s="11" t="s">
-        <v>520</v>
+        <v>556</v>
       </c>
       <c r="G146" s="11">
-        <v>0.15</v>
+        <v>0.8504</v>
       </c>
       <c r="H146" s="12">
-        <v>15203482.79</v>
+        <v>74609626.42</v>
       </c>
       <c r="I146" s="13">
-        <v>2279930.05</v>
+        <v>63449041.49</v>
       </c>
       <c r="J146" s="12">
-        <v>12923552.739999998</v>
+        <v>11160584.93</v>
       </c>
       <c r="K146" s="14">
-        <v>44757</v>
+        <v>45555</v>
       </c>
       <c r="L146" s="14">
-        <v>46287</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B147" s="11" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C147" s="11" t="s">
-        <v>490</v>
+        <v>558</v>
       </c>
       <c r="D147" s="11" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E147" s="11" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="F147" s="11" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="G147" s="11">
-        <v>0.0216</v>
+        <v>0.15</v>
       </c>
       <c r="H147" s="12">
-        <v>13677862.32</v>
+        <v>15203482.79</v>
       </c>
       <c r="I147" s="13">
-        <v>296101.87</v>
+        <v>2279930.05</v>
       </c>
       <c r="J147" s="12">
-        <v>13381760.450000001</v>
+        <v>12923552.739999998</v>
       </c>
       <c r="K147" s="14">
-        <v>44581</v>
+        <v>44757</v>
       </c>
       <c r="L147" s="14">
-        <v>45561</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A148" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B148" s="11" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C148" s="11" t="s">
-        <v>559</v>
+        <v>495</v>
       </c>
       <c r="D148" s="11" t="s">
         <v>20</v>
       </c>
       <c r="E148" s="11" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F148" s="11" t="s">
-        <v>561</v>
+        <v>524</v>
       </c>
       <c r="G148" s="11">
-        <v>0</v>
+        <v>0.0216</v>
       </c>
       <c r="H148" s="12">
-        <v>14144248.92</v>
+        <v>13677862.32</v>
       </c>
       <c r="I148" s="13">
-        <v>0</v>
+        <v>296101.87</v>
       </c>
       <c r="J148" s="12">
-        <v>14144248.92</v>
+        <v>13381760.450000001</v>
       </c>
       <c r="K148" s="14">
-        <v>41443</v>
+        <v>44581</v>
       </c>
       <c r="L148" s="14">
-        <v>44012</v>
+        <v>45561</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B149" s="11" t="s">
         <v>562</v>
@@ -8035,68 +8047,68 @@
         <v>564</v>
       </c>
       <c r="F149" s="11" t="s">
-        <v>336</v>
+        <v>565</v>
       </c>
       <c r="G149" s="11">
-        <v>0.3475</v>
+        <v>0</v>
       </c>
       <c r="H149" s="12">
-        <v>24165422.12</v>
+        <v>14144248.92</v>
       </c>
       <c r="I149" s="13">
-        <v>8398407.23</v>
+        <v>0</v>
       </c>
       <c r="J149" s="12">
-        <v>15767014.89</v>
+        <v>14144248.92</v>
       </c>
       <c r="K149" s="14">
-        <v>44538</v>
+        <v>41443</v>
       </c>
       <c r="L149" s="14">
-        <v>45426</v>
+        <v>44012</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B150" s="11" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C150" s="11" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D150" s="11" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E150" s="11" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F150" s="11" t="s">
-        <v>568</v>
+        <v>341</v>
       </c>
       <c r="G150" s="11">
-        <v>0.5169</v>
+        <v>0.3475</v>
       </c>
       <c r="H150" s="12">
-        <v>104939756.55</v>
+        <v>24165422.12</v>
       </c>
       <c r="I150" s="13">
-        <v>54247297.54</v>
+        <v>8398407.23</v>
       </c>
       <c r="J150" s="12">
-        <v>50692459.01</v>
+        <v>15767014.89</v>
       </c>
       <c r="K150" s="14">
-        <v>45624</v>
+        <v>44538</v>
       </c>
       <c r="L150" s="14">
-        <v>46074</v>
+        <v>45426</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B151" s="11" t="s">
         <v>569</v>
@@ -8111,30 +8123,30 @@
         <v>571</v>
       </c>
       <c r="F151" s="11" t="s">
-        <v>336</v>
+        <v>572</v>
       </c>
       <c r="G151" s="11">
-        <v>0.18899999999999997</v>
+        <v>0.5169</v>
       </c>
       <c r="H151" s="12">
-        <v>116500000</v>
+        <v>104939756.55</v>
       </c>
       <c r="I151" s="13">
-        <v>22022321.06</v>
+        <v>54247297.54</v>
       </c>
       <c r="J151" s="12">
-        <v>94477678.94</v>
+        <v>50692459.01</v>
       </c>
       <c r="K151" s="14">
-        <v>45897</v>
+        <v>45624</v>
       </c>
       <c r="L151" s="14">
-        <v>46107</v>
+        <v>46074</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152" s="11" t="s">
-        <v>572</v>
+        <v>510</v>
       </c>
       <c r="B152" s="11" t="s">
         <v>573</v>
@@ -8143,145 +8155,145 @@
         <v>574</v>
       </c>
       <c r="D152" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E152" s="11" t="s">
         <v>575</v>
       </c>
       <c r="F152" s="11" t="s">
-        <v>576</v>
+        <v>341</v>
       </c>
       <c r="G152" s="11">
-        <v>1</v>
+        <v>0.18899999999999997</v>
       </c>
       <c r="H152" s="12">
-        <v>10061005.41</v>
+        <v>116500000</v>
       </c>
       <c r="I152" s="13">
-        <v>10061005.39</v>
+        <v>22022321.06</v>
       </c>
       <c r="J152" s="12">
-        <v>0.019999999552965164</v>
+        <v>94477678.94</v>
       </c>
       <c r="K152" s="14">
-        <v>45261</v>
+        <v>45897</v>
       </c>
       <c r="L152" s="14">
-        <v>45833</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153" s="11" t="s">
+        <v>576</v>
+      </c>
+      <c r="B153" s="11" t="s">
         <v>577</v>
       </c>
-      <c r="B153" s="11" t="s">
+      <c r="C153" s="11" t="s">
         <v>578</v>
       </c>
-      <c r="C153" s="11" t="s">
+      <c r="D153" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E153" s="11" t="s">
         <v>579</v>
       </c>
-      <c r="D153" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E153" s="11" t="s">
+      <c r="F153" s="11" t="s">
         <v>580</v>
-      </c>
-      <c r="F153" s="11" t="s">
-        <v>45</v>
       </c>
       <c r="G153" s="11">
         <v>1</v>
       </c>
       <c r="H153" s="12">
-        <v>81950979.23</v>
+        <v>10061005.41</v>
       </c>
       <c r="I153" s="13">
-        <v>81950979</v>
+        <v>10061005.39</v>
       </c>
       <c r="J153" s="12">
-        <v>0.23000000417232513</v>
+        <v>0.019999999552965164</v>
       </c>
       <c r="K153" s="14">
-        <v>44792</v>
+        <v>45261</v>
       </c>
       <c r="L153" s="14">
-        <v>46022</v>
+        <v>45833</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154" s="11" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="B154" s="11" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C154" s="11" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D154" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E154" s="11" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="F154" s="11" t="s">
-        <v>584</v>
+        <v>45</v>
       </c>
       <c r="G154" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H154" s="12">
-        <v>41522873.42</v>
+        <v>81950979.23</v>
       </c>
       <c r="I154" s="13">
-        <v>0</v>
+        <v>81950979</v>
       </c>
       <c r="J154" s="12">
-        <v>41522873.42</v>
+        <v>0.23000000417232513</v>
       </c>
       <c r="K154" s="14">
-        <v>45901</v>
+        <v>44792</v>
       </c>
       <c r="L154" s="14">
-        <v>46801</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A155" s="11" t="s">
+        <v>581</v>
+      </c>
+      <c r="B155" s="11" t="s">
         <v>585</v>
       </c>
-      <c r="B155" s="11" t="s">
+      <c r="C155" s="11" t="s">
         <v>586</v>
       </c>
-      <c r="C155" s="11" t="s">
+      <c r="D155" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E155" s="11" t="s">
         <v>587</v>
       </c>
-      <c r="D155" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E155" s="11" t="s">
+      <c r="F155" s="11" t="s">
         <v>588</v>
       </c>
-      <c r="F155" s="11" t="s">
-        <v>318</v>
-      </c>
       <c r="G155" s="11">
-        <v>0.9728</v>
+        <v>0</v>
       </c>
       <c r="H155" s="12">
-        <v>4444784.22</v>
+        <v>41522873.42</v>
       </c>
       <c r="I155" s="13">
-        <v>4324004.81</v>
+        <v>0</v>
       </c>
       <c r="J155" s="12">
-        <v>120779.41000000015</v>
+        <v>41522873.42</v>
       </c>
       <c r="K155" s="14">
-        <v>45155</v>
+        <v>45901</v>
       </c>
       <c r="L155" s="14">
-        <v>45576</v>
+        <v>46801</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
@@ -8295,31 +8307,31 @@
         <v>591</v>
       </c>
       <c r="D156" s="11" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E156" s="11" t="s">
         <v>592</v>
       </c>
       <c r="F156" s="11" t="s">
-        <v>105</v>
+        <v>323</v>
       </c>
       <c r="G156" s="11">
-        <v>0</v>
+        <v>0.9728</v>
       </c>
       <c r="H156" s="12">
-        <v>8995898.05</v>
+        <v>4444784.22</v>
       </c>
       <c r="I156" s="13">
-        <v>266299.23</v>
+        <v>4324004.81</v>
       </c>
       <c r="J156" s="12">
-        <v>8729598.82</v>
+        <v>120779.41000000015</v>
       </c>
       <c r="K156" s="14">
-        <v>44816</v>
+        <v>45155</v>
       </c>
       <c r="L156" s="14">
-        <v>44996</v>
+        <v>45576</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
@@ -8333,31 +8345,31 @@
         <v>595</v>
       </c>
       <c r="D157" s="11" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E157" s="11" t="s">
         <v>596</v>
       </c>
       <c r="F157" s="11" t="s">
-        <v>576</v>
+        <v>111</v>
       </c>
       <c r="G157" s="11">
-        <v>0.3153</v>
+        <v>0</v>
       </c>
       <c r="H157" s="12">
-        <v>3294597.99</v>
+        <v>8995898.05</v>
       </c>
       <c r="I157" s="13">
-        <v>1038880.21</v>
+        <v>266299.23</v>
       </c>
       <c r="J157" s="12">
-        <v>2255717.7800000003</v>
+        <v>8729598.82</v>
       </c>
       <c r="K157" s="14">
-        <v>45278</v>
+        <v>44816</v>
       </c>
       <c r="L157" s="14">
-        <v>46122</v>
+        <v>44996</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
@@ -8377,226 +8389,226 @@
         <v>600</v>
       </c>
       <c r="F158" s="11" t="s">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="G158" s="11">
-        <v>0.9922</v>
+        <v>0.3153</v>
       </c>
       <c r="H158" s="12">
-        <v>6055289.34</v>
+        <v>3294597.99</v>
       </c>
       <c r="I158" s="13">
-        <v>6007931.02</v>
+        <v>1038880.21</v>
       </c>
       <c r="J158" s="12">
-        <v>47358.3200000003</v>
+        <v>2255717.7800000003</v>
       </c>
       <c r="K158" s="14">
-        <v>44715</v>
+        <v>45278</v>
       </c>
       <c r="L158" s="14">
-        <v>45075</v>
+        <v>46122</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A159" s="11" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="B159" s="11" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C159" s="11" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D159" s="11" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E159" s="11" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F159" s="11" t="s">
-        <v>45</v>
+        <v>505</v>
       </c>
       <c r="G159" s="11">
-        <v>0.22760000000000002</v>
+        <v>0.9922</v>
       </c>
       <c r="H159" s="12">
-        <v>8973983.87</v>
+        <v>6055289.34</v>
       </c>
       <c r="I159" s="13">
-        <v>2042159.29</v>
+        <v>6007931.02</v>
       </c>
       <c r="J159" s="12">
-        <v>6931824.579999999</v>
+        <v>47358.3200000003</v>
       </c>
       <c r="K159" s="14">
-        <v>44707</v>
+        <v>44715</v>
       </c>
       <c r="L159" s="14">
-        <v>45280</v>
+        <v>45075</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160" s="11" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="B160" s="11" t="s">
         <v>605</v>
       </c>
       <c r="C160" s="11" t="s">
-        <v>244</v>
+        <v>606</v>
       </c>
       <c r="D160" s="11" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E160" s="11" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F160" s="11" t="s">
-        <v>143</v>
+        <v>45</v>
       </c>
       <c r="G160" s="11">
-        <v>1</v>
+        <v>0.22760000000000002</v>
       </c>
       <c r="H160" s="12">
-        <v>13792679.79</v>
+        <v>8973983.87</v>
       </c>
       <c r="I160" s="13">
-        <v>13792679.79</v>
+        <v>2042159.29</v>
       </c>
       <c r="J160" s="12">
-        <v>0</v>
+        <v>6931824.579999999</v>
       </c>
       <c r="K160" s="14">
-        <v>44767</v>
+        <v>44707</v>
       </c>
       <c r="L160" s="14">
-        <v>45411</v>
+        <v>45280</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161" s="11" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="B161" s="11" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C161" s="11" t="s">
-        <v>130</v>
+        <v>249</v>
       </c>
       <c r="D161" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E161" s="11" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="F161" s="11" t="s">
-        <v>57</v>
+        <v>149</v>
       </c>
       <c r="G161" s="11">
-        <v>0.9122</v>
+        <v>1</v>
       </c>
       <c r="H161" s="12">
-        <v>22472818</v>
+        <v>13792679.79</v>
       </c>
       <c r="I161" s="13">
-        <v>20500685.68</v>
+        <v>13792679.79</v>
       </c>
       <c r="J161" s="12">
-        <v>1972132.3200000003</v>
+        <v>0</v>
       </c>
       <c r="K161" s="14">
-        <v>44827</v>
+        <v>44767</v>
       </c>
       <c r="L161" s="14">
-        <v>45460</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162" s="11" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="B162" s="11" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C162" s="11" t="s">
-        <v>610</v>
+        <v>136</v>
       </c>
       <c r="D162" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E162" s="11" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F162" s="11" t="s">
-        <v>612</v>
+        <v>57</v>
       </c>
       <c r="G162" s="11">
-        <v>0.8996</v>
+        <v>0.9122</v>
       </c>
       <c r="H162" s="12">
-        <v>51414775.09</v>
+        <v>22472818</v>
       </c>
       <c r="I162" s="13">
-        <v>46254135.59</v>
+        <v>20500685.68</v>
       </c>
       <c r="J162" s="12">
-        <v>5160639.5</v>
+        <v>1972132.3200000003</v>
       </c>
       <c r="K162" s="14">
-        <v>45566</v>
+        <v>44827</v>
       </c>
       <c r="L162" s="14">
-        <v>46106</v>
+        <v>45460</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163" s="11" t="s">
+        <v>608</v>
+      </c>
+      <c r="B163" s="11" t="s">
         <v>613</v>
       </c>
-      <c r="B163" s="11" t="s">
+      <c r="C163" s="11" t="s">
         <v>614</v>
-      </c>
-      <c r="C163" s="11" t="s">
-        <v>615</v>
       </c>
       <c r="D163" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E163" s="11" t="s">
+        <v>615</v>
+      </c>
+      <c r="F163" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="F163" s="11" t="s">
-        <v>617</v>
-      </c>
       <c r="G163" s="11">
-        <v>0</v>
+        <v>0.8996</v>
       </c>
       <c r="H163" s="12">
-        <v>1302281.25</v>
+        <v>51414775.09</v>
       </c>
       <c r="I163" s="13">
-        <v>0</v>
+        <v>46254135.59</v>
       </c>
       <c r="J163" s="12">
-        <v>1302281.25</v>
+        <v>5160639.5</v>
       </c>
       <c r="K163" s="14">
-        <v>46080</v>
+        <v>45566</v>
       </c>
       <c r="L163" s="14">
-        <v>46440</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164" s="11" t="s">
+        <v>617</v>
+      </c>
+      <c r="B164" s="11" t="s">
         <v>618</v>
       </c>
-      <c r="B164" s="11" t="s">
+      <c r="C164" s="11" t="s">
         <v>619</v>
-      </c>
-      <c r="C164" s="11" t="s">
-        <v>155</v>
       </c>
       <c r="D164" s="11" t="s">
         <v>34</v>
@@ -8608,173 +8620,211 @@
         <v>621</v>
       </c>
       <c r="G164" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H164" s="12">
-        <v>18264452.89</v>
+        <v>1302281.25</v>
       </c>
       <c r="I164" s="13">
-        <v>18264452.89</v>
+        <v>0</v>
       </c>
       <c r="J164" s="12">
-        <v>0</v>
+        <v>1302281.25</v>
       </c>
       <c r="K164" s="14">
-        <v>44722</v>
+        <v>46080</v>
       </c>
       <c r="L164" s="14">
-        <v>45723</v>
+        <v>46440</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165" s="11" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="B165" s="11" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C165" s="11" t="s">
-        <v>623</v>
+        <v>161</v>
       </c>
       <c r="D165" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E165" s="11" t="s">
         <v>624</v>
       </c>
       <c r="F165" s="11" t="s">
-        <v>40</v>
+        <v>625</v>
       </c>
       <c r="G165" s="11">
-        <v>0.9953</v>
+        <v>1</v>
       </c>
       <c r="H165" s="12">
-        <v>30599999.01</v>
+        <v>18264452.89</v>
       </c>
       <c r="I165" s="13">
-        <v>30456294.33</v>
+        <v>18264452.89</v>
       </c>
       <c r="J165" s="12">
-        <v>143704.68000000343</v>
+        <v>0</v>
       </c>
       <c r="K165" s="14">
-        <v>45019</v>
+        <v>44722</v>
       </c>
       <c r="L165" s="14">
-        <v>45743</v>
+        <v>45723</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166" s="11" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="B166" s="11" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C166" s="11" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D166" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E166" s="11" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F166" s="11" t="s">
-        <v>216</v>
+        <v>40</v>
       </c>
       <c r="G166" s="11">
-        <v>0.9601000000000001</v>
+        <v>0.9953</v>
       </c>
       <c r="H166" s="12">
-        <v>43796954.98</v>
+        <v>30599999.01</v>
       </c>
       <c r="I166" s="13">
-        <v>42048979.52</v>
+        <v>30456294.33</v>
       </c>
       <c r="J166" s="12">
-        <v>1747975.4599999934</v>
+        <v>143704.68000000343</v>
       </c>
       <c r="K166" s="14">
-        <v>44641</v>
+        <v>45019</v>
       </c>
       <c r="L166" s="14">
-        <v>46091</v>
+        <v>45743</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A167" s="11" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="B167" s="11" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C167" s="11" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D167" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E167" s="11" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="F167" s="11" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="G167" s="11">
-        <v>0.7956</v>
+        <v>0.9601000000000001</v>
       </c>
       <c r="H167" s="12">
-        <v>45726170.25</v>
+        <v>43796954.98</v>
       </c>
       <c r="I167" s="13">
-        <v>36377601.26</v>
+        <v>42048979.52</v>
       </c>
       <c r="J167" s="12">
-        <v>9348568.990000002</v>
+        <v>1747975.4599999934</v>
       </c>
       <c r="K167" s="14">
-        <v>44623</v>
+        <v>44641</v>
       </c>
       <c r="L167" s="14">
-        <v>46222</v>
+        <v>46091</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A168" s="11" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="B168" s="11" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C168" s="11" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D168" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E168" s="11" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F168" s="11" t="s">
-        <v>105</v>
+        <v>222</v>
       </c>
       <c r="G168" s="11">
-        <v>0.30670000000000003</v>
+        <v>0.7956</v>
       </c>
       <c r="H168" s="12">
-        <v>65678550.13</v>
+        <v>45726170.25</v>
       </c>
       <c r="I168" s="13">
-        <v>20145177.51</v>
+        <v>36377601.26</v>
       </c>
       <c r="J168" s="12">
-        <v>45533372.620000005</v>
+        <v>9348568.990000002</v>
       </c>
       <c r="K168" s="14">
         <v>44623</v>
       </c>
       <c r="L168" s="14">
+        <v>46222</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A169" s="11" t="s">
+        <v>622</v>
+      </c>
+      <c r="B169" s="11" t="s">
+        <v>635</v>
+      </c>
+      <c r="C169" s="11" t="s">
+        <v>636</v>
+      </c>
+      <c r="D169" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E169" s="11" t="s">
+        <v>637</v>
+      </c>
+      <c r="F169" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="G169" s="11">
+        <v>0.30670000000000003</v>
+      </c>
+      <c r="H169" s="12">
+        <v>65678550.13</v>
+      </c>
+      <c r="I169" s="13">
+        <v>20145177.51</v>
+      </c>
+      <c r="J169" s="12">
+        <v>45533372.620000005</v>
+      </c>
+      <c r="K169" s="14">
+        <v>44623</v>
+      </c>
+      <c r="L169" s="14">
         <v>46170</v>
       </c>
     </row>

--- a/ANALITICA.xlsx
+++ b/ANALITICA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="638">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="641">
   <si>
     <t>Municipio</t>
   </si>
@@ -1740,6 +1740,15 @@
   </si>
   <si>
     <t>RECUPERAÇÃO DE EQUIPAMENTOS DO TELEFÉRICO DO ALEMÃO - RJ</t>
+  </si>
+  <si>
+    <t>330001/001152/2025</t>
+  </si>
+  <si>
+    <t>CONTRATAÇÃO DE UMA EMPRESA ESPECIALIZADA NA EXECUÇÃO DE SERVIÇOS DE ESTABILIZAÇÃO DE SOLOS COM ESTABILIZADOR IÔNICO LÍQUIDO, COM PROPRIEDADES DE AUMENTO DA RESISTÊNCIA DO SOLO E RESISTÊNCIA À ÁGUA, 100% AMBIENTALMENTE SUSTENTÁVEL, MONOCOMPONENTE, APLICADO IN SITU, COM O FORNECIMENTO DE TODOS OS EQUIPAMENTOS, MAQUINÁRIO, MÃO DE OBRA E TODOS OS MATERIAIS NECESSÁRIOS PARA CADA TIPO DE SERVIÇO, CONFORME AS CONDIÇÕES E EXIGÊNCIAS ESTABELECIDAS.</t>
+  </si>
+  <si>
+    <t>Não existe na tabela Contratadas</t>
   </si>
   <si>
     <t>São Francisco de Itabapoana</t>
@@ -1936,7 +1945,7 @@
     <numFmt numFmtId="164" formatCode="R$#,##0.00;-R$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="DD-MM-YYYY"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1946,7 +1955,11 @@
     </font>
     <font>
       <color rgb="FF404040"/>
-      <sz val="13"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <color rgb="FF404040"/>
+      <sz val="15"/>
     </font>
   </fonts>
   <fills count="4">
@@ -2021,20 +2034,20 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2391,21 +2404,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L169"/>
+  <dimension ref="A1:L170"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="16.46153846153846" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.571428571428573" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.153846153846153" style="1" customWidth="1"/>
-    <col min="5" max="5" width="36.15384615384615" style="1" customWidth="1"/>
-    <col min="6" max="6" width="33.07692307692308" style="1" customWidth="1"/>
+    <col min="1" max="1" width="18" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25" style="1" customWidth="1"/>
+    <col min="3" max="3" width="22.76923076923077" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.384615384615383" style="1" customWidth="1"/>
+    <col min="5" max="5" width="41.07692307692308" style="1" customWidth="1"/>
+    <col min="6" max="6" width="36.15384615384615" style="1" customWidth="1"/>
     <col min="7" max="7" width="18.76923076923077" style="1" customWidth="1"/>
     <col min="8" max="8" width="21.23076923076923" style="2" customWidth="1"/>
     <col min="9" max="9" width="20.76923076923077" style="3" customWidth="1"/>
     <col min="10" max="10" width="19.846153846153847" style="2" customWidth="1"/>
-    <col min="11" max="11" width="18.92857142857143" style="4" customWidth="1"/>
-    <col min="12" max="12" width="15.214285714285715" style="4" customWidth="1"/>
+    <col min="11" max="11" width="16.923076923076923" style="4" customWidth="1"/>
+    <col min="12" max="12" width="16.615384615384617" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -3682,16 +3695,16 @@
         <v>154</v>
       </c>
       <c r="G34" s="11">
-        <v>0.5958</v>
+        <v>0.7181000000000001</v>
       </c>
       <c r="H34" s="12">
         <v>6016602.48</v>
       </c>
       <c r="I34" s="13">
-        <v>3584685.32</v>
+        <v>4320723.47</v>
       </c>
       <c r="J34" s="12">
-        <v>2431917.1600000006</v>
+        <v>1695879.0100000007</v>
       </c>
       <c r="K34" s="14">
         <v>45133</v>
@@ -4153,7 +4166,7 @@
         <v>44753</v>
       </c>
       <c r="L46" s="14">
-        <v>46077</v>
+        <v>46443</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
@@ -5647,7 +5660,7 @@
         <v>347</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E86" s="11" t="s">
         <v>348</v>
@@ -6910,16 +6923,16 @@
         <v>45</v>
       </c>
       <c r="G119" s="11">
-        <v>0.0165</v>
+        <v>0.0321</v>
       </c>
       <c r="H119" s="12">
         <v>7430869.32</v>
       </c>
       <c r="I119" s="13">
-        <v>122778.19</v>
+        <v>238550.07</v>
       </c>
       <c r="J119" s="12">
-        <v>7308091.13</v>
+        <v>7192319.25</v>
       </c>
       <c r="K119" s="14">
         <v>45865</v>
@@ -8184,83 +8197,81 @@
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153" s="11" t="s">
+        <v>510</v>
+      </c>
+      <c r="B153" s="11" t="s">
         <v>576</v>
       </c>
-      <c r="B153" s="11" t="s">
+      <c r="C153" s="11"/>
+      <c r="D153" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="E153" s="11" t="s">
         <v>577</v>
       </c>
-      <c r="C153" s="11" t="s">
+      <c r="F153" s="11" t="s">
         <v>578</v>
       </c>
-      <c r="D153" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E153" s="11" t="s">
-        <v>579</v>
-      </c>
-      <c r="F153" s="11" t="s">
-        <v>580</v>
-      </c>
       <c r="G153" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H153" s="12">
-        <v>10061005.41</v>
+        <v>201720000</v>
       </c>
       <c r="I153" s="13">
-        <v>10061005.39</v>
+        <v>0</v>
       </c>
       <c r="J153" s="12">
-        <v>0.019999999552965164</v>
-      </c>
-      <c r="K153" s="14">
-        <v>45261</v>
-      </c>
-      <c r="L153" s="14">
-        <v>45833</v>
+        <v>201720000</v>
+      </c>
+      <c r="K153" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="L153" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154" s="11" t="s">
+        <v>579</v>
+      </c>
+      <c r="B154" s="11" t="s">
+        <v>580</v>
+      </c>
+      <c r="C154" s="11" t="s">
         <v>581</v>
       </c>
-      <c r="B154" s="11" t="s">
+      <c r="D154" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E154" s="11" t="s">
         <v>582</v>
       </c>
-      <c r="C154" s="11" t="s">
+      <c r="F154" s="11" t="s">
         <v>583</v>
-      </c>
-      <c r="D154" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E154" s="11" t="s">
-        <v>584</v>
-      </c>
-      <c r="F154" s="11" t="s">
-        <v>45</v>
       </c>
       <c r="G154" s="11">
         <v>1</v>
       </c>
       <c r="H154" s="12">
-        <v>81950979.23</v>
+        <v>10061005.41</v>
       </c>
       <c r="I154" s="13">
-        <v>81950979</v>
+        <v>10061005.39</v>
       </c>
       <c r="J154" s="12">
-        <v>0.23000000417232513</v>
+        <v>0.019999999552965164</v>
       </c>
       <c r="K154" s="14">
-        <v>44792</v>
+        <v>45261</v>
       </c>
       <c r="L154" s="14">
-        <v>46022</v>
+        <v>45833</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A155" s="11" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="B155" s="11" t="s">
         <v>585</v>
@@ -8275,182 +8286,182 @@
         <v>587</v>
       </c>
       <c r="F155" s="11" t="s">
-        <v>588</v>
+        <v>45</v>
       </c>
       <c r="G155" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H155" s="12">
-        <v>41522873.42</v>
+        <v>81950979.23</v>
       </c>
       <c r="I155" s="13">
-        <v>0</v>
+        <v>81950979</v>
       </c>
       <c r="J155" s="12">
-        <v>41522873.42</v>
+        <v>0.23000000417232513</v>
       </c>
       <c r="K155" s="14">
-        <v>45901</v>
+        <v>44792</v>
       </c>
       <c r="L155" s="14">
-        <v>46801</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156" s="11" t="s">
+        <v>584</v>
+      </c>
+      <c r="B156" s="11" t="s">
+        <v>588</v>
+      </c>
+      <c r="C156" s="11" t="s">
         <v>589</v>
       </c>
-      <c r="B156" s="11" t="s">
+      <c r="D156" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E156" s="11" t="s">
         <v>590</v>
       </c>
-      <c r="C156" s="11" t="s">
+      <c r="F156" s="11" t="s">
         <v>591</v>
       </c>
-      <c r="D156" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E156" s="11" t="s">
-        <v>592</v>
-      </c>
-      <c r="F156" s="11" t="s">
-        <v>323</v>
-      </c>
       <c r="G156" s="11">
-        <v>0.9728</v>
+        <v>0</v>
       </c>
       <c r="H156" s="12">
-        <v>4444784.22</v>
+        <v>41522873.42</v>
       </c>
       <c r="I156" s="13">
-        <v>4324004.81</v>
+        <v>0</v>
       </c>
       <c r="J156" s="12">
-        <v>120779.41000000015</v>
+        <v>41522873.42</v>
       </c>
       <c r="K156" s="14">
-        <v>45155</v>
+        <v>45901</v>
       </c>
       <c r="L156" s="14">
-        <v>45576</v>
+        <v>46801</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157" s="11" t="s">
+        <v>592</v>
+      </c>
+      <c r="B157" s="11" t="s">
         <v>593</v>
       </c>
-      <c r="B157" s="11" t="s">
+      <c r="C157" s="11" t="s">
         <v>594</v>
       </c>
-      <c r="C157" s="11" t="s">
+      <c r="D157" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E157" s="11" t="s">
         <v>595</v>
       </c>
-      <c r="D157" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E157" s="11" t="s">
-        <v>596</v>
-      </c>
       <c r="F157" s="11" t="s">
-        <v>111</v>
+        <v>323</v>
       </c>
       <c r="G157" s="11">
-        <v>0</v>
+        <v>0.9728</v>
       </c>
       <c r="H157" s="12">
-        <v>8995898.05</v>
+        <v>4444784.22</v>
       </c>
       <c r="I157" s="13">
-        <v>266299.23</v>
+        <v>4324004.81</v>
       </c>
       <c r="J157" s="12">
-        <v>8729598.82</v>
+        <v>120779.41000000015</v>
       </c>
       <c r="K157" s="14">
-        <v>44816</v>
+        <v>45155</v>
       </c>
       <c r="L157" s="14">
-        <v>44996</v>
+        <v>45576</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A158" s="11" t="s">
+        <v>596</v>
+      </c>
+      <c r="B158" s="11" t="s">
         <v>597</v>
       </c>
-      <c r="B158" s="11" t="s">
+      <c r="C158" s="11" t="s">
         <v>598</v>
       </c>
-      <c r="C158" s="11" t="s">
+      <c r="D158" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E158" s="11" t="s">
         <v>599</v>
       </c>
-      <c r="D158" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E158" s="11" t="s">
-        <v>600</v>
-      </c>
       <c r="F158" s="11" t="s">
-        <v>580</v>
+        <v>111</v>
       </c>
       <c r="G158" s="11">
-        <v>0.3153</v>
+        <v>0</v>
       </c>
       <c r="H158" s="12">
-        <v>3294597.99</v>
+        <v>8995898.05</v>
       </c>
       <c r="I158" s="13">
-        <v>1038880.21</v>
+        <v>266299.23</v>
       </c>
       <c r="J158" s="12">
-        <v>2255717.7800000003</v>
+        <v>8729598.82</v>
       </c>
       <c r="K158" s="14">
-        <v>45278</v>
+        <v>44816</v>
       </c>
       <c r="L158" s="14">
-        <v>46122</v>
+        <v>44996</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A159" s="11" t="s">
+        <v>600</v>
+      </c>
+      <c r="B159" s="11" t="s">
         <v>601</v>
       </c>
-      <c r="B159" s="11" t="s">
+      <c r="C159" s="11" t="s">
         <v>602</v>
-      </c>
-      <c r="C159" s="11" t="s">
-        <v>603</v>
       </c>
       <c r="D159" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E159" s="11" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F159" s="11" t="s">
-        <v>505</v>
+        <v>583</v>
       </c>
       <c r="G159" s="11">
-        <v>0.9922</v>
+        <v>0.3153</v>
       </c>
       <c r="H159" s="12">
-        <v>6055289.34</v>
+        <v>3294597.99</v>
       </c>
       <c r="I159" s="13">
-        <v>6007931.02</v>
+        <v>1038880.21</v>
       </c>
       <c r="J159" s="12">
-        <v>47358.3200000003</v>
+        <v>2255717.7800000003</v>
       </c>
       <c r="K159" s="14">
-        <v>44715</v>
+        <v>45278</v>
       </c>
       <c r="L159" s="14">
-        <v>45075</v>
+        <v>46122</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160" s="11" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="B160" s="11" t="s">
         <v>605</v>
@@ -8459,264 +8470,264 @@
         <v>606</v>
       </c>
       <c r="D160" s="11" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E160" s="11" t="s">
         <v>607</v>
       </c>
       <c r="F160" s="11" t="s">
-        <v>45</v>
+        <v>505</v>
       </c>
       <c r="G160" s="11">
-        <v>0.22760000000000002</v>
+        <v>0.9922</v>
       </c>
       <c r="H160" s="12">
-        <v>8973983.87</v>
+        <v>6055289.34</v>
       </c>
       <c r="I160" s="13">
-        <v>2042159.29</v>
+        <v>6007931.02</v>
       </c>
       <c r="J160" s="12">
-        <v>6931824.579999999</v>
+        <v>47358.3200000003</v>
       </c>
       <c r="K160" s="14">
-        <v>44707</v>
+        <v>44715</v>
       </c>
       <c r="L160" s="14">
-        <v>45280</v>
+        <v>45075</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161" s="11" t="s">
+        <v>604</v>
+      </c>
+      <c r="B161" s="11" t="s">
         <v>608</v>
       </c>
-      <c r="B161" s="11" t="s">
+      <c r="C161" s="11" t="s">
         <v>609</v>
       </c>
-      <c r="C161" s="11" t="s">
-        <v>249</v>
-      </c>
       <c r="D161" s="11" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E161" s="11" t="s">
         <v>610</v>
       </c>
       <c r="F161" s="11" t="s">
-        <v>149</v>
+        <v>45</v>
       </c>
       <c r="G161" s="11">
-        <v>1</v>
+        <v>0.22760000000000002</v>
       </c>
       <c r="H161" s="12">
-        <v>13792679.79</v>
+        <v>8973983.87</v>
       </c>
       <c r="I161" s="13">
-        <v>13792679.79</v>
+        <v>2042159.29</v>
       </c>
       <c r="J161" s="12">
-        <v>0</v>
+        <v>6931824.579999999</v>
       </c>
       <c r="K161" s="14">
-        <v>44767</v>
+        <v>44707</v>
       </c>
       <c r="L161" s="14">
-        <v>45411</v>
+        <v>45280</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162" s="11" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="B162" s="11" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C162" s="11" t="s">
-        <v>136</v>
+        <v>249</v>
       </c>
       <c r="D162" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E162" s="11" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="F162" s="11" t="s">
-        <v>57</v>
+        <v>149</v>
       </c>
       <c r="G162" s="11">
-        <v>0.9122</v>
+        <v>1</v>
       </c>
       <c r="H162" s="12">
-        <v>22472818</v>
+        <v>13792679.79</v>
       </c>
       <c r="I162" s="13">
-        <v>20500685.68</v>
+        <v>13792679.79</v>
       </c>
       <c r="J162" s="12">
-        <v>1972132.3200000003</v>
+        <v>0</v>
       </c>
       <c r="K162" s="14">
-        <v>44827</v>
+        <v>44767</v>
       </c>
       <c r="L162" s="14">
-        <v>45460</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163" s="11" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="B163" s="11" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C163" s="11" t="s">
-        <v>614</v>
+        <v>136</v>
       </c>
       <c r="D163" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E163" s="11" t="s">
         <v>615</v>
       </c>
       <c r="F163" s="11" t="s">
-        <v>616</v>
+        <v>57</v>
       </c>
       <c r="G163" s="11">
-        <v>0.8996</v>
+        <v>0.9122</v>
       </c>
       <c r="H163" s="12">
-        <v>51414775.09</v>
+        <v>22472818</v>
       </c>
       <c r="I163" s="13">
-        <v>46254135.59</v>
+        <v>20500685.68</v>
       </c>
       <c r="J163" s="12">
-        <v>5160639.5</v>
+        <v>1972132.3200000003</v>
       </c>
       <c r="K163" s="14">
-        <v>45566</v>
+        <v>44827</v>
       </c>
       <c r="L163" s="14">
-        <v>46106</v>
+        <v>45460</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164" s="11" t="s">
+        <v>611</v>
+      </c>
+      <c r="B164" s="11" t="s">
+        <v>616</v>
+      </c>
+      <c r="C164" s="11" t="s">
         <v>617</v>
-      </c>
-      <c r="B164" s="11" t="s">
-        <v>618</v>
-      </c>
-      <c r="C164" s="11" t="s">
-        <v>619</v>
       </c>
       <c r="D164" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E164" s="11" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="F164" s="11" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="G164" s="11">
-        <v>0</v>
+        <v>0.8996</v>
       </c>
       <c r="H164" s="12">
-        <v>1302281.25</v>
+        <v>51414775.09</v>
       </c>
       <c r="I164" s="13">
-        <v>0</v>
+        <v>46254135.59</v>
       </c>
       <c r="J164" s="12">
-        <v>1302281.25</v>
+        <v>5160639.5</v>
       </c>
       <c r="K164" s="14">
-        <v>46080</v>
+        <v>45566</v>
       </c>
       <c r="L164" s="14">
-        <v>46440</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165" s="11" t="s">
+        <v>620</v>
+      </c>
+      <c r="B165" s="11" t="s">
+        <v>621</v>
+      </c>
+      <c r="C165" s="11" t="s">
         <v>622</v>
-      </c>
-      <c r="B165" s="11" t="s">
-        <v>623</v>
-      </c>
-      <c r="C165" s="11" t="s">
-        <v>161</v>
       </c>
       <c r="D165" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E165" s="11" t="s">
+        <v>623</v>
+      </c>
+      <c r="F165" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="F165" s="11" t="s">
-        <v>625</v>
-      </c>
       <c r="G165" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H165" s="12">
-        <v>18264452.89</v>
+        <v>1302281.25</v>
       </c>
       <c r="I165" s="13">
-        <v>18264452.89</v>
+        <v>0</v>
       </c>
       <c r="J165" s="12">
-        <v>0</v>
+        <v>1302281.25</v>
       </c>
       <c r="K165" s="14">
-        <v>44722</v>
+        <v>46080</v>
       </c>
       <c r="L165" s="14">
-        <v>45723</v>
+        <v>46440</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166" s="11" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="B166" s="11" t="s">
         <v>626</v>
       </c>
       <c r="C166" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="D166" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E166" s="11" t="s">
         <v>627</v>
       </c>
-      <c r="D166" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E166" s="11" t="s">
+      <c r="F166" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="F166" s="11" t="s">
-        <v>40</v>
-      </c>
       <c r="G166" s="11">
-        <v>0.9953</v>
+        <v>1</v>
       </c>
       <c r="H166" s="12">
-        <v>30599999.01</v>
+        <v>18264452.89</v>
       </c>
       <c r="I166" s="13">
-        <v>30456294.33</v>
+        <v>18264452.89</v>
       </c>
       <c r="J166" s="12">
-        <v>143704.68000000343</v>
+        <v>0</v>
       </c>
       <c r="K166" s="14">
-        <v>45019</v>
+        <v>44722</v>
       </c>
       <c r="L166" s="14">
-        <v>45743</v>
+        <v>45723</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A167" s="11" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="B167" s="11" t="s">
         <v>629</v>
@@ -8725,36 +8736,36 @@
         <v>630</v>
       </c>
       <c r="D167" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E167" s="11" t="s">
         <v>631</v>
       </c>
       <c r="F167" s="11" t="s">
-        <v>222</v>
+        <v>40</v>
       </c>
       <c r="G167" s="11">
-        <v>0.9601000000000001</v>
+        <v>0.9953</v>
       </c>
       <c r="H167" s="12">
-        <v>43796954.98</v>
+        <v>30599999.01</v>
       </c>
       <c r="I167" s="13">
-        <v>42048979.52</v>
+        <v>30456294.33</v>
       </c>
       <c r="J167" s="12">
-        <v>1747975.4599999934</v>
+        <v>143704.68000000343</v>
       </c>
       <c r="K167" s="14">
-        <v>44641</v>
+        <v>45019</v>
       </c>
       <c r="L167" s="14">
-        <v>46091</v>
+        <v>45743</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A168" s="11" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="B168" s="11" t="s">
         <v>632</v>
@@ -8772,27 +8783,27 @@
         <v>222</v>
       </c>
       <c r="G168" s="11">
-        <v>0.7956</v>
+        <v>0.9601000000000001</v>
       </c>
       <c r="H168" s="12">
-        <v>45726170.25</v>
+        <v>43796954.98</v>
       </c>
       <c r="I168" s="13">
-        <v>36377601.26</v>
+        <v>42048979.52</v>
       </c>
       <c r="J168" s="12">
-        <v>9348568.990000002</v>
+        <v>1747975.4599999934</v>
       </c>
       <c r="K168" s="14">
-        <v>44623</v>
+        <v>44641</v>
       </c>
       <c r="L168" s="14">
-        <v>46222</v>
+        <v>46091</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A169" s="11" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="B169" s="11" t="s">
         <v>635</v>
@@ -8807,24 +8818,62 @@
         <v>637</v>
       </c>
       <c r="F169" s="11" t="s">
-        <v>111</v>
+        <v>222</v>
       </c>
       <c r="G169" s="11">
-        <v>0.30670000000000003</v>
+        <v>0.7956</v>
       </c>
       <c r="H169" s="12">
-        <v>65678550.13</v>
+        <v>45726170.25</v>
       </c>
       <c r="I169" s="13">
-        <v>20145177.51</v>
+        <v>36377601.26</v>
       </c>
       <c r="J169" s="12">
-        <v>45533372.620000005</v>
+        <v>9348568.990000002</v>
       </c>
       <c r="K169" s="14">
         <v>44623</v>
       </c>
       <c r="L169" s="14">
+        <v>46222</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A170" s="11" t="s">
+        <v>625</v>
+      </c>
+      <c r="B170" s="11" t="s">
+        <v>638</v>
+      </c>
+      <c r="C170" s="11" t="s">
+        <v>639</v>
+      </c>
+      <c r="D170" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E170" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="F170" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="G170" s="11">
+        <v>0.30670000000000003</v>
+      </c>
+      <c r="H170" s="12">
+        <v>65678550.13</v>
+      </c>
+      <c r="I170" s="13">
+        <v>20145177.51</v>
+      </c>
+      <c r="J170" s="12">
+        <v>45533372.620000005</v>
+      </c>
+      <c r="K170" s="14">
+        <v>44623</v>
+      </c>
+      <c r="L170" s="14">
         <v>46170</v>
       </c>
     </row>

--- a/ANALITICA.xlsx
+++ b/ANALITICA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="643">
   <si>
     <t>Municipio</t>
   </si>
@@ -296,6 +296,24 @@
     <t>DRV ENGENHARIA - EIRELI</t>
   </si>
   <si>
+    <t>330001/001345/2025</t>
+  </si>
+  <si>
+    <t>025/2025</t>
+  </si>
+  <si>
+    <t>ATA DE REGISTRO</t>
+  </si>
+  <si>
+    <t>ADESÃO DE ATA DE REGISTRO DE PREÇO PARA SERVIÇOS DE URBANIZAÇÃO, DIVIDIDOS EM 4 LOTES POR REGIÕES, (EXECUÇÃO DE CONSTRUÇÃO/RECUPERAÇÃO DE CALÇADAS, CICLOVIAS E PAVIMENTOS DE DIVERSOS TRECHOS DESCONTÍNUOS DE VIAS NÃO CADASTRADAS EM LOGRADOUROS PÚBLICOS MUNICIPAIS) A SER IMPLEMENTADO NAS IMEDIAÇÕES DAS HABITAÇÕES DE INTERESSE SOCIAL OU EM ÁREAS CONFIGURADAS COMO DE ESPECIAL INTERESSE SOCIAL - LOTE IV (SERRANA e CENTRO NORTE)</t>
+  </si>
+  <si>
+    <t>FAB MIX CONCRETOS LTDA</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
     <t>330018/000695/2021</t>
   </si>
   <si>
@@ -692,9 +710,6 @@
     <t>CRATER CONSTRUÇÕES LTDA.</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>Itaperuna</t>
   </si>
   <si>
@@ -1166,6 +1181,15 @@
     <t>ENGE PRAT ENGENHARIA E SERVICOS LTDA.</t>
   </si>
   <si>
+    <t>330018/000421/2023</t>
+  </si>
+  <si>
+    <t>006/2025</t>
+  </si>
+  <si>
+    <t>CONTENÇÃO E DRENAGEM EM VILA VASCONCELOS, PETRÓPOLIS</t>
+  </si>
+  <si>
     <t>460001/000779/2023</t>
   </si>
   <si>
@@ -1187,15 +1211,6 @@
     <t>CONSÓRCIO ECONORTE GEOSONDA - CASTELÃNEA  - PETROPOLIS ( ECONORTE, MEIO AMBIENTE, INFRAESTRUTURA E SERVIÇO LTDA E GEOSONDA S/A)</t>
   </si>
   <si>
-    <t>330018/000421/2023</t>
-  </si>
-  <si>
-    <t>006/2025</t>
-  </si>
-  <si>
-    <t>CONTENÇÃO E DRENAGEM EM VILA VASCONCELOS, PETRÓPOLIS</t>
-  </si>
-  <si>
     <t>170026/000537/2022</t>
   </si>
   <si>
@@ -1538,9 +1553,6 @@
     <t>PROJETO E OBRAS DE RESTAURANTE DO POVO, RIO DE JANEIRO/RJ (LOTE 02)</t>
   </si>
   <si>
-    <t>FAB MIX CONCRETOS LTDA</t>
-  </si>
-  <si>
     <t>e-17/026/1892/2019-1</t>
   </si>
   <si>
@@ -1709,6 +1721,12 @@
     <t>CONCLUSÃO DAS OBRAS DO MUSEU DA IMAGEM E DO SOM - COPACABANA - RJ</t>
   </si>
   <si>
+    <t>330001/000434/2026</t>
+  </si>
+  <si>
+    <t>ATA DE REGISTRO DE PREÇO PARA SERVIÇO DE PAVIMENTAÇÃO COM ASTALTO CBUQ- DIVERSOS MUNICIPÍOS</t>
+  </si>
+  <si>
     <t>170026/000214/2022</t>
   </si>
   <si>
@@ -1728,6 +1746,15 @@
   </si>
   <si>
     <t>RECUPERAÇÃO DE EQUIPAMENTOS DO TELEFÉRICO DO ALEMÃO - RJ</t>
+  </si>
+  <si>
+    <t>330001/001152/2025</t>
+  </si>
+  <si>
+    <t>CONTRATAÇÃO DE UMA EMPRESA ESPECIALIZADA NA EXECUÇÃO DE SERVIÇOS DE ESTABILIZAÇÃO DE SOLOS COM ESTABILIZADOR IÔNICO LÍQUIDO, COM PROPRIEDADES DE AUMENTO DA RESISTÊNCIA DO SOLO E RESISTÊNCIA À ÁGUA, 100% AMBIENTALMENTE SUSTENTÁVEL, MONOCOMPONENTE, APLICADO IN SITU, COM O FORNECIMENTO DE TODOS OS EQUIPAMENTOS, MAQUINÁRIO, MÃO DE OBRA E TODOS OS MATERIAIS NECESSÁRIOS PARA CADA TIPO DE SERVIÇO, CONFORME AS CONDIÇÕES E EXIGÊNCIAS ESTABELECIDAS.</t>
+  </si>
+  <si>
+    <t>Não existe na tabela Contratadas</t>
   </si>
   <si>
     <t>São Francisco de Itabapoana</t>
@@ -1999,7 +2026,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2042,6 +2069,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2383,7 +2413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L168"/>
+  <dimension ref="A1:L171"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" style="1" customWidth="1"/>
@@ -2990,16 +3020,16 @@
         <v>73</v>
       </c>
       <c r="G16" s="11">
-        <v>0.8856</v>
+        <v>0.9754</v>
       </c>
       <c r="H16" s="12">
         <v>6765672.29</v>
       </c>
       <c r="I16" s="13">
-        <v>5991696.58</v>
+        <v>6599141.25</v>
       </c>
       <c r="J16" s="12">
-        <v>773975.71</v>
+        <v>166531.04000000004</v>
       </c>
       <c r="K16" s="14">
         <v>45398</v>
@@ -3171,31 +3201,31 @@
         <v>95</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G21" s="11">
-        <v>0.5163</v>
+        <v>0</v>
       </c>
       <c r="H21" s="12">
-        <v>31022838.12</v>
+        <v>5054505.24</v>
       </c>
       <c r="I21" s="13">
-        <v>16018051.23</v>
+        <v>0</v>
       </c>
       <c r="J21" s="12">
-        <v>15004786.89</v>
-      </c>
-      <c r="K21" s="14">
-        <v>45309</v>
+        <v>5054505.24</v>
+      </c>
+      <c r="K21" s="15" t="s">
+        <v>99</v>
       </c>
       <c r="L21" s="14">
-        <v>46392</v>
+        <v>46312</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -3203,37 +3233,37 @@
         <v>82</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G22" s="11">
-        <v>0.6607999999999999</v>
+        <v>0.5163</v>
       </c>
       <c r="H22" s="12">
-        <v>48872552.26</v>
+        <v>31022838.12</v>
       </c>
       <c r="I22" s="13">
-        <v>32294745.04</v>
+        <v>16018051.23</v>
       </c>
       <c r="J22" s="12">
-        <v>16577807.219999999</v>
+        <v>15004786.89</v>
       </c>
       <c r="K22" s="14">
-        <v>44875</v>
+        <v>45309</v>
       </c>
       <c r="L22" s="14">
-        <v>46375</v>
+        <v>46392</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -3241,37 +3271,37 @@
         <v>82</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G23" s="11">
-        <v>0.7193</v>
+        <v>0.6714</v>
       </c>
       <c r="H23" s="12">
-        <v>89008310.65</v>
+        <v>48872552.26</v>
       </c>
       <c r="I23" s="13">
-        <v>64026819.34</v>
+        <v>32814331.78</v>
       </c>
       <c r="J23" s="12">
-        <v>24981491.310000002</v>
+        <v>16058220.479999997</v>
       </c>
       <c r="K23" s="14">
-        <v>44789</v>
+        <v>44875</v>
       </c>
       <c r="L23" s="14">
-        <v>45510</v>
+        <v>46375</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -3279,943 +3309,943 @@
         <v>82</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G24" s="11">
-        <v>0.44920000000000004</v>
+        <v>0.7193</v>
       </c>
       <c r="H24" s="12">
-        <v>62211091.02</v>
+        <v>89008310.65</v>
       </c>
       <c r="I24" s="13">
-        <v>27948056.39</v>
+        <v>64026819.34</v>
       </c>
       <c r="J24" s="12">
-        <v>34263034.63</v>
+        <v>24981491.310000002</v>
       </c>
       <c r="K24" s="14">
-        <v>44883</v>
+        <v>44789</v>
       </c>
       <c r="L24" s="14">
-        <v>46144</v>
+        <v>45510</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G25" s="11">
-        <v>0.9922</v>
+        <v>0.44920000000000004</v>
       </c>
       <c r="H25" s="12">
-        <v>5361446.28</v>
+        <v>62211091.02</v>
       </c>
       <c r="I25" s="13">
-        <v>5319761.7</v>
+        <v>27948056.39</v>
       </c>
       <c r="J25" s="12">
-        <v>41684.580000000075</v>
+        <v>34263034.63</v>
       </c>
       <c r="K25" s="14">
-        <v>44637</v>
+        <v>44883</v>
       </c>
       <c r="L25" s="14">
-        <v>45484</v>
+        <v>46144</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G26" s="11">
-        <v>0.8786</v>
+        <v>0.9922</v>
       </c>
       <c r="H26" s="12">
-        <v>2601911.32</v>
+        <v>5361446.28</v>
       </c>
       <c r="I26" s="13">
-        <v>2286080.42</v>
+        <v>5319761.7</v>
       </c>
       <c r="J26" s="12">
-        <v>315830.8999999999</v>
+        <v>41684.580000000075</v>
       </c>
       <c r="K26" s="14">
-        <v>45624</v>
+        <v>44637</v>
       </c>
       <c r="L26" s="14">
-        <v>46106</v>
+        <v>45484</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G27" s="11">
-        <v>0.1104</v>
+        <v>0.8786</v>
       </c>
       <c r="H27" s="12">
-        <v>2394811.95</v>
+        <v>2601911.32</v>
       </c>
       <c r="I27" s="13">
-        <v>264324.6</v>
+        <v>2286080.42</v>
       </c>
       <c r="J27" s="12">
-        <v>2130487.35</v>
+        <v>315830.8999999999</v>
       </c>
       <c r="K27" s="14">
-        <v>44840</v>
+        <v>45624</v>
       </c>
       <c r="L27" s="14">
-        <v>45390</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G28" s="11">
-        <v>0.9998999999999999</v>
+        <v>0.1104</v>
       </c>
       <c r="H28" s="12">
-        <v>2975474.34</v>
+        <v>2394811.95</v>
       </c>
       <c r="I28" s="13">
-        <v>2975297.32</v>
+        <v>264324.6</v>
       </c>
       <c r="J28" s="12">
-        <v>177.02000000001863</v>
+        <v>2130487.35</v>
       </c>
       <c r="K28" s="14">
-        <v>44883</v>
+        <v>44840</v>
       </c>
       <c r="L28" s="14">
-        <v>45411</v>
+        <v>45390</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D29" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G29" s="11">
-        <v>1</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="H29" s="12">
-        <v>4808707.09</v>
+        <v>2975474.34</v>
       </c>
       <c r="I29" s="13">
-        <v>4808707.09</v>
+        <v>2975297.32</v>
       </c>
       <c r="J29" s="12">
-        <v>0</v>
+        <v>177.02000000001863</v>
       </c>
       <c r="K29" s="14">
-        <v>44743</v>
+        <v>44883</v>
       </c>
       <c r="L29" s="14">
-        <v>45341</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D30" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>45</v>
+        <v>138</v>
       </c>
       <c r="G30" s="11">
-        <v>0.9109999999999999</v>
+        <v>1</v>
       </c>
       <c r="H30" s="12">
-        <v>13208831.36</v>
+        <v>4808707.09</v>
       </c>
       <c r="I30" s="13">
-        <v>12032786.93</v>
+        <v>4808707.09</v>
       </c>
       <c r="J30" s="12">
-        <v>1176044.4299999997</v>
+        <v>0</v>
       </c>
       <c r="K30" s="14">
-        <v>44708</v>
+        <v>44743</v>
       </c>
       <c r="L30" s="14">
-        <v>45398</v>
+        <v>45341</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D31" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="G31" s="11">
-        <v>1</v>
+        <v>0.9109999999999999</v>
       </c>
       <c r="H31" s="12">
-        <v>11551184.44</v>
+        <v>13208831.36</v>
       </c>
       <c r="I31" s="13">
-        <v>11551184.4</v>
+        <v>12032786.93</v>
       </c>
       <c r="J31" s="12">
-        <v>0.03999999910593033</v>
+        <v>1176044.4299999997</v>
       </c>
       <c r="K31" s="14">
-        <v>44733</v>
+        <v>44708</v>
       </c>
       <c r="L31" s="14">
-        <v>45953</v>
+        <v>45398</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>143</v>
+        <v>65</v>
       </c>
       <c r="G32" s="11">
-        <v>0.9908</v>
+        <v>1</v>
       </c>
       <c r="H32" s="12">
-        <v>9751616.37</v>
+        <v>11551184.44</v>
       </c>
       <c r="I32" s="13">
-        <v>9661616.37</v>
+        <v>11551184.4</v>
       </c>
       <c r="J32" s="12">
-        <v>90000</v>
+        <v>0.03999999910593033</v>
       </c>
       <c r="K32" s="14">
-        <v>44873</v>
+        <v>44733</v>
       </c>
       <c r="L32" s="14">
-        <v>45485</v>
+        <v>45953</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G33" s="11">
-        <v>0.7181000000000001</v>
+        <v>0.9908</v>
       </c>
       <c r="H33" s="12">
-        <v>6016602.48</v>
+        <v>9751616.37</v>
       </c>
       <c r="I33" s="13">
-        <v>4320723.47</v>
+        <v>9661616.37</v>
       </c>
       <c r="J33" s="12">
-        <v>1695879.0100000007</v>
+        <v>90000</v>
       </c>
       <c r="K33" s="14">
-        <v>45133</v>
+        <v>44873</v>
       </c>
       <c r="L33" s="14">
-        <v>46128</v>
+        <v>45485</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G34" s="11">
-        <v>0.9998</v>
+        <v>0.7181000000000001</v>
       </c>
       <c r="H34" s="12">
-        <v>8396309.76</v>
+        <v>6016602.48</v>
       </c>
       <c r="I34" s="13">
-        <v>8394769.02</v>
+        <v>4320723.47</v>
       </c>
       <c r="J34" s="12">
-        <v>1540.7400000002235</v>
+        <v>1695879.0100000007</v>
       </c>
       <c r="K34" s="14">
-        <v>44868</v>
+        <v>45133</v>
       </c>
       <c r="L34" s="14">
-        <v>45560</v>
+        <v>46128</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D35" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G35" s="11">
-        <v>0.9865</v>
+        <v>0.9998</v>
       </c>
       <c r="H35" s="12">
-        <v>45237596.81</v>
+        <v>8396309.76</v>
       </c>
       <c r="I35" s="13">
-        <v>44626728.2</v>
+        <v>8394769.02</v>
       </c>
       <c r="J35" s="12">
-        <v>610868.6099999994</v>
+        <v>1540.7400000002235</v>
       </c>
       <c r="K35" s="14">
-        <v>44769</v>
+        <v>44868</v>
       </c>
       <c r="L35" s="14">
-        <v>45701</v>
+        <v>45560</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>22</v>
+        <v>163</v>
       </c>
       <c r="G36" s="11">
-        <v>0.9899</v>
+        <v>0.9865</v>
       </c>
       <c r="H36" s="12">
-        <v>148784461.49</v>
+        <v>45237596.81</v>
       </c>
       <c r="I36" s="13">
-        <v>147280622.62</v>
+        <v>44626728.2</v>
       </c>
       <c r="J36" s="12">
-        <v>1503838.8700000048</v>
+        <v>610868.6099999994</v>
       </c>
       <c r="K36" s="14">
-        <v>45503</v>
+        <v>44769</v>
       </c>
       <c r="L36" s="14">
-        <v>46043</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>164</v>
+        <v>22</v>
       </c>
       <c r="G37" s="11">
-        <v>0.9781</v>
+        <v>0.9899</v>
       </c>
       <c r="H37" s="12">
-        <v>90986818.17</v>
+        <v>148784461.49</v>
       </c>
       <c r="I37" s="13">
-        <v>88995375.53</v>
+        <v>147280622.62</v>
       </c>
       <c r="J37" s="12">
-        <v>1991442.6400000006</v>
+        <v>1503838.8700000048</v>
       </c>
       <c r="K37" s="14">
-        <v>44986</v>
+        <v>45503</v>
       </c>
       <c r="L37" s="14">
-        <v>45589</v>
+        <v>46043</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>45</v>
+        <v>170</v>
       </c>
       <c r="G38" s="11">
-        <v>0.9786</v>
+        <v>0.9781</v>
       </c>
       <c r="H38" s="12">
-        <v>113557951.65</v>
+        <v>90986818.17</v>
       </c>
       <c r="I38" s="13">
-        <v>111133195.68</v>
+        <v>88995375.53</v>
       </c>
       <c r="J38" s="12">
-        <v>2424755.969999999</v>
+        <v>1991442.6400000006</v>
       </c>
       <c r="K38" s="14">
-        <v>45498</v>
+        <v>44986</v>
       </c>
       <c r="L38" s="14">
-        <v>46038</v>
+        <v>45589</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D39" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="G39" s="11">
-        <v>0.9301</v>
+        <v>0.9786</v>
       </c>
       <c r="H39" s="12">
-        <v>41651255.98</v>
+        <v>113557951.65</v>
       </c>
       <c r="I39" s="13">
-        <v>38738669.02</v>
+        <v>111133195.68</v>
       </c>
       <c r="J39" s="12">
-        <v>2912586.9599999934</v>
+        <v>2424755.969999999</v>
       </c>
       <c r="K39" s="14">
-        <v>45391</v>
+        <v>45498</v>
       </c>
       <c r="L39" s="14">
-        <v>46057</v>
+        <v>46038</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F40" s="11" t="s">
         <v>22</v>
       </c>
       <c r="G40" s="11">
-        <v>0.5526</v>
+        <v>0.9301</v>
       </c>
       <c r="H40" s="12">
-        <v>22759968.59</v>
+        <v>41651255.98</v>
       </c>
       <c r="I40" s="13">
-        <v>12576165.07</v>
+        <v>38738669.02</v>
       </c>
       <c r="J40" s="12">
-        <v>10183803.52</v>
+        <v>2912586.9599999934</v>
       </c>
       <c r="K40" s="14">
-        <v>44511</v>
+        <v>45391</v>
       </c>
       <c r="L40" s="14">
-        <v>44958</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="G41" s="11">
-        <v>0.5414</v>
+        <v>0.5526</v>
       </c>
       <c r="H41" s="12">
-        <v>26504288.68</v>
+        <v>22759968.59</v>
       </c>
       <c r="I41" s="13">
-        <v>14348711.09</v>
+        <v>12576165.07</v>
       </c>
       <c r="J41" s="12">
-        <v>12155577.59</v>
+        <v>10183803.52</v>
       </c>
       <c r="K41" s="14">
-        <v>45190</v>
+        <v>44511</v>
       </c>
       <c r="L41" s="14">
-        <v>46153</v>
+        <v>44958</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>157</v>
+        <v>40</v>
       </c>
       <c r="G42" s="11">
-        <v>0.0105</v>
+        <v>0.5414</v>
       </c>
       <c r="H42" s="12">
-        <v>12679339.18</v>
+        <v>26504288.68</v>
       </c>
       <c r="I42" s="13">
-        <v>133236.58</v>
+        <v>14348711.09</v>
       </c>
       <c r="J42" s="12">
-        <v>12546102.6</v>
+        <v>12155577.59</v>
       </c>
       <c r="K42" s="14">
-        <v>44753</v>
+        <v>45190</v>
       </c>
       <c r="L42" s="14">
-        <v>44984</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D43" s="11" t="s">
         <v>20</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>73</v>
+        <v>163</v>
       </c>
       <c r="G43" s="11">
-        <v>0.0063</v>
+        <v>0.0105</v>
       </c>
       <c r="H43" s="12">
-        <v>21672861.46</v>
+        <v>12679339.18</v>
       </c>
       <c r="I43" s="13">
-        <v>137475.09</v>
+        <v>133236.58</v>
       </c>
       <c r="J43" s="12">
-        <v>21535386.37</v>
+        <v>12546102.6</v>
       </c>
       <c r="K43" s="14">
-        <v>44783</v>
+        <v>44753</v>
       </c>
       <c r="L43" s="14">
-        <v>44998</v>
+        <v>44984</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D44" s="11" t="s">
         <v>20</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>186</v>
+        <v>73</v>
       </c>
       <c r="G44" s="11">
-        <v>0.2034</v>
+        <v>0.0063</v>
       </c>
       <c r="H44" s="12">
-        <v>30334596.91</v>
+        <v>21672861.46</v>
       </c>
       <c r="I44" s="13">
-        <v>6171237.78</v>
+        <v>137475.09</v>
       </c>
       <c r="J44" s="12">
-        <v>24163359.13</v>
+        <v>21535386.37</v>
       </c>
       <c r="K44" s="14">
-        <v>44753</v>
+        <v>44783</v>
       </c>
       <c r="L44" s="14">
-        <v>45505</v>
+        <v>44998</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>22</v>
+        <v>192</v>
       </c>
       <c r="G45" s="11">
-        <v>0.38670000000000004</v>
+        <v>0.2034</v>
       </c>
       <c r="H45" s="12">
-        <v>58032411.71</v>
+        <v>30334596.91</v>
       </c>
       <c r="I45" s="13">
-        <v>22442987.53</v>
+        <v>6171237.78</v>
       </c>
       <c r="J45" s="12">
-        <v>35589424.18</v>
+        <v>24163359.13</v>
       </c>
       <c r="K45" s="14">
         <v>44753</v>
       </c>
       <c r="L45" s="14">
-        <v>46443</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D46" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="G46" s="11">
-        <v>0.25579999999999997</v>
+        <v>0.38670000000000004</v>
       </c>
       <c r="H46" s="12">
-        <v>51119038.92</v>
+        <v>58032411.71</v>
       </c>
       <c r="I46" s="13">
-        <v>13076598.15</v>
+        <v>22442987.53</v>
       </c>
       <c r="J46" s="12">
-        <v>38042440.77</v>
+        <v>35589424.18</v>
       </c>
       <c r="K46" s="14">
         <v>44753</v>
       </c>
       <c r="L46" s="14">
-        <v>46209</v>
+        <v>46443</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G47" s="11">
-        <v>0.4456</v>
+        <v>0.25579999999999997</v>
       </c>
       <c r="H47" s="12">
-        <v>69450000</v>
+        <v>51119038.92</v>
       </c>
       <c r="I47" s="13">
-        <v>30949430.48</v>
+        <v>13076598.15</v>
       </c>
       <c r="J47" s="12">
-        <v>38500569.519999996</v>
+        <v>38042440.77</v>
       </c>
       <c r="K47" s="14">
-        <v>44449</v>
+        <v>44753</v>
       </c>
       <c r="L47" s="14">
-        <v>45329</v>
+        <v>46209</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D48" s="11" t="s">
         <v>20</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G48" s="11">
-        <v>0.4495</v>
+        <v>0.4456</v>
       </c>
       <c r="H48" s="12">
-        <v>84484346.71</v>
+        <v>69450000</v>
       </c>
       <c r="I48" s="13">
-        <v>37978980.67</v>
+        <v>30949430.48</v>
       </c>
       <c r="J48" s="12">
-        <v>46505366.03999999</v>
+        <v>38500569.519999996</v>
       </c>
       <c r="K48" s="14">
         <v>44449</v>
@@ -4226,230 +4256,230 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D49" s="11" t="s">
         <v>20</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>202</v>
+        <v>103</v>
       </c>
       <c r="G49" s="11">
-        <v>0.0028000000000000004</v>
+        <v>0.4495</v>
       </c>
       <c r="H49" s="12">
-        <v>47996411.38</v>
+        <v>84484346.71</v>
       </c>
       <c r="I49" s="13">
-        <v>133579.45</v>
+        <v>37978980.67</v>
       </c>
       <c r="J49" s="12">
-        <v>47862831.93</v>
+        <v>46505366.03999999</v>
       </c>
       <c r="K49" s="14">
-        <v>44887</v>
+        <v>44449</v>
       </c>
       <c r="L49" s="14">
-        <v>45187</v>
+        <v>45329</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G50" s="11">
-        <v>0.0377</v>
+        <v>0.0028000000000000004</v>
       </c>
       <c r="H50" s="12">
-        <v>54283415</v>
+        <v>47996411.38</v>
       </c>
       <c r="I50" s="13">
-        <v>2045374.39</v>
+        <v>133579.45</v>
       </c>
       <c r="J50" s="12">
-        <v>52238040.61</v>
+        <v>47862831.93</v>
       </c>
       <c r="K50" s="14">
-        <v>44753</v>
+        <v>44887</v>
       </c>
       <c r="L50" s="14">
-        <v>46195</v>
+        <v>45187</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
-        <v>207</v>
+        <v>155</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G51" s="11">
-        <v>0.9643999999999999</v>
+        <v>0.0377</v>
       </c>
       <c r="H51" s="12">
-        <v>1332580.86</v>
+        <v>54283415</v>
       </c>
       <c r="I51" s="13">
-        <v>1285178.36</v>
+        <v>2045374.39</v>
       </c>
       <c r="J51" s="12">
-        <v>47402.5</v>
+        <v>52238040.61</v>
       </c>
       <c r="K51" s="14">
-        <v>44536</v>
+        <v>44753</v>
       </c>
       <c r="L51" s="14">
-        <v>45230</v>
+        <v>46195</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D52" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G52" s="11">
-        <v>1</v>
+        <v>0.9643999999999999</v>
       </c>
       <c r="H52" s="12">
-        <v>8156656.19</v>
+        <v>1332580.86</v>
       </c>
       <c r="I52" s="13">
-        <v>8156656.13</v>
+        <v>1285178.36</v>
       </c>
       <c r="J52" s="12">
-        <v>0.06000000052154064</v>
+        <v>47402.5</v>
       </c>
       <c r="K52" s="14">
-        <v>44832</v>
+        <v>44536</v>
       </c>
       <c r="L52" s="14">
-        <v>45378</v>
+        <v>45230</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="11" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G53" s="11">
-        <v>0.8421</v>
+        <v>1</v>
       </c>
       <c r="H53" s="12">
-        <v>7704834.91</v>
+        <v>8156656.19</v>
       </c>
       <c r="I53" s="13">
-        <v>6488132.94</v>
+        <v>8156656.13</v>
       </c>
       <c r="J53" s="12">
-        <v>1216701.9699999997</v>
+        <v>0.06000000052154064</v>
       </c>
       <c r="K53" s="14">
-        <v>45286</v>
+        <v>44832</v>
       </c>
       <c r="L53" s="14">
-        <v>46098</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="11" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G54" s="11">
-        <v>0</v>
+        <v>0.8421</v>
       </c>
       <c r="H54" s="12">
-        <v>11620104.78</v>
+        <v>7704834.91</v>
       </c>
       <c r="I54" s="13">
-        <v>0</v>
+        <v>6488132.94</v>
       </c>
       <c r="J54" s="12">
-        <v>11620104.78</v>
-      </c>
-      <c r="K54" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="L54" s="15" t="s">
-        <v>226</v>
+        <v>1216701.9699999997</v>
+      </c>
+      <c r="K54" s="14">
+        <v>45286</v>
+      </c>
+      <c r="L54" s="14">
+        <v>46098</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
@@ -4463,7 +4493,7 @@
         <v>229</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E55" s="11" t="s">
         <v>230</v>
@@ -4472,22 +4502,22 @@
         <v>231</v>
       </c>
       <c r="G55" s="11">
-        <v>0.9754</v>
+        <v>0</v>
       </c>
       <c r="H55" s="12">
-        <v>56189486.28</v>
+        <v>11620104.78</v>
       </c>
       <c r="I55" s="13">
-        <v>54809333.5</v>
+        <v>0</v>
       </c>
       <c r="J55" s="12">
-        <v>1380152.7800000012</v>
-      </c>
-      <c r="K55" s="14">
-        <v>45035</v>
-      </c>
-      <c r="L55" s="14">
-        <v>46360</v>
+        <v>11620104.78</v>
+      </c>
+      <c r="K55" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="L55" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
@@ -4501,7 +4531,7 @@
         <v>234</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E56" s="11" t="s">
         <v>235</v>
@@ -4510,141 +4540,141 @@
         <v>236</v>
       </c>
       <c r="G56" s="11">
-        <v>1</v>
+        <v>0.8714</v>
       </c>
       <c r="H56" s="12">
-        <v>4374443.78</v>
+        <v>62900387.42</v>
       </c>
       <c r="I56" s="13">
-        <v>4374443.78</v>
+        <v>54809333.5</v>
       </c>
       <c r="J56" s="12">
-        <v>0</v>
+        <v>8091053.920000002</v>
       </c>
       <c r="K56" s="14">
-        <v>44707</v>
+        <v>45035</v>
       </c>
       <c r="L56" s="14">
-        <v>45488</v>
+        <v>46360</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>112</v>
+        <v>239</v>
       </c>
       <c r="D57" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>22</v>
+        <v>241</v>
       </c>
       <c r="G57" s="11">
-        <v>0.9994</v>
+        <v>1</v>
       </c>
       <c r="H57" s="12">
-        <v>14995089.28</v>
+        <v>4374443.78</v>
       </c>
       <c r="I57" s="13">
-        <v>14985558.45</v>
+        <v>4374443.78</v>
       </c>
       <c r="J57" s="12">
-        <v>9530.830000000075</v>
+        <v>0</v>
       </c>
       <c r="K57" s="14">
-        <v>44719</v>
+        <v>44707</v>
       </c>
       <c r="L57" s="14">
-        <v>45476</v>
+        <v>45488</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="11" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>240</v>
+        <v>118</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>241</v>
+        <v>15</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>236</v>
+        <v>22</v>
       </c>
       <c r="G58" s="11">
-        <v>0.8652</v>
+        <v>0.9994</v>
       </c>
       <c r="H58" s="12">
-        <v>8463890.94</v>
+        <v>14995089.28</v>
       </c>
       <c r="I58" s="13">
-        <v>7322834.12</v>
+        <v>14985558.45</v>
       </c>
       <c r="J58" s="12">
-        <v>1141056.8199999994</v>
+        <v>9530.830000000075</v>
       </c>
       <c r="K58" s="14">
-        <v>44688</v>
+        <v>44719</v>
       </c>
       <c r="L58" s="14">
-        <v>46045</v>
+        <v>45476</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="11" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G59" s="11">
-        <v>0.4113</v>
+        <v>0.8652</v>
       </c>
       <c r="H59" s="12">
-        <v>30477728.43</v>
+        <v>8463890.94</v>
       </c>
       <c r="I59" s="13">
-        <v>12534756.7</v>
+        <v>7322834.12</v>
       </c>
       <c r="J59" s="12">
-        <v>17942971.73</v>
+        <v>1141056.8199999994</v>
       </c>
       <c r="K59" s="14">
-        <v>44708</v>
+        <v>44688</v>
       </c>
       <c r="L59" s="14">
-        <v>45437</v>
+        <v>46045</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="11" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>248</v>
@@ -4653,7 +4683,7 @@
         <v>249</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E60" s="11" t="s">
         <v>250</v>
@@ -4662,22 +4692,22 @@
         <v>251</v>
       </c>
       <c r="G60" s="11">
-        <v>0.97</v>
+        <v>0.4113</v>
       </c>
       <c r="H60" s="12">
-        <v>5722613.87</v>
+        <v>30477728.43</v>
       </c>
       <c r="I60" s="13">
-        <v>5551029.21</v>
+        <v>12534756.7</v>
       </c>
       <c r="J60" s="12">
-        <v>171584.66000000015</v>
+        <v>17942971.73</v>
       </c>
       <c r="K60" s="14">
-        <v>44727</v>
+        <v>44708</v>
       </c>
       <c r="L60" s="14">
-        <v>45489</v>
+        <v>45437</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -4691,7 +4721,7 @@
         <v>254</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E61" s="11" t="s">
         <v>255</v>
@@ -4700,22 +4730,22 @@
         <v>256</v>
       </c>
       <c r="G61" s="11">
-        <v>0.8092</v>
+        <v>0.97</v>
       </c>
       <c r="H61" s="12">
-        <v>51359899.57</v>
+        <v>5722613.87</v>
       </c>
       <c r="I61" s="13">
-        <v>41562191.24</v>
+        <v>5551029.21</v>
       </c>
       <c r="J61" s="12">
-        <v>9797708.329999998</v>
+        <v>171584.66000000015</v>
       </c>
       <c r="K61" s="14">
-        <v>45105</v>
+        <v>44727</v>
       </c>
       <c r="L61" s="14">
-        <v>45769</v>
+        <v>45489</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -4729,264 +4759,264 @@
         <v>259</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E62" s="11" t="s">
         <v>260</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>17</v>
+        <v>261</v>
       </c>
       <c r="G62" s="11">
-        <v>1</v>
+        <v>0.8092</v>
       </c>
       <c r="H62" s="12">
-        <v>6948720.19</v>
+        <v>51359899.57</v>
       </c>
       <c r="I62" s="13">
-        <v>6948720.19</v>
+        <v>41562191.24</v>
       </c>
       <c r="J62" s="12">
-        <v>0</v>
+        <v>9797708.329999998</v>
       </c>
       <c r="K62" s="14">
-        <v>44882</v>
+        <v>45105</v>
       </c>
       <c r="L62" s="14">
-        <v>45147</v>
+        <v>45769</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="11" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D63" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>264</v>
+        <v>17</v>
       </c>
       <c r="G63" s="11">
-        <v>0.9765999999999999</v>
+        <v>1</v>
       </c>
       <c r="H63" s="12">
-        <v>3107538.75</v>
+        <v>6948720.19</v>
       </c>
       <c r="I63" s="13">
-        <v>3034704.58</v>
+        <v>6948720.19</v>
       </c>
       <c r="J63" s="12">
-        <v>72834.16999999993</v>
+        <v>0</v>
       </c>
       <c r="K63" s="14">
-        <v>44536</v>
+        <v>44882</v>
       </c>
       <c r="L63" s="14">
-        <v>45386</v>
+        <v>45147</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="11" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D64" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G64" s="11">
-        <v>0.9577</v>
+        <v>0.9765999999999999</v>
       </c>
       <c r="H64" s="12">
-        <v>2994510.29</v>
+        <v>3107538.75</v>
       </c>
       <c r="I64" s="13">
-        <v>2867705.32</v>
+        <v>3034704.58</v>
       </c>
       <c r="J64" s="12">
-        <v>126804.9700000002</v>
+        <v>72834.16999999993</v>
       </c>
       <c r="K64" s="14">
-        <v>44804</v>
+        <v>44536</v>
       </c>
       <c r="L64" s="14">
-        <v>45208</v>
+        <v>45386</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="11" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>63</v>
+        <v>271</v>
       </c>
       <c r="D65" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>93</v>
+        <v>273</v>
       </c>
       <c r="G65" s="11">
-        <v>0.8787</v>
+        <v>0.9577</v>
       </c>
       <c r="H65" s="12">
-        <v>6519257.05</v>
+        <v>2994510.29</v>
       </c>
       <c r="I65" s="13">
-        <v>5728240.86</v>
+        <v>2867705.32</v>
       </c>
       <c r="J65" s="12">
-        <v>791016.1899999995</v>
+        <v>126804.9700000002</v>
       </c>
       <c r="K65" s="14">
         <v>44804</v>
       </c>
       <c r="L65" s="14">
-        <v>45569</v>
+        <v>45208</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="11" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>272</v>
+        <v>63</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="G66" s="11">
-        <v>0.545</v>
+        <v>0.8787</v>
       </c>
       <c r="H66" s="12">
-        <v>2069000</v>
+        <v>6519257.05</v>
       </c>
       <c r="I66" s="13">
-        <v>1127516.06</v>
+        <v>5728240.86</v>
       </c>
       <c r="J66" s="12">
-        <v>941483.94</v>
+        <v>791016.1899999995</v>
       </c>
       <c r="K66" s="14">
-        <v>45972</v>
+        <v>44804</v>
       </c>
       <c r="L66" s="14">
-        <v>46167</v>
+        <v>45569</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="11" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D67" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G67" s="11">
-        <v>0.6604000000000001</v>
+        <v>0.545</v>
       </c>
       <c r="H67" s="12">
-        <v>12950372.72</v>
+        <v>2069000</v>
       </c>
       <c r="I67" s="13">
-        <v>8552770.91</v>
+        <v>1127516.06</v>
       </c>
       <c r="J67" s="12">
-        <v>4397601.8100000005</v>
+        <v>941483.94</v>
       </c>
       <c r="K67" s="14">
-        <v>44742</v>
+        <v>45972</v>
       </c>
       <c r="L67" s="14">
-        <v>46219</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" s="11" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>280</v>
+        <v>45</v>
       </c>
       <c r="G68" s="11">
-        <v>0.47490000000000004</v>
+        <v>0.6604000000000001</v>
       </c>
       <c r="H68" s="12">
-        <v>18996888.26</v>
+        <v>12950372.72</v>
       </c>
       <c r="I68" s="13">
-        <v>9021796.75</v>
+        <v>8552770.91</v>
       </c>
       <c r="J68" s="12">
-        <v>9975091.510000002</v>
-      </c>
-      <c r="K68" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="L68" s="15" t="s">
-        <v>226</v>
+        <v>4397601.8100000005</v>
+      </c>
+      <c r="K68" s="14">
+        <v>44742</v>
+      </c>
+      <c r="L68" s="14">
+        <v>46219</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="11" t="s">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>282</v>
@@ -4995,7 +5025,7 @@
         <v>283</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E69" s="11" t="s">
         <v>284</v>
@@ -5004,65 +5034,65 @@
         <v>285</v>
       </c>
       <c r="G69" s="11">
-        <v>0.9969</v>
+        <v>0.47490000000000004</v>
       </c>
       <c r="H69" s="12">
-        <v>25179808.67</v>
+        <v>18996888.26</v>
       </c>
       <c r="I69" s="13">
-        <v>25102278.03</v>
+        <v>9021796.75</v>
       </c>
       <c r="J69" s="12">
-        <v>77530.6400000006</v>
-      </c>
-      <c r="K69" s="14">
-        <v>45646</v>
-      </c>
-      <c r="L69" s="14">
-        <v>46005</v>
+        <v>9975091.510000002</v>
+      </c>
+      <c r="K69" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="L69" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" s="11" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D70" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G70" s="11">
-        <v>0.8062999999999999</v>
+        <v>0.9969</v>
       </c>
       <c r="H70" s="12">
-        <v>8811881.78</v>
+        <v>25179808.67</v>
       </c>
       <c r="I70" s="13">
-        <v>7104640.05</v>
+        <v>25102278.03</v>
       </c>
       <c r="J70" s="12">
-        <v>1707241.7299999995</v>
+        <v>77530.6400000006</v>
       </c>
       <c r="K70" s="14">
-        <v>45360</v>
+        <v>45646</v>
       </c>
       <c r="L70" s="14">
-        <v>45566</v>
+        <v>46005</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" s="11" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>291</v>
@@ -5080,331 +5110,331 @@
         <v>294</v>
       </c>
       <c r="G71" s="11">
-        <v>1</v>
+        <v>0.8062999999999999</v>
       </c>
       <c r="H71" s="12">
-        <v>724764.22</v>
+        <v>8811881.78</v>
       </c>
       <c r="I71" s="13">
-        <v>724764.22</v>
+        <v>7104640.05</v>
       </c>
       <c r="J71" s="12">
-        <v>0</v>
+        <v>1707241.7299999995</v>
       </c>
       <c r="K71" s="14">
-        <v>44911</v>
+        <v>45360</v>
       </c>
       <c r="L71" s="14">
-        <v>45182</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" s="11" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>45</v>
+        <v>299</v>
       </c>
       <c r="G72" s="11">
-        <v>0.8592</v>
+        <v>1</v>
       </c>
       <c r="H72" s="12">
-        <v>34662990.03</v>
+        <v>724764.22</v>
       </c>
       <c r="I72" s="13">
-        <v>29783877.3</v>
+        <v>724764.22</v>
       </c>
       <c r="J72" s="12">
-        <v>4879112.73</v>
+        <v>0</v>
       </c>
       <c r="K72" s="14">
-        <v>45155</v>
+        <v>44911</v>
       </c>
       <c r="L72" s="14">
-        <v>46239</v>
+        <v>45182</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" s="11" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>241</v>
+        <v>34</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>148</v>
+        <v>45</v>
       </c>
       <c r="G73" s="11">
-        <v>0.07</v>
+        <v>0.8592</v>
       </c>
       <c r="H73" s="12">
-        <v>27739392.32</v>
+        <v>34662990.03</v>
       </c>
       <c r="I73" s="13">
-        <v>1940441.71</v>
+        <v>29783877.3</v>
       </c>
       <c r="J73" s="12">
-        <v>25798950.61</v>
+        <v>4879112.73</v>
       </c>
       <c r="K73" s="14">
-        <v>45541</v>
+        <v>45155</v>
       </c>
       <c r="L73" s="14">
-        <v>46081</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" s="11" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>15</v>
+        <v>246</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>305</v>
+        <v>154</v>
       </c>
       <c r="G74" s="11">
-        <v>0.8991</v>
+        <v>0.07</v>
       </c>
       <c r="H74" s="12">
-        <v>666913.68</v>
+        <v>27739392.32</v>
       </c>
       <c r="I74" s="13">
-        <v>599641.31</v>
+        <v>1940441.71</v>
       </c>
       <c r="J74" s="12">
-        <v>67272.37</v>
+        <v>25798950.61</v>
       </c>
       <c r="K74" s="14">
-        <v>45783</v>
+        <v>45541</v>
       </c>
       <c r="L74" s="14">
-        <v>45964</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" s="11" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E75" s="11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="G75" s="11">
-        <v>0.8976000000000001</v>
+        <v>0.8991</v>
       </c>
       <c r="H75" s="12">
-        <v>763285.07</v>
+        <v>666913.68</v>
       </c>
       <c r="I75" s="13">
-        <v>685145.56</v>
+        <v>599641.31</v>
       </c>
       <c r="J75" s="12">
-        <v>78139.5099999999</v>
+        <v>67272.37</v>
       </c>
       <c r="K75" s="14">
         <v>45783</v>
       </c>
       <c r="L75" s="14">
-        <v>46115</v>
+        <v>45964</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="11" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C76" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="D76" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E76" s="11" t="s">
+        <v>313</v>
+      </c>
+      <c r="F76" s="11" t="s">
         <v>310</v>
       </c>
-      <c r="D76" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E76" s="11" t="s">
-        <v>311</v>
-      </c>
-      <c r="F76" s="11" t="s">
-        <v>73</v>
-      </c>
       <c r="G76" s="11">
-        <v>0.9495</v>
+        <v>0.8976000000000001</v>
       </c>
       <c r="H76" s="12">
-        <v>32836774.76</v>
+        <v>763285.07</v>
       </c>
       <c r="I76" s="13">
-        <v>31178236.21</v>
+        <v>685145.56</v>
       </c>
       <c r="J76" s="12">
-        <v>1658538.5500000007</v>
+        <v>78139.5099999999</v>
       </c>
       <c r="K76" s="14">
-        <v>44564</v>
+        <v>45783</v>
       </c>
       <c r="L76" s="14">
-        <v>44944</v>
+        <v>46115</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="11" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D77" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E77" s="11" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F77" s="11" t="s">
-        <v>164</v>
+        <v>73</v>
       </c>
       <c r="G77" s="11">
-        <v>0.9543</v>
+        <v>0.9495</v>
       </c>
       <c r="H77" s="12">
-        <v>36880209</v>
+        <v>32836774.76</v>
       </c>
       <c r="I77" s="13">
-        <v>35196032.93</v>
+        <v>31178236.21</v>
       </c>
       <c r="J77" s="12">
-        <v>1684176.0700000003</v>
+        <v>1658538.5500000007</v>
       </c>
       <c r="K77" s="14">
-        <v>44648</v>
+        <v>44564</v>
       </c>
       <c r="L77" s="14">
-        <v>45498</v>
+        <v>44944</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="11" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E78" s="11" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F78" s="11" t="s">
-        <v>318</v>
+        <v>170</v>
       </c>
       <c r="G78" s="11">
-        <v>0.0134</v>
+        <v>0.9543</v>
       </c>
       <c r="H78" s="12">
-        <v>4705907.3</v>
+        <v>36880209</v>
       </c>
       <c r="I78" s="13">
-        <v>63006.28</v>
+        <v>35196032.93</v>
       </c>
       <c r="J78" s="12">
-        <v>4642901.02</v>
+        <v>1684176.0700000003</v>
       </c>
       <c r="K78" s="14">
-        <v>46009</v>
+        <v>44648</v>
       </c>
       <c r="L78" s="14">
-        <v>46189</v>
+        <v>45498</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="11" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D79" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E79" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F79" s="11" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G79" s="11">
-        <v>0.5292</v>
+        <v>0.0134</v>
       </c>
       <c r="H79" s="12">
-        <v>10349390.52</v>
+        <v>4705907.3</v>
       </c>
       <c r="I79" s="13">
-        <v>5476795.79</v>
+        <v>63006.28</v>
       </c>
       <c r="J79" s="12">
-        <v>4872594.7299999995</v>
+        <v>4642901.02</v>
       </c>
       <c r="K79" s="14">
-        <v>45867</v>
+        <v>46009</v>
       </c>
       <c r="L79" s="14">
-        <v>46227</v>
+        <v>46189</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" s="11" t="s">
-        <v>323</v>
+        <v>306</v>
       </c>
       <c r="B80" s="11" t="s">
         <v>324</v>
@@ -5413,561 +5443,561 @@
         <v>325</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E80" s="11" t="s">
         <v>326</v>
       </c>
       <c r="F80" s="11" t="s">
-        <v>305</v>
+        <v>327</v>
       </c>
       <c r="G80" s="11">
-        <v>1</v>
+        <v>0.5292</v>
       </c>
       <c r="H80" s="12">
-        <v>1923627.23</v>
+        <v>10349390.52</v>
       </c>
       <c r="I80" s="13">
-        <v>1923627.26</v>
+        <v>5476795.79</v>
       </c>
       <c r="J80" s="12">
-        <v>-0.030000000027939677</v>
+        <v>4872594.7299999995</v>
       </c>
       <c r="K80" s="14">
-        <v>44708</v>
+        <v>45867</v>
       </c>
       <c r="L80" s="14">
-        <v>45640</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" s="11" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D81" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E81" s="11" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F81" s="11" t="s">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="G81" s="11">
         <v>1</v>
       </c>
       <c r="H81" s="12">
-        <v>3552093.82</v>
+        <v>1923627.23</v>
       </c>
       <c r="I81" s="13">
-        <v>3552073.13</v>
+        <v>1923627.26</v>
       </c>
       <c r="J81" s="12">
-        <v>20.68999999994412</v>
+        <v>-0.030000000027939677</v>
       </c>
       <c r="K81" s="14">
-        <v>45034</v>
+        <v>44708</v>
       </c>
       <c r="L81" s="14">
-        <v>45034</v>
+        <v>45640</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" s="11" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>249</v>
+        <v>333</v>
       </c>
       <c r="D82" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E82" s="11" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>22</v>
+        <v>335</v>
       </c>
       <c r="G82" s="11">
-        <v>0.9723</v>
+        <v>1</v>
       </c>
       <c r="H82" s="12">
-        <v>15078640.21</v>
+        <v>3552093.82</v>
       </c>
       <c r="I82" s="13">
-        <v>14660282.37</v>
+        <v>3552073.13</v>
       </c>
       <c r="J82" s="12">
-        <v>418357.8400000017</v>
+        <v>20.68999999994412</v>
       </c>
       <c r="K82" s="14">
-        <v>45497</v>
+        <v>45034</v>
       </c>
       <c r="L82" s="14">
-        <v>45301</v>
+        <v>45034</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" s="11" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>334</v>
+        <v>254</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E83" s="11" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F83" s="11" t="s">
-        <v>336</v>
+        <v>22</v>
       </c>
       <c r="G83" s="11">
-        <v>0.948</v>
+        <v>0.9723</v>
       </c>
       <c r="H83" s="12">
-        <v>59148617.81</v>
+        <v>15078640.21</v>
       </c>
       <c r="I83" s="13">
-        <v>56075178.64</v>
+        <v>14660282.37</v>
       </c>
       <c r="J83" s="12">
-        <v>3073439.170000002</v>
+        <v>418357.8400000017</v>
       </c>
       <c r="K83" s="14">
-        <v>44726</v>
+        <v>45497</v>
       </c>
       <c r="L83" s="14">
-        <v>46006</v>
+        <v>45301</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" s="11" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="B84" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="C84" s="11"/>
+      <c r="C84" s="11" t="s">
+        <v>339</v>
+      </c>
       <c r="D84" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E84" s="11" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F84" s="11" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G84" s="11">
-        <v>0</v>
+        <v>0.948</v>
       </c>
       <c r="H84" s="12">
-        <v>62980000</v>
+        <v>59148617.81</v>
       </c>
       <c r="I84" s="13">
-        <v>62980000</v>
+        <v>56075178.64</v>
       </c>
       <c r="J84" s="12">
-        <v>0</v>
+        <v>3073439.170000002</v>
       </c>
       <c r="K84" s="14">
-        <v>43930</v>
+        <v>44726</v>
       </c>
       <c r="L84" s="14">
-        <v>44011</v>
+        <v>46006</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" s="11" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>341</v>
-      </c>
-      <c r="C85" s="11" t="s">
-        <v>342</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="C85" s="11"/>
       <c r="D85" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E85" s="11" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F85" s="11" t="s">
-        <v>202</v>
+        <v>345</v>
       </c>
       <c r="G85" s="11">
-        <v>0.9976999999999999</v>
+        <v>0</v>
       </c>
       <c r="H85" s="12">
-        <v>19451386.88</v>
+        <v>62980000</v>
       </c>
       <c r="I85" s="13">
-        <v>19406169.39</v>
+        <v>62980000</v>
       </c>
       <c r="J85" s="12">
-        <v>45217.48999999836</v>
+        <v>0</v>
       </c>
       <c r="K85" s="14">
-        <v>45247</v>
+        <v>43930</v>
       </c>
       <c r="L85" s="14">
-        <v>46001</v>
+        <v>44011</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" s="11" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E86" s="11" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F86" s="11" t="s">
-        <v>40</v>
+        <v>208</v>
       </c>
       <c r="G86" s="11">
-        <v>0.9666</v>
+        <v>0.9976999999999999</v>
       </c>
       <c r="H86" s="12">
-        <v>20106028.53</v>
+        <v>19451386.88</v>
       </c>
       <c r="I86" s="13">
-        <v>19434508.22</v>
+        <v>19406169.39</v>
       </c>
       <c r="J86" s="12">
-        <v>671520.3100000024</v>
+        <v>45217.48999999836</v>
       </c>
       <c r="K86" s="14">
-        <v>44991</v>
+        <v>45247</v>
       </c>
       <c r="L86" s="14">
-        <v>46094</v>
+        <v>46001</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" s="11" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>138</v>
+        <v>350</v>
       </c>
       <c r="D87" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E87" s="11" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F87" s="11" t="s">
-        <v>157</v>
+        <v>40</v>
       </c>
       <c r="G87" s="11">
-        <v>0.9577</v>
+        <v>0.9666</v>
       </c>
       <c r="H87" s="12">
-        <v>34508101.15</v>
+        <v>20106028.53</v>
       </c>
       <c r="I87" s="13">
-        <v>33048630.33</v>
+        <v>19434508.22</v>
       </c>
       <c r="J87" s="12">
-        <v>1459470.8200000003</v>
+        <v>671520.3100000024</v>
       </c>
       <c r="K87" s="14">
-        <v>44690</v>
+        <v>44991</v>
       </c>
       <c r="L87" s="14">
-        <v>45621</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" s="11" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>350</v>
+        <v>144</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E88" s="11" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F88" s="11" t="s">
-        <v>352</v>
+        <v>163</v>
       </c>
       <c r="G88" s="11">
-        <v>0.9711</v>
+        <v>0.9577</v>
       </c>
       <c r="H88" s="12">
-        <v>58086688.76</v>
+        <v>34508101.15</v>
       </c>
       <c r="I88" s="13">
-        <v>56408550.91</v>
+        <v>33048630.33</v>
       </c>
       <c r="J88" s="12">
-        <v>1678137.8500000015</v>
+        <v>1459470.8200000003</v>
       </c>
       <c r="K88" s="14">
-        <v>44831</v>
+        <v>44690</v>
       </c>
       <c r="L88" s="14">
-        <v>45619</v>
+        <v>45621</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" s="11" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D89" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E89" s="11" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F89" s="11" t="s">
-        <v>216</v>
+        <v>357</v>
       </c>
       <c r="G89" s="11">
-        <v>0.6973</v>
+        <v>0.9711</v>
       </c>
       <c r="H89" s="12">
-        <v>28459856.91</v>
+        <v>58086688.76</v>
       </c>
       <c r="I89" s="13">
-        <v>19844966.58</v>
+        <v>56408550.91</v>
       </c>
       <c r="J89" s="12">
-        <v>8614890.330000002</v>
+        <v>1678137.8500000015</v>
       </c>
       <c r="K89" s="14">
-        <v>45035</v>
+        <v>44831</v>
       </c>
       <c r="L89" s="14">
-        <v>46205</v>
+        <v>45619</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" s="11" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D90" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E90" s="11" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F90" s="11" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="G90" s="11">
-        <v>0.7805</v>
+        <v>0.6973</v>
       </c>
       <c r="H90" s="12">
-        <v>45862409.69</v>
+        <v>28459856.91</v>
       </c>
       <c r="I90" s="13">
-        <v>35796161.98</v>
+        <v>19844966.58</v>
       </c>
       <c r="J90" s="12">
-        <v>10066247.71</v>
+        <v>8614890.330000002</v>
       </c>
       <c r="K90" s="14">
-        <v>45352</v>
+        <v>45035</v>
       </c>
       <c r="L90" s="14">
-        <v>46255</v>
+        <v>46205</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" s="11" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D91" s="11" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E91" s="11" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F91" s="11" t="s">
-        <v>157</v>
+        <v>212</v>
       </c>
       <c r="G91" s="11">
-        <v>0.0132</v>
+        <v>0.7805</v>
       </c>
       <c r="H91" s="12">
-        <v>11494433.26</v>
+        <v>45862409.69</v>
       </c>
       <c r="I91" s="13">
-        <v>151285.62</v>
+        <v>35796161.98</v>
       </c>
       <c r="J91" s="12">
-        <v>11343147.64</v>
+        <v>10066247.71</v>
       </c>
       <c r="K91" s="14">
-        <v>45105</v>
+        <v>45352</v>
       </c>
       <c r="L91" s="14">
-        <v>45706</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" s="11" t="s">
-        <v>362</v>
+        <v>342</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>172</v>
+        <v>365</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E92" s="11" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F92" s="11" t="s">
-        <v>365</v>
+        <v>163</v>
       </c>
       <c r="G92" s="11">
-        <v>0.898</v>
+        <v>0.0132</v>
       </c>
       <c r="H92" s="12">
-        <v>1212482.21</v>
+        <v>11494433.26</v>
       </c>
       <c r="I92" s="13">
-        <v>1088826.01</v>
+        <v>151285.62</v>
       </c>
       <c r="J92" s="12">
-        <v>123656.19999999995</v>
+        <v>11343147.64</v>
       </c>
       <c r="K92" s="14">
-        <v>44326</v>
+        <v>45105</v>
       </c>
       <c r="L92" s="14">
-        <v>44536</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" s="11" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>367</v>
+        <v>178</v>
       </c>
       <c r="D93" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E93" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F93" s="11" t="s">
-        <v>57</v>
+        <v>370</v>
       </c>
       <c r="G93" s="11">
-        <v>0.9209</v>
+        <v>0.898</v>
       </c>
       <c r="H93" s="12">
-        <v>12560309.12</v>
+        <v>1212482.21</v>
       </c>
       <c r="I93" s="13">
-        <v>11566432.39</v>
+        <v>1088826.01</v>
       </c>
       <c r="J93" s="12">
-        <v>993876.7299999986</v>
+        <v>123656.19999999995</v>
       </c>
       <c r="K93" s="14">
-        <v>44831</v>
+        <v>44326</v>
       </c>
       <c r="L93" s="14">
-        <v>45477</v>
+        <v>44536</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" s="11" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D94" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E94" s="11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F94" s="11" t="s">
-        <v>373</v>
+        <v>57</v>
       </c>
       <c r="G94" s="11">
-        <v>0.9990000000000001</v>
+        <v>0.9209</v>
       </c>
       <c r="H94" s="12">
-        <v>17695067.23</v>
+        <v>12560309.12</v>
       </c>
       <c r="I94" s="13">
-        <v>17677149.84</v>
+        <v>11566432.39</v>
       </c>
       <c r="J94" s="12">
-        <v>17917.390000000596</v>
+        <v>993876.7299999986</v>
       </c>
       <c r="K94" s="14">
-        <v>44994</v>
+        <v>44831</v>
       </c>
       <c r="L94" s="14">
-        <v>45928</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -5978,381 +6008,381 @@
         <v>375</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>95</v>
+        <v>376</v>
       </c>
       <c r="D95" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E95" s="11" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F95" s="11" t="s">
-        <v>17</v>
+        <v>378</v>
       </c>
       <c r="G95" s="11">
-        <v>1</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="H95" s="12">
-        <v>12092480.69</v>
+        <v>17695067.23</v>
       </c>
       <c r="I95" s="13">
-        <v>12092480.69</v>
+        <v>17677149.84</v>
       </c>
       <c r="J95" s="12">
-        <v>0</v>
+        <v>17917.390000000596</v>
       </c>
       <c r="K95" s="14">
-        <v>44734</v>
+        <v>44994</v>
       </c>
       <c r="L95" s="14">
-        <v>45202</v>
+        <v>45928</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" s="11" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="D96" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E96" s="11" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="F96" s="11" t="s">
-        <v>379</v>
+        <v>17</v>
       </c>
       <c r="G96" s="11">
-        <v>0.9117000000000001</v>
+        <v>1</v>
       </c>
       <c r="H96" s="12">
-        <v>5978542.15</v>
+        <v>12092480.69</v>
       </c>
       <c r="I96" s="13">
-        <v>5450477.04</v>
+        <v>12092480.69</v>
       </c>
       <c r="J96" s="12">
-        <v>528065.1100000003</v>
+        <v>0</v>
       </c>
       <c r="K96" s="14">
-        <v>44753</v>
+        <v>44734</v>
       </c>
       <c r="L96" s="14">
-        <v>44933</v>
+        <v>45202</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" s="11" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>381</v>
+        <v>126</v>
       </c>
       <c r="D97" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E97" s="11" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F97" s="11" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G97" s="11">
-        <v>0.8362</v>
+        <v>0.9117000000000001</v>
       </c>
       <c r="H97" s="12">
-        <v>11942741.09</v>
+        <v>5978542.15</v>
       </c>
       <c r="I97" s="13">
-        <v>9986334.63</v>
+        <v>5450477.04</v>
       </c>
       <c r="J97" s="12">
-        <v>1956406.459999999</v>
+        <v>528065.1100000003</v>
       </c>
       <c r="K97" s="14">
-        <v>44734</v>
+        <v>44753</v>
       </c>
       <c r="L97" s="14">
-        <v>45098</v>
+        <v>44933</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" s="11" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D98" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E98" s="11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F98" s="11" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="G98" s="11">
-        <v>0.9493</v>
+        <v>0.8362</v>
       </c>
       <c r="H98" s="12">
-        <v>48302952.43</v>
+        <v>11942741.09</v>
       </c>
       <c r="I98" s="13">
-        <v>45853223.3</v>
+        <v>9986334.63</v>
       </c>
       <c r="J98" s="12">
-        <v>2449729.1300000027</v>
+        <v>1956406.459999999</v>
       </c>
       <c r="K98" s="14">
-        <v>45189</v>
+        <v>44734</v>
       </c>
       <c r="L98" s="14">
-        <v>45729</v>
+        <v>45098</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" s="11" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D99" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E99" s="11" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F99" s="11" t="s">
-        <v>390</v>
+        <v>285</v>
       </c>
       <c r="G99" s="11">
-        <v>0.9181999999999999</v>
+        <v>0.7289</v>
       </c>
       <c r="H99" s="12">
-        <v>30543662.31</v>
+        <v>8684179.36</v>
       </c>
       <c r="I99" s="13">
-        <v>28044628.6</v>
+        <v>6330271.19</v>
       </c>
       <c r="J99" s="12">
-        <v>2499033.709999997</v>
+        <v>2353908.169999999</v>
       </c>
       <c r="K99" s="14">
-        <v>44826</v>
+        <v>45848</v>
       </c>
       <c r="L99" s="14">
-        <v>45540</v>
+        <v>46222</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" s="11" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D100" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E100" s="11" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F100" s="11" t="s">
-        <v>280</v>
+        <v>388</v>
       </c>
       <c r="G100" s="11">
-        <v>0.6526000000000001</v>
+        <v>0.9493</v>
       </c>
       <c r="H100" s="12">
-        <v>8684179.36</v>
+        <v>48302952.43</v>
       </c>
       <c r="I100" s="13">
-        <v>5666949.72</v>
+        <v>45853223.3</v>
       </c>
       <c r="J100" s="12">
-        <v>3017229.6399999997</v>
+        <v>2449729.1300000027</v>
       </c>
       <c r="K100" s="14">
-        <v>45848</v>
+        <v>45189</v>
       </c>
       <c r="L100" s="14">
-        <v>46222</v>
+        <v>45729</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" s="11" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D101" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E101" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F101" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G101" s="11">
-        <v>0.9188</v>
+        <v>0.9181999999999999</v>
       </c>
       <c r="H101" s="12">
-        <v>54913544.95</v>
+        <v>30543662.31</v>
       </c>
       <c r="I101" s="13">
-        <v>50454918.61</v>
+        <v>28044628.6</v>
       </c>
       <c r="J101" s="12">
-        <v>4458626.340000004</v>
+        <v>2499033.709999997</v>
       </c>
       <c r="K101" s="14">
-        <v>44769</v>
+        <v>44826</v>
       </c>
       <c r="L101" s="14">
-        <v>45174</v>
+        <v>45540</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" s="11" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D102" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E102" s="11" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F102" s="11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G102" s="11">
-        <v>0.7935</v>
+        <v>0.9188</v>
       </c>
       <c r="H102" s="12">
-        <v>27434724</v>
+        <v>54913544.95</v>
       </c>
       <c r="I102" s="13">
-        <v>21770451.06</v>
+        <v>50454918.61</v>
       </c>
       <c r="J102" s="12">
-        <v>5664272.940000001</v>
+        <v>4458626.340000004</v>
       </c>
       <c r="K102" s="14">
-        <v>46002</v>
+        <v>44769</v>
       </c>
       <c r="L102" s="14">
-        <v>46242</v>
+        <v>45174</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" s="11" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D103" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E103" s="11" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F103" s="11" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="G103" s="11">
-        <v>0.9224</v>
+        <v>0.7935</v>
       </c>
       <c r="H103" s="12">
-        <v>80552394.92</v>
+        <v>27434724</v>
       </c>
       <c r="I103" s="13">
-        <v>74305045.47</v>
+        <v>21770451.06</v>
       </c>
       <c r="J103" s="12">
-        <v>6247349.450000003</v>
+        <v>5664272.940000001</v>
       </c>
       <c r="K103" s="14">
-        <v>44709</v>
+        <v>46002</v>
       </c>
       <c r="L103" s="14">
-        <v>45114</v>
+        <v>46242</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" s="11" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D104" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E104" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F104" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G104" s="11">
-        <v>0.4476</v>
+        <v>0.9224</v>
       </c>
       <c r="H104" s="12">
-        <v>68148567.14</v>
+        <v>80552394.92</v>
       </c>
       <c r="I104" s="13">
-        <v>30502735.41</v>
+        <v>74305045.47</v>
       </c>
       <c r="J104" s="12">
-        <v>37645831.730000004</v>
+        <v>6247349.450000003</v>
       </c>
       <c r="K104" s="14">
-        <v>44767</v>
+        <v>44709</v>
       </c>
       <c r="L104" s="14">
-        <v>45173</v>
+        <v>45114</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" s="11" t="s">
-        <v>410</v>
+        <v>379</v>
       </c>
       <c r="B105" s="11" t="s">
         <v>411</v>
@@ -6370,217 +6400,217 @@
         <v>414</v>
       </c>
       <c r="G105" s="11">
-        <v>0.9984000000000001</v>
+        <v>0.4476</v>
       </c>
       <c r="H105" s="12">
-        <v>1498793.43</v>
+        <v>68148567.14</v>
       </c>
       <c r="I105" s="13">
-        <v>1496414.32</v>
+        <v>30502735.41</v>
       </c>
       <c r="J105" s="12">
-        <v>2379.1099999998696</v>
+        <v>37645831.730000004</v>
       </c>
       <c r="K105" s="14">
-        <v>45195</v>
+        <v>44767</v>
       </c>
       <c r="L105" s="14">
-        <v>45121</v>
+        <v>45173</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" s="11" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D106" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E106" s="11" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F106" s="11" t="s">
-        <v>294</v>
+        <v>419</v>
       </c>
       <c r="G106" s="11">
-        <v>0.9718000000000001</v>
+        <v>0.9984000000000001</v>
       </c>
       <c r="H106" s="12">
-        <v>1988555.07</v>
+        <v>1498793.43</v>
       </c>
       <c r="I106" s="13">
-        <v>1932548.63</v>
+        <v>1496414.32</v>
       </c>
       <c r="J106" s="12">
-        <v>56006.44000000018</v>
+        <v>2379.1099999998696</v>
       </c>
       <c r="K106" s="14">
-        <v>44742</v>
+        <v>45195</v>
       </c>
       <c r="L106" s="14">
-        <v>45412</v>
+        <v>45121</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107" s="11" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D107" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E107" s="11" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F107" s="11" t="s">
-        <v>397</v>
+        <v>299</v>
       </c>
       <c r="G107" s="11">
-        <v>0.608</v>
+        <v>0.9718000000000001</v>
       </c>
       <c r="H107" s="12">
-        <v>2860442.12</v>
+        <v>1988555.07</v>
       </c>
       <c r="I107" s="13">
-        <v>1739254.2</v>
+        <v>1932548.63</v>
       </c>
       <c r="J107" s="12">
-        <v>1121187.9200000002</v>
+        <v>56006.44000000018</v>
       </c>
       <c r="K107" s="14">
-        <v>45782</v>
+        <v>44742</v>
       </c>
       <c r="L107" s="14">
-        <v>46083</v>
+        <v>45412</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108" s="11" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C108" s="11" t="s">
-        <v>403</v>
+        <v>424</v>
       </c>
       <c r="D108" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E108" s="11" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="F108" s="11" t="s">
-        <v>424</v>
+        <v>402</v>
       </c>
       <c r="G108" s="11">
-        <v>0.9998999999999999</v>
+        <v>0.608</v>
       </c>
       <c r="H108" s="12">
-        <v>5272095.08</v>
+        <v>2860442.12</v>
       </c>
       <c r="I108" s="13">
-        <v>5271693.21</v>
+        <v>1739254.2</v>
       </c>
       <c r="J108" s="12">
-        <v>401.87000000011176</v>
+        <v>1121187.9200000002</v>
       </c>
       <c r="K108" s="14">
-        <v>44746</v>
+        <v>45782</v>
       </c>
       <c r="L108" s="14">
-        <v>45560</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109" s="11" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>426</v>
+        <v>408</v>
       </c>
       <c r="D109" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E109" s="11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F109" s="11" t="s">
-        <v>294</v>
+        <v>429</v>
       </c>
       <c r="G109" s="11">
-        <v>0.9931</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="H109" s="12">
-        <v>1690234.37</v>
+        <v>5272095.08</v>
       </c>
       <c r="I109" s="13">
-        <v>1678610.19</v>
+        <v>5271693.21</v>
       </c>
       <c r="J109" s="12">
-        <v>11624.180000000168</v>
+        <v>401.87000000011176</v>
       </c>
       <c r="K109" s="14">
-        <v>44772</v>
+        <v>44746</v>
       </c>
       <c r="L109" s="14">
-        <v>45316</v>
+        <v>45560</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A110" s="11" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D110" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E110" s="11" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F110" s="11" t="s">
-        <v>431</v>
+        <v>299</v>
       </c>
       <c r="G110" s="11">
-        <v>0.9994</v>
+        <v>0.9931</v>
       </c>
       <c r="H110" s="12">
-        <v>26946699.36</v>
+        <v>1690234.37</v>
       </c>
       <c r="I110" s="13">
-        <v>26930984.02</v>
+        <v>1678610.19</v>
       </c>
       <c r="J110" s="12">
-        <v>15715.339999999851</v>
+        <v>11624.180000000168</v>
       </c>
       <c r="K110" s="14">
-        <v>44823</v>
+        <v>44772</v>
       </c>
       <c r="L110" s="14">
-        <v>45816</v>
+        <v>45316</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111" s="11" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="B111" s="11" t="s">
         <v>433</v>
@@ -6595,443 +6625,443 @@
         <v>435</v>
       </c>
       <c r="F111" s="11" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="G111" s="11">
-        <v>1</v>
+        <v>0.9994</v>
       </c>
       <c r="H111" s="12">
-        <v>3607367.42</v>
+        <v>26946699.36</v>
       </c>
       <c r="I111" s="13">
-        <v>3607318.65</v>
+        <v>26930984.02</v>
       </c>
       <c r="J111" s="12">
-        <v>48.77000000001863</v>
+        <v>15715.339999999851</v>
       </c>
       <c r="K111" s="14">
-        <v>45061</v>
+        <v>44823</v>
       </c>
       <c r="L111" s="14">
-        <v>45016</v>
+        <v>45816</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112" s="11" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C112" s="11" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D112" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E112" s="11" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="F112" s="11" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="G112" s="11">
-        <v>0.9958</v>
+        <v>1</v>
       </c>
       <c r="H112" s="12">
-        <v>4645152.25</v>
+        <v>3607367.42</v>
       </c>
       <c r="I112" s="13">
-        <v>4625557.49</v>
+        <v>3607318.65</v>
       </c>
       <c r="J112" s="12">
-        <v>19594.759999999776</v>
+        <v>48.77000000001863</v>
       </c>
       <c r="K112" s="14">
-        <v>44918</v>
+        <v>45061</v>
       </c>
       <c r="L112" s="14">
-        <v>45485</v>
+        <v>45016</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113" s="11" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D113" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E113" s="11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F113" s="11" t="s">
-        <v>443</v>
+        <v>429</v>
       </c>
       <c r="G113" s="11">
-        <v>1</v>
+        <v>0.9958</v>
       </c>
       <c r="H113" s="12">
-        <v>13242425.64</v>
+        <v>4645152.25</v>
       </c>
       <c r="I113" s="13">
-        <v>13242495.84</v>
+        <v>4625557.49</v>
       </c>
       <c r="J113" s="12">
-        <v>-70.19999999925494</v>
+        <v>19594.759999999776</v>
       </c>
       <c r="K113" s="14">
-        <v>44923</v>
+        <v>44918</v>
       </c>
       <c r="L113" s="14">
-        <v>45531</v>
+        <v>45485</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" s="11" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D114" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E114" s="11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F114" s="11" t="s">
-        <v>45</v>
+        <v>448</v>
       </c>
       <c r="G114" s="11">
         <v>1</v>
       </c>
       <c r="H114" s="12">
-        <v>20859068.44</v>
+        <v>13242425.64</v>
       </c>
       <c r="I114" s="13">
-        <v>20859068.44</v>
+        <v>13242495.84</v>
       </c>
       <c r="J114" s="12">
-        <v>0</v>
+        <v>-70.19999999925494</v>
       </c>
       <c r="K114" s="14">
-        <v>45007</v>
+        <v>44923</v>
       </c>
       <c r="L114" s="14">
-        <v>45851</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" s="11" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D115" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E115" s="11" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="F115" s="11" t="s">
-        <v>450</v>
+        <v>45</v>
       </c>
       <c r="G115" s="11">
-        <v>0.9842</v>
+        <v>1</v>
       </c>
       <c r="H115" s="12">
-        <v>20229149.79</v>
+        <v>20859068.44</v>
       </c>
       <c r="I115" s="13">
-        <v>19910398.37</v>
+        <v>20859068.44</v>
       </c>
       <c r="J115" s="12">
-        <v>318751.41999999806</v>
+        <v>0</v>
       </c>
       <c r="K115" s="14">
-        <v>44697</v>
+        <v>45007</v>
       </c>
       <c r="L115" s="14">
-        <v>45783</v>
+        <v>45851</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116" s="11" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E116" s="11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F116" s="11" t="s">
-        <v>40</v>
+        <v>455</v>
       </c>
       <c r="G116" s="11">
-        <v>0</v>
+        <v>0.9842</v>
       </c>
       <c r="H116" s="12">
-        <v>6784130.44</v>
+        <v>20229149.79</v>
       </c>
       <c r="I116" s="13">
-        <v>0</v>
+        <v>19910398.37</v>
       </c>
       <c r="J116" s="12">
-        <v>6784130.44</v>
+        <v>318751.41999999806</v>
       </c>
       <c r="K116" s="14">
-        <v>45100</v>
+        <v>44697</v>
       </c>
       <c r="L116" s="14">
-        <v>45400</v>
+        <v>45783</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117" s="11" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>334</v>
+        <v>457</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E117" s="11" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="F117" s="11" t="s">
-        <v>157</v>
+        <v>40</v>
       </c>
       <c r="G117" s="11">
-        <v>0.6605</v>
+        <v>0</v>
       </c>
       <c r="H117" s="12">
-        <v>20185137.81</v>
+        <v>6784130.44</v>
       </c>
       <c r="I117" s="13">
-        <v>13332401.6</v>
+        <v>0</v>
       </c>
       <c r="J117" s="12">
-        <v>6852736.209999999</v>
+        <v>6784130.44</v>
       </c>
       <c r="K117" s="14">
-        <v>44754</v>
+        <v>45100</v>
       </c>
       <c r="L117" s="14">
-        <v>45566</v>
+        <v>45400</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118" s="11" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C118" s="11" t="s">
-        <v>457</v>
+        <v>339</v>
       </c>
       <c r="D118" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E118" s="11" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="F118" s="11" t="s">
-        <v>45</v>
+        <v>163</v>
       </c>
       <c r="G118" s="11">
-        <v>0.0321</v>
+        <v>0.6605</v>
       </c>
       <c r="H118" s="12">
-        <v>7430869.32</v>
+        <v>20185137.81</v>
       </c>
       <c r="I118" s="13">
-        <v>238550.07</v>
+        <v>13332401.6</v>
       </c>
       <c r="J118" s="12">
-        <v>7192319.25</v>
+        <v>6852736.209999999</v>
       </c>
       <c r="K118" s="14">
-        <v>45865</v>
+        <v>44754</v>
       </c>
       <c r="L118" s="14">
-        <v>46166</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119" s="11" t="s">
-        <v>459</v>
+        <v>444</v>
       </c>
       <c r="B119" s="11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C119" s="11" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D119" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E119" s="11" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F119" s="11" t="s">
-        <v>424</v>
+        <v>45</v>
       </c>
       <c r="G119" s="11">
-        <v>0.9903</v>
+        <v>0.0321</v>
       </c>
       <c r="H119" s="12">
-        <v>11046611.98</v>
+        <v>7430869.32</v>
       </c>
       <c r="I119" s="13">
-        <v>10939879.39</v>
+        <v>238550.07</v>
       </c>
       <c r="J119" s="12">
-        <v>106732.58999999985</v>
+        <v>7192319.25</v>
       </c>
       <c r="K119" s="14">
-        <v>44663</v>
+        <v>45865</v>
       </c>
       <c r="L119" s="14">
-        <v>45507</v>
+        <v>46166</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120" s="11" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="B120" s="11" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C120" s="11" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D120" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E120" s="11" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="F120" s="11" t="s">
-        <v>466</v>
+        <v>429</v>
       </c>
       <c r="G120" s="11">
-        <v>0.8079000000000001</v>
+        <v>0.9903</v>
       </c>
       <c r="H120" s="12">
-        <v>2755604.93</v>
+        <v>11046611.98</v>
       </c>
       <c r="I120" s="13">
-        <v>2226331.45</v>
+        <v>10939879.39</v>
       </c>
       <c r="J120" s="12">
-        <v>529273.48</v>
+        <v>106732.58999999985</v>
       </c>
       <c r="K120" s="14">
-        <v>45026</v>
+        <v>44663</v>
       </c>
       <c r="L120" s="14">
-        <v>46023</v>
+        <v>45507</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121" s="11" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="B121" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C121" s="11" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D121" s="11" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E121" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F121" s="11" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="G121" s="11">
-        <v>0</v>
+        <v>0.8079000000000001</v>
       </c>
       <c r="H121" s="12">
-        <v>1712576.84</v>
+        <v>2755604.93</v>
       </c>
       <c r="I121" s="13">
-        <v>0</v>
+        <v>2226331.45</v>
       </c>
       <c r="J121" s="12">
-        <v>1712576.84</v>
+        <v>529273.48</v>
       </c>
       <c r="K121" s="14">
-        <v>44823</v>
+        <v>45026</v>
       </c>
       <c r="L121" s="14">
-        <v>44706</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122" s="11" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="B122" s="11" t="s">
+        <v>472</v>
+      </c>
+      <c r="C122" s="11" t="s">
+        <v>473</v>
+      </c>
+      <c r="D122" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E122" s="11" t="s">
+        <v>474</v>
+      </c>
+      <c r="F122" s="11" t="s">
         <v>471</v>
       </c>
-      <c r="C122" s="11" t="s">
-        <v>472</v>
-      </c>
-      <c r="D122" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E122" s="11" t="s">
-        <v>473</v>
-      </c>
-      <c r="F122" s="11" t="s">
-        <v>474</v>
-      </c>
       <c r="G122" s="11">
-        <v>0.9998999999999999</v>
+        <v>0</v>
       </c>
       <c r="H122" s="12">
-        <v>1612154.63</v>
+        <v>1712576.84</v>
       </c>
       <c r="I122" s="13">
-        <v>1612024.85</v>
+        <v>0</v>
       </c>
       <c r="J122" s="12">
-        <v>129.7799999997951</v>
+        <v>1712576.84</v>
       </c>
       <c r="K122" s="14">
-        <v>45776</v>
+        <v>44823</v>
       </c>
       <c r="L122" s="14">
-        <v>45986</v>
+        <v>44706</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
@@ -7042,229 +7072,229 @@
         <v>476</v>
       </c>
       <c r="C123" s="11" t="s">
-        <v>151</v>
+        <v>477</v>
       </c>
       <c r="D123" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E123" s="11" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F123" s="11" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="G123" s="11">
-        <v>1</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="H123" s="12">
-        <v>6453162.72</v>
+        <v>1612154.63</v>
       </c>
       <c r="I123" s="13">
-        <v>6453162.72</v>
+        <v>1612024.85</v>
       </c>
       <c r="J123" s="12">
-        <v>0</v>
+        <v>129.7799999997951</v>
       </c>
       <c r="K123" s="14">
-        <v>44760</v>
+        <v>45776</v>
       </c>
       <c r="L123" s="14">
-        <v>45201</v>
+        <v>45986</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124" s="11" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B124" s="11" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C124" s="11" t="s">
-        <v>480</v>
+        <v>157</v>
       </c>
       <c r="D124" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E124" s="11" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F124" s="11" t="s">
-        <v>236</v>
+        <v>483</v>
       </c>
       <c r="G124" s="11">
-        <v>0.9993000000000001</v>
+        <v>1</v>
       </c>
       <c r="H124" s="12">
-        <v>1741703.69</v>
+        <v>6453162.72</v>
       </c>
       <c r="I124" s="13">
-        <v>1740561.74</v>
+        <v>6453162.72</v>
       </c>
       <c r="J124" s="12">
-        <v>1141.9499999999534</v>
+        <v>0</v>
       </c>
       <c r="K124" s="14">
-        <v>44683</v>
+        <v>44760</v>
       </c>
       <c r="L124" s="14">
-        <v>45889</v>
+        <v>45201</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" s="11" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B125" s="11" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C125" s="11" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D125" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E125" s="11" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="F125" s="11" t="s">
-        <v>485</v>
+        <v>241</v>
       </c>
       <c r="G125" s="11">
-        <v>0.997</v>
+        <v>0.9993000000000001</v>
       </c>
       <c r="H125" s="12">
-        <v>6014775.77</v>
+        <v>1741703.69</v>
       </c>
       <c r="I125" s="13">
-        <v>5996889.68</v>
+        <v>1740561.74</v>
       </c>
       <c r="J125" s="12">
-        <v>17886.08999999985</v>
+        <v>1141.9499999999534</v>
       </c>
       <c r="K125" s="14">
-        <v>44708</v>
+        <v>44683</v>
       </c>
       <c r="L125" s="14">
-        <v>45467</v>
+        <v>45889</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126" s="11" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B126" s="11" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C126" s="11" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D126" s="11" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E126" s="11" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F126" s="11" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="G126" s="11">
-        <v>0.9913</v>
+        <v>0.997</v>
       </c>
       <c r="H126" s="12">
-        <v>3569195.39</v>
+        <v>6014775.77</v>
       </c>
       <c r="I126" s="13">
-        <v>3538001.16</v>
+        <v>5996889.68</v>
       </c>
       <c r="J126" s="12">
-        <v>31194.22999999998</v>
+        <v>17886.08999999985</v>
       </c>
       <c r="K126" s="14">
-        <v>44658</v>
+        <v>44708</v>
       </c>
       <c r="L126" s="14">
-        <v>45426</v>
+        <v>45467</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127" s="11" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B127" s="11" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C127" s="11" t="s">
+        <v>492</v>
+      </c>
+      <c r="D127" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E127" s="11" t="s">
+        <v>493</v>
+      </c>
+      <c r="F127" s="11" t="s">
         <v>490</v>
       </c>
-      <c r="D127" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E127" s="11" t="s">
-        <v>491</v>
-      </c>
-      <c r="F127" s="11" t="s">
-        <v>236</v>
-      </c>
       <c r="G127" s="11">
-        <v>0.7993000000000001</v>
+        <v>0.9913</v>
       </c>
       <c r="H127" s="12">
-        <v>1528883.61</v>
+        <v>3569195.39</v>
       </c>
       <c r="I127" s="13">
-        <v>1222003.41</v>
+        <v>3538001.16</v>
       </c>
       <c r="J127" s="12">
-        <v>306880.2000000002</v>
+        <v>31194.22999999998</v>
       </c>
       <c r="K127" s="14">
-        <v>44655</v>
+        <v>44658</v>
       </c>
       <c r="L127" s="14">
-        <v>46164</v>
+        <v>45426</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" s="11" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B128" s="11" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C128" s="11" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D128" s="11" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E128" s="11" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="F128" s="11" t="s">
-        <v>495</v>
+        <v>241</v>
       </c>
       <c r="G128" s="11">
-        <v>0.0245</v>
+        <v>0.7993000000000001</v>
       </c>
       <c r="H128" s="12">
-        <v>2317778.22</v>
+        <v>1528883.61</v>
       </c>
       <c r="I128" s="13">
-        <v>56828.03</v>
+        <v>1222003.41</v>
       </c>
       <c r="J128" s="12">
-        <v>2260950.1900000004</v>
+        <v>306880.2000000002</v>
       </c>
       <c r="K128" s="14">
-        <v>45035</v>
+        <v>44655</v>
       </c>
       <c r="L128" s="14">
-        <v>45396</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129" s="11" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
       <c r="B129" s="11" t="s">
         <v>497</v>
@@ -7273,7 +7303,7 @@
         <v>498</v>
       </c>
       <c r="D129" s="11" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E129" s="11" t="s">
         <v>499</v>
@@ -7282,217 +7312,217 @@
         <v>500</v>
       </c>
       <c r="G129" s="11">
-        <v>1</v>
+        <v>0.0245</v>
       </c>
       <c r="H129" s="12">
-        <v>6478069.43</v>
+        <v>2317778.22</v>
       </c>
       <c r="I129" s="13">
-        <v>6478029.44</v>
+        <v>56828.03</v>
       </c>
       <c r="J129" s="12">
-        <v>39.989999999292195</v>
+        <v>2260950.1900000004</v>
       </c>
       <c r="K129" s="14">
-        <v>44827</v>
+        <v>45035</v>
       </c>
       <c r="L129" s="14">
-        <v>45690</v>
+        <v>45396</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130" s="11" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="B130" s="11" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C130" s="11" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D130" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E130" s="11" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F130" s="11" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="G130" s="11">
-        <v>0.7809</v>
+        <v>1</v>
       </c>
       <c r="H130" s="12">
-        <v>544550.48</v>
+        <v>6478069.43</v>
       </c>
       <c r="I130" s="13">
-        <v>425261.4</v>
+        <v>6478029.44</v>
       </c>
       <c r="J130" s="12">
-        <v>119289.07999999996</v>
+        <v>39.989999999292195</v>
       </c>
       <c r="K130" s="14">
-        <v>45925</v>
+        <v>44827</v>
       </c>
       <c r="L130" s="14">
-        <v>46165</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131" s="11" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="B131" s="11" t="s">
         <v>506</v>
       </c>
       <c r="C131" s="11" t="s">
-        <v>178</v>
+        <v>507</v>
       </c>
       <c r="D131" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E131" s="11" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F131" s="11" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="G131" s="11">
-        <v>1</v>
+        <v>0.7809</v>
       </c>
       <c r="H131" s="12">
-        <v>2389346</v>
+        <v>544550.48</v>
       </c>
       <c r="I131" s="13">
-        <v>2389346</v>
+        <v>425261.4</v>
       </c>
       <c r="J131" s="12">
-        <v>0</v>
+        <v>119289.07999999996</v>
       </c>
       <c r="K131" s="14">
-        <v>44693</v>
+        <v>45925</v>
       </c>
       <c r="L131" s="14">
-        <v>45456</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B132" s="11" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C132" s="11" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D132" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E132" s="11" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="F132" s="11" t="s">
-        <v>340</v>
+        <v>98</v>
       </c>
       <c r="G132" s="11">
         <v>1</v>
       </c>
       <c r="H132" s="12">
-        <v>6743574.04</v>
+        <v>2389346</v>
       </c>
       <c r="I132" s="13">
-        <v>6743573.85</v>
+        <v>2389346</v>
       </c>
       <c r="J132" s="12">
-        <v>0.19000000040978193</v>
+        <v>0</v>
       </c>
       <c r="K132" s="14">
         <v>44693</v>
       </c>
       <c r="L132" s="14">
-        <v>45152</v>
+        <v>45456</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B133" s="11" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C133" s="11" t="s">
-        <v>313</v>
+        <v>194</v>
       </c>
       <c r="D133" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E133" s="11" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="F133" s="11" t="s">
-        <v>365</v>
+        <v>345</v>
       </c>
       <c r="G133" s="11">
-        <v>0.9562999999999999</v>
+        <v>1</v>
       </c>
       <c r="H133" s="12">
-        <v>1052239.53</v>
+        <v>6743574.04</v>
       </c>
       <c r="I133" s="13">
-        <v>1006235.15</v>
+        <v>6743573.85</v>
       </c>
       <c r="J133" s="12">
-        <v>46004.380000000005</v>
+        <v>0.19000000040978193</v>
       </c>
       <c r="K133" s="14">
-        <v>44613</v>
+        <v>44693</v>
       </c>
       <c r="L133" s="14">
-        <v>45183</v>
+        <v>45152</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B134" s="11" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C134" s="11" t="s">
-        <v>514</v>
+        <v>318</v>
       </c>
       <c r="D134" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E134" s="11" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F134" s="11" t="s">
-        <v>516</v>
+        <v>370</v>
       </c>
       <c r="G134" s="11">
-        <v>0.6409999999999999</v>
+        <v>0.9562999999999999</v>
       </c>
       <c r="H134" s="12">
-        <v>256613.37</v>
+        <v>1052239.53</v>
       </c>
       <c r="I134" s="13">
-        <v>164482.69</v>
+        <v>1006235.15</v>
       </c>
       <c r="J134" s="12">
-        <v>92130.68</v>
+        <v>46004.380000000005</v>
       </c>
       <c r="K134" s="14">
-        <v>45915</v>
+        <v>44613</v>
       </c>
       <c r="L134" s="14">
-        <v>46005</v>
+        <v>45183</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B135" s="11" t="s">
         <v>517</v>
@@ -7510,74 +7540,74 @@
         <v>520</v>
       </c>
       <c r="G135" s="11">
-        <v>0.9508</v>
+        <v>0.6409999999999999</v>
       </c>
       <c r="H135" s="12">
-        <v>13554947.83</v>
+        <v>256613.37</v>
       </c>
       <c r="I135" s="13">
-        <v>12888506.56</v>
+        <v>164482.69</v>
       </c>
       <c r="J135" s="12">
-        <v>666441.2699999996</v>
+        <v>92130.68</v>
       </c>
       <c r="K135" s="14">
-        <v>44537</v>
+        <v>45915</v>
       </c>
       <c r="L135" s="14">
-        <v>46075</v>
+        <v>46005</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B136" s="11" t="s">
         <v>521</v>
       </c>
       <c r="C136" s="11" t="s">
-        <v>448</v>
+        <v>522</v>
       </c>
       <c r="D136" s="11" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E136" s="11" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F136" s="11" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="G136" s="11">
-        <v>0</v>
+        <v>0.9508</v>
       </c>
       <c r="H136" s="12">
-        <v>1305890.95</v>
+        <v>13554947.83</v>
       </c>
       <c r="I136" s="13">
-        <v>0</v>
+        <v>12888506.56</v>
       </c>
       <c r="J136" s="12">
-        <v>1305890.95</v>
+        <v>666441.2699999996</v>
       </c>
       <c r="K136" s="14">
-        <v>44610</v>
+        <v>44537</v>
       </c>
       <c r="L136" s="14">
-        <v>45567</v>
+        <v>46075</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B137" s="11" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C137" s="11" t="s">
-        <v>525</v>
+        <v>453</v>
       </c>
       <c r="D137" s="11" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E137" s="11" t="s">
         <v>526</v>
@@ -7586,27 +7616,27 @@
         <v>527</v>
       </c>
       <c r="G137" s="11">
-        <v>0.9765999999999999</v>
+        <v>0</v>
       </c>
       <c r="H137" s="12">
-        <v>56185153.92</v>
+        <v>1305890.95</v>
       </c>
       <c r="I137" s="13">
-        <v>54872063.4</v>
+        <v>0</v>
       </c>
       <c r="J137" s="12">
-        <v>1313090.5200000033</v>
+        <v>1305890.95</v>
       </c>
       <c r="K137" s="14">
-        <v>44872</v>
+        <v>44610</v>
       </c>
       <c r="L137" s="14">
-        <v>45475</v>
+        <v>45567</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B138" s="11" t="s">
         <v>528</v>
@@ -7615,7 +7645,7 @@
         <v>529</v>
       </c>
       <c r="D138" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E138" s="11" t="s">
         <v>530</v>
@@ -7624,27 +7654,27 @@
         <v>531</v>
       </c>
       <c r="G138" s="11">
-        <v>0.8667</v>
+        <v>0.9765999999999999</v>
       </c>
       <c r="H138" s="12">
-        <v>12100122.6</v>
+        <v>56185153.92</v>
       </c>
       <c r="I138" s="13">
-        <v>10486811.37</v>
+        <v>54872063.4</v>
       </c>
       <c r="J138" s="12">
-        <v>1613311.2300000004</v>
+        <v>1313090.5200000033</v>
       </c>
       <c r="K138" s="14">
-        <v>45758</v>
+        <v>44872</v>
       </c>
       <c r="L138" s="14">
-        <v>46123</v>
+        <v>45475</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B139" s="11" t="s">
         <v>532</v>
@@ -7659,191 +7689,191 @@
         <v>534</v>
       </c>
       <c r="F139" s="11" t="s">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="G139" s="11">
-        <v>0.8621</v>
+        <v>0.8667</v>
       </c>
       <c r="H139" s="12">
-        <v>12432476.25</v>
+        <v>12100122.6</v>
       </c>
       <c r="I139" s="13">
-        <v>10511270.47</v>
+        <v>10486811.37</v>
       </c>
       <c r="J139" s="12">
-        <v>1714359.4299999997</v>
+        <v>1613311.2300000004</v>
       </c>
       <c r="K139" s="14">
-        <v>45894</v>
+        <v>45758</v>
       </c>
       <c r="L139" s="14">
-        <v>46112</v>
+        <v>46123</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B140" s="11" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C140" s="11" t="s">
-        <v>434</v>
+        <v>537</v>
       </c>
       <c r="D140" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E140" s="11" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="F140" s="11" t="s">
-        <v>148</v>
+        <v>98</v>
       </c>
       <c r="G140" s="11">
-        <v>0.8916</v>
+        <v>0.8621</v>
       </c>
       <c r="H140" s="12">
-        <v>24590858.27</v>
+        <v>12432476.25</v>
       </c>
       <c r="I140" s="13">
-        <v>21925638.52</v>
+        <v>10718116.82</v>
       </c>
       <c r="J140" s="12">
-        <v>2665219.75</v>
+        <v>1714359.4299999997</v>
       </c>
       <c r="K140" s="14">
-        <v>44638</v>
+        <v>45894</v>
       </c>
       <c r="L140" s="14">
-        <v>45936</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B141" s="11" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C141" s="11" t="s">
-        <v>141</v>
+        <v>439</v>
       </c>
       <c r="D141" s="11" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E141" s="11" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="F141" s="11" t="s">
-        <v>336</v>
+        <v>154</v>
       </c>
       <c r="G141" s="11">
-        <v>0.0707</v>
+        <v>0.8916</v>
       </c>
       <c r="H141" s="12">
-        <v>3615856.15</v>
+        <v>24590858.27</v>
       </c>
       <c r="I141" s="13">
-        <v>255684.47</v>
+        <v>21925638.52</v>
       </c>
       <c r="J141" s="12">
-        <v>3360171.6799999997</v>
+        <v>2665219.75</v>
       </c>
       <c r="K141" s="14">
-        <v>44791</v>
+        <v>44638</v>
       </c>
       <c r="L141" s="14">
-        <v>45259</v>
+        <v>45936</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B142" s="11" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C142" s="11" t="s">
-        <v>540</v>
+        <v>147</v>
       </c>
       <c r="D142" s="11" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E142" s="11" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F142" s="11" t="s">
-        <v>508</v>
+        <v>341</v>
       </c>
       <c r="G142" s="11">
-        <v>0.1637</v>
+        <v>0.0707</v>
       </c>
       <c r="H142" s="12">
-        <v>7848019.53</v>
+        <v>3615856.15</v>
       </c>
       <c r="I142" s="13">
-        <v>1284711.9</v>
+        <v>255684.47</v>
       </c>
       <c r="J142" s="12">
-        <v>6563307.630000001</v>
+        <v>3360171.6799999997</v>
       </c>
       <c r="K142" s="14">
-        <v>45986</v>
+        <v>44791</v>
       </c>
       <c r="L142" s="14">
-        <v>46351</v>
+        <v>45259</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B143" s="11" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C143" s="11" t="s">
-        <v>99</v>
+        <v>544</v>
       </c>
       <c r="D143" s="11" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E143" s="11" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="F143" s="11" t="s">
-        <v>544</v>
+        <v>98</v>
       </c>
       <c r="G143" s="11">
-        <v>0.5364</v>
+        <v>0.1637</v>
       </c>
       <c r="H143" s="12">
-        <v>16932981.45</v>
+        <v>7848019.53</v>
       </c>
       <c r="I143" s="13">
-        <v>9082408.67</v>
+        <v>1284711.9</v>
       </c>
       <c r="J143" s="12">
-        <v>7850572.779999999</v>
+        <v>6563307.630000001</v>
       </c>
       <c r="K143" s="14">
-        <v>44791</v>
+        <v>45986</v>
       </c>
       <c r="L143" s="14">
-        <v>45393</v>
+        <v>46351</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B144" s="11" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C144" s="11" t="s">
-        <v>546</v>
+        <v>105</v>
       </c>
       <c r="D144" s="11" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E144" s="11" t="s">
         <v>547</v>
@@ -7852,27 +7882,27 @@
         <v>548</v>
       </c>
       <c r="G144" s="11">
-        <v>0.6043</v>
+        <v>0.5364</v>
       </c>
       <c r="H144" s="12">
-        <v>24187461.93</v>
+        <v>16932981.45</v>
       </c>
       <c r="I144" s="13">
-        <v>14615806.69</v>
+        <v>9082408.67</v>
       </c>
       <c r="J144" s="12">
-        <v>9571655.24</v>
+        <v>7850572.779999999</v>
       </c>
       <c r="K144" s="14">
-        <v>45723</v>
+        <v>44791</v>
       </c>
       <c r="L144" s="14">
-        <v>46203</v>
+        <v>45393</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B145" s="11" t="s">
         <v>549</v>
@@ -7890,27 +7920,27 @@
         <v>552</v>
       </c>
       <c r="G145" s="11">
-        <v>0.8504</v>
+        <v>0.6097</v>
       </c>
       <c r="H145" s="12">
-        <v>74609626.42</v>
+        <v>24187461.93</v>
       </c>
       <c r="I145" s="13">
-        <v>63449041.49</v>
+        <v>14747400.15</v>
       </c>
       <c r="J145" s="12">
-        <v>11160584.93</v>
+        <v>9440061.78</v>
       </c>
       <c r="K145" s="14">
-        <v>45555</v>
+        <v>45723</v>
       </c>
       <c r="L145" s="14">
-        <v>46112</v>
+        <v>46203</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A146" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B146" s="11" t="s">
         <v>553</v>
@@ -7925,106 +7955,106 @@
         <v>555</v>
       </c>
       <c r="F146" s="11" t="s">
-        <v>520</v>
+        <v>556</v>
       </c>
       <c r="G146" s="11">
-        <v>0.15</v>
+        <v>0.8504</v>
       </c>
       <c r="H146" s="12">
-        <v>15203482.79</v>
+        <v>74609626.42</v>
       </c>
       <c r="I146" s="13">
-        <v>2279930.05</v>
+        <v>63449041.49</v>
       </c>
       <c r="J146" s="12">
-        <v>12923552.739999998</v>
+        <v>11160584.93</v>
       </c>
       <c r="K146" s="14">
-        <v>44757</v>
+        <v>45555</v>
       </c>
       <c r="L146" s="14">
-        <v>46287</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B147" s="11" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C147" s="11" t="s">
-        <v>490</v>
+        <v>558</v>
       </c>
       <c r="D147" s="11" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E147" s="11" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="F147" s="11" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="G147" s="11">
-        <v>0.0216</v>
+        <v>0.15</v>
       </c>
       <c r="H147" s="12">
-        <v>13677862.32</v>
+        <v>15203482.79</v>
       </c>
       <c r="I147" s="13">
-        <v>296101.87</v>
+        <v>2279930.05</v>
       </c>
       <c r="J147" s="12">
-        <v>13381760.450000001</v>
+        <v>12923552.739999998</v>
       </c>
       <c r="K147" s="14">
-        <v>44581</v>
+        <v>44757</v>
       </c>
       <c r="L147" s="14">
-        <v>45561</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A148" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B148" s="11" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C148" s="11" t="s">
-        <v>559</v>
+        <v>495</v>
       </c>
       <c r="D148" s="11" t="s">
         <v>20</v>
       </c>
       <c r="E148" s="11" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F148" s="11" t="s">
-        <v>561</v>
+        <v>524</v>
       </c>
       <c r="G148" s="11">
-        <v>0</v>
+        <v>0.0216</v>
       </c>
       <c r="H148" s="12">
-        <v>14144248.92</v>
+        <v>13677862.32</v>
       </c>
       <c r="I148" s="13">
-        <v>0</v>
+        <v>296101.87</v>
       </c>
       <c r="J148" s="12">
-        <v>14144248.92</v>
+        <v>13381760.450000001</v>
       </c>
       <c r="K148" s="14">
-        <v>41443</v>
+        <v>44581</v>
       </c>
       <c r="L148" s="14">
-        <v>44012</v>
+        <v>45561</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B149" s="11" t="s">
         <v>562</v>
@@ -8039,519 +8069,513 @@
         <v>564</v>
       </c>
       <c r="F149" s="11" t="s">
-        <v>336</v>
+        <v>565</v>
       </c>
       <c r="G149" s="11">
-        <v>0.3475</v>
+        <v>0</v>
       </c>
       <c r="H149" s="12">
-        <v>24165422.12</v>
+        <v>14144248.92</v>
       </c>
       <c r="I149" s="13">
-        <v>8398407.23</v>
+        <v>0</v>
       </c>
       <c r="J149" s="12">
-        <v>15767014.89</v>
+        <v>14144248.92</v>
       </c>
       <c r="K149" s="14">
-        <v>44538</v>
+        <v>41443</v>
       </c>
       <c r="L149" s="14">
-        <v>45426</v>
+        <v>44012</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B150" s="11" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C150" s="11" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D150" s="11" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E150" s="11" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F150" s="11" t="s">
-        <v>568</v>
+        <v>341</v>
       </c>
       <c r="G150" s="11">
-        <v>0.5169</v>
+        <v>0.3475</v>
       </c>
       <c r="H150" s="12">
-        <v>104939756.55</v>
+        <v>24165422.12</v>
       </c>
       <c r="I150" s="13">
-        <v>54247297.54</v>
+        <v>8398407.23</v>
       </c>
       <c r="J150" s="12">
-        <v>50692459.01</v>
+        <v>15767014.89</v>
       </c>
       <c r="K150" s="14">
-        <v>45624</v>
+        <v>44538</v>
       </c>
       <c r="L150" s="14">
-        <v>46074</v>
+        <v>45426</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151" s="11" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B151" s="11" t="s">
         <v>569</v>
       </c>
-      <c r="C151" s="11" t="s">
+      <c r="C151" s="11"/>
+      <c r="D151" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="E151" s="11" t="s">
         <v>570</v>
       </c>
-      <c r="D151" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E151" s="11" t="s">
-        <v>571</v>
-      </c>
-      <c r="F151" s="11" t="s">
-        <v>336</v>
-      </c>
-      <c r="G151" s="11">
-        <v>0.2304</v>
+      <c r="F151" s="11"/>
+      <c r="G151" s="16" t="s">
+        <v>99</v>
       </c>
       <c r="H151" s="12">
-        <v>116500000</v>
+        <v>31744937.05</v>
       </c>
       <c r="I151" s="13">
-        <v>26845813.79</v>
+        <v>0</v>
       </c>
       <c r="J151" s="12">
-        <v>89654186.21000001</v>
-      </c>
-      <c r="K151" s="14">
-        <v>45897</v>
-      </c>
-      <c r="L151" s="14">
-        <v>46107</v>
+        <v>31744937.05</v>
+      </c>
+      <c r="K151" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="L151" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152" s="11" t="s">
+        <v>510</v>
+      </c>
+      <c r="B152" s="11" t="s">
+        <v>571</v>
+      </c>
+      <c r="C152" s="11" t="s">
         <v>572</v>
       </c>
-      <c r="B152" s="11" t="s">
+      <c r="D152" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E152" s="11" t="s">
         <v>573</v>
       </c>
-      <c r="C152" s="11" t="s">
+      <c r="F152" s="11" t="s">
         <v>574</v>
       </c>
-      <c r="D152" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E152" s="11" t="s">
-        <v>575</v>
-      </c>
-      <c r="F152" s="11" t="s">
-        <v>576</v>
-      </c>
       <c r="G152" s="11">
-        <v>1</v>
+        <v>0.5169</v>
       </c>
       <c r="H152" s="12">
-        <v>10061005.41</v>
+        <v>104939756.55</v>
       </c>
       <c r="I152" s="13">
-        <v>10061005.39</v>
+        <v>54247297.54</v>
       </c>
       <c r="J152" s="12">
-        <v>0.019999999552965164</v>
+        <v>50692459.01</v>
       </c>
       <c r="K152" s="14">
-        <v>45261</v>
+        <v>45624</v>
       </c>
       <c r="L152" s="14">
-        <v>45833</v>
+        <v>46074</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153" s="11" t="s">
-        <v>577</v>
+        <v>510</v>
       </c>
       <c r="B153" s="11" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="C153" s="11" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="D153" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E153" s="11" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="F153" s="11" t="s">
-        <v>45</v>
+        <v>341</v>
       </c>
       <c r="G153" s="11">
-        <v>1</v>
+        <v>0.2304</v>
       </c>
       <c r="H153" s="12">
-        <v>81950979.23</v>
+        <v>116500000</v>
       </c>
       <c r="I153" s="13">
-        <v>81950979</v>
+        <v>26845813.79</v>
       </c>
       <c r="J153" s="12">
-        <v>0.23000000417232513</v>
+        <v>89654186.21000001</v>
       </c>
       <c r="K153" s="14">
-        <v>44792</v>
+        <v>45897</v>
       </c>
       <c r="L153" s="14">
-        <v>46022</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154" s="11" t="s">
-        <v>577</v>
+        <v>510</v>
       </c>
       <c r="B154" s="11" t="s">
-        <v>581</v>
-      </c>
-      <c r="C154" s="11" t="s">
-        <v>582</v>
-      </c>
+        <v>578</v>
+      </c>
+      <c r="C154" s="11"/>
       <c r="D154" s="11" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="E154" s="11" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="F154" s="11" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="G154" s="11">
         <v>0</v>
       </c>
       <c r="H154" s="12">
-        <v>41522873.42</v>
+        <v>201720000</v>
       </c>
       <c r="I154" s="13">
         <v>0</v>
       </c>
       <c r="J154" s="12">
-        <v>41522873.42</v>
-      </c>
-      <c r="K154" s="14">
-        <v>45901</v>
-      </c>
-      <c r="L154" s="14">
-        <v>46801</v>
+        <v>201720000</v>
+      </c>
+      <c r="K154" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="L154" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A155" s="11" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="B155" s="11" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="C155" s="11" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="D155" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E155" s="11" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="F155" s="11" t="s">
-        <v>318</v>
+        <v>585</v>
       </c>
       <c r="G155" s="11">
-        <v>0.9728</v>
+        <v>1</v>
       </c>
       <c r="H155" s="12">
-        <v>4444784.22</v>
+        <v>10061005.41</v>
       </c>
       <c r="I155" s="13">
-        <v>4324004.81</v>
+        <v>10061005.39</v>
       </c>
       <c r="J155" s="12">
-        <v>120779.41000000015</v>
+        <v>0.019999999552965164</v>
       </c>
       <c r="K155" s="14">
-        <v>45155</v>
+        <v>45261</v>
       </c>
       <c r="L155" s="14">
-        <v>45576</v>
+        <v>45833</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156" s="11" t="s">
+        <v>586</v>
+      </c>
+      <c r="B156" s="11" t="s">
+        <v>587</v>
+      </c>
+      <c r="C156" s="11" t="s">
+        <v>588</v>
+      </c>
+      <c r="D156" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E156" s="11" t="s">
         <v>589</v>
       </c>
-      <c r="B156" s="11" t="s">
-        <v>590</v>
-      </c>
-      <c r="C156" s="11" t="s">
-        <v>591</v>
-      </c>
-      <c r="D156" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E156" s="11" t="s">
-        <v>592</v>
-      </c>
       <c r="F156" s="11" t="s">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="G156" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H156" s="12">
-        <v>8995898.05</v>
+        <v>81950979.23</v>
       </c>
       <c r="I156" s="13">
-        <v>266299.23</v>
+        <v>81950979</v>
       </c>
       <c r="J156" s="12">
-        <v>8729598.82</v>
+        <v>0.23000000417232513</v>
       </c>
       <c r="K156" s="14">
-        <v>44816</v>
+        <v>44792</v>
       </c>
       <c r="L156" s="14">
-        <v>44996</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157" s="11" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="B157" s="11" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="C157" s="11" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="D157" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E157" s="11" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="F157" s="11" t="s">
-        <v>576</v>
+        <v>593</v>
       </c>
       <c r="G157" s="11">
-        <v>0.3153</v>
+        <v>0</v>
       </c>
       <c r="H157" s="12">
-        <v>3294597.99</v>
+        <v>41522873.42</v>
       </c>
       <c r="I157" s="13">
-        <v>1038880.21</v>
+        <v>0</v>
       </c>
       <c r="J157" s="12">
-        <v>2255717.7800000003</v>
+        <v>41522873.42</v>
       </c>
       <c r="K157" s="14">
-        <v>45278</v>
+        <v>45901</v>
       </c>
       <c r="L157" s="14">
-        <v>46122</v>
+        <v>46801</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A158" s="11" t="s">
+        <v>594</v>
+      </c>
+      <c r="B158" s="11" t="s">
+        <v>595</v>
+      </c>
+      <c r="C158" s="11" t="s">
+        <v>596</v>
+      </c>
+      <c r="D158" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E158" s="11" t="s">
         <v>597</v>
       </c>
-      <c r="B158" s="11" t="s">
-        <v>598</v>
-      </c>
-      <c r="C158" s="11" t="s">
-        <v>599</v>
-      </c>
-      <c r="D158" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E158" s="11" t="s">
-        <v>600</v>
-      </c>
       <c r="F158" s="11" t="s">
-        <v>500</v>
+        <v>323</v>
       </c>
       <c r="G158" s="11">
-        <v>0.9922</v>
+        <v>0.9728</v>
       </c>
       <c r="H158" s="12">
-        <v>6055289.34</v>
+        <v>4444784.22</v>
       </c>
       <c r="I158" s="13">
-        <v>6007931.02</v>
+        <v>4324004.81</v>
       </c>
       <c r="J158" s="12">
-        <v>47358.3200000003</v>
+        <v>120779.41000000015</v>
       </c>
       <c r="K158" s="14">
-        <v>44715</v>
+        <v>45155</v>
       </c>
       <c r="L158" s="14">
-        <v>45075</v>
+        <v>45576</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A159" s="11" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B159" s="11" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C159" s="11" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="D159" s="11" t="s">
         <v>20</v>
       </c>
       <c r="E159" s="11" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F159" s="11" t="s">
-        <v>45</v>
+        <v>111</v>
       </c>
       <c r="G159" s="11">
-        <v>0.22760000000000002</v>
+        <v>0</v>
       </c>
       <c r="H159" s="12">
-        <v>8973983.87</v>
+        <v>8995898.05</v>
       </c>
       <c r="I159" s="13">
-        <v>2042159.29</v>
+        <v>266299.23</v>
       </c>
       <c r="J159" s="12">
-        <v>6931824.579999999</v>
+        <v>8729598.82</v>
       </c>
       <c r="K159" s="14">
-        <v>44707</v>
+        <v>44816</v>
       </c>
       <c r="L159" s="14">
-        <v>45280</v>
+        <v>44996</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160" s="11" t="s">
+        <v>602</v>
+      </c>
+      <c r="B160" s="11" t="s">
+        <v>603</v>
+      </c>
+      <c r="C160" s="11" t="s">
         <v>604</v>
       </c>
-      <c r="B160" s="11" t="s">
+      <c r="D160" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E160" s="11" t="s">
         <v>605</v>
       </c>
-      <c r="C160" s="11" t="s">
-        <v>244</v>
-      </c>
-      <c r="D160" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E160" s="11" t="s">
-        <v>606</v>
-      </c>
       <c r="F160" s="11" t="s">
-        <v>143</v>
+        <v>585</v>
       </c>
       <c r="G160" s="11">
-        <v>1</v>
+        <v>0.3153</v>
       </c>
       <c r="H160" s="12">
-        <v>13792679.79</v>
+        <v>3294597.99</v>
       </c>
       <c r="I160" s="13">
-        <v>13792679.79</v>
+        <v>1038880.21</v>
       </c>
       <c r="J160" s="12">
-        <v>0</v>
+        <v>2255717.7800000003</v>
       </c>
       <c r="K160" s="14">
-        <v>44767</v>
+        <v>45278</v>
       </c>
       <c r="L160" s="14">
-        <v>45411</v>
+        <v>46122</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161" s="11" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B161" s="11" t="s">
         <v>607</v>
       </c>
       <c r="C161" s="11" t="s">
-        <v>130</v>
+        <v>608</v>
       </c>
       <c r="D161" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E161" s="11" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F161" s="11" t="s">
-        <v>57</v>
+        <v>505</v>
       </c>
       <c r="G161" s="11">
-        <v>0.9122</v>
+        <v>0.9922</v>
       </c>
       <c r="H161" s="12">
-        <v>22472818</v>
+        <v>6055289.34</v>
       </c>
       <c r="I161" s="13">
-        <v>20500685.68</v>
+        <v>6007931.02</v>
       </c>
       <c r="J161" s="12">
-        <v>1972132.3200000003</v>
+        <v>47358.3200000003</v>
       </c>
       <c r="K161" s="14">
-        <v>44827</v>
+        <v>44715</v>
       </c>
       <c r="L161" s="14">
-        <v>45460</v>
+        <v>45075</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162" s="11" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B162" s="11" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C162" s="11" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D162" s="11" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E162" s="11" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F162" s="11" t="s">
-        <v>612</v>
+        <v>45</v>
       </c>
       <c r="G162" s="11">
-        <v>0.8996</v>
+        <v>0.22760000000000002</v>
       </c>
       <c r="H162" s="12">
-        <v>51414775.09</v>
+        <v>8973983.87</v>
       </c>
       <c r="I162" s="13">
-        <v>46254135.59</v>
+        <v>2042159.29</v>
       </c>
       <c r="J162" s="12">
-        <v>5160639.5</v>
+        <v>6931824.579999999</v>
       </c>
       <c r="K162" s="14">
-        <v>45566</v>
+        <v>44707</v>
       </c>
       <c r="L162" s="14">
-        <v>46106</v>
+        <v>45280</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
@@ -8562,191 +8586,191 @@
         <v>614</v>
       </c>
       <c r="C163" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="D163" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E163" s="11" t="s">
         <v>615</v>
       </c>
-      <c r="D163" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E163" s="11" t="s">
-        <v>616</v>
-      </c>
       <c r="F163" s="11" t="s">
-        <v>617</v>
+        <v>149</v>
       </c>
       <c r="G163" s="11">
+        <v>1</v>
+      </c>
+      <c r="H163" s="12">
+        <v>13792679.79</v>
+      </c>
+      <c r="I163" s="13">
+        <v>13792679.79</v>
+      </c>
+      <c r="J163" s="12">
         <v>0</v>
       </c>
-      <c r="H163" s="12">
-        <v>1302281.25</v>
-      </c>
-      <c r="I163" s="13">
-        <v>0</v>
-      </c>
-      <c r="J163" s="12">
-        <v>1302281.25</v>
-      </c>
       <c r="K163" s="14">
-        <v>46080</v>
+        <v>44767</v>
       </c>
       <c r="L163" s="14">
-        <v>46440</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164" s="11" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="B164" s="11" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="C164" s="11" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="D164" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E164" s="11" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="F164" s="11" t="s">
-        <v>621</v>
+        <v>57</v>
       </c>
       <c r="G164" s="11">
-        <v>1</v>
+        <v>0.9122</v>
       </c>
       <c r="H164" s="12">
-        <v>18264452.89</v>
+        <v>22472818</v>
       </c>
       <c r="I164" s="13">
-        <v>18264452.89</v>
+        <v>20500685.68</v>
       </c>
       <c r="J164" s="12">
-        <v>0</v>
+        <v>1972132.3200000003</v>
       </c>
       <c r="K164" s="14">
-        <v>44722</v>
+        <v>44827</v>
       </c>
       <c r="L164" s="14">
-        <v>45723</v>
+        <v>45460</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165" s="11" t="s">
+        <v>613</v>
+      </c>
+      <c r="B165" s="11" t="s">
         <v>618</v>
       </c>
-      <c r="B165" s="11" t="s">
-        <v>622</v>
-      </c>
       <c r="C165" s="11" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="D165" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E165" s="11" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="F165" s="11" t="s">
-        <v>40</v>
+        <v>621</v>
       </c>
       <c r="G165" s="11">
-        <v>0.9953</v>
+        <v>0.8996</v>
       </c>
       <c r="H165" s="12">
-        <v>30599999.01</v>
+        <v>51414775.09</v>
       </c>
       <c r="I165" s="13">
-        <v>30456294.33</v>
+        <v>46254135.59</v>
       </c>
       <c r="J165" s="12">
-        <v>143704.68000000343</v>
+        <v>5160639.5</v>
       </c>
       <c r="K165" s="14">
-        <v>45019</v>
+        <v>45566</v>
       </c>
       <c r="L165" s="14">
-        <v>45743</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166" s="11" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="B166" s="11" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C166" s="11" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="D166" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E166" s="11" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="F166" s="11" t="s">
-        <v>216</v>
+        <v>626</v>
       </c>
       <c r="G166" s="11">
-        <v>0.9601000000000001</v>
+        <v>0</v>
       </c>
       <c r="H166" s="12">
-        <v>43796954.98</v>
+        <v>1302281.25</v>
       </c>
       <c r="I166" s="13">
-        <v>42048979.52</v>
+        <v>0</v>
       </c>
       <c r="J166" s="12">
-        <v>1747975.4599999934</v>
+        <v>1302281.25</v>
       </c>
       <c r="K166" s="14">
-        <v>44641</v>
+        <v>46080</v>
       </c>
       <c r="L166" s="14">
-        <v>46091</v>
+        <v>46440</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A167" s="11" t="s">
-        <v>618</v>
+        <v>627</v>
       </c>
       <c r="B167" s="11" t="s">
         <v>628</v>
       </c>
       <c r="C167" s="11" t="s">
-        <v>629</v>
+        <v>161</v>
       </c>
       <c r="D167" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E167" s="11" t="s">
+        <v>629</v>
+      </c>
+      <c r="F167" s="11" t="s">
         <v>630</v>
       </c>
-      <c r="F167" s="11" t="s">
-        <v>216</v>
-      </c>
       <c r="G167" s="11">
-        <v>0.7956</v>
+        <v>1</v>
       </c>
       <c r="H167" s="12">
-        <v>45726170.25</v>
+        <v>18264452.89</v>
       </c>
       <c r="I167" s="13">
-        <v>36377601.26</v>
+        <v>18264452.89</v>
       </c>
       <c r="J167" s="12">
-        <v>9348568.990000002</v>
+        <v>0</v>
       </c>
       <c r="K167" s="14">
-        <v>44623</v>
+        <v>44722</v>
       </c>
       <c r="L167" s="14">
-        <v>46222</v>
+        <v>45723</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A168" s="11" t="s">
-        <v>618</v>
+        <v>627</v>
       </c>
       <c r="B168" s="11" t="s">
         <v>631</v>
@@ -8755,30 +8779,144 @@
         <v>632</v>
       </c>
       <c r="D168" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E168" s="11" t="s">
         <v>633</v>
       </c>
       <c r="F168" s="11" t="s">
-        <v>105</v>
+        <v>40</v>
       </c>
       <c r="G168" s="11">
+        <v>0.9953</v>
+      </c>
+      <c r="H168" s="12">
+        <v>30599999.01</v>
+      </c>
+      <c r="I168" s="13">
+        <v>30456294.33</v>
+      </c>
+      <c r="J168" s="12">
+        <v>143704.68000000343</v>
+      </c>
+      <c r="K168" s="14">
+        <v>45019</v>
+      </c>
+      <c r="L168" s="14">
+        <v>45743</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A169" s="11" t="s">
+        <v>627</v>
+      </c>
+      <c r="B169" s="11" t="s">
+        <v>634</v>
+      </c>
+      <c r="C169" s="11" t="s">
+        <v>635</v>
+      </c>
+      <c r="D169" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E169" s="11" t="s">
+        <v>636</v>
+      </c>
+      <c r="F169" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="G169" s="11">
+        <v>0.9601000000000001</v>
+      </c>
+      <c r="H169" s="12">
+        <v>43796954.98</v>
+      </c>
+      <c r="I169" s="13">
+        <v>42048979.52</v>
+      </c>
+      <c r="J169" s="12">
+        <v>1747975.4599999934</v>
+      </c>
+      <c r="K169" s="14">
+        <v>44641</v>
+      </c>
+      <c r="L169" s="14">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A170" s="11" t="s">
+        <v>627</v>
+      </c>
+      <c r="B170" s="11" t="s">
+        <v>637</v>
+      </c>
+      <c r="C170" s="11" t="s">
+        <v>638</v>
+      </c>
+      <c r="D170" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E170" s="11" t="s">
+        <v>639</v>
+      </c>
+      <c r="F170" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="G170" s="11">
+        <v>0.7956</v>
+      </c>
+      <c r="H170" s="12">
+        <v>45726170.25</v>
+      </c>
+      <c r="I170" s="13">
+        <v>36377601.26</v>
+      </c>
+      <c r="J170" s="12">
+        <v>9348568.990000002</v>
+      </c>
+      <c r="K170" s="14">
+        <v>44623</v>
+      </c>
+      <c r="L170" s="14">
+        <v>46222</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A171" s="11" t="s">
+        <v>627</v>
+      </c>
+      <c r="B171" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="C171" s="11" t="s">
+        <v>641</v>
+      </c>
+      <c r="D171" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E171" s="11" t="s">
+        <v>642</v>
+      </c>
+      <c r="F171" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="G171" s="11">
         <v>0.30870000000000003</v>
       </c>
-      <c r="H168" s="12">
+      <c r="H171" s="12">
         <v>65678550.13</v>
       </c>
-      <c r="I168" s="13">
+      <c r="I171" s="13">
         <v>20274364.25</v>
       </c>
-      <c r="J168" s="12">
+      <c r="J171" s="12">
         <v>45404185.88</v>
       </c>
-      <c r="K168" s="14">
+      <c r="K171" s="14">
         <v>44623</v>
       </c>
-      <c r="L168" s="14">
+      <c r="L171" s="14">
         <v>46170</v>
       </c>
     </row>

--- a/ANALITICA.xlsx
+++ b/ANALITICA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="643">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="649">
   <si>
     <t>Municipio</t>
   </si>
@@ -752,186 +752,201 @@
     <t>019/2022</t>
   </si>
   <si>
+    <t>DRENAGEM E PAVIMENTAÇÃO NO BAIRRO NOVA BELEM – JAPERI/RJ</t>
+  </si>
+  <si>
+    <t>170026/002777/2021</t>
+  </si>
+  <si>
+    <t>034/2022</t>
+  </si>
+  <si>
+    <t>PROJETO EXECUTIVO E EXECUÇÃO DE OBRAS DE DRENAGEM, PAVIMENTAÇÃO E INFRAESTRUTURA – SÃO JOSÉ – JAPERI/RJ</t>
+  </si>
+  <si>
+    <t>CONSÓRCIO SÃO JOSÉ HM ( HYDRA ENGENHARIA E SANEAMENTO LTDA E CONSTRUTORA MEDEIROS CARVALHO DE ALMEIDA LTDA)</t>
+  </si>
+  <si>
+    <t>Macaé</t>
+  </si>
+  <si>
+    <t>170026/002217/2021</t>
+  </si>
+  <si>
+    <t>036/2022</t>
+  </si>
+  <si>
+    <t>REVITALIZAÇÃO DA AV. RUI BARBOSA - MACAÉ/RJ</t>
+  </si>
+  <si>
+    <t>KROFMAN COMERCIO SERVIÇO EIRELI ME</t>
+  </si>
+  <si>
+    <t>Magé</t>
+  </si>
+  <si>
+    <t>330018/000333/2022</t>
+  </si>
+  <si>
+    <t>023/2023</t>
+  </si>
+  <si>
+    <t>RECAPEAMENTO DE LOGRADOUROS EM MAGÉ – RJ</t>
+  </si>
+  <si>
+    <t>GRAVISA ENHENHARIA E EMPREENDIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>Mangaratiba</t>
+  </si>
+  <si>
+    <t>170026/001229/2022</t>
+  </si>
+  <si>
+    <t>080/2022</t>
+  </si>
+  <si>
+    <t>ESTABILIZAÇÃO DE TALUDE - RJ 014, MANGARATIBA/RJ</t>
+  </si>
+  <si>
+    <t>170026/001611/2020</t>
+  </si>
+  <si>
+    <t>028/2021</t>
+  </si>
+  <si>
+    <t>REVITALIZAÇÃO DA CICLOVIA E CALÇADA DA ORLA DA PRAIA DO SACO - MANGARATIBA/RJ</t>
+  </si>
+  <si>
+    <t>GONÇALVES E NEVES CONSTRUÇÃO CIVIL LTDA</t>
+  </si>
+  <si>
+    <t>170026/001230/2022</t>
+  </si>
+  <si>
+    <t>063/2020</t>
+  </si>
+  <si>
+    <t>ESTABILIZAÇÃO DE TALUDES - RUA LITORÂNEA, MANGARATIBA/RJ</t>
+  </si>
+  <si>
+    <t>RIVALL ENGENHARIA LTDA</t>
+  </si>
+  <si>
+    <t>170026/001228/2022</t>
+  </si>
+  <si>
+    <t>ESTABILIZAÇÃO DE TALUDE - VILA MURIQUI, MANGARATIBA/RJ</t>
+  </si>
+  <si>
+    <t>330001/001441/2024</t>
+  </si>
+  <si>
+    <t>005/2025</t>
+  </si>
+  <si>
+    <t>DRENAGEM E PAVIMENTAÇÃO - ITACURUÇÁ, MANGARATIBA/RJ</t>
+  </si>
+  <si>
+    <t>170026/000318/2022</t>
+  </si>
+  <si>
+    <t>048/2022</t>
+  </si>
+  <si>
+    <t>CANALIZAÇÃO DO CANAL DO LEITÃO - MANGARATIBA/RJ</t>
+  </si>
+  <si>
+    <t>170026/001231/2022</t>
+  </si>
+  <si>
+    <t>087/2022</t>
+  </si>
+  <si>
+    <t>PROJETO EXECUTIVO E ESTABILIZAÇÃO DE TALUDE EM MANGARATIBA/RJ</t>
+  </si>
+  <si>
+    <t>ECONORTE, MEIO AMBIENTE, INFRAESTRUTURA E SERVIÇOS LTDA</t>
+  </si>
+  <si>
+    <t>Mendes</t>
+  </si>
+  <si>
+    <t>330001/001217/2024</t>
+  </si>
+  <si>
+    <t>025/2024</t>
+  </si>
+  <si>
+    <t>CONTENÇÃO COM SOLO GRAMPEADO PRÓXIMO À KLABIN – MENDES/RJ (#FUNDO SOBERANO)</t>
+  </si>
+  <si>
+    <t>CONSÓRCIO MENDES KLABIN (MARENGE X DRV ENGENHARIA)</t>
+  </si>
+  <si>
+    <t>330018/000737/2022</t>
+  </si>
+  <si>
+    <t>005/2023</t>
+  </si>
+  <si>
+    <t>PROJETO, DRENAGEM E INFRAESTRUTURA - MENDES/RJ</t>
+  </si>
+  <si>
+    <t>CMHR EMPREENDIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>Miguel Pereira</t>
+  </si>
+  <si>
+    <t>170026/002388/2021</t>
+  </si>
+  <si>
+    <t>082/20022</t>
+  </si>
+  <si>
+    <t>CONSTRUÇÃO DE CAMPO DE GRAMA SINTÉTICA EM MANGUEIRAS – MIGUEL PEREIRA/RJ</t>
+  </si>
+  <si>
+    <t>WTE ENGENHARIA EIRELI</t>
+  </si>
+  <si>
+    <t>330018/001440/2022</t>
+  </si>
+  <si>
+    <t>028/2023</t>
+  </si>
+  <si>
+    <t>DRENAGEM E PAVIMENTAÇÃO - MIGUEL PEREIRA/RJ</t>
+  </si>
+  <si>
+    <t>170026/001837/2022</t>
+  </si>
+  <si>
+    <t>011/2024</t>
+  </si>
+  <si>
     <t>SUSPENSA</t>
   </si>
   <si>
-    <t>DRENAGEM E PAVIMENTAÇÃO NO BAIRRO NOVA BELEM – JAPERI/RJ</t>
-  </si>
-  <si>
-    <t>170026/002777/2021</t>
-  </si>
-  <si>
-    <t>034/2022</t>
-  </si>
-  <si>
-    <t>PROJETO EXECUTIVO E EXECUÇÃO DE OBRAS DE DRENAGEM, PAVIMENTAÇÃO E INFRAESTRUTURA – SÃO JOSÉ – JAPERI/RJ</t>
-  </si>
-  <si>
-    <t>CONSÓRCIO SÃO JOSÉ HM ( HYDRA ENGENHARIA E SANEAMENTO LTDA E CONSTRUTORA MEDEIROS CARVALHO DE ALMEIDA LTDA)</t>
-  </si>
-  <si>
-    <t>Macaé</t>
-  </si>
-  <si>
-    <t>170026/002217/2021</t>
-  </si>
-  <si>
-    <t>036/2022</t>
-  </si>
-  <si>
-    <t>REVITALIZAÇÃO DA AV. RUI BARBOSA - MACAÉ/RJ</t>
-  </si>
-  <si>
-    <t>KROFMAN COMERCIO SERVIÇO EIRELI ME</t>
-  </si>
-  <si>
-    <t>Magé</t>
-  </si>
-  <si>
-    <t>330018/000333/2022</t>
-  </si>
-  <si>
-    <t>023/2023</t>
-  </si>
-  <si>
-    <t>RECAPEAMENTO DE LOGRADOUROS EM MAGÉ – RJ</t>
-  </si>
-  <si>
-    <t>GRAVISA ENHENHARIA E EMPREENDIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>Mangaratiba</t>
-  </si>
-  <si>
-    <t>170026/001229/2022</t>
-  </si>
-  <si>
-    <t>080/2022</t>
-  </si>
-  <si>
-    <t>ESTABILIZAÇÃO DE TALUDE - RJ 014, MANGARATIBA/RJ</t>
-  </si>
-  <si>
-    <t>170026/001611/2020</t>
-  </si>
-  <si>
-    <t>028/2021</t>
-  </si>
-  <si>
-    <t>REVITALIZAÇÃO DA CICLOVIA E CALÇADA DA ORLA DA PRAIA DO SACO - MANGARATIBA/RJ</t>
-  </si>
-  <si>
-    <t>GONÇALVES E NEVES CONSTRUÇÃO CIVIL LTDA</t>
-  </si>
-  <si>
-    <t>170026/001230/2022</t>
-  </si>
-  <si>
-    <t>063/2020</t>
-  </si>
-  <si>
-    <t>ESTABILIZAÇÃO DE TALUDES - RUA LITORÂNEA, MANGARATIBA/RJ</t>
-  </si>
-  <si>
-    <t>RIVALL ENGENHARIA LTDA</t>
-  </si>
-  <si>
-    <t>170026/001228/2022</t>
-  </si>
-  <si>
-    <t>ESTABILIZAÇÃO DE TALUDE - VILA MURIQUI, MANGARATIBA/RJ</t>
-  </si>
-  <si>
-    <t>330001/001441/2024</t>
-  </si>
-  <si>
-    <t>005/2025</t>
-  </si>
-  <si>
-    <t>DRENAGEM E PAVIMENTAÇÃO - ITACURUÇÁ, MANGARATIBA/RJ</t>
-  </si>
-  <si>
-    <t>170026/000318/2022</t>
-  </si>
-  <si>
-    <t>048/2022</t>
-  </si>
-  <si>
-    <t>CANALIZAÇÃO DO CANAL DO LEITÃO - MANGARATIBA/RJ</t>
-  </si>
-  <si>
-    <t>170026/001231/2022</t>
-  </si>
-  <si>
-    <t>087/2022</t>
-  </si>
-  <si>
-    <t>PROJETO EXECUTIVO E ESTABILIZAÇÃO DE TALUDE EM MANGARATIBA/RJ</t>
-  </si>
-  <si>
-    <t>ECONORTE, MEIO AMBIENTE, INFRAESTRUTURA E SERVIÇOS LTDA</t>
-  </si>
-  <si>
-    <t>Mendes</t>
-  </si>
-  <si>
-    <t>330001/001217/2024</t>
-  </si>
-  <si>
-    <t>025/2024</t>
-  </si>
-  <si>
-    <t>CONTENÇÃO COM SOLO GRAMPEADO PRÓXIMO À KLABIN – MENDES/RJ (#FUNDO SOBERANO)</t>
-  </si>
-  <si>
-    <t>CONSÓRCIO MENDES KLABIN (MARENGE X DRV ENGENHARIA)</t>
-  </si>
-  <si>
-    <t>330018/000737/2022</t>
-  </si>
-  <si>
-    <t>005/2023</t>
-  </si>
-  <si>
-    <t>PROJETO, DRENAGEM E INFRAESTRUTURA - MENDES/RJ</t>
-  </si>
-  <si>
-    <t>CMHR EMPREENDIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>Miguel Pereira</t>
-  </si>
-  <si>
-    <t>170026/002388/2021</t>
-  </si>
-  <si>
-    <t>082/20022</t>
-  </si>
-  <si>
-    <t>CONSTRUÇÃO DE CAMPO DE GRAMA SINTÉTICA EM MANGUEIRAS – MIGUEL PEREIRA/RJ</t>
-  </si>
-  <si>
-    <t>WTE ENGENHARIA EIRELI</t>
-  </si>
-  <si>
-    <t>330018/001440/2022</t>
-  </si>
-  <si>
-    <t>028/2023</t>
-  </si>
-  <si>
-    <t>DRENAGEM E PAVIMENTAÇÃO - MIGUEL PEREIRA/RJ</t>
-  </si>
-  <si>
-    <t>170026/001837/2022</t>
-  </si>
-  <si>
-    <t>011/2024</t>
-  </si>
-  <si>
     <t>CONSTRUÇÃO DO CENTRO DE CONVENÇÕES JACKSON UCHOA VIANNA – MIGUEL PEREIRA/RJ</t>
   </si>
   <si>
+    <t>Natividade</t>
+  </si>
+  <si>
+    <t>330001/001238/2025</t>
+  </si>
+  <si>
+    <t>005/2026</t>
+  </si>
+  <si>
+    <t>RECONSTRUÇÃO DA ESCOLA CRECHE SEIS DE SETEMBRO - NATIVIDADE/RJ</t>
+  </si>
+  <si>
+    <t>ENEX CONSTRUÇÕES LTDA</t>
+  </si>
+  <si>
     <t>Nilópolis</t>
   </si>
   <si>
@@ -1451,9 +1466,6 @@
     <t>DEMOLIÇÃO E CONSTRUÇÃO DA PONTE SOBRE O RIO BOA ESPERANÇA – RIO BONITO/RJ</t>
   </si>
   <si>
-    <t>ENEX CONSTRUÇÕES LTDA</t>
-  </si>
-  <si>
     <t>Rio Claro</t>
   </si>
   <si>
@@ -1589,6 +1601,15 @@
     <t>CARLETTI CONSTRUCOES E SERVICOS LTDA</t>
   </si>
   <si>
+    <t>330001/000247/2025</t>
+  </si>
+  <si>
+    <t>015/2025</t>
+  </si>
+  <si>
+    <t>PAINÉIS DE MARCENARIA DO MIS</t>
+  </si>
+  <si>
     <t>170026/001763/2021</t>
   </si>
   <si>
@@ -1622,15 +1643,6 @@
     <t>CONSORCIO FACHADA MIS R2X/TANGRAN (CONSTRUTORA R2X E TANGRAN ENGENHARIA)</t>
   </si>
   <si>
-    <t>330001/000247/2025</t>
-  </si>
-  <si>
-    <t>015/2025</t>
-  </si>
-  <si>
-    <t>PAINÉIS DE MARCENARIA DO MIS</t>
-  </si>
-  <si>
     <t>170026/003470/2021</t>
   </si>
   <si>
@@ -1652,6 +1664,18 @@
     <t>ADESÃO DE ATA DE REGISTRO DE PREÇO PARA SERVIÇOS DE URBANIZAÇÃO, DIVIDIDOS EM 4 LOTES POR REGIÕES, (EXECUÇÃO DE CONSTRUÇÃO/RECUPERAÇÃO DE CALÇADAS, CICLOVIAS E PAVIMENTOS DE DIVERSOS TRECHOS DESCONTÍNUOS DE VIAS NÃO CADASTRADAS EM LOGRADOUROS PÚBLICOS MUNICIPAIS) A SER IMPLEMENTADO NAS IMEDIAÇÕES DAS HABITAÇÕES DE INTERESSE SOCIAL OU EM ÁREAS CONFIGURADAS COMO DE ESPECIAL INTERESSE SOCIAL - LOTE II (METROPOLITANA)</t>
   </si>
   <si>
+    <t>330001/000097/2024</t>
+  </si>
+  <si>
+    <t>012/2024</t>
+  </si>
+  <si>
+    <t>CONCLUSÃO DAS OBRAS DA NOVA SEDE DO MIS – RIO DE JANEIRO</t>
+  </si>
+  <si>
+    <t>CONSÓRCIO COPACABANA R2X/TANGRAN  (CONSTRUTORA R2X E TANGRAN ENGENHARIA)</t>
+  </si>
+  <si>
     <t>E-17/026/1514/2019</t>
   </si>
   <si>
@@ -1673,18 +1697,6 @@
     <t>CONSTRUPOWER ENGENHARIA LTDA</t>
   </si>
   <si>
-    <t>330001/000097/2024</t>
-  </si>
-  <si>
-    <t>012/2024</t>
-  </si>
-  <si>
-    <t>CONCLUSÃO DAS OBRAS DA NOVA SEDE DO MIS – RIO DE JANEIRO</t>
-  </si>
-  <si>
-    <t>CONSÓRCIO COPACABANA R2X/TANGRAN  (CONSTRUTORA R2X E TANGRAN ENGENHARIA)</t>
-  </si>
-  <si>
     <t>170026/000277/2021</t>
   </si>
   <si>
@@ -1727,6 +1739,15 @@
     <t>ATA DE REGISTRO DE PREÇO PARA SERVIÇO DE PAVIMENTAÇÃO COM ASTALTO CBUQ- DIVERSOS MUNICIPÍOS</t>
   </si>
   <si>
+    <t>Não existe na tabela Contratadas</t>
+  </si>
+  <si>
+    <t>330001/000113/2026</t>
+  </si>
+  <si>
+    <t>INFRAESTRUTURA URBANA DE RECUPERAÇÃO DE CALÇADAS, CICLOVIAS E PAVIMENTAÇÕES DE DIVERSOS LOGRADOUROS (LOTE 1 - METROPOLITANA E LOTE 2 - 2 SERRANA E CENTRO NORTE)</t>
+  </si>
+  <si>
     <t>170026/000214/2022</t>
   </si>
   <si>
@@ -1752,9 +1773,6 @@
   </si>
   <si>
     <t>CONTRATAÇÃO DE UMA EMPRESA ESPECIALIZADA NA EXECUÇÃO DE SERVIÇOS DE ESTABILIZAÇÃO DE SOLOS COM ESTABILIZADOR IÔNICO LÍQUIDO, COM PROPRIEDADES DE AUMENTO DA RESISTÊNCIA DO SOLO E RESISTÊNCIA À ÁGUA, 100% AMBIENTALMENTE SUSTENTÁVEL, MONOCOMPONENTE, APLICADO IN SITU, COM O FORNECIMENTO DE TODOS OS EQUIPAMENTOS, MAQUINÁRIO, MÃO DE OBRA E TODOS OS MATERIAIS NECESSÁRIOS PARA CADA TIPO DE SERVIÇO, CONFORME AS CONDIÇÕES E EXIGÊNCIAS ESTABELECIDAS.</t>
-  </si>
-  <si>
-    <t>Não existe na tabela Contratadas</t>
   </si>
   <si>
     <t>São Francisco de Itabapoana</t>
@@ -2413,7 +2431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L171"/>
+  <dimension ref="A1:L173"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" style="1" customWidth="1"/>
@@ -2640,16 +2658,16 @@
         <v>36</v>
       </c>
       <c r="G6" s="11">
-        <v>0.2004</v>
+        <v>0.33159999999999995</v>
       </c>
       <c r="H6" s="12">
         <v>18990162.94</v>
       </c>
       <c r="I6" s="13">
-        <v>3806174.66</v>
+        <v>6297414.64</v>
       </c>
       <c r="J6" s="12">
-        <v>15183988.280000001</v>
+        <v>12692748.3</v>
       </c>
       <c r="K6" s="14">
         <v>45868</v>
@@ -2944,16 +2962,16 @@
         <v>40</v>
       </c>
       <c r="G14" s="11">
-        <v>0.5746</v>
+        <v>0.6143</v>
       </c>
       <c r="H14" s="12">
         <v>22825141.32</v>
       </c>
       <c r="I14" s="13">
-        <v>13115141.81</v>
+        <v>14020616.05</v>
       </c>
       <c r="J14" s="12">
-        <v>9709999.51</v>
+        <v>8804525.27</v>
       </c>
       <c r="K14" s="14">
         <v>45019</v>
@@ -3073,7 +3091,7 @@
         <v>45917</v>
       </c>
       <c r="L17" s="14">
-        <v>46097</v>
+        <v>46278</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -3286,16 +3304,16 @@
         <v>107</v>
       </c>
       <c r="G23" s="11">
-        <v>0.6714</v>
+        <v>0.6853</v>
       </c>
       <c r="H23" s="12">
         <v>48872552.26</v>
       </c>
       <c r="I23" s="13">
-        <v>32814331.78</v>
+        <v>33494376.98</v>
       </c>
       <c r="J23" s="12">
-        <v>16058220.479999997</v>
+        <v>15378175.279999997</v>
       </c>
       <c r="K23" s="14">
         <v>44875</v>
@@ -4008,16 +4026,16 @@
         <v>40</v>
       </c>
       <c r="G42" s="11">
-        <v>0.5414</v>
+        <v>0.5587</v>
       </c>
       <c r="H42" s="12">
         <v>26504288.68</v>
       </c>
       <c r="I42" s="13">
-        <v>14348711.09</v>
+        <v>14807551.24</v>
       </c>
       <c r="J42" s="12">
-        <v>12155577.59</v>
+        <v>11696737.44</v>
       </c>
       <c r="K42" s="14">
         <v>45190</v>
@@ -4645,10 +4663,10 @@
         <v>245</v>
       </c>
       <c r="D59" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E59" s="11" t="s">
         <v>246</v>
-      </c>
-      <c r="E59" s="11" t="s">
-        <v>247</v>
       </c>
       <c r="F59" s="11" t="s">
         <v>241</v>
@@ -4677,19 +4695,19 @@
         <v>237</v>
       </c>
       <c r="B60" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="C60" s="11" t="s">
         <v>248</v>
-      </c>
-      <c r="C60" s="11" t="s">
-        <v>249</v>
       </c>
       <c r="D60" s="11" t="s">
         <v>20</v>
       </c>
       <c r="E60" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="F60" s="11" t="s">
         <v>250</v>
-      </c>
-      <c r="F60" s="11" t="s">
-        <v>251</v>
       </c>
       <c r="G60" s="11">
         <v>0.4113</v>
@@ -4712,22 +4730,22 @@
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="B61" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="B61" s="11" t="s">
+      <c r="C61" s="11" t="s">
         <v>253</v>
-      </c>
-      <c r="C61" s="11" t="s">
-        <v>254</v>
       </c>
       <c r="D61" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E61" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="F61" s="11" t="s">
         <v>255</v>
-      </c>
-      <c r="F61" s="11" t="s">
-        <v>256</v>
       </c>
       <c r="G61" s="11">
         <v>0.97</v>
@@ -4750,22 +4768,22 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="B62" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="B62" s="11" t="s">
+      <c r="C62" s="11" t="s">
         <v>258</v>
-      </c>
-      <c r="C62" s="11" t="s">
-        <v>259</v>
       </c>
       <c r="D62" s="11" t="s">
         <v>20</v>
       </c>
       <c r="E62" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="F62" s="11" t="s">
         <v>260</v>
-      </c>
-      <c r="F62" s="11" t="s">
-        <v>261</v>
       </c>
       <c r="G62" s="11">
         <v>0.8092</v>
@@ -4788,19 +4806,19 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="B63" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="B63" s="11" t="s">
+      <c r="C63" s="11" t="s">
         <v>263</v>
-      </c>
-      <c r="C63" s="11" t="s">
-        <v>264</v>
       </c>
       <c r="D63" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F63" s="11" t="s">
         <v>17</v>
@@ -4826,22 +4844,22 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B64" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="C64" s="11" t="s">
         <v>266</v>
-      </c>
-      <c r="C64" s="11" t="s">
-        <v>267</v>
       </c>
       <c r="D64" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E64" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="F64" s="11" t="s">
         <v>268</v>
-      </c>
-      <c r="F64" s="11" t="s">
-        <v>269</v>
       </c>
       <c r="G64" s="11">
         <v>0.9765999999999999</v>
@@ -4864,22 +4882,22 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B65" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="C65" s="11" t="s">
         <v>270</v>
-      </c>
-      <c r="C65" s="11" t="s">
-        <v>271</v>
       </c>
       <c r="D65" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E65" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="F65" s="11" t="s">
         <v>272</v>
-      </c>
-      <c r="F65" s="11" t="s">
-        <v>273</v>
       </c>
       <c r="G65" s="11">
         <v>0.9577</v>
@@ -4902,10 +4920,10 @@
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C66" s="11" t="s">
         <v>63</v>
@@ -4914,7 +4932,7 @@
         <v>15</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F66" s="11" t="s">
         <v>93</v>
@@ -4940,19 +4958,19 @@
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B67" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="C67" s="11" t="s">
         <v>276</v>
-      </c>
-      <c r="C67" s="11" t="s">
-        <v>277</v>
       </c>
       <c r="D67" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F67" s="11" t="s">
         <v>36</v>
@@ -4978,19 +4996,19 @@
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" s="11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B68" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="C68" s="11" t="s">
         <v>279</v>
-      </c>
-      <c r="C68" s="11" t="s">
-        <v>280</v>
       </c>
       <c r="D68" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F68" s="11" t="s">
         <v>45</v>
@@ -5016,22 +5034,22 @@
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B69" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="C69" s="11" t="s">
         <v>282</v>
-      </c>
-      <c r="C69" s="11" t="s">
-        <v>283</v>
       </c>
       <c r="D69" s="11" t="s">
         <v>20</v>
       </c>
       <c r="E69" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="F69" s="11" t="s">
         <v>284</v>
-      </c>
-      <c r="F69" s="11" t="s">
-        <v>285</v>
       </c>
       <c r="G69" s="11">
         <v>0.47490000000000004</v>
@@ -5054,22 +5072,22 @@
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="B70" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="B70" s="11" t="s">
+      <c r="C70" s="11" t="s">
         <v>287</v>
-      </c>
-      <c r="C70" s="11" t="s">
-        <v>288</v>
       </c>
       <c r="D70" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E70" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="F70" s="11" t="s">
         <v>289</v>
-      </c>
-      <c r="F70" s="11" t="s">
-        <v>290</v>
       </c>
       <c r="G70" s="11">
         <v>0.9969</v>
@@ -5092,22 +5110,22 @@
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" s="11" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B71" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="C71" s="11" t="s">
         <v>291</v>
-      </c>
-      <c r="C71" s="11" t="s">
-        <v>292</v>
       </c>
       <c r="D71" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E71" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="F71" s="11" t="s">
         <v>293</v>
-      </c>
-      <c r="F71" s="11" t="s">
-        <v>294</v>
       </c>
       <c r="G71" s="11">
         <v>0.8062999999999999</v>
@@ -5130,22 +5148,22 @@
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="B72" s="11" t="s">
         <v>295</v>
       </c>
-      <c r="B72" s="11" t="s">
+      <c r="C72" s="11" t="s">
         <v>296</v>
-      </c>
-      <c r="C72" s="11" t="s">
-        <v>297</v>
       </c>
       <c r="D72" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E72" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="F72" s="11" t="s">
         <v>298</v>
-      </c>
-      <c r="F72" s="11" t="s">
-        <v>299</v>
       </c>
       <c r="G72" s="11">
         <v>1</v>
@@ -5168,19 +5186,19 @@
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" s="11" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B73" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="C73" s="11" t="s">
         <v>300</v>
-      </c>
-      <c r="C73" s="11" t="s">
-        <v>301</v>
       </c>
       <c r="D73" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F73" s="11" t="s">
         <v>45</v>
@@ -5206,16 +5224,16 @@
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" s="11" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B74" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="C74" s="11" t="s">
         <v>303</v>
       </c>
-      <c r="C74" s="11" t="s">
+      <c r="D74" s="11" t="s">
         <v>304</v>
-      </c>
-      <c r="D74" s="11" t="s">
-        <v>246</v>
       </c>
       <c r="E74" s="11" t="s">
         <v>305</v>
@@ -5253,7 +5271,7 @@
         <v>308</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E75" s="11" t="s">
         <v>309</v>
@@ -5262,217 +5280,217 @@
         <v>310</v>
       </c>
       <c r="G75" s="11">
-        <v>0.8991</v>
+        <v>0</v>
       </c>
       <c r="H75" s="12">
-        <v>666913.68</v>
+        <v>2960000</v>
       </c>
       <c r="I75" s="13">
-        <v>599641.31</v>
+        <v>0</v>
       </c>
       <c r="J75" s="12">
-        <v>67272.37</v>
-      </c>
-      <c r="K75" s="14">
-        <v>45783</v>
-      </c>
-      <c r="L75" s="14">
-        <v>45964</v>
+        <v>2960000</v>
+      </c>
+      <c r="K75" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="L75" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="11" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E76" s="11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="G76" s="11">
-        <v>0.8976000000000001</v>
+        <v>0.8991</v>
       </c>
       <c r="H76" s="12">
-        <v>763285.07</v>
+        <v>666913.68</v>
       </c>
       <c r="I76" s="13">
-        <v>685145.56</v>
+        <v>599641.31</v>
       </c>
       <c r="J76" s="12">
-        <v>78139.5099999999</v>
+        <v>67272.37</v>
       </c>
       <c r="K76" s="14">
         <v>45783</v>
       </c>
       <c r="L76" s="14">
-        <v>46115</v>
+        <v>45964</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="11" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C77" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="D77" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E77" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="F77" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="D77" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E77" s="11" t="s">
-        <v>316</v>
-      </c>
-      <c r="F77" s="11" t="s">
-        <v>73</v>
-      </c>
       <c r="G77" s="11">
-        <v>0.9495</v>
+        <v>0.8976000000000001</v>
       </c>
       <c r="H77" s="12">
-        <v>32836774.76</v>
+        <v>763285.07</v>
       </c>
       <c r="I77" s="13">
-        <v>31178236.21</v>
+        <v>685145.56</v>
       </c>
       <c r="J77" s="12">
-        <v>1658538.5500000007</v>
+        <v>78139.5099999999</v>
       </c>
       <c r="K77" s="14">
-        <v>44564</v>
+        <v>45783</v>
       </c>
       <c r="L77" s="14">
-        <v>44944</v>
+        <v>46115</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="11" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D78" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E78" s="11" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F78" s="11" t="s">
-        <v>170</v>
+        <v>73</v>
       </c>
       <c r="G78" s="11">
-        <v>0.9543</v>
+        <v>0.9495</v>
       </c>
       <c r="H78" s="12">
-        <v>36880209</v>
+        <v>32836774.76</v>
       </c>
       <c r="I78" s="13">
-        <v>35196032.93</v>
+        <v>31178236.21</v>
       </c>
       <c r="J78" s="12">
-        <v>1684176.0700000003</v>
+        <v>1658538.5500000007</v>
       </c>
       <c r="K78" s="14">
-        <v>44648</v>
+        <v>44564</v>
       </c>
       <c r="L78" s="14">
-        <v>45498</v>
+        <v>44944</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="11" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E79" s="11" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F79" s="11" t="s">
-        <v>323</v>
+        <v>170</v>
       </c>
       <c r="G79" s="11">
-        <v>0.0134</v>
+        <v>0.9543</v>
       </c>
       <c r="H79" s="12">
-        <v>4705907.3</v>
+        <v>36880209</v>
       </c>
       <c r="I79" s="13">
-        <v>63006.28</v>
+        <v>35196032.93</v>
       </c>
       <c r="J79" s="12">
-        <v>4642901.02</v>
+        <v>1684176.0700000003</v>
       </c>
       <c r="K79" s="14">
-        <v>46009</v>
+        <v>44648</v>
       </c>
       <c r="L79" s="14">
-        <v>46189</v>
+        <v>45498</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" s="11" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D80" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E80" s="11" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F80" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G80" s="11">
-        <v>0.5292</v>
+        <v>0.0274</v>
       </c>
       <c r="H80" s="12">
-        <v>10349390.52</v>
+        <v>4705907.3</v>
       </c>
       <c r="I80" s="13">
-        <v>5476795.79</v>
+        <v>128869.78</v>
       </c>
       <c r="J80" s="12">
-        <v>4872594.7299999995</v>
+        <v>4577037.52</v>
       </c>
       <c r="K80" s="14">
-        <v>45867</v>
+        <v>46009</v>
       </c>
       <c r="L80" s="14">
-        <v>46227</v>
+        <v>46190</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" s="11" t="s">
-        <v>328</v>
+        <v>311</v>
       </c>
       <c r="B81" s="11" t="s">
         <v>329</v>
@@ -5481,561 +5499,561 @@
         <v>330</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E81" s="11" t="s">
         <v>331</v>
       </c>
       <c r="F81" s="11" t="s">
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="G81" s="11">
-        <v>1</v>
+        <v>0.4253</v>
       </c>
       <c r="H81" s="12">
-        <v>1923627.23</v>
+        <v>12878551.89</v>
       </c>
       <c r="I81" s="13">
-        <v>1923627.26</v>
+        <v>5476795.79</v>
       </c>
       <c r="J81" s="12">
-        <v>-0.030000000027939677</v>
+        <v>7401756.100000001</v>
       </c>
       <c r="K81" s="14">
-        <v>44708</v>
+        <v>45867</v>
       </c>
       <c r="L81" s="14">
-        <v>45640</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" s="11" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D82" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E82" s="11" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>335</v>
+        <v>315</v>
       </c>
       <c r="G82" s="11">
         <v>1</v>
       </c>
       <c r="H82" s="12">
-        <v>3552093.82</v>
+        <v>1923627.23</v>
       </c>
       <c r="I82" s="13">
-        <v>3552073.13</v>
+        <v>1923627.26</v>
       </c>
       <c r="J82" s="12">
-        <v>20.68999999994412</v>
+        <v>-0.030000000027939677</v>
       </c>
       <c r="K82" s="14">
-        <v>45034</v>
+        <v>44708</v>
       </c>
       <c r="L82" s="14">
-        <v>45034</v>
+        <v>45640</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" s="11" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>254</v>
+        <v>338</v>
       </c>
       <c r="D83" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E83" s="11" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F83" s="11" t="s">
-        <v>22</v>
+        <v>340</v>
       </c>
       <c r="G83" s="11">
-        <v>0.9723</v>
+        <v>1</v>
       </c>
       <c r="H83" s="12">
-        <v>15078640.21</v>
+        <v>3552093.82</v>
       </c>
       <c r="I83" s="13">
-        <v>14660282.37</v>
+        <v>3552073.13</v>
       </c>
       <c r="J83" s="12">
-        <v>418357.8400000017</v>
+        <v>20.68999999994412</v>
       </c>
       <c r="K83" s="14">
-        <v>45497</v>
+        <v>45034</v>
       </c>
       <c r="L83" s="14">
-        <v>45301</v>
+        <v>45034</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" s="11" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>339</v>
+        <v>253</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E84" s="11" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F84" s="11" t="s">
-        <v>341</v>
+        <v>22</v>
       </c>
       <c r="G84" s="11">
-        <v>0.948</v>
+        <v>0.9723</v>
       </c>
       <c r="H84" s="12">
-        <v>59148617.81</v>
+        <v>15078640.21</v>
       </c>
       <c r="I84" s="13">
-        <v>56075178.64</v>
+        <v>14660282.37</v>
       </c>
       <c r="J84" s="12">
-        <v>3073439.170000002</v>
+        <v>418357.8400000017</v>
       </c>
       <c r="K84" s="14">
-        <v>44726</v>
+        <v>45497</v>
       </c>
       <c r="L84" s="14">
-        <v>46006</v>
+        <v>45301</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" s="11" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="B85" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="C85" s="11"/>
+      <c r="C85" s="11" t="s">
+        <v>344</v>
+      </c>
       <c r="D85" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E85" s="11" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F85" s="11" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G85" s="11">
-        <v>0</v>
+        <v>0.948</v>
       </c>
       <c r="H85" s="12">
-        <v>62980000</v>
+        <v>59148617.81</v>
       </c>
       <c r="I85" s="13">
-        <v>62980000</v>
+        <v>56075178.64</v>
       </c>
       <c r="J85" s="12">
-        <v>0</v>
+        <v>3073439.170000002</v>
       </c>
       <c r="K85" s="14">
-        <v>43930</v>
+        <v>44726</v>
       </c>
       <c r="L85" s="14">
-        <v>44011</v>
+        <v>46006</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" s="11" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>346</v>
-      </c>
-      <c r="C86" s="11" t="s">
-        <v>347</v>
-      </c>
+        <v>348</v>
+      </c>
+      <c r="C86" s="11"/>
       <c r="D86" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E86" s="11" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F86" s="11" t="s">
-        <v>208</v>
+        <v>350</v>
       </c>
       <c r="G86" s="11">
-        <v>0.9976999999999999</v>
+        <v>0</v>
       </c>
       <c r="H86" s="12">
-        <v>19451386.88</v>
+        <v>62980000</v>
       </c>
       <c r="I86" s="13">
-        <v>19406169.39</v>
+        <v>62980000</v>
       </c>
       <c r="J86" s="12">
-        <v>45217.48999999836</v>
+        <v>0</v>
       </c>
       <c r="K86" s="14">
-        <v>45247</v>
+        <v>43930</v>
       </c>
       <c r="L86" s="14">
-        <v>46001</v>
+        <v>44011</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" s="11" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D87" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E87" s="11" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F87" s="11" t="s">
-        <v>40</v>
+        <v>208</v>
       </c>
       <c r="G87" s="11">
-        <v>0.9666</v>
+        <v>0.9976999999999999</v>
       </c>
       <c r="H87" s="12">
-        <v>20106028.53</v>
+        <v>19451386.88</v>
       </c>
       <c r="I87" s="13">
-        <v>19434508.22</v>
+        <v>19406169.39</v>
       </c>
       <c r="J87" s="12">
-        <v>671520.3100000024</v>
+        <v>45217.48999999836</v>
       </c>
       <c r="K87" s="14">
-        <v>44991</v>
+        <v>45247</v>
       </c>
       <c r="L87" s="14">
-        <v>46094</v>
+        <v>46001</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" s="11" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>144</v>
+        <v>355</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E88" s="11" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F88" s="11" t="s">
-        <v>163</v>
+        <v>40</v>
       </c>
       <c r="G88" s="11">
-        <v>0.9577</v>
+        <v>0.9666</v>
       </c>
       <c r="H88" s="12">
-        <v>34508101.15</v>
+        <v>20106028.53</v>
       </c>
       <c r="I88" s="13">
-        <v>33048630.33</v>
+        <v>19434508.22</v>
       </c>
       <c r="J88" s="12">
-        <v>1459470.8200000003</v>
+        <v>671520.3100000024</v>
       </c>
       <c r="K88" s="14">
-        <v>44690</v>
+        <v>44991</v>
       </c>
       <c r="L88" s="14">
-        <v>45621</v>
+        <v>46184</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" s="11" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>355</v>
+        <v>144</v>
       </c>
       <c r="D89" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E89" s="11" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F89" s="11" t="s">
-        <v>357</v>
+        <v>163</v>
       </c>
       <c r="G89" s="11">
-        <v>0.9711</v>
+        <v>0.9577</v>
       </c>
       <c r="H89" s="12">
-        <v>58086688.76</v>
+        <v>34508101.15</v>
       </c>
       <c r="I89" s="13">
-        <v>56408550.91</v>
+        <v>33048630.33</v>
       </c>
       <c r="J89" s="12">
-        <v>1678137.8500000015</v>
+        <v>1459470.8200000003</v>
       </c>
       <c r="K89" s="14">
-        <v>44831</v>
+        <v>44690</v>
       </c>
       <c r="L89" s="14">
-        <v>45619</v>
+        <v>45621</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" s="11" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D90" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E90" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F90" s="11" t="s">
-        <v>222</v>
+        <v>362</v>
       </c>
       <c r="G90" s="11">
-        <v>0.6973</v>
+        <v>0.9711</v>
       </c>
       <c r="H90" s="12">
-        <v>28459856.91</v>
+        <v>58086688.76</v>
       </c>
       <c r="I90" s="13">
-        <v>19844966.58</v>
+        <v>56408550.91</v>
       </c>
       <c r="J90" s="12">
-        <v>8614890.330000002</v>
+        <v>1678137.8500000015</v>
       </c>
       <c r="K90" s="14">
-        <v>45035</v>
+        <v>44831</v>
       </c>
       <c r="L90" s="14">
-        <v>46205</v>
+        <v>45619</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" s="11" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D91" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E91" s="11" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F91" s="11" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="G91" s="11">
-        <v>0.7805</v>
+        <v>0.6973</v>
       </c>
       <c r="H91" s="12">
-        <v>45862409.69</v>
+        <v>28459856.91</v>
       </c>
       <c r="I91" s="13">
-        <v>35796161.98</v>
+        <v>19844966.58</v>
       </c>
       <c r="J91" s="12">
-        <v>10066247.71</v>
+        <v>8614890.330000002</v>
       </c>
       <c r="K91" s="14">
-        <v>45352</v>
+        <v>45035</v>
       </c>
       <c r="L91" s="14">
-        <v>46255</v>
+        <v>46205</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" s="11" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E92" s="11" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F92" s="11" t="s">
-        <v>163</v>
+        <v>212</v>
       </c>
       <c r="G92" s="11">
-        <v>0.0132</v>
+        <v>0.7805</v>
       </c>
       <c r="H92" s="12">
-        <v>11494433.26</v>
+        <v>45862409.69</v>
       </c>
       <c r="I92" s="13">
-        <v>151285.62</v>
+        <v>35796161.98</v>
       </c>
       <c r="J92" s="12">
-        <v>11343147.64</v>
+        <v>10066247.71</v>
       </c>
       <c r="K92" s="14">
-        <v>45105</v>
+        <v>45352</v>
       </c>
       <c r="L92" s="14">
-        <v>45706</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" s="11" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>178</v>
+        <v>370</v>
       </c>
       <c r="D93" s="11" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E93" s="11" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F93" s="11" t="s">
-        <v>370</v>
+        <v>163</v>
       </c>
       <c r="G93" s="11">
-        <v>0.898</v>
+        <v>0.0132</v>
       </c>
       <c r="H93" s="12">
-        <v>1212482.21</v>
+        <v>11494433.26</v>
       </c>
       <c r="I93" s="13">
-        <v>1088826.01</v>
+        <v>151285.62</v>
       </c>
       <c r="J93" s="12">
-        <v>123656.19999999995</v>
+        <v>11343147.64</v>
       </c>
       <c r="K93" s="14">
-        <v>44326</v>
+        <v>45105</v>
       </c>
       <c r="L93" s="14">
-        <v>44536</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" s="11" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>372</v>
+        <v>178</v>
       </c>
       <c r="D94" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E94" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F94" s="11" t="s">
-        <v>57</v>
+        <v>375</v>
       </c>
       <c r="G94" s="11">
-        <v>0.9209</v>
+        <v>0.898</v>
       </c>
       <c r="H94" s="12">
-        <v>12560309.12</v>
+        <v>1212482.21</v>
       </c>
       <c r="I94" s="13">
-        <v>11566432.39</v>
+        <v>1088826.01</v>
       </c>
       <c r="J94" s="12">
-        <v>993876.7299999986</v>
+        <v>123656.19999999995</v>
       </c>
       <c r="K94" s="14">
-        <v>44831</v>
+        <v>44326</v>
       </c>
       <c r="L94" s="14">
-        <v>45477</v>
+        <v>44536</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" s="11" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D95" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E95" s="11" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F95" s="11" t="s">
-        <v>378</v>
+        <v>57</v>
       </c>
       <c r="G95" s="11">
-        <v>0.9990000000000001</v>
+        <v>0.9209</v>
       </c>
       <c r="H95" s="12">
-        <v>17695067.23</v>
+        <v>12560309.12</v>
       </c>
       <c r="I95" s="13">
-        <v>17677149.84</v>
+        <v>11566432.39</v>
       </c>
       <c r="J95" s="12">
-        <v>17917.390000000596</v>
+        <v>993876.7299999986</v>
       </c>
       <c r="K95" s="14">
-        <v>44994</v>
+        <v>44831</v>
       </c>
       <c r="L95" s="14">
-        <v>45928</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
@@ -6046,381 +6064,381 @@
         <v>380</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>101</v>
+        <v>381</v>
       </c>
       <c r="D96" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E96" s="11" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F96" s="11" t="s">
-        <v>17</v>
+        <v>383</v>
       </c>
       <c r="G96" s="11">
-        <v>1</v>
+        <v>0.9990000000000001</v>
       </c>
       <c r="H96" s="12">
-        <v>12092480.69</v>
+        <v>17695067.23</v>
       </c>
       <c r="I96" s="13">
-        <v>12092480.69</v>
+        <v>17677149.84</v>
       </c>
       <c r="J96" s="12">
-        <v>0</v>
+        <v>17917.390000000596</v>
       </c>
       <c r="K96" s="14">
-        <v>44734</v>
+        <v>44994</v>
       </c>
       <c r="L96" s="14">
-        <v>45202</v>
+        <v>45928</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" s="11" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="D97" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E97" s="11" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="F97" s="11" t="s">
-        <v>384</v>
+        <v>17</v>
       </c>
       <c r="G97" s="11">
-        <v>0.9117000000000001</v>
+        <v>1</v>
       </c>
       <c r="H97" s="12">
-        <v>5978542.15</v>
+        <v>12092480.69</v>
       </c>
       <c r="I97" s="13">
-        <v>5450477.04</v>
+        <v>12092480.69</v>
       </c>
       <c r="J97" s="12">
-        <v>528065.1100000003</v>
+        <v>0</v>
       </c>
       <c r="K97" s="14">
-        <v>44753</v>
+        <v>44734</v>
       </c>
       <c r="L97" s="14">
-        <v>44933</v>
+        <v>45202</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" s="11" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>386</v>
+        <v>126</v>
       </c>
       <c r="D98" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E98" s="11" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F98" s="11" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G98" s="11">
-        <v>0.8362</v>
+        <v>0.9117000000000001</v>
       </c>
       <c r="H98" s="12">
-        <v>11942741.09</v>
+        <v>5978542.15</v>
       </c>
       <c r="I98" s="13">
-        <v>9986334.63</v>
+        <v>5450477.04</v>
       </c>
       <c r="J98" s="12">
-        <v>1956406.459999999</v>
+        <v>528065.1100000003</v>
       </c>
       <c r="K98" s="14">
-        <v>44734</v>
+        <v>44753</v>
       </c>
       <c r="L98" s="14">
-        <v>45098</v>
+        <v>44933</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" s="11" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D99" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E99" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F99" s="11" t="s">
-        <v>285</v>
+        <v>393</v>
       </c>
       <c r="G99" s="11">
-        <v>0.7289</v>
+        <v>0.8362</v>
       </c>
       <c r="H99" s="12">
-        <v>8684179.36</v>
+        <v>11942741.09</v>
       </c>
       <c r="I99" s="13">
-        <v>6330271.19</v>
+        <v>9986334.63</v>
       </c>
       <c r="J99" s="12">
-        <v>2353908.169999999</v>
+        <v>1956406.459999999</v>
       </c>
       <c r="K99" s="14">
-        <v>45848</v>
+        <v>44734</v>
       </c>
       <c r="L99" s="14">
-        <v>46222</v>
+        <v>45098</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" s="11" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D100" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E100" s="11" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F100" s="11" t="s">
-        <v>388</v>
+        <v>284</v>
       </c>
       <c r="G100" s="11">
-        <v>0.9493</v>
+        <v>0.7289</v>
       </c>
       <c r="H100" s="12">
-        <v>48302952.43</v>
+        <v>8684179.36</v>
       </c>
       <c r="I100" s="13">
-        <v>45853223.3</v>
+        <v>6330271.19</v>
       </c>
       <c r="J100" s="12">
-        <v>2449729.1300000027</v>
+        <v>2353908.169999999</v>
       </c>
       <c r="K100" s="14">
-        <v>45189</v>
+        <v>45848</v>
       </c>
       <c r="L100" s="14">
-        <v>45729</v>
+        <v>46222</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" s="11" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D101" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E101" s="11" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F101" s="11" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G101" s="11">
-        <v>0.9181999999999999</v>
+        <v>0.9493</v>
       </c>
       <c r="H101" s="12">
-        <v>30543662.31</v>
+        <v>48302952.43</v>
       </c>
       <c r="I101" s="13">
-        <v>28044628.6</v>
+        <v>45853223.3</v>
       </c>
       <c r="J101" s="12">
-        <v>2499033.709999997</v>
+        <v>2449729.1300000027</v>
       </c>
       <c r="K101" s="14">
-        <v>44826</v>
+        <v>45189</v>
       </c>
       <c r="L101" s="14">
-        <v>45540</v>
+        <v>45729</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" s="11" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D102" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E102" s="11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F102" s="11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G102" s="11">
-        <v>0.9188</v>
+        <v>0.9181999999999999</v>
       </c>
       <c r="H102" s="12">
-        <v>54913544.95</v>
+        <v>30543662.31</v>
       </c>
       <c r="I102" s="13">
-        <v>50454918.61</v>
+        <v>28044628.6</v>
       </c>
       <c r="J102" s="12">
-        <v>4458626.340000004</v>
+        <v>2499033.709999997</v>
       </c>
       <c r="K102" s="14">
-        <v>44769</v>
+        <v>44826</v>
       </c>
       <c r="L102" s="14">
-        <v>45174</v>
+        <v>45540</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" s="11" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D103" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E103" s="11" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F103" s="11" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="G103" s="11">
-        <v>0.7935</v>
+        <v>0.9188</v>
       </c>
       <c r="H103" s="12">
-        <v>27434724</v>
+        <v>54913544.95</v>
       </c>
       <c r="I103" s="13">
-        <v>21770451.06</v>
+        <v>50454918.61</v>
       </c>
       <c r="J103" s="12">
-        <v>5664272.940000001</v>
+        <v>4458626.340000004</v>
       </c>
       <c r="K103" s="14">
-        <v>46002</v>
+        <v>44769</v>
       </c>
       <c r="L103" s="14">
-        <v>46242</v>
+        <v>45174</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" s="11" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D104" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E104" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F104" s="11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="G104" s="11">
-        <v>0.9224</v>
+        <v>0.7935</v>
       </c>
       <c r="H104" s="12">
-        <v>80552394.92</v>
+        <v>27434724</v>
       </c>
       <c r="I104" s="13">
-        <v>74305045.47</v>
+        <v>21770451.06</v>
       </c>
       <c r="J104" s="12">
-        <v>6247349.450000003</v>
+        <v>5664272.940000001</v>
       </c>
       <c r="K104" s="14">
-        <v>44709</v>
+        <v>46002</v>
       </c>
       <c r="L104" s="14">
-        <v>45114</v>
+        <v>46242</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" s="11" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D105" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E105" s="11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F105" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G105" s="11">
-        <v>0.4476</v>
+        <v>0.9224</v>
       </c>
       <c r="H105" s="12">
-        <v>68148567.14</v>
+        <v>80552394.92</v>
       </c>
       <c r="I105" s="13">
-        <v>30502735.41</v>
+        <v>74305045.47</v>
       </c>
       <c r="J105" s="12">
-        <v>37645831.730000004</v>
+        <v>6247349.450000003</v>
       </c>
       <c r="K105" s="14">
-        <v>44767</v>
+        <v>44709</v>
       </c>
       <c r="L105" s="14">
-        <v>45173</v>
+        <v>45114</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" s="11" t="s">
-        <v>415</v>
+        <v>384</v>
       </c>
       <c r="B106" s="11" t="s">
         <v>416</v>
@@ -6438,217 +6456,217 @@
         <v>419</v>
       </c>
       <c r="G106" s="11">
-        <v>0.9984000000000001</v>
+        <v>0.4476</v>
       </c>
       <c r="H106" s="12">
-        <v>1498793.43</v>
+        <v>68148567.14</v>
       </c>
       <c r="I106" s="13">
-        <v>1496414.32</v>
+        <v>30502735.41</v>
       </c>
       <c r="J106" s="12">
-        <v>2379.1099999998696</v>
+        <v>37645831.730000004</v>
       </c>
       <c r="K106" s="14">
-        <v>45195</v>
+        <v>44767</v>
       </c>
       <c r="L106" s="14">
-        <v>45121</v>
+        <v>45173</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107" s="11" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D107" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E107" s="11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F107" s="11" t="s">
-        <v>299</v>
+        <v>424</v>
       </c>
       <c r="G107" s="11">
-        <v>0.9718000000000001</v>
+        <v>0.9984000000000001</v>
       </c>
       <c r="H107" s="12">
-        <v>1988555.07</v>
+        <v>1498793.43</v>
       </c>
       <c r="I107" s="13">
-        <v>1932548.63</v>
+        <v>1496414.32</v>
       </c>
       <c r="J107" s="12">
-        <v>56006.44000000018</v>
+        <v>2379.1099999998696</v>
       </c>
       <c r="K107" s="14">
-        <v>44742</v>
+        <v>45195</v>
       </c>
       <c r="L107" s="14">
-        <v>45412</v>
+        <v>45121</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108" s="11" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C108" s="11" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D108" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E108" s="11" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="F108" s="11" t="s">
-        <v>402</v>
+        <v>298</v>
       </c>
       <c r="G108" s="11">
-        <v>0.608</v>
+        <v>0.9718000000000001</v>
       </c>
       <c r="H108" s="12">
-        <v>2860442.12</v>
+        <v>1988555.07</v>
       </c>
       <c r="I108" s="13">
-        <v>1739254.2</v>
+        <v>1932548.63</v>
       </c>
       <c r="J108" s="12">
-        <v>1121187.9200000002</v>
+        <v>56006.44000000018</v>
       </c>
       <c r="K108" s="14">
-        <v>45782</v>
+        <v>44742</v>
       </c>
       <c r="L108" s="14">
-        <v>46083</v>
+        <v>45412</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109" s="11" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>408</v>
+        <v>429</v>
       </c>
       <c r="D109" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E109" s="11" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="F109" s="11" t="s">
-        <v>429</v>
+        <v>407</v>
       </c>
       <c r="G109" s="11">
-        <v>0.9998999999999999</v>
+        <v>0.608</v>
       </c>
       <c r="H109" s="12">
-        <v>5272095.08</v>
+        <v>2860442.12</v>
       </c>
       <c r="I109" s="13">
-        <v>5271693.21</v>
+        <v>1739254.2</v>
       </c>
       <c r="J109" s="12">
-        <v>401.87000000011176</v>
+        <v>1121187.9200000002</v>
       </c>
       <c r="K109" s="14">
-        <v>44746</v>
+        <v>45782</v>
       </c>
       <c r="L109" s="14">
-        <v>45560</v>
+        <v>46114</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A110" s="11" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>431</v>
+        <v>413</v>
       </c>
       <c r="D110" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E110" s="11" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F110" s="11" t="s">
-        <v>299</v>
+        <v>434</v>
       </c>
       <c r="G110" s="11">
-        <v>0.9931</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="H110" s="12">
-        <v>1690234.37</v>
+        <v>5272095.08</v>
       </c>
       <c r="I110" s="13">
-        <v>1678610.19</v>
+        <v>5271693.21</v>
       </c>
       <c r="J110" s="12">
-        <v>11624.180000000168</v>
+        <v>401.87000000011176</v>
       </c>
       <c r="K110" s="14">
-        <v>44772</v>
+        <v>44746</v>
       </c>
       <c r="L110" s="14">
-        <v>45316</v>
+        <v>45560</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111" s="11" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C111" s="11" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D111" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E111" s="11" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="F111" s="11" t="s">
-        <v>436</v>
+        <v>298</v>
       </c>
       <c r="G111" s="11">
-        <v>0.9994</v>
+        <v>0.9931</v>
       </c>
       <c r="H111" s="12">
-        <v>26946699.36</v>
+        <v>1690234.37</v>
       </c>
       <c r="I111" s="13">
-        <v>26930984.02</v>
+        <v>1678610.19</v>
       </c>
       <c r="J111" s="12">
-        <v>15715.339999999851</v>
+        <v>11624.180000000168</v>
       </c>
       <c r="K111" s="14">
-        <v>44823</v>
+        <v>44772</v>
       </c>
       <c r="L111" s="14">
-        <v>45816</v>
+        <v>45316</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112" s="11" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="B112" s="11" t="s">
         <v>438</v>
@@ -6663,443 +6681,443 @@
         <v>440</v>
       </c>
       <c r="F112" s="11" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="G112" s="11">
-        <v>1</v>
+        <v>0.9994</v>
       </c>
       <c r="H112" s="12">
-        <v>3607367.42</v>
+        <v>26946699.36</v>
       </c>
       <c r="I112" s="13">
-        <v>3607318.65</v>
+        <v>26930984.02</v>
       </c>
       <c r="J112" s="12">
-        <v>48.77000000001863</v>
+        <v>15715.339999999851</v>
       </c>
       <c r="K112" s="14">
-        <v>45061</v>
+        <v>44823</v>
       </c>
       <c r="L112" s="14">
-        <v>45016</v>
+        <v>45816</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113" s="11" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D113" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E113" s="11" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="F113" s="11" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="G113" s="11">
-        <v>0.9958</v>
+        <v>1</v>
       </c>
       <c r="H113" s="12">
-        <v>4645152.25</v>
+        <v>3607367.42</v>
       </c>
       <c r="I113" s="13">
-        <v>4625557.49</v>
+        <v>3607318.65</v>
       </c>
       <c r="J113" s="12">
-        <v>19594.759999999776</v>
+        <v>48.77000000001863</v>
       </c>
       <c r="K113" s="14">
-        <v>44918</v>
+        <v>45061</v>
       </c>
       <c r="L113" s="14">
-        <v>45485</v>
+        <v>45016</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" s="11" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D114" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E114" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F114" s="11" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="G114" s="11">
-        <v>1</v>
+        <v>0.9958</v>
       </c>
       <c r="H114" s="12">
-        <v>13242425.64</v>
+        <v>4645152.25</v>
       </c>
       <c r="I114" s="13">
-        <v>13242495.84</v>
+        <v>4625557.49</v>
       </c>
       <c r="J114" s="12">
-        <v>-70.19999999925494</v>
+        <v>19594.759999999776</v>
       </c>
       <c r="K114" s="14">
-        <v>44923</v>
+        <v>44918</v>
       </c>
       <c r="L114" s="14">
-        <v>45531</v>
+        <v>45485</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" s="11" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D115" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E115" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F115" s="11" t="s">
-        <v>45</v>
+        <v>453</v>
       </c>
       <c r="G115" s="11">
         <v>1</v>
       </c>
       <c r="H115" s="12">
-        <v>20859068.44</v>
+        <v>13242425.64</v>
       </c>
       <c r="I115" s="13">
-        <v>20859068.44</v>
+        <v>13242495.84</v>
       </c>
       <c r="J115" s="12">
-        <v>0</v>
+        <v>-70.19999999925494</v>
       </c>
       <c r="K115" s="14">
-        <v>45007</v>
+        <v>44923</v>
       </c>
       <c r="L115" s="14">
-        <v>45851</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116" s="11" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D116" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E116" s="11" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="F116" s="11" t="s">
-        <v>455</v>
+        <v>45</v>
       </c>
       <c r="G116" s="11">
-        <v>0.9842</v>
+        <v>1</v>
       </c>
       <c r="H116" s="12">
-        <v>20229149.79</v>
+        <v>20859068.44</v>
       </c>
       <c r="I116" s="13">
-        <v>19910398.37</v>
+        <v>20859068.44</v>
       </c>
       <c r="J116" s="12">
-        <v>318751.41999999806</v>
+        <v>0</v>
       </c>
       <c r="K116" s="14">
-        <v>44697</v>
+        <v>45007</v>
       </c>
       <c r="L116" s="14">
-        <v>45783</v>
+        <v>45851</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117" s="11" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E117" s="11" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F117" s="11" t="s">
-        <v>40</v>
+        <v>460</v>
       </c>
       <c r="G117" s="11">
-        <v>0</v>
+        <v>0.9842</v>
       </c>
       <c r="H117" s="12">
-        <v>6784130.44</v>
+        <v>20229149.79</v>
       </c>
       <c r="I117" s="13">
-        <v>0</v>
+        <v>19910398.37</v>
       </c>
       <c r="J117" s="12">
-        <v>6784130.44</v>
+        <v>318751.41999999806</v>
       </c>
       <c r="K117" s="14">
-        <v>45100</v>
+        <v>44697</v>
       </c>
       <c r="L117" s="14">
-        <v>45400</v>
+        <v>45783</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118" s="11" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C118" s="11" t="s">
-        <v>339</v>
+        <v>462</v>
       </c>
       <c r="D118" s="11" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E118" s="11" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="F118" s="11" t="s">
-        <v>163</v>
+        <v>40</v>
       </c>
       <c r="G118" s="11">
-        <v>0.6605</v>
+        <v>0</v>
       </c>
       <c r="H118" s="12">
-        <v>20185137.81</v>
+        <v>6784130.44</v>
       </c>
       <c r="I118" s="13">
-        <v>13332401.6</v>
+        <v>0</v>
       </c>
       <c r="J118" s="12">
-        <v>6852736.209999999</v>
+        <v>6784130.44</v>
       </c>
       <c r="K118" s="14">
-        <v>44754</v>
+        <v>45100</v>
       </c>
       <c r="L118" s="14">
-        <v>45566</v>
+        <v>45400</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119" s="11" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="B119" s="11" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C119" s="11" t="s">
-        <v>462</v>
+        <v>344</v>
       </c>
       <c r="D119" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E119" s="11" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F119" s="11" t="s">
-        <v>45</v>
+        <v>163</v>
       </c>
       <c r="G119" s="11">
-        <v>0.0321</v>
+        <v>0.6605</v>
       </c>
       <c r="H119" s="12">
-        <v>7430869.32</v>
+        <v>20185137.81</v>
       </c>
       <c r="I119" s="13">
-        <v>238550.07</v>
+        <v>13332401.6</v>
       </c>
       <c r="J119" s="12">
-        <v>7192319.25</v>
+        <v>6852736.209999999</v>
       </c>
       <c r="K119" s="14">
-        <v>45865</v>
+        <v>44754</v>
       </c>
       <c r="L119" s="14">
-        <v>46166</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120" s="11" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
       <c r="B120" s="11" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C120" s="11" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D120" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E120" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F120" s="11" t="s">
-        <v>429</v>
+        <v>45</v>
       </c>
       <c r="G120" s="11">
-        <v>0.9903</v>
+        <v>0.0321</v>
       </c>
       <c r="H120" s="12">
-        <v>11046611.98</v>
+        <v>7430869.32</v>
       </c>
       <c r="I120" s="13">
-        <v>10939879.39</v>
+        <v>238550.07</v>
       </c>
       <c r="J120" s="12">
-        <v>106732.58999999985</v>
+        <v>7192319.25</v>
       </c>
       <c r="K120" s="14">
-        <v>44663</v>
+        <v>45865</v>
       </c>
       <c r="L120" s="14">
-        <v>45507</v>
+        <v>46166</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121" s="11" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="B121" s="11" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C121" s="11" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D121" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E121" s="11" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F121" s="11" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="G121" s="11">
-        <v>0.8079000000000001</v>
+        <v>0.9903</v>
       </c>
       <c r="H121" s="12">
-        <v>2755604.93</v>
+        <v>11046611.98</v>
       </c>
       <c r="I121" s="13">
-        <v>2226331.45</v>
+        <v>10939879.39</v>
       </c>
       <c r="J121" s="12">
-        <v>529273.48</v>
+        <v>106732.58999999985</v>
       </c>
       <c r="K121" s="14">
-        <v>45026</v>
+        <v>44663</v>
       </c>
       <c r="L121" s="14">
-        <v>46023</v>
+        <v>45507</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122" s="11" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="B122" s="11" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C122" s="11" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D122" s="11" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E122" s="11" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F122" s="11" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="G122" s="11">
-        <v>0</v>
+        <v>0.8079000000000001</v>
       </c>
       <c r="H122" s="12">
-        <v>1712576.84</v>
+        <v>2755604.93</v>
       </c>
       <c r="I122" s="13">
-        <v>0</v>
+        <v>2226331.45</v>
       </c>
       <c r="J122" s="12">
-        <v>1712576.84</v>
+        <v>529273.48</v>
       </c>
       <c r="K122" s="14">
-        <v>44823</v>
+        <v>45026</v>
       </c>
       <c r="L122" s="14">
-        <v>44706</v>
+        <v>46023</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123" s="11" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="B123" s="11" t="s">
+        <v>477</v>
+      </c>
+      <c r="C123" s="11" t="s">
+        <v>478</v>
+      </c>
+      <c r="D123" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E123" s="11" t="s">
+        <v>479</v>
+      </c>
+      <c r="F123" s="11" t="s">
         <v>476</v>
       </c>
-      <c r="C123" s="11" t="s">
-        <v>477</v>
-      </c>
-      <c r="D123" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E123" s="11" t="s">
-        <v>478</v>
-      </c>
-      <c r="F123" s="11" t="s">
-        <v>479</v>
-      </c>
       <c r="G123" s="11">
-        <v>0.9998999999999999</v>
+        <v>0</v>
       </c>
       <c r="H123" s="12">
-        <v>1612154.63</v>
+        <v>1712576.84</v>
       </c>
       <c r="I123" s="13">
-        <v>1612024.85</v>
+        <v>0</v>
       </c>
       <c r="J123" s="12">
-        <v>129.7799999997951</v>
+        <v>1712576.84</v>
       </c>
       <c r="K123" s="14">
-        <v>45776</v>
+        <v>44823</v>
       </c>
       <c r="L123" s="14">
-        <v>45986</v>
+        <v>44706</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
@@ -7110,115 +7128,115 @@
         <v>481</v>
       </c>
       <c r="C124" s="11" t="s">
-        <v>157</v>
+        <v>482</v>
       </c>
       <c r="D124" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E124" s="11" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F124" s="11" t="s">
-        <v>483</v>
+        <v>310</v>
       </c>
       <c r="G124" s="11">
-        <v>1</v>
+        <v>0.9998999999999999</v>
       </c>
       <c r="H124" s="12">
-        <v>6453162.72</v>
+        <v>1612154.63</v>
       </c>
       <c r="I124" s="13">
-        <v>6453162.72</v>
+        <v>1612024.85</v>
       </c>
       <c r="J124" s="12">
-        <v>0</v>
+        <v>129.7799999997951</v>
       </c>
       <c r="K124" s="14">
-        <v>44760</v>
+        <v>45776</v>
       </c>
       <c r="L124" s="14">
-        <v>45201</v>
+        <v>45986</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" s="11" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B125" s="11" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C125" s="11" t="s">
-        <v>485</v>
+        <v>157</v>
       </c>
       <c r="D125" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E125" s="11" t="s">
         <v>486</v>
       </c>
       <c r="F125" s="11" t="s">
-        <v>241</v>
+        <v>487</v>
       </c>
       <c r="G125" s="11">
-        <v>0.9993000000000001</v>
+        <v>1</v>
       </c>
       <c r="H125" s="12">
-        <v>1741703.69</v>
+        <v>6453162.72</v>
       </c>
       <c r="I125" s="13">
-        <v>1740561.74</v>
+        <v>6453162.72</v>
       </c>
       <c r="J125" s="12">
-        <v>1141.9499999999534</v>
+        <v>0</v>
       </c>
       <c r="K125" s="14">
-        <v>44683</v>
+        <v>44760</v>
       </c>
       <c r="L125" s="14">
-        <v>45889</v>
+        <v>45201</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126" s="11" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B126" s="11" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C126" s="11" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D126" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E126" s="11" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F126" s="11" t="s">
-        <v>490</v>
+        <v>241</v>
       </c>
       <c r="G126" s="11">
-        <v>0.997</v>
+        <v>0.9993000000000001</v>
       </c>
       <c r="H126" s="12">
-        <v>6014775.77</v>
+        <v>1741703.69</v>
       </c>
       <c r="I126" s="13">
-        <v>5996889.68</v>
+        <v>1740561.74</v>
       </c>
       <c r="J126" s="12">
-        <v>17886.08999999985</v>
+        <v>1141.9499999999534</v>
       </c>
       <c r="K126" s="14">
-        <v>44708</v>
+        <v>44683</v>
       </c>
       <c r="L126" s="14">
-        <v>45467</v>
+        <v>45889</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127" s="11" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B127" s="11" t="s">
         <v>491</v>
@@ -7227,150 +7245,150 @@
         <v>492</v>
       </c>
       <c r="D127" s="11" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E127" s="11" t="s">
         <v>493</v>
       </c>
       <c r="F127" s="11" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="G127" s="11">
-        <v>0.9913</v>
+        <v>0.997</v>
       </c>
       <c r="H127" s="12">
-        <v>3569195.39</v>
+        <v>6014775.77</v>
       </c>
       <c r="I127" s="13">
-        <v>3538001.16</v>
+        <v>5996889.68</v>
       </c>
       <c r="J127" s="12">
-        <v>31194.22999999998</v>
+        <v>17886.08999999985</v>
       </c>
       <c r="K127" s="14">
-        <v>44658</v>
+        <v>44708</v>
       </c>
       <c r="L127" s="14">
-        <v>45426</v>
+        <v>45467</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" s="11" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B128" s="11" t="s">
+        <v>495</v>
+      </c>
+      <c r="C128" s="11" t="s">
+        <v>496</v>
+      </c>
+      <c r="D128" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E128" s="11" t="s">
+        <v>497</v>
+      </c>
+      <c r="F128" s="11" t="s">
         <v>494</v>
       </c>
-      <c r="C128" s="11" t="s">
-        <v>495</v>
-      </c>
-      <c r="D128" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E128" s="11" t="s">
-        <v>496</v>
-      </c>
-      <c r="F128" s="11" t="s">
-        <v>241</v>
-      </c>
       <c r="G128" s="11">
-        <v>0.7993000000000001</v>
+        <v>0.9913</v>
       </c>
       <c r="H128" s="12">
-        <v>1528883.61</v>
+        <v>3569195.39</v>
       </c>
       <c r="I128" s="13">
-        <v>1222003.41</v>
+        <v>3538001.16</v>
       </c>
       <c r="J128" s="12">
-        <v>306880.2000000002</v>
+        <v>31194.22999999998</v>
       </c>
       <c r="K128" s="14">
-        <v>44655</v>
+        <v>44658</v>
       </c>
       <c r="L128" s="14">
-        <v>46164</v>
+        <v>45426</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129" s="11" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B129" s="11" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C129" s="11" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D129" s="11" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E129" s="11" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F129" s="11" t="s">
-        <v>500</v>
+        <v>241</v>
       </c>
       <c r="G129" s="11">
-        <v>0.0245</v>
+        <v>0.7993000000000001</v>
       </c>
       <c r="H129" s="12">
-        <v>2317778.22</v>
+        <v>1528883.61</v>
       </c>
       <c r="I129" s="13">
-        <v>56828.03</v>
+        <v>1222003.41</v>
       </c>
       <c r="J129" s="12">
-        <v>2260950.1900000004</v>
+        <v>306880.2000000002</v>
       </c>
       <c r="K129" s="14">
-        <v>45035</v>
+        <v>44655</v>
       </c>
       <c r="L129" s="14">
-        <v>45396</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130" s="11" t="s">
+        <v>484</v>
+      </c>
+      <c r="B130" s="11" t="s">
         <v>501</v>
       </c>
-      <c r="B130" s="11" t="s">
+      <c r="C130" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="C130" s="11" t="s">
+      <c r="D130" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E130" s="11" t="s">
         <v>503</v>
       </c>
-      <c r="D130" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E130" s="11" t="s">
+      <c r="F130" s="11" t="s">
         <v>504</v>
       </c>
-      <c r="F130" s="11" t="s">
-        <v>505</v>
-      </c>
       <c r="G130" s="11">
-        <v>1</v>
+        <v>0.0245</v>
       </c>
       <c r="H130" s="12">
-        <v>6478069.43</v>
+        <v>2317778.22</v>
       </c>
       <c r="I130" s="13">
-        <v>6478029.44</v>
+        <v>56828.03</v>
       </c>
       <c r="J130" s="12">
-        <v>39.989999999292195</v>
+        <v>2260950.1900000004</v>
       </c>
       <c r="K130" s="14">
-        <v>44827</v>
+        <v>45035</v>
       </c>
       <c r="L130" s="14">
-        <v>45690</v>
+        <v>45396</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131" s="11" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B131" s="11" t="s">
         <v>506</v>
@@ -7388,179 +7406,179 @@
         <v>509</v>
       </c>
       <c r="G131" s="11">
-        <v>0.7809</v>
+        <v>1</v>
       </c>
       <c r="H131" s="12">
-        <v>544550.48</v>
+        <v>6478069.43</v>
       </c>
       <c r="I131" s="13">
-        <v>425261.4</v>
+        <v>6478029.44</v>
       </c>
       <c r="J131" s="12">
-        <v>119289.07999999996</v>
+        <v>39.989999999292195</v>
       </c>
       <c r="K131" s="14">
-        <v>45925</v>
+        <v>44827</v>
       </c>
       <c r="L131" s="14">
-        <v>46165</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132" s="11" t="s">
+        <v>505</v>
+      </c>
+      <c r="B132" s="11" t="s">
         <v>510</v>
       </c>
-      <c r="B132" s="11" t="s">
+      <c r="C132" s="11" t="s">
         <v>511</v>
       </c>
-      <c r="C132" s="11" t="s">
-        <v>184</v>
-      </c>
       <c r="D132" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E132" s="11" t="s">
         <v>512</v>
       </c>
       <c r="F132" s="11" t="s">
-        <v>98</v>
+        <v>513</v>
       </c>
       <c r="G132" s="11">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H132" s="12">
-        <v>2389346</v>
+        <v>544550.48</v>
       </c>
       <c r="I132" s="13">
-        <v>2389346</v>
+        <v>490095.44</v>
       </c>
       <c r="J132" s="12">
-        <v>0</v>
+        <v>54455.03999999998</v>
       </c>
       <c r="K132" s="14">
-        <v>44693</v>
+        <v>45925</v>
       </c>
       <c r="L132" s="14">
-        <v>45456</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133" s="11" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B133" s="11" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C133" s="11" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="D133" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E133" s="11" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="F133" s="11" t="s">
-        <v>345</v>
+        <v>98</v>
       </c>
       <c r="G133" s="11">
         <v>1</v>
       </c>
       <c r="H133" s="12">
-        <v>6743574.04</v>
+        <v>2389346</v>
       </c>
       <c r="I133" s="13">
-        <v>6743573.85</v>
+        <v>2389346</v>
       </c>
       <c r="J133" s="12">
-        <v>0.19000000040978193</v>
+        <v>0</v>
       </c>
       <c r="K133" s="14">
         <v>44693</v>
       </c>
       <c r="L133" s="14">
-        <v>45152</v>
+        <v>45456</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134" s="11" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B134" s="11" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C134" s="11" t="s">
-        <v>318</v>
+        <v>194</v>
       </c>
       <c r="D134" s="11" t="s">
         <v>15</v>
       </c>
       <c r="E134" s="11" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="F134" s="11" t="s">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="G134" s="11">
-        <v>0.9562999999999999</v>
+        <v>1</v>
       </c>
       <c r="H134" s="12">
-        <v>1052239.53</v>
+        <v>6743574.04</v>
       </c>
       <c r="I134" s="13">
-        <v>1006235.15</v>
+        <v>6743573.85</v>
       </c>
       <c r="J134" s="12">
-        <v>46004.380000000005</v>
+        <v>0.19000000040978193</v>
       </c>
       <c r="K134" s="14">
-        <v>44613</v>
+        <v>44693</v>
       </c>
       <c r="L134" s="14">
-        <v>45183</v>
+        <v>45152</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135" s="11" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B135" s="11" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C135" s="11" t="s">
-        <v>518</v>
+        <v>323</v>
       </c>
       <c r="D135" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E135" s="11" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F135" s="11" t="s">
-        <v>520</v>
+        <v>375</v>
       </c>
       <c r="G135" s="11">
-        <v>0.6409999999999999</v>
+        <v>0.9562999999999999</v>
       </c>
       <c r="H135" s="12">
-        <v>256613.37</v>
+        <v>1052239.53</v>
       </c>
       <c r="I135" s="13">
-        <v>164482.69</v>
+        <v>1006235.15</v>
       </c>
       <c r="J135" s="12">
-        <v>92130.68</v>
+        <v>46004.380000000005</v>
       </c>
       <c r="K135" s="14">
-        <v>45915</v>
+        <v>44613</v>
       </c>
       <c r="L135" s="14">
-        <v>46005</v>
+        <v>45183</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136" s="11" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B136" s="11" t="s">
         <v>521</v>
@@ -7578,378 +7596,378 @@
         <v>524</v>
       </c>
       <c r="G136" s="11">
-        <v>0.9508</v>
+        <v>0.6409999999999999</v>
       </c>
       <c r="H136" s="12">
-        <v>13554947.83</v>
+        <v>256613.37</v>
       </c>
       <c r="I136" s="13">
-        <v>12888506.56</v>
+        <v>164482.69</v>
       </c>
       <c r="J136" s="12">
-        <v>666441.2699999996</v>
+        <v>92130.68</v>
       </c>
       <c r="K136" s="14">
-        <v>44537</v>
+        <v>45915</v>
       </c>
       <c r="L136" s="14">
-        <v>46075</v>
+        <v>46005</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137" s="11" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B137" s="11" t="s">
         <v>525</v>
       </c>
       <c r="C137" s="11" t="s">
-        <v>453</v>
+        <v>526</v>
       </c>
       <c r="D137" s="11" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E137" s="11" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F137" s="11" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="G137" s="11">
-        <v>0</v>
+        <v>0.9726</v>
       </c>
       <c r="H137" s="12">
-        <v>1305890.95</v>
+        <v>13554947.83</v>
       </c>
       <c r="I137" s="13">
-        <v>0</v>
+        <v>13183162.22</v>
       </c>
       <c r="J137" s="12">
-        <v>1305890.95</v>
+        <v>371785.6099999994</v>
       </c>
       <c r="K137" s="14">
-        <v>44610</v>
+        <v>44537</v>
       </c>
       <c r="L137" s="14">
-        <v>45567</v>
+        <v>46075</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138" s="11" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B138" s="11" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C138" s="11" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D138" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E138" s="11" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F138" s="11" t="s">
-        <v>531</v>
+        <v>98</v>
       </c>
       <c r="G138" s="11">
-        <v>0.9765999999999999</v>
+        <v>0.8996999999999999</v>
       </c>
       <c r="H138" s="12">
-        <v>56185153.92</v>
+        <v>12432476.25</v>
       </c>
       <c r="I138" s="13">
-        <v>54872063.4</v>
+        <v>11184973.93</v>
       </c>
       <c r="J138" s="12">
-        <v>1313090.5200000033</v>
+        <v>1247502.3200000003</v>
       </c>
       <c r="K138" s="14">
-        <v>44872</v>
+        <v>45894</v>
       </c>
       <c r="L138" s="14">
-        <v>45475</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139" s="11" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B139" s="11" t="s">
         <v>532</v>
       </c>
       <c r="C139" s="11" t="s">
+        <v>458</v>
+      </c>
+      <c r="D139" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E139" s="11" t="s">
         <v>533</v>
       </c>
-      <c r="D139" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E139" s="11" t="s">
+      <c r="F139" s="11" t="s">
         <v>534</v>
       </c>
-      <c r="F139" s="11" t="s">
-        <v>535</v>
-      </c>
       <c r="G139" s="11">
-        <v>0.8667</v>
+        <v>0</v>
       </c>
       <c r="H139" s="12">
-        <v>12100122.6</v>
+        <v>1305890.95</v>
       </c>
       <c r="I139" s="13">
-        <v>10486811.37</v>
+        <v>0</v>
       </c>
       <c r="J139" s="12">
-        <v>1613311.2300000004</v>
+        <v>1305890.95</v>
       </c>
       <c r="K139" s="14">
-        <v>45758</v>
+        <v>44610</v>
       </c>
       <c r="L139" s="14">
-        <v>46123</v>
+        <v>45567</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140" s="11" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B140" s="11" t="s">
+        <v>535</v>
+      </c>
+      <c r="C140" s="11" t="s">
         <v>536</v>
       </c>
-      <c r="C140" s="11" t="s">
+      <c r="D140" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E140" s="11" t="s">
         <v>537</v>
       </c>
-      <c r="D140" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E140" s="11" t="s">
+      <c r="F140" s="11" t="s">
         <v>538</v>
       </c>
-      <c r="F140" s="11" t="s">
-        <v>98</v>
-      </c>
       <c r="G140" s="11">
-        <v>0.8621</v>
+        <v>0.9765999999999999</v>
       </c>
       <c r="H140" s="12">
-        <v>12432476.25</v>
+        <v>56185153.92</v>
       </c>
       <c r="I140" s="13">
-        <v>10718116.82</v>
+        <v>54872063.4</v>
       </c>
       <c r="J140" s="12">
-        <v>1714359.4299999997</v>
+        <v>1313090.5200000033</v>
       </c>
       <c r="K140" s="14">
-        <v>45894</v>
+        <v>44872</v>
       </c>
       <c r="L140" s="14">
-        <v>46112</v>
+        <v>45475</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141" s="11" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B141" s="11" t="s">
         <v>539</v>
       </c>
       <c r="C141" s="11" t="s">
-        <v>439</v>
+        <v>540</v>
       </c>
       <c r="D141" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E141" s="11" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F141" s="11" t="s">
-        <v>154</v>
+        <v>542</v>
       </c>
       <c r="G141" s="11">
-        <v>0.8916</v>
+        <v>0.8667</v>
       </c>
       <c r="H141" s="12">
-        <v>24590858.27</v>
+        <v>12100122.6</v>
       </c>
       <c r="I141" s="13">
-        <v>21925638.52</v>
+        <v>10486811.37</v>
       </c>
       <c r="J141" s="12">
-        <v>2665219.75</v>
+        <v>1613311.2300000004</v>
       </c>
       <c r="K141" s="14">
-        <v>44638</v>
+        <v>45758</v>
       </c>
       <c r="L141" s="14">
-        <v>45936</v>
+        <v>46123</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142" s="11" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B142" s="11" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C142" s="11" t="s">
-        <v>147</v>
+        <v>444</v>
       </c>
       <c r="D142" s="11" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E142" s="11" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F142" s="11" t="s">
-        <v>341</v>
+        <v>154</v>
       </c>
       <c r="G142" s="11">
-        <v>0.0707</v>
+        <v>0.8916</v>
       </c>
       <c r="H142" s="12">
-        <v>3615856.15</v>
+        <v>24590858.27</v>
       </c>
       <c r="I142" s="13">
-        <v>255684.47</v>
+        <v>21925638.52</v>
       </c>
       <c r="J142" s="12">
-        <v>3360171.6799999997</v>
+        <v>2665219.75</v>
       </c>
       <c r="K142" s="14">
-        <v>44791</v>
+        <v>44638</v>
       </c>
       <c r="L142" s="14">
-        <v>45259</v>
+        <v>45936</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143" s="11" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B143" s="11" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C143" s="11" t="s">
-        <v>544</v>
+        <v>147</v>
       </c>
       <c r="D143" s="11" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E143" s="11" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F143" s="11" t="s">
-        <v>98</v>
+        <v>346</v>
       </c>
       <c r="G143" s="11">
-        <v>0.1637</v>
+        <v>0.0707</v>
       </c>
       <c r="H143" s="12">
-        <v>7848019.53</v>
+        <v>3615856.15</v>
       </c>
       <c r="I143" s="13">
-        <v>1284711.9</v>
+        <v>255684.47</v>
       </c>
       <c r="J143" s="12">
-        <v>6563307.630000001</v>
+        <v>3360171.6799999997</v>
       </c>
       <c r="K143" s="14">
-        <v>45986</v>
+        <v>44791</v>
       </c>
       <c r="L143" s="14">
-        <v>46351</v>
+        <v>45259</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144" s="11" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B144" s="11" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C144" s="11" t="s">
-        <v>105</v>
+        <v>548</v>
       </c>
       <c r="D144" s="11" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E144" s="11" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="F144" s="11" t="s">
-        <v>548</v>
+        <v>98</v>
       </c>
       <c r="G144" s="11">
-        <v>0.5364</v>
+        <v>0.1637</v>
       </c>
       <c r="H144" s="12">
-        <v>16932981.45</v>
+        <v>7848019.53</v>
       </c>
       <c r="I144" s="13">
-        <v>9082408.67</v>
+        <v>1284711.9</v>
       </c>
       <c r="J144" s="12">
-        <v>7850572.779999999</v>
+        <v>6563307.630000001</v>
       </c>
       <c r="K144" s="14">
-        <v>44791</v>
+        <v>45986</v>
       </c>
       <c r="L144" s="14">
-        <v>45393</v>
+        <v>46351</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145" s="11" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B145" s="11" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C145" s="11" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D145" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E145" s="11" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F145" s="11" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="G145" s="11">
-        <v>0.6097</v>
+        <v>0.8998</v>
       </c>
       <c r="H145" s="12">
-        <v>24187461.93</v>
+        <v>74609626.42</v>
       </c>
       <c r="I145" s="13">
-        <v>14747400.15</v>
+        <v>67130533.6</v>
       </c>
       <c r="J145" s="12">
-        <v>9440061.78</v>
+        <v>7479092.820000008</v>
       </c>
       <c r="K145" s="14">
-        <v>45723</v>
+        <v>45555</v>
       </c>
       <c r="L145" s="14">
-        <v>46203</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A146" s="11" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B146" s="11" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C146" s="11" t="s">
-        <v>554</v>
+        <v>105</v>
       </c>
       <c r="D146" s="11" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E146" s="11" t="s">
         <v>555</v>
@@ -7958,27 +7976,27 @@
         <v>556</v>
       </c>
       <c r="G146" s="11">
-        <v>0.8504</v>
+        <v>0.5364</v>
       </c>
       <c r="H146" s="12">
-        <v>74609626.42</v>
+        <v>16932981.45</v>
       </c>
       <c r="I146" s="13">
-        <v>63449041.49</v>
+        <v>9082408.67</v>
       </c>
       <c r="J146" s="12">
-        <v>11160584.93</v>
+        <v>7850572.779999999</v>
       </c>
       <c r="K146" s="14">
-        <v>45555</v>
+        <v>44791</v>
       </c>
       <c r="L146" s="14">
-        <v>46112</v>
+        <v>45393</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147" s="11" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B147" s="11" t="s">
         <v>557</v>
@@ -7993,106 +8011,106 @@
         <v>559</v>
       </c>
       <c r="F147" s="11" t="s">
-        <v>524</v>
+        <v>560</v>
       </c>
       <c r="G147" s="11">
-        <v>0.15</v>
+        <v>0.6097</v>
       </c>
       <c r="H147" s="12">
-        <v>15203482.79</v>
+        <v>24187461.93</v>
       </c>
       <c r="I147" s="13">
-        <v>2279930.05</v>
+        <v>14747400.15</v>
       </c>
       <c r="J147" s="12">
-        <v>12923552.739999998</v>
+        <v>9440061.78</v>
       </c>
       <c r="K147" s="14">
-        <v>44757</v>
+        <v>45723</v>
       </c>
       <c r="L147" s="14">
-        <v>46287</v>
+        <v>46203</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A148" s="11" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B148" s="11" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C148" s="11" t="s">
-        <v>495</v>
+        <v>562</v>
       </c>
       <c r="D148" s="11" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E148" s="11" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="F148" s="11" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="G148" s="11">
-        <v>0.0216</v>
+        <v>0.15</v>
       </c>
       <c r="H148" s="12">
-        <v>13677862.32</v>
+        <v>15203482.79</v>
       </c>
       <c r="I148" s="13">
-        <v>296101.87</v>
+        <v>2279930.05</v>
       </c>
       <c r="J148" s="12">
-        <v>13381760.450000001</v>
+        <v>12923552.739999998</v>
       </c>
       <c r="K148" s="14">
-        <v>44581</v>
+        <v>44757</v>
       </c>
       <c r="L148" s="14">
-        <v>45561</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149" s="11" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B149" s="11" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C149" s="11" t="s">
-        <v>563</v>
+        <v>499</v>
       </c>
       <c r="D149" s="11" t="s">
         <v>20</v>
       </c>
       <c r="E149" s="11" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="F149" s="11" t="s">
-        <v>565</v>
+        <v>528</v>
       </c>
       <c r="G149" s="11">
-        <v>0</v>
+        <v>0.0216</v>
       </c>
       <c r="H149" s="12">
-        <v>14144248.92</v>
+        <v>13677862.32</v>
       </c>
       <c r="I149" s="13">
-        <v>0</v>
+        <v>296101.87</v>
       </c>
       <c r="J149" s="12">
-        <v>14144248.92</v>
+        <v>13381760.450000001</v>
       </c>
       <c r="K149" s="14">
-        <v>41443</v>
+        <v>44581</v>
       </c>
       <c r="L149" s="14">
-        <v>44012</v>
+        <v>45561</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150" s="11" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B150" s="11" t="s">
         <v>566</v>
@@ -8107,176 +8125,178 @@
         <v>568</v>
       </c>
       <c r="F150" s="11" t="s">
-        <v>341</v>
+        <v>569</v>
       </c>
       <c r="G150" s="11">
-        <v>0.3475</v>
+        <v>0</v>
       </c>
       <c r="H150" s="12">
-        <v>24165422.12</v>
+        <v>14144248.92</v>
       </c>
       <c r="I150" s="13">
-        <v>8398407.23</v>
+        <v>0</v>
       </c>
       <c r="J150" s="12">
-        <v>15767014.89</v>
+        <v>14144248.92</v>
       </c>
       <c r="K150" s="14">
-        <v>44538</v>
+        <v>41443</v>
       </c>
       <c r="L150" s="14">
-        <v>45426</v>
+        <v>44012</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151" s="11" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B151" s="11" t="s">
-        <v>569</v>
-      </c>
-      <c r="C151" s="11"/>
+        <v>570</v>
+      </c>
+      <c r="C151" s="11" t="s">
+        <v>571</v>
+      </c>
       <c r="D151" s="11" t="s">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="E151" s="11" t="s">
-        <v>570</v>
-      </c>
-      <c r="F151" s="11"/>
-      <c r="G151" s="16" t="s">
-        <v>99</v>
+        <v>572</v>
+      </c>
+      <c r="F151" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="G151" s="11">
+        <v>0.3475</v>
       </c>
       <c r="H151" s="12">
-        <v>31744937.05</v>
+        <v>24165422.12</v>
       </c>
       <c r="I151" s="13">
-        <v>0</v>
+        <v>8398407.23</v>
       </c>
       <c r="J151" s="12">
-        <v>31744937.05</v>
-      </c>
-      <c r="K151" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="L151" s="15" t="s">
-        <v>99</v>
+        <v>15767014.89</v>
+      </c>
+      <c r="K151" s="14">
+        <v>44538</v>
+      </c>
+      <c r="L151" s="14">
+        <v>45426</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152" s="11" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B152" s="11" t="s">
-        <v>571</v>
-      </c>
-      <c r="C152" s="11" t="s">
-        <v>572</v>
-      </c>
+        <v>573</v>
+      </c>
+      <c r="C152" s="11"/>
       <c r="D152" s="11" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="E152" s="11" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F152" s="11" t="s">
-        <v>574</v>
-      </c>
-      <c r="G152" s="11">
-        <v>0.5169</v>
+        <v>575</v>
+      </c>
+      <c r="G152" s="16" t="s">
+        <v>99</v>
       </c>
       <c r="H152" s="12">
-        <v>104939756.55</v>
+        <v>31744937.05</v>
       </c>
       <c r="I152" s="13">
-        <v>54247297.54</v>
+        <v>0</v>
       </c>
       <c r="J152" s="12">
-        <v>50692459.01</v>
-      </c>
-      <c r="K152" s="14">
-        <v>45624</v>
-      </c>
-      <c r="L152" s="14">
-        <v>46074</v>
+        <v>31744937.05</v>
+      </c>
+      <c r="K152" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="L152" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153" s="11" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B153" s="11" t="s">
-        <v>575</v>
-      </c>
-      <c r="C153" s="11" t="s">
         <v>576</v>
       </c>
+      <c r="C153" s="11"/>
       <c r="D153" s="11" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="E153" s="11" t="s">
         <v>577</v>
       </c>
       <c r="F153" s="11" t="s">
-        <v>341</v>
-      </c>
-      <c r="G153" s="11">
-        <v>0.2304</v>
+        <v>575</v>
+      </c>
+      <c r="G153" s="16" t="s">
+        <v>99</v>
       </c>
       <c r="H153" s="12">
-        <v>116500000</v>
+        <v>31899639.14</v>
       </c>
       <c r="I153" s="13">
-        <v>26845813.79</v>
+        <v>0</v>
       </c>
       <c r="J153" s="12">
-        <v>89654186.21000001</v>
-      </c>
-      <c r="K153" s="14">
-        <v>45897</v>
-      </c>
-      <c r="L153" s="14">
-        <v>46107</v>
+        <v>31899639.14</v>
+      </c>
+      <c r="K153" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="L153" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154" s="11" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B154" s="11" t="s">
         <v>578</v>
       </c>
-      <c r="C154" s="11"/>
+      <c r="C154" s="11" t="s">
+        <v>579</v>
+      </c>
       <c r="D154" s="11" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="E154" s="11" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F154" s="11" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="G154" s="11">
-        <v>0</v>
+        <v>0.5169</v>
       </c>
       <c r="H154" s="12">
-        <v>201720000</v>
+        <v>104939756.55</v>
       </c>
       <c r="I154" s="13">
-        <v>0</v>
+        <v>54247297.54</v>
       </c>
       <c r="J154" s="12">
-        <v>201720000</v>
-      </c>
-      <c r="K154" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="L154" s="15" t="s">
-        <v>99</v>
+        <v>50692459.01</v>
+      </c>
+      <c r="K154" s="14">
+        <v>45624</v>
+      </c>
+      <c r="L154" s="14">
+        <v>46074</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A155" s="11" t="s">
-        <v>581</v>
+        <v>514</v>
       </c>
       <c r="B155" s="11" t="s">
         <v>582</v>
@@ -8285,568 +8305,566 @@
         <v>583</v>
       </c>
       <c r="D155" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E155" s="11" t="s">
         <v>584</v>
       </c>
       <c r="F155" s="11" t="s">
-        <v>585</v>
+        <v>346</v>
       </c>
       <c r="G155" s="11">
-        <v>1</v>
+        <v>0.2304</v>
       </c>
       <c r="H155" s="12">
-        <v>10061005.41</v>
+        <v>116500000</v>
       </c>
       <c r="I155" s="13">
-        <v>10061005.39</v>
+        <v>26845813.79</v>
       </c>
       <c r="J155" s="12">
-        <v>0.019999999552965164</v>
+        <v>89654186.21000001</v>
       </c>
       <c r="K155" s="14">
-        <v>45261</v>
+        <v>45897</v>
       </c>
       <c r="L155" s="14">
-        <v>45833</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156" s="11" t="s">
+        <v>514</v>
+      </c>
+      <c r="B156" s="11" t="s">
+        <v>585</v>
+      </c>
+      <c r="C156" s="11"/>
+      <c r="D156" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="E156" s="11" t="s">
         <v>586</v>
       </c>
-      <c r="B156" s="11" t="s">
-        <v>587</v>
-      </c>
-      <c r="C156" s="11" t="s">
-        <v>588</v>
-      </c>
-      <c r="D156" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E156" s="11" t="s">
-        <v>589</v>
-      </c>
       <c r="F156" s="11" t="s">
-        <v>45</v>
+        <v>575</v>
       </c>
       <c r="G156" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H156" s="12">
-        <v>81950979.23</v>
+        <v>201720000</v>
       </c>
       <c r="I156" s="13">
-        <v>81950979</v>
+        <v>0</v>
       </c>
       <c r="J156" s="12">
-        <v>0.23000000417232513</v>
-      </c>
-      <c r="K156" s="14">
-        <v>44792</v>
-      </c>
-      <c r="L156" s="14">
-        <v>46022</v>
+        <v>201720000</v>
+      </c>
+      <c r="K156" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="L156" s="15" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157" s="11" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B157" s="11" t="s">
+        <v>588</v>
+      </c>
+      <c r="C157" s="11" t="s">
+        <v>589</v>
+      </c>
+      <c r="D157" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E157" s="11" t="s">
         <v>590</v>
       </c>
-      <c r="C157" s="11" t="s">
+      <c r="F157" s="11" t="s">
         <v>591</v>
       </c>
-      <c r="D157" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E157" s="11" t="s">
-        <v>592</v>
-      </c>
-      <c r="F157" s="11" t="s">
-        <v>593</v>
-      </c>
       <c r="G157" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H157" s="12">
-        <v>41522873.42</v>
+        <v>10061005.41</v>
       </c>
       <c r="I157" s="13">
-        <v>0</v>
+        <v>10061005.39</v>
       </c>
       <c r="J157" s="12">
-        <v>41522873.42</v>
+        <v>0.019999999552965164</v>
       </c>
       <c r="K157" s="14">
-        <v>45901</v>
+        <v>45261</v>
       </c>
       <c r="L157" s="14">
-        <v>46801</v>
+        <v>45833</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A158" s="11" t="s">
+        <v>592</v>
+      </c>
+      <c r="B158" s="11" t="s">
+        <v>593</v>
+      </c>
+      <c r="C158" s="11" t="s">
         <v>594</v>
       </c>
-      <c r="B158" s="11" t="s">
+      <c r="D158" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E158" s="11" t="s">
         <v>595</v>
       </c>
-      <c r="C158" s="11" t="s">
-        <v>596</v>
-      </c>
-      <c r="D158" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E158" s="11" t="s">
-        <v>597</v>
-      </c>
       <c r="F158" s="11" t="s">
-        <v>323</v>
+        <v>45</v>
       </c>
       <c r="G158" s="11">
-        <v>0.9728</v>
+        <v>1</v>
       </c>
       <c r="H158" s="12">
-        <v>4444784.22</v>
+        <v>81950979.23</v>
       </c>
       <c r="I158" s="13">
-        <v>4324004.81</v>
+        <v>81950979</v>
       </c>
       <c r="J158" s="12">
-        <v>120779.41000000015</v>
+        <v>0.23000000417232513</v>
       </c>
       <c r="K158" s="14">
-        <v>45155</v>
+        <v>44792</v>
       </c>
       <c r="L158" s="14">
-        <v>45576</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A159" s="11" t="s">
+        <v>592</v>
+      </c>
+      <c r="B159" s="11" t="s">
+        <v>596</v>
+      </c>
+      <c r="C159" s="11" t="s">
+        <v>597</v>
+      </c>
+      <c r="D159" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E159" s="11" t="s">
         <v>598</v>
       </c>
-      <c r="B159" s="11" t="s">
+      <c r="F159" s="11" t="s">
         <v>599</v>
-      </c>
-      <c r="C159" s="11" t="s">
-        <v>600</v>
-      </c>
-      <c r="D159" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E159" s="11" t="s">
-        <v>601</v>
-      </c>
-      <c r="F159" s="11" t="s">
-        <v>111</v>
       </c>
       <c r="G159" s="11">
         <v>0</v>
       </c>
       <c r="H159" s="12">
-        <v>8995898.05</v>
+        <v>41522873.42</v>
       </c>
       <c r="I159" s="13">
-        <v>266299.23</v>
+        <v>0</v>
       </c>
       <c r="J159" s="12">
-        <v>8729598.82</v>
+        <v>41522873.42</v>
       </c>
       <c r="K159" s="14">
-        <v>44816</v>
+        <v>45901</v>
       </c>
       <c r="L159" s="14">
-        <v>44996</v>
+        <v>46801</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160" s="11" t="s">
+        <v>600</v>
+      </c>
+      <c r="B160" s="11" t="s">
+        <v>601</v>
+      </c>
+      <c r="C160" s="11" t="s">
         <v>602</v>
       </c>
-      <c r="B160" s="11" t="s">
+      <c r="D160" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E160" s="11" t="s">
         <v>603</v>
       </c>
-      <c r="C160" s="11" t="s">
-        <v>604</v>
-      </c>
-      <c r="D160" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E160" s="11" t="s">
-        <v>605</v>
-      </c>
       <c r="F160" s="11" t="s">
-        <v>585</v>
+        <v>328</v>
       </c>
       <c r="G160" s="11">
-        <v>0.3153</v>
+        <v>0.9728</v>
       </c>
       <c r="H160" s="12">
-        <v>3294597.99</v>
+        <v>4444784.22</v>
       </c>
       <c r="I160" s="13">
-        <v>1038880.21</v>
+        <v>4324004.81</v>
       </c>
       <c r="J160" s="12">
-        <v>2255717.7800000003</v>
+        <v>120779.41000000015</v>
       </c>
       <c r="K160" s="14">
-        <v>45278</v>
+        <v>45155</v>
       </c>
       <c r="L160" s="14">
-        <v>46122</v>
+        <v>45576</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161" s="11" t="s">
+        <v>604</v>
+      </c>
+      <c r="B161" s="11" t="s">
+        <v>605</v>
+      </c>
+      <c r="C161" s="11" t="s">
         <v>606</v>
       </c>
-      <c r="B161" s="11" t="s">
+      <c r="D161" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E161" s="11" t="s">
         <v>607</v>
       </c>
-      <c r="C161" s="11" t="s">
-        <v>608</v>
-      </c>
-      <c r="D161" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E161" s="11" t="s">
-        <v>609</v>
-      </c>
       <c r="F161" s="11" t="s">
-        <v>505</v>
+        <v>111</v>
       </c>
       <c r="G161" s="11">
-        <v>0.9922</v>
+        <v>0</v>
       </c>
       <c r="H161" s="12">
-        <v>6055289.34</v>
+        <v>8995898.05</v>
       </c>
       <c r="I161" s="13">
-        <v>6007931.02</v>
+        <v>266299.23</v>
       </c>
       <c r="J161" s="12">
-        <v>47358.3200000003</v>
+        <v>8729598.82</v>
       </c>
       <c r="K161" s="14">
-        <v>44715</v>
+        <v>44816</v>
       </c>
       <c r="L161" s="14">
-        <v>45075</v>
+        <v>44996</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162" s="11" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B162" s="11" t="s">
+        <v>609</v>
+      </c>
+      <c r="C162" s="11" t="s">
         <v>610</v>
       </c>
-      <c r="C162" s="11" t="s">
+      <c r="D162" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E162" s="11" t="s">
         <v>611</v>
       </c>
-      <c r="D162" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E162" s="11" t="s">
-        <v>612</v>
-      </c>
       <c r="F162" s="11" t="s">
-        <v>45</v>
+        <v>591</v>
       </c>
       <c r="G162" s="11">
-        <v>0.22760000000000002</v>
+        <v>0.3153</v>
       </c>
       <c r="H162" s="12">
-        <v>8973983.87</v>
+        <v>3294597.99</v>
       </c>
       <c r="I162" s="13">
-        <v>2042159.29</v>
+        <v>1038880.21</v>
       </c>
       <c r="J162" s="12">
-        <v>6931824.579999999</v>
+        <v>2255717.7800000003</v>
       </c>
       <c r="K162" s="14">
-        <v>44707</v>
+        <v>45278</v>
       </c>
       <c r="L162" s="14">
-        <v>45280</v>
+        <v>46122</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163" s="11" t="s">
+        <v>612</v>
+      </c>
+      <c r="B163" s="11" t="s">
         <v>613</v>
       </c>
-      <c r="B163" s="11" t="s">
+      <c r="C163" s="11" t="s">
         <v>614</v>
       </c>
-      <c r="C163" s="11" t="s">
-        <v>249</v>
-      </c>
       <c r="D163" s="11" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E163" s="11" t="s">
         <v>615</v>
       </c>
       <c r="F163" s="11" t="s">
-        <v>149</v>
+        <v>509</v>
       </c>
       <c r="G163" s="11">
-        <v>1</v>
+        <v>0.9922</v>
       </c>
       <c r="H163" s="12">
-        <v>13792679.79</v>
+        <v>6055289.34</v>
       </c>
       <c r="I163" s="13">
-        <v>13792679.79</v>
+        <v>6007931.02</v>
       </c>
       <c r="J163" s="12">
-        <v>0</v>
+        <v>47358.3200000003</v>
       </c>
       <c r="K163" s="14">
-        <v>44767</v>
+        <v>44715</v>
       </c>
       <c r="L163" s="14">
-        <v>45411</v>
+        <v>45075</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164" s="11" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B164" s="11" t="s">
         <v>616</v>
       </c>
       <c r="C164" s="11" t="s">
-        <v>136</v>
+        <v>617</v>
       </c>
       <c r="D164" s="11" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E164" s="11" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="F164" s="11" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="G164" s="11">
-        <v>0.9122</v>
+        <v>0.22760000000000002</v>
       </c>
       <c r="H164" s="12">
-        <v>22472818</v>
+        <v>8973983.87</v>
       </c>
       <c r="I164" s="13">
-        <v>20500685.68</v>
+        <v>2042159.29</v>
       </c>
       <c r="J164" s="12">
-        <v>1972132.3200000003</v>
+        <v>6931824.579999999</v>
       </c>
       <c r="K164" s="14">
-        <v>44827</v>
+        <v>44707</v>
       </c>
       <c r="L164" s="14">
-        <v>45460</v>
+        <v>45280</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165" s="11" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="B165" s="11" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C165" s="11" t="s">
-        <v>619</v>
+        <v>248</v>
       </c>
       <c r="D165" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E165" s="11" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F165" s="11" t="s">
-        <v>621</v>
+        <v>149</v>
       </c>
       <c r="G165" s="11">
-        <v>0.8996</v>
+        <v>1</v>
       </c>
       <c r="H165" s="12">
-        <v>51414775.09</v>
+        <v>13792679.79</v>
       </c>
       <c r="I165" s="13">
-        <v>46254135.59</v>
+        <v>13792679.79</v>
       </c>
       <c r="J165" s="12">
-        <v>5160639.5</v>
+        <v>0</v>
       </c>
       <c r="K165" s="14">
-        <v>45566</v>
+        <v>44767</v>
       </c>
       <c r="L165" s="14">
-        <v>46106</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166" s="11" t="s">
+        <v>619</v>
+      </c>
+      <c r="B166" s="11" t="s">
         <v>622</v>
       </c>
-      <c r="B166" s="11" t="s">
+      <c r="C166" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="D166" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E166" s="11" t="s">
         <v>623</v>
       </c>
-      <c r="C166" s="11" t="s">
-        <v>624</v>
-      </c>
-      <c r="D166" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E166" s="11" t="s">
-        <v>625</v>
-      </c>
       <c r="F166" s="11" t="s">
-        <v>626</v>
+        <v>57</v>
       </c>
       <c r="G166" s="11">
-        <v>0</v>
+        <v>0.9122</v>
       </c>
       <c r="H166" s="12">
-        <v>1302281.25</v>
+        <v>22472818</v>
       </c>
       <c r="I166" s="13">
-        <v>0</v>
+        <v>20500685.68</v>
       </c>
       <c r="J166" s="12">
-        <v>1302281.25</v>
+        <v>1972132.3200000003</v>
       </c>
       <c r="K166" s="14">
-        <v>46080</v>
+        <v>44827</v>
       </c>
       <c r="L166" s="14">
-        <v>46440</v>
+        <v>45460</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A167" s="11" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="B167" s="11" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="C167" s="11" t="s">
-        <v>161</v>
+        <v>625</v>
       </c>
       <c r="D167" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E167" s="11" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="F167" s="11" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="G167" s="11">
-        <v>1</v>
+        <v>0.8996</v>
       </c>
       <c r="H167" s="12">
-        <v>18264452.89</v>
+        <v>51414775.09</v>
       </c>
       <c r="I167" s="13">
-        <v>18264452.89</v>
+        <v>46254135.59</v>
       </c>
       <c r="J167" s="12">
-        <v>0</v>
+        <v>5160639.5</v>
       </c>
       <c r="K167" s="14">
-        <v>44722</v>
+        <v>45566</v>
       </c>
       <c r="L167" s="14">
-        <v>45723</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A168" s="11" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B168" s="11" t="s">
+        <v>629</v>
+      </c>
+      <c r="C168" s="11" t="s">
+        <v>630</v>
+      </c>
+      <c r="D168" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E168" s="11" t="s">
         <v>631</v>
       </c>
-      <c r="C168" s="11" t="s">
+      <c r="F168" s="11" t="s">
         <v>632</v>
       </c>
-      <c r="D168" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E168" s="11" t="s">
-        <v>633</v>
-      </c>
-      <c r="F168" s="11" t="s">
-        <v>40</v>
-      </c>
       <c r="G168" s="11">
-        <v>0.9953</v>
+        <v>0</v>
       </c>
       <c r="H168" s="12">
-        <v>30599999.01</v>
+        <v>1302281.25</v>
       </c>
       <c r="I168" s="13">
-        <v>30456294.33</v>
+        <v>0</v>
       </c>
       <c r="J168" s="12">
-        <v>143704.68000000343</v>
+        <v>1302281.25</v>
       </c>
       <c r="K168" s="14">
-        <v>45019</v>
+        <v>46080</v>
       </c>
       <c r="L168" s="14">
-        <v>45743</v>
+        <v>46440</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A169" s="11" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="B169" s="11" t="s">
         <v>634</v>
       </c>
       <c r="C169" s="11" t="s">
-        <v>635</v>
+        <v>161</v>
       </c>
       <c r="D169" s="11" t="s">
         <v>34</v>
       </c>
       <c r="E169" s="11" t="s">
+        <v>635</v>
+      </c>
+      <c r="F169" s="11" t="s">
         <v>636</v>
       </c>
-      <c r="F169" s="11" t="s">
-        <v>222</v>
-      </c>
       <c r="G169" s="11">
-        <v>0.9601000000000001</v>
+        <v>1</v>
       </c>
       <c r="H169" s="12">
-        <v>43796954.98</v>
+        <v>18264452.89</v>
       </c>
       <c r="I169" s="13">
-        <v>42048979.52</v>
+        <v>18264452.89</v>
       </c>
       <c r="J169" s="12">
-        <v>1747975.4599999934</v>
+        <v>0</v>
       </c>
       <c r="K169" s="14">
-        <v>44641</v>
+        <v>44722</v>
       </c>
       <c r="L169" s="14">
-        <v>46091</v>
+        <v>45723</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A170" s="11" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="B170" s="11" t="s">
         <v>637</v>
@@ -8855,36 +8873,36 @@
         <v>638</v>
       </c>
       <c r="D170" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E170" s="11" t="s">
         <v>639</v>
       </c>
       <c r="F170" s="11" t="s">
-        <v>222</v>
+        <v>40</v>
       </c>
       <c r="G170" s="11">
-        <v>0.7956</v>
+        <v>0.9953</v>
       </c>
       <c r="H170" s="12">
-        <v>45726170.25</v>
+        <v>30599999.01</v>
       </c>
       <c r="I170" s="13">
-        <v>36377601.26</v>
+        <v>30456294.33</v>
       </c>
       <c r="J170" s="12">
-        <v>9348568.990000002</v>
+        <v>143704.68000000343</v>
       </c>
       <c r="K170" s="14">
-        <v>44623</v>
+        <v>45019</v>
       </c>
       <c r="L170" s="14">
-        <v>46222</v>
+        <v>45743</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A171" s="11" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="B171" s="11" t="s">
         <v>640</v>
@@ -8899,24 +8917,100 @@
         <v>642</v>
       </c>
       <c r="F171" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="G171" s="11">
+        <v>0.9601000000000001</v>
+      </c>
+      <c r="H171" s="12">
+        <v>43796954.98</v>
+      </c>
+      <c r="I171" s="13">
+        <v>42048979.52</v>
+      </c>
+      <c r="J171" s="12">
+        <v>1747975.4599999934</v>
+      </c>
+      <c r="K171" s="14">
+        <v>44641</v>
+      </c>
+      <c r="L171" s="14">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A172" s="11" t="s">
+        <v>633</v>
+      </c>
+      <c r="B172" s="11" t="s">
+        <v>643</v>
+      </c>
+      <c r="C172" s="11" t="s">
+        <v>644</v>
+      </c>
+      <c r="D172" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E172" s="11" t="s">
+        <v>645</v>
+      </c>
+      <c r="F172" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="G172" s="11">
+        <v>0.7956</v>
+      </c>
+      <c r="H172" s="12">
+        <v>45726170.25</v>
+      </c>
+      <c r="I172" s="13">
+        <v>36377601.26</v>
+      </c>
+      <c r="J172" s="12">
+        <v>9348568.990000002</v>
+      </c>
+      <c r="K172" s="14">
+        <v>44623</v>
+      </c>
+      <c r="L172" s="14">
+        <v>46222</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A173" s="11" t="s">
+        <v>633</v>
+      </c>
+      <c r="B173" s="11" t="s">
+        <v>646</v>
+      </c>
+      <c r="C173" s="11" t="s">
+        <v>647</v>
+      </c>
+      <c r="D173" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E173" s="11" t="s">
+        <v>648</v>
+      </c>
+      <c r="F173" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="G171" s="11">
+      <c r="G173" s="11">
         <v>0.30870000000000003</v>
       </c>
-      <c r="H171" s="12">
+      <c r="H173" s="12">
         <v>65678550.13</v>
       </c>
-      <c r="I171" s="13">
+      <c r="I173" s="13">
         <v>20274364.25</v>
       </c>
-      <c r="J171" s="12">
+      <c r="J173" s="12">
         <v>45404185.88</v>
       </c>
-      <c r="K171" s="14">
+      <c r="K173" s="14">
         <v>44623</v>
       </c>
-      <c r="L171" s="14">
+      <c r="L173" s="14">
         <v>46170</v>
       </c>
     </row>
